--- a/research/brics_universities/output/BRICS_universities_egypt.xlsx
+++ b/research/brics_universities/output/BRICS_universities_egypt.xlsx
@@ -561,7 +561,7 @@
         <v>57</v>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -6766,7 +6766,11 @@
           <t>https://du.edu.eg</t>
         </is>
       </c>
-      <c r="P30" s="4" t="inlineStr"/>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>Prof. Hamdan Rabie (أ.د. حمدان ربيع)</t>
+        </is>
+      </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>President</t>
@@ -6809,8 +6813,9 @@
       <c r="AF30" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт du.edu.eg недоступен (503 / обрыв соединения, октябрь 2026); контакты из справочника universitiesegypt.com — требуют сверки
-• Имя действующего президента не удалось проверить (сайт недоступен, лимит поиска исчерпан) — уточнить перед отправкой
-• Космическая активность не проверялась поиском (лимит исчерпан); в nanosats.csv спутников нет</t>
+• Космическая активность не проверялась поиском (лимит исчерпан); в nanosats.csv спутников нет
+• Президент д-р Хамдан Рабиа (حمدان ربيع) — подтверждён публикациями СМИ сентября–октября 2026 г. (Sada El-Omma, Al-Dostor); на официальном сайте не проверен (du.edu.eg и med.du.edu.eg недоступны 04.10.2026)
+• Перепроверка: Сайт по-прежнему недоступен; по СМИ 10.2026 добавлен президент д-р Хамдан Рабиа; контакты не перепроверены</t>
         </is>
       </c>
       <c r="AG30" s="4" t="inlineStr">
@@ -6896,7 +6901,7 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>+20 50 2770140</t>
+          <t>15955 (hotline, official site); +20 50 2770140</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
@@ -6949,16 +6954,17 @@
       </c>
       <c r="AE31" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF31" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт рендерится через JavaScript — руководство и международный отдел на сайте проверить не удалось
+          <t>• Официальный сайт new.deltauniv.edu.eg рендерится через JavaScript (навигация через JS, страница «президент» отсутствует) — руководство и международный отдел на сайте проверить не удалось; info@deltauniv.edu.eg и горячая линия 15955 подтверждены на сайте 04.10.2026
 • Президент (Dr. Yehia El-Meshad / يحيى المشد) подтверждён только СМИ (июнь 2026); председатель совета попечителей — Dr. Mohamed Rabie
-• Телефон и адрес — со стороннего справочника egyptianeducation.com; горячая линия 15955 (с сайта)
+• Телефон +20 50 2770140 и адрес — со стороннего справочника egyptianeducation.com
 • Не путать с Delta Technological University (جامعة الدلتا التكنولوجية)
-• Отдельного международного e-mail не найдено</t>
+• Отдельного международного e-mail не найдено
+• Перепроверка: Общий e-mail и горячая линия подтверждены на официальном сайте 04.10.2026; президент — по СМИ 06.2026, на сайте не найден</t>
         </is>
       </c>
       <c r="AG31" s="4" t="inlineStr">
@@ -7179,7 +7185,11 @@
           <t>https://www.gu.edu.eg</t>
         </is>
       </c>
-      <c r="P33" s="4" t="inlineStr"/>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Mohamed El-Shinawi</t>
+        </is>
+      </c>
       <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>President</t>
@@ -7217,15 +7227,17 @@
       </c>
       <c r="AF33" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт недоступен из нашей сети (503/таймаут), поиск исчерпан — контакты и руководитель не верифицированы; требуется ручная проверка
-• По Википедии (не верифицировано на 2025–2026) президент — Dr. Mohamed El-Shinawi
-• Партнёрство с Arizona State University (двойные дипломы); спутниковых проектов не найдено</t>
+          <t>• Официальный сайт gu.edu.eg недоступен из нашей сети (503 / ошибка TLS, повторно 04.10.2026) — контакты не верифицированы; требуется ручная проверка
+• Президент Prof. Dr. Mohamed El-Shinawi (проф. хирургии Ain Shams) — по официальным новостям gu.edu.eg 2026 г., видимым в поисковой выдаче
+• Партнёрство с Arizona State University (двойные дипломы); спутниковых проектов не найдено
+• Перепроверка: Президент проф. Mohamed El-Shinawi подтверждается официальными новостями gu.edu.eg (06.2026) по поисковой выдаче; сайт по-прежнему недоступен — контакты не найдены</t>
         </is>
       </c>
       <c r="AG33" s="4" t="inlineStr">
         <is>
           <t>• Https://www.timeshighereducation.com/world-university-rankings/galala-university
-• Https://en.wikipedia.org/wiki/Galala_University</t>
+• Https://en.wikipedia.org/wiki/Galala_University
+• Https://www.gu.edu.eg/2026/06/galala-university-president-speaks-at-international-conference-in-madrid-on-strengthening-public-private-collaboration-in-higher-education (snippet)</t>
         </is>
       </c>
       <c r="AH33" s="4" t="inlineStr">
@@ -7629,7 +7641,8 @@
 • ВАЖНО: в сент. 2026 Высший совет университетов объявил конкурс на пост президента (приём заявок с 10.10.2026) — руководитель может смениться в ближайшие месяцы; проверить перед отправкой
 • Непроверенные (из поисковой выдачи) адреса: president@menofia.edu.eg, menofia@menofia.edu.eg; телефоны из справочников: +20 48 2224216 (edarabia), +20 48 232 9094 (WIPO TISC)
 • Адрес — по справочнику WIPO TISC
-• В QS2027 не найден; космической активности не найдено</t>
+• В QS2027 не найден; космической активности не найдено
+• Перепроверка: 04.10.2026: menofia.edu.eg недоступен (503/сброс), портал Высшего совета университетов scu.eg не отдаёт данные без JS — данные не изменены</t>
         </is>
       </c>
       <c r="AG36" s="4" t="inlineStr">
@@ -8245,7 +8258,7 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Canal El Mahmoudia Street, beside Green Plaza Complex, Alexandria, Egypt</t>
+          <t>Pharos University in Alexandria, Canal El Mahmoudia Street, beside Green Plaza Complex, Smouha, Alexandria, Egypt</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -8268,17 +8281,17 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>+20 3 3877000</t>
+          <t>+20 3 3877700</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>https://pua.edu.eg</t>
+          <t>https://www.pua.edu.eg</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>Prof. Mahmoud Mohy El Din</t>
+          <t>Prof. Mahmoud Mohy El-Din</t>
         </is>
       </c>
       <c r="Q41" s="4" t="inlineStr">
@@ -8317,19 +8330,21 @@
       </c>
       <c r="AE41" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF41" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт pua.edu.eg недоступен (ошибка базы данных, октябрь 2026); контакты из справочника universitiesegypt.com
-• Имя президента взято из Википедии, подтверждения 2025–2026 нет — обязательно сверить
-• Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет</t>
+          <t>• Сайт pua.edu.eg снова доступен (04.10.2026): президент, общий e-mail, телефон и адрес подтверждены; прежний номер +20 3 3877000 из справочника был неверным — исправлен на +20 3 3877700
+• На сайте есть ящик International.Students@pua.edu.eg (тел. +20 3 3877872 / 3877886) — офис регистрации иностранных студентов, не отдел партнёрств; отдельный e-mail международного отдела не найден
+• Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет
+• Перепроверка: Президент проф. Махмуд Мохи Эль-Дин, info@pua.edu.eg, телефон и адрес подтверждены на pua.edu.eg 04.10.2026; телефон исправлен</t>
         </is>
       </c>
       <c r="AG41" s="4" t="inlineStr">
         <is>
-          <t>• Https://www.universitiesegypt.com/pharos-university-alexandria/contacts
+          <t>• Https://www.pua.edu.eg/
+• Https://www.pua.edu.eg/about-pua/message-from-the-president-of-pharos-university/
 • Https://en.wikipedia.org/wiki/Pharos_University_in_Alexandria</t>
         </is>
       </c>
@@ -8583,7 +8598,8 @@
         <is>
           <t>• Официальный сайт недоступен из нашей сети (503/таймаут), поиск исчерпан — контакты и руководитель не верифицированы; требуется ручная проверка
 • По Википедии (не верифицировано) президент — Abdul Azim Al-Sharkawy
-• Не путать с Suez Canal University (Исмаилия), которая подписала протокол с EgSA в 2021 г</t>
+• Не путать с Suez Canal University (Исмаилия), которая подписала протокол с EgSA в 2021 г
+• Перепроверка: 04.10.2026: сайт suezuni.edu.eg по-прежнему недоступен (curl — нет соединения, WebFetch — 503); данные не изменены</t>
         </is>
       </c>
       <c r="AG43" s="4" t="inlineStr">
@@ -9026,7 +9042,9 @@
 • Президент Dr. Nasser Abdel-Bary (ناصر عبد الباري) подтверждён СМИ за сен. 2026; в WHED указан устаревший и.о. Ahmed Azab; учёное звание Prof. не проверено
 • Директор Центра интернационализации (по WHED): Nashwa Suleiman — e-mail не найден
 • E-mail info@usc.edu.eg и телефон — со стороннего справочника universitiesegypt.com
-• В QS2027 не найден</t>
+• В QS2027 не найден
+• Сайт Минвысобразования Египта (mohesr.gov.eg, 30.08.2025) называл президентом д-р Шаден Муавия (شادن معاوية); СМИ фев. и сен. 2026 — Nasser Abdel-Bary, т.е. вероятна смена руководителя; официального решения о назначении не найдено
+• Перепроверка: Сайт usc.edu.eg по-прежнему недоступен (curl/WebFetch 503); на сайте Минвысобразования найдено, что в авг. 2025 президентом была д-р Шаден Муавия — текущий президент Nasser Abdel-Bary (СМИ 2026) официально не подтверждён; контакты не изменены</t>
         </is>
       </c>
       <c r="AG46" s="4" t="inlineStr">
@@ -9090,7 +9108,7 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>4th Industrial Zone, Banks Complex, 6th of October City, Giza, Egypt</t>
+          <t>Banks Complex Street, Fourth Industrial Zone, 6th of October City, Giza, Egypt</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
@@ -9113,17 +9131,17 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>+20 2 38333078</t>
+          <t>19228 (hotline, Egypt)</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>https://www.acu.edu.eg</t>
+          <t>https://acu.edu.eg</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>Prof. Amal Fawzy Ahmed</t>
+          <t>Prof. Ahmed Mohamed Anani (أ.د. أحمد محمد عناني)</t>
         </is>
       </c>
       <c r="Q47" s="4" t="inlineStr">
@@ -9158,20 +9176,24 @@
       </c>
       <c r="AE47" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>высокая</t>
         </is>
       </c>
       <c r="AF47" s="4" t="inlineStr">
         <is>
           <t>• THE2027: только статус Reporter (без ранга)
-• Сайт acu.edu.eg блокирует доступ (403); контакты и имя президента взяты из поисковых выдержек (статья Ahram Online, май 2026) — требуют проверки
-• В Википедии/WHED указан прежний президент (Khaled Hamdy Abdel Rahman) — устарело
-• Спутниковой активности не найдено</t>
+• Сайт www.acu.edu.eg отдаёт 403, но acu.edu.eg (без www) доступен
+• Ранее указанный телефон +20 2 38333078 на официальном сайте не найден — заменён горячей линией 19228; отдельный e-mail международного отдела не опубликован (есть раздел «Международные партнёрства»)
+• Председатель совета попечителей — проф. Мохамед Фаиз Фархат (глава Al-Ahram)
+• Спутниковой активности не найдено
+• Перепроверка: Сайт открылся по адресу без www (acu.edu.eg) 04.10.2026: президент — проф. Ахмед Мохамед Анани (страница руководства + новость 19.07.2026), прежнее имя Amal Fawzy Ahmed исправлено; адрес, info@acu.edu.eg и горячая линия 19228 подтверждены на странице контактов</t>
         </is>
       </c>
       <c r="AG47" s="4" t="inlineStr">
         <is>
-          <t>• Https://acu.edu.eg/UI/Front/ContactUs.aspx
+          <t>• Https://acu.edu.eg/about-the-council/university-leaders
+• Https://acu.edu.eg/en/contact-us
+• Https://acu.edu.eg/news
 • Https://english.ahram.org.eg/NewsContent/1/2/569449/Egypt/Society/Ahram-Canadian-University-achieves-new-milestone-i.aspx</t>
         </is>
       </c>
@@ -9275,9 +9297,11 @@
       </c>
       <c r="AF48" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт недоступен из нашей сети (503/таймаут), поиск исчерпан — контакты и руководитель не верифицированы; требуется ручная проверка
-• По Википедии (не верифицировано) президент — Prof. Dr. Essam Elkordi
-• Арабское название не сверено с официальным сайтом</t>
+          <t>• Официальный сайт aiu.edu.eg (http/https, www) по-прежнему недоступен из нашей сети (503/таймаут, в т.ч. через WebFetch) — контакты и руководитель не верифицированы; требуется ручная проверка
+• По Википедии и поисковой выдаче (без даты/официального источника) президент — Prof. Dr. Essam Elkordi (عصام الكردي); председатель совета — Dr. Ahmed Mahmoud — не подтверждено, в поля не внесено
+• Вуз активен в международной работе (участие в EAIE 2026, Глазго — по СМИ)
+• Арабское название не сверено с официальным сайтом
+• Перепроверка: Сайт недоступен; данные не изменены (президент Essam Elkordi — только по вторичным источникам)</t>
         </is>
       </c>
       <c r="AG48" s="4" t="inlineStr">
@@ -9360,7 +9384,11 @@
           <t>info@anu.edu.eg</t>
         </is>
       </c>
-      <c r="N49" s="4" t="inlineStr"/>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>+20 122 885 8407</t>
+        </is>
+      </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
           <t>https://anu.edu.eg</t>
@@ -9373,7 +9401,7 @@
       </c>
       <c r="Q49" s="4" t="inlineStr">
         <is>
-          <t>Acting President</t>
+          <t>President</t>
         </is>
       </c>
       <c r="R49" s="4" t="inlineStr"/>
@@ -9403,21 +9431,24 @@
       </c>
       <c r="AE49" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF49" s="4" t="inlineStr">
         <is>
           <t>• Национальный (ахлия) университет при Alexandria University; руководство — и.о. (Ahmed Adel Abdel Hakim, он же и.о. президента Alexandria University по данным СМИ, сентябрь 2026)
-• Сайт anu.edu.eg недоступен; info@anu.edu.eg и адрес — из поисковой выдержки страницы контактов
-• Спутниковой активности не найдено</t>
+• Спутниковой активности не найдено
+• Сайт anu.edu.eg доступен (04.10.2026): страница «Meet The President» называет Prof. Dr. Ahmed Adel Abdel Hakim президентом; контакты (адрес, info@anu.edu.eg, +201228858407) — на странице Contact; страницы без даты
+• Перепроверка: Сайт открылся 04.10.2026: президент, адрес, e-mail info@anu.edu.eg подтверждены, добавлен телефон +20 122 885 8407 (страницы без даты)</t>
         </is>
       </c>
       <c r="AG49" s="4" t="inlineStr">
         <is>
           <t>• Https://anu.edu.eg/en/contact
 • Https://www.dostor.org/5708804
-• Https://www.youm7.com/story/2026/9/20/7552597</t>
+• Https://www.youm7.com/story/2026/9/20/7552597
+• Https://anu.edu.eg/en/president
+• Https://anu.edu.eg/en/contact</t>
         </is>
       </c>
       <c r="AH49" s="4" t="inlineStr">
@@ -9745,9 +9776,10 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>ФИО не найдено
+          <t>Prof. Dr. Mohamed Morsi El-Gohary
+President, Borg El Arab Technological University
 Общий ящик университета (General inbox)
-Обращение: Dear Director of International Relations,</t>
+Обращение: Dear Professor El-Gohary,</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr"/>
@@ -9762,7 +9794,11 @@
           <t>https://batechu.com</t>
         </is>
       </c>
-      <c r="P52" s="4" t="inlineStr"/>
+      <c r="P52" s="4" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Mohamed Morsi El-Gohary (محمد مرسي الجوهري)</t>
+        </is>
+      </c>
       <c r="Q52" s="4" t="inlineStr">
         <is>
           <t>President</t>
@@ -9795,15 +9831,16 @@
       </c>
       <c r="AE52" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF52" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт (по Википедии) — batechu.com, не в зоне .edu.eg; опубликован только contact@batechu.com, телефон и полный адрес не найдены
-• Действующий президент не подтверждён: по Википедии в 2022 г. президентом был назначен (по откомандированию) д-р Мохамед Мурси аль-Гохари — сверить актуальность
+          <t>• Официальный сайт batechu.com (не в зоне .edu.eg); e-mail contact@batechu.com подтверждён на странице Contact Us; телефон и полный почтовый адрес на сайте не опубликованы
+• Президент проф. д-р Мохамед Мурси аль-Гохари — по обращению президента на главной странице официального сайта (подвал © 2026); дата назначения не указана
 • Форма собственности не подтверждена (технологический университет; в Википедии — «National university»)
-• Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет</t>
+• Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет
+• Перепроверка: 04.10.2026: президент и e-mail подтверждены на официальном сайте batechu.com; телефон и адрес не опубликованы</t>
         </is>
       </c>
       <c r="AG52" s="4" t="inlineStr">
@@ -10177,7 +10214,8 @@
         <is>
           <t>• Официальный сайт не найден (epsnu.edu.eg недоступен), лимит веб-поиска исчерпан — все контактные поля требуют ручного заполнения
 • Национальный (ахлия) университет, созданный при государственном Порт-Саидском университете (по арабской Википедии)
-• Космическая активность не проверялась; в nanosats.csv спутников нет</t>
+• Космическая активность не проверялась; в nanosats.csv спутников нет
+• Перепроверка: Домены epsnu.edu.eg недоступны (04.10.2026); на сайте Порт-Саидского университета (psu.edu.eg) ссылки на национальный университет не найдено; данные не изменены</t>
         </is>
       </c>
       <c r="AG55" s="4" t="inlineStr">
@@ -10394,7 +10432,11 @@
           <t>https://www.ecu.edu.eg</t>
         </is>
       </c>
-      <c r="P57" s="4" t="inlineStr"/>
+      <c r="P57" s="4" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Rasha El-Kholy</t>
+        </is>
+      </c>
       <c r="Q57" s="4" t="inlineStr">
         <is>
           <t>President</t>
@@ -10428,15 +10470,18 @@
       </c>
       <c r="AF57" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт ecu.edu.eg блокирует автоматический доступ (403, Cloudflare); e-mail, телефон и руководство не проверены — найти вручную
+          <t>• Официальный сайт ecu.edu.eg блокирует автоматический доступ (403, Cloudflare, повторно 04.10.2026); e-mail и телефон не найдены — найти вручную
+• Президент Prof. Dr. Rasha El-Kholy — по поисковой выдаче официальных страниц ECU (University President’s Message) и интервью на портале Belt and Road; дата назначения не установлена (предыдущий президент Ashraf El-Shihy, 2017–2023) — перепроверить
 • Адрес и профиль — только по арабской Википедии
-• Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет
-• В THE 2027 — статус Reporter (без ранга)</t>
+• Космическая активность поиском не проверялась; в nanosats.csv спутников нет
+• В THE 2027 — статус Reporter (без ранга)
+• Перепроверка: Сайт ecu.edu.eg по-прежнему 403 (Cloudflare); президент проф. Rasha El-Kholy внесена по выдаче официальных страниц ECU и портала Belt and Road (дата не установлена) — контакты не найдены</t>
         </is>
       </c>
       <c r="AG57" s="4" t="inlineStr">
         <is>
-          <t>Https://ar.wikipedia.org/wiki/الجامعة_المصرية_الصينية</t>
+          <t>• Https://ar.wikipedia.org/wiki/الجامعة_المصرية_الصينية
+• Https://ecu.edu.eg/about-ecu/university-presidents-message/ (snippet)</t>
         </is>
       </c>
       <c r="AH57" s="4" t="inlineStr">
@@ -10805,17 +10850,19 @@
       </c>
       <c r="AF60" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт hnu.edu.eg недоступен (503 / блокировка прокси); поисковая квота исчерпана — руководство и контакты НЕ проверены
-• Национальный (ахлия) некоммерческий университет, выделен из Helwan University (65 федданов); материнский Helwan University переименован в Capital University (جامعة العاصمة, capu.edu.eg), президент — Prof. El-Sayed Kandil (السيد قنديل); руководство HNU уточнить
-• У Capital University есть Office of International Relations (capu.edu.eg) — возможный канал связи
-• Космической активности не проверено</t>
+          <t>• Официальный сайт hnu.edu.eg недоступен (503 / сброс соединения, проверка 04.10.2026) — руководство и контакты HNU НЕ проверены
+• Национальный (ахлия) некоммерческий университет, выделен из Helwan University; материнский вуз переименован в Capital University (جامعة العاصمة, capu.edu.eg). На capu.edu.eg (новость 30.09.2026) подтверждено: президент Capital University — проф. Эль-Сайед Кандиль, он курирует проекты HNU (учебная больница HNU); генеральный секретарь (أمين) HNU — Сайед Атта. Имя президента HNU не найдено
+• Возможный канал связи — Офис международных отношений Capital University (capu.edu.eg): директор проф. Мохамед Шими, iroffice@hq.helwan.edu.eg, тел. +20 2 2556 9067 / +20 2 2555 5021 (это контакты материнского вуза, не HNU)
+• Космической активности не проверено
+• Перепроверка: Сайт hnu.edu.eg недоступен; по capu.edu.eg уточнены связь с Capital University и контакты его международного офиса, руководитель HNU не найден</t>
         </is>
       </c>
       <c r="AG60" s="4" t="inlineStr">
         <is>
           <t>• Https://www.wikidata.org/wiki/Q105600196
 • Https://ar.wikipedia.org/wiki/جامعة_حلوان_الأهلية
-• Https://www.capu.edu.eg/index.php/ar/</t>
+• Https://www.capu.edu.eg/index.php/ar/
+• Https://capu.edu.eg/index.php/ar/about-ar/agreements-and-partnerships/office-of-international-relations</t>
         </is>
       </c>
       <c r="AH60" s="4" t="inlineStr">
@@ -10902,7 +10949,8 @@
       <c r="AF61" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт не найден/недоступен; веб-поиск исчерпан — все контакты требуют ручной проверки
-• Создан в 2020–2021 на базе филиала South Valley University в Хургаде (по арабской Википедии)</t>
+• Создан в 2020–2021 на базе филиала South Valley University в Хургаде (по арабской Википедии)
+• Перепроверка: Официальный домен не найден (варианты hurghada.edu.eg, hurghadauniv.edu.eg и др. недоступны); сайт Минвысобразования (mohesr.gov.eg, 30.08.2025) подтверждает существование вуза (утверждение фирменного стиля Хургадского университета Высшим советом университетов), но руководителя и контактов не даёт; данные не изменены</t>
         </is>
       </c>
       <c r="AG61" s="4" t="inlineStr">
@@ -11175,7 +11223,8 @@
           <t>• THE2027: только статус Reporter (без ранга)
 • Сайт ksiu.edu.eg недоступен (503); данные из поисковых выдержек официального сайта, дата не подтверждена
 • Персональный e-mail президента по выдержке: ashraf@ksiu.edu.eg; горячая линия 16949
-• Спутниковой активности не найдено</t>
+• Спутниковой активности не найдено
+• Перепроверка: 04.10.2026: ksiu.edu.eg недоступен (ошибка TLS-цепочки, en.-поддомен — 502); по поиску президент проф. Ashraf Hussein указан на сайте — данные не изменены</t>
         </is>
       </c>
       <c r="AG63" s="4" t="inlineStr">
@@ -11291,7 +11340,8 @@
           <t>• Официальный сайт mansnu.edu.eg недоступен (503 / блокировка прокси); поисковая квота исчерпана — руководство и контакты НЕ проверены
 • Национальный (ахлия) некоммерческий университет при Mansoura University (кампус 42 федданa в Новой Мансуре); обычно возглавляется президентом Mansoura University — уточнить
 • Перечень факультетов частичный (по арабской Википедии)
-• Космической активности не проверено</t>
+• Космической активности не проверено
+• Перепроверка: Сайт mansnu.edu.eg (www и без www) недоступен — таймаут через curl и reader-сервис 04.10.2026; данные не изменены</t>
         </is>
       </c>
       <c r="AG64" s="4" t="inlineStr">
@@ -11353,7 +11403,7 @@
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>Administration Building, Km 4, Marsa Matrouh 51511, Matrouh Governorate, Egypt</t>
+          <t>Matrouh University, New University Campus, Km 9, Marsa Matrouh, Matrouh Governorate, Egypt</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr"/>
@@ -11372,7 +11422,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>Prof. Amr El-Masry</t>
+          <t>Prof. Amr Ahmed El-Masry</t>
         </is>
       </c>
       <c r="Q65" s="4" t="inlineStr">
@@ -11403,14 +11453,16 @@
       <c r="AD65" s="4" t="inlineStr"/>
       <c r="AE65" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>средняя</t>
         </is>
       </c>
       <c r="AF65" s="4" t="inlineStr">
         <is>
-          <t>• Сайт mau.edu.eg недоступен — официальный общий и международный e-mail не найдены (в каталоге WIPO только личный адрес сотрудника)
-• Президент Amr El-Masry назначен после конкурса (собеседования ноябрь 2025); латинское написание имени по транслитерации
-• Спутниковой активности не найдено</t>
+          <t>• Сайт mau.edu.eg (Blazor, рендер JS) открыт через reader-сервис 04.10.2026: на сайте нет e-mail и телефонов (в т.ч. на странице International Relations) — официальный общий и международный e-mail не найдены (в каталоге WIPO только личный адрес сотрудника)
+• Президент назван «President» (новость 01.10.2026) и «Acting President» (сентябрь 2025/2026) — статус и.о. мог измениться после конкурса (собеседования ноябрь 2025)
+• Телефон +20 46 4948489 взят ранее из стороннего источника, на официальном сайте не подтверждён. Генеральный секретарь — Walid Yahya
+• Спутниковой активности не найдено
+• Перепроверка: Президент Prof. Amr Ahmed El-Masry и адрес кампуса (Km 9) подтверждены на mau.edu.eg 04.10.2026 (новость от 01.10.2026); e-mail на сайте не опубликован; адрес исправлен (было «Km 4»)</t>
         </is>
       </c>
       <c r="AG65" s="4" t="inlineStr">
@@ -11512,7 +11564,8 @@
         <is>
           <t>• Официальный сайт недоступен из нашей сети (503/таймаут), поиск исчерпан — контакты и руководитель не верифицированы; требуется ручная проверка
 • Описание в профиле THE скопировано с государственного Menoufia University — не использовать его для профиля
-• Национальный (ахлия) университет при Menoufia University — проверить точное название и руководство</t>
+• Национальный (ахлия) университет при Menoufia University — проверить точное название и руководство
+• Перепроверка: Сайты mnu.menofia.education, mnu.edu.eg и menofia.edu.eg недоступны (04.10.2026, сброс соединения); данные не изменены</t>
         </is>
       </c>
       <c r="AG66" s="4" t="inlineStr">
@@ -11974,7 +12027,11 @@
           <t>https://nctu.edu.eg</t>
         </is>
       </c>
-      <c r="P70" s="4" t="inlineStr"/>
+      <c r="P70" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Tarek Abdel Malak (د. طارق عبد الملاك)</t>
+        </is>
+      </c>
       <c r="Q70" s="4" t="inlineStr">
         <is>
           <t>President</t>
@@ -12008,9 +12065,11 @@
       </c>
       <c r="AF70" s="4" t="inlineStr">
         <is>
-          <t>• Официальный сайт nctu.edu.eg недоступен (503 / блокировка прокси); поисковая квота исчерпана — руководство и контакты НЕ проверены
-• Государственный технологический университет (прикладное технологическое образование); подтверждён только факультет технологий промышленности и энергетики (по арабской Википедии)
-• Космической активности не проверено</t>
+          <t>• Государственный технологический университет (прикладное технологическое образование); подтверждён только факультет технологий промышленности и энергетики (по арабской Википедии)
+• Космической активности не проверено
+• Сайт nctu.edu.eg по-прежнему недоступен (04.10.2026) — контакты не найдены
+• Президент д-р Тарек Абдель Малак (طارق عبد الملاك) — по статье Masrawy от 18.09.2026 (выпуск 2025/2026); на официальном сайте не проверен
+• Перепроверка: Сайт недоступен; по СМИ 09.2026 добавлен президент д-р Тарек Абдель Малак; контактов по-прежнему нет</t>
         </is>
       </c>
       <c r="AG70" s="4" t="inlineStr">
@@ -12478,7 +12537,7 @@
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>New Assiut City, Assiut Governorate, Egypt</t>
+          <t>Regional Service Zone, New Assiut City, Assiut Governorate, Egypt</t>
         </is>
       </c>
       <c r="J74" s="4" t="inlineStr">
@@ -12499,7 +12558,11 @@
           <t>Info@Sphinx.edu.eg</t>
         </is>
       </c>
-      <c r="N74" s="4" t="inlineStr"/>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>17090 (короткий номер, Египет)</t>
+        </is>
+      </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
           <t>https://sphinx.edu.eg</t>
@@ -12551,13 +12614,16 @@
 • Сайт почти пустой (JS, без страниц руководства/контактов) — президент не установлен; поисковая проверка невозможна (исчерпана квота поиска)
 • Опубликован только короткий номер 17090
 • Международного отдела не найдено; космической активности не найдено
-• Точный почтовый адрес (улица) не опубликован</t>
+• Точный почтовый адрес (улица) не опубликован
+• Повторная проверка 04.10.2026: на сайте нет страниц руководства; по поисковой выдаче (СМИ, не официальный источник) и.о. президента — д-р Мансур Каббаш (منصور كباش) — не подтверждено, в поля не внесено
+• Перепроверка: Сайт открылся 04.10.2026: подтверждены только Info@Sphinx.edu.eg, номер 17090 и адрес «Regional service zone, New Assiut»; президент на сайте не указан</t>
         </is>
       </c>
       <c r="AG74" s="4" t="inlineStr">
         <is>
           <t>• Https://sphinx.edu.eg/en/home/index
-• Https://ar.wikipedia.org/wiki/جامعة_سفنكس</t>
+• Https://ar.wikipedia.org/wiki/جامعة_سفنكس
+• Https://sphinx.edu.eg/en/home/index</t>
         </is>
       </c>
       <c r="AH74" s="4" t="inlineStr">

--- a/research/brics_universities/output/BRICS_universities_egypt.xlsx
+++ b/research/brics_universities/output/BRICS_universities_egypt.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Египет" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AI$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Египет'!$A$1:$AI$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AJ$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Египет'!$A$1:$AJ$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Дата формирования: 2026-10-04</t>
+          <t>Дата формирования: 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AJ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -666,30 +666,31 @@
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="45" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="45" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="40" customWidth="1" min="25" max="25"/>
-    <col width="45" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="55" customWidth="1" min="32" max="32"/>
-    <col width="60" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="24" customWidth="1" min="35" max="35"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="45" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="55" customWidth="1" min="33" max="33"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="24" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -750,120 +751,125 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Стыковка e-mail и адресата</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>E-mail (международный отдел)</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>E-mail (общий / ректорат)</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Телефон</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Ректор / президент</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Должность</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Рейтинг QS</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Рейтинг THE</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Национальный рейтинг</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Запущено КА (спутников)</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Названия запущенных КА (год)</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>КА в разработке</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Наземная станция</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Космические подразделения</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Партнёрства в космической сфере</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>Космический индекс (0–100)</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>Волна рассылки</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Секретарь парткома (справочно, Китай)</t>
         </is>
@@ -920,57 +926,62 @@
       </c>
       <c r="J2" s="4" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr"/>
-      <c r="L2" s="4" t="inlineStr"/>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>+20 2 26251200</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>https://www.narss.sci.eg</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>Prof. Abdelaziz Ballal</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>Acting Chairman (President)</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr"/>
       <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="n">
+      <c r="U2" s="4" t="inlineStr"/>
+      <c r="V2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>• EgyptSat-1 (2007)
 • NARSSCube-2 (2019)
 • NARSSCube-1 (2019)</t>
         </is>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>6U agricultural monitoring CubeSat (announced 2023)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>Satellite data receiving station in Aswan (X-band; Landsat/SPOT reception)</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>Space Technology Division</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>• Egyptian Space Agency (EgSA)
 • African Space Agency (host country Egypt)
@@ -978,22 +989,22 @@
 • Cooperation protocols with Egyptian universities (e.g., Beni-Suef National University)</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr"/>
-      <c r="AB2" s="4" t="n">
+      <c r="AB2" s="4" t="inlineStr"/>
+      <c r="AC2" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="AC2" s="5" t="inlineStr">
+      <c r="AD2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD2" s="4" t="inlineStr"/>
-      <c r="AE2" s="4" t="inlineStr">
+      <c r="AE2" s="4" t="inlineStr"/>
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>• Руководитель — и.о. председателя Prof. Abdelaziz Ballal (назначен 3 июня 2026 г.; ранее — Prof. Islam Abou El-Magd)
 • Сайт narss.sci.eg недоступен (503)
@@ -1001,7 +1012,7 @@
 • EgyptSat-1 создан совместно с КБ «Южное» (Украина); EgyptSat-2 не учтён (построен РКК «Энергия», позже передан EgSA)</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>• Https://www.elwatannews.com/news/details/8295289
 • Https://spaceinafrica.com/2023/08/02/bridging-science-and-society-narsss-impact-on-egypts-development-and-technological-progress/
@@ -1010,12 +1021,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI2" s="4" t="inlineStr"/>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -1079,52 +1090,57 @@
 Обращение: Dear Dr. Ismail,</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>info@egsa.gov.eg</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>+20 2 21297950</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>https://www.egsa.gov.eg</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>Dr. Eng. Majed Ismail</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>• MisrSat-2 (2023)
 • NExSat-1 (2024)
 • SPNeX (2025)</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr"/>
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>EgSA ground control station at Egyptian Space City (MisrSat-2 ground segment)</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>• Satellite Assembly, Integration and Testing Center (AITC)
 • Egyptian Space City
@@ -1132,7 +1148,7 @@
 • Egyptian Universities Satellite (CubeSat) programme</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>• China (MisrSat-2 grant, AITC)
 • Berlin Space Technologies (NExSat-1)
@@ -1142,26 +1158,26 @@
 • China Meteorological Administration (talks, Sep 2026)</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="n">
+      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="AC3" s="5" t="inlineStr">
+      <c r="AD3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD3" s="4" t="inlineStr">
+      <c r="AE3" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>• Агентство, не университет; сайт egsa.gov.eg — SPA, контактные данные подгружаются из API (недоступен); адрес/e-mail/телефон с iafastro.org и WIPO TISC
 • CEO д-р инж. Маджид Исмаил назначен 19.08.2025 на 1 год; в сентябре 2026 продолжает исполнять обязанности (новости youm7/elbalad) — проверить продление
@@ -1169,7 +1185,7 @@
 • Отдельный e-mail международного отдела не найден — использовать info@egsa.gov.eg</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>• Https://www.iafastro.org/membership/all-members/egyptian-space-agency-egsa.html
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=11051
@@ -1185,12 +1201,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1256,83 +1272,88 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
           <t>international.affairs@ejust.edu.eg</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>+20 3 4599855</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>https://www.ejust.edu.eg</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Prof. Ahmed El-Sabbagh</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="n">
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>EgSA educational satellite model (lab satellite for communication, remote sensing and space-environment applications)</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>Ground station simulation unit (educational, supplied under EgSA agreement)</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>EgSA educational satellite laboratory (satellite model, operation/testing simulators, ground-station simulator)</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>• Egyptian Space Agency (EgSA) – executive agreement on educational satellite lab, 2021
 • EgSA cooperation protocol with universities, 2021
 • JICA / Japanese partner universities consortium</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="n">
+      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="AC4" s="6" t="inlineStr">
+      <c r="AD4" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AE4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>• Президент сменился: Prof. Ahmed El-Sabbagh с 1 июля 2026 г. (вместо Prof. Amr Adly)
 • Сайт ejust.edu.eg недоступен (503) — контакты Управления международных связей взяты из поисковой выдержки официальной страницы
@@ -1340,7 +1361,7 @@
 • Спутников на орбите нет; есть учебная спутниковая лаборатория EgSA</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>• Https://ejust.edu.eg/get/news/details/215
 • Https://eng.pressbee.net/show4898887.html
@@ -1348,12 +1369,12 @@
 • Https://spaceinafrica.com/2021/03/09/egsa-signs-agreement-with-egypt-japan-university-of-science-and-technology/</t>
         </is>
       </c>
-      <c r="AH4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1419,91 +1440,96 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
           <t>info_intoffice@bsu.edu.eg</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>info@bsu.edu.eg</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>+20 82 2356845</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>https://www.bsu.edu.eg</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Prof. Tarek Ali</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>Acting President</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1201–1400</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr">
+      <c r="T5" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="n">
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="4" t="inlineStr"/>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>Educational CubeSat supplied by EgSA under 2021 executive agreement (student training)</t>
         </is>
       </c>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>AI-powered autonomous optical satellite-tracking ground station (student graduation project, telescope-based)</t>
         </is>
       </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>• Faculty of Navigation Science and Space Technology (est. 2016
 • Depts. of Space Navigation, Space Science, Space Communications)</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>• Egyptian Space Agency (EgSA) — executive agreement on educational satellite (Feb 2021)
 • NARSS (student visits)</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="n">
+      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="AC5" s="6" t="inlineStr">
+      <c r="AD5" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD5" s="4" t="inlineStr">
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>• Prof. Tarek Ali — исполняющий обязанности президента (القائم بأعمال رئيس الجامعة), не постоянный президент
 • Единственный в Египте профильный факультет навигации и космических технологий; декан — Prof. Osama Shalabiea (أسامة شلبية)
@@ -1511,7 +1537,7 @@
 • Факультет дал интервью китайскому CGTN (сен. 2026) — интерес к сотрудничеству с Китаем/БРИКС</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t>• Https://www.bsu.edu.eg/ContentSide.aspx?section_id=14&amp;cat_id=1
 • Https://www.bsu.edu.eg/NewsDetails_New.aspx?NID=167895&amp;cat_id=1&amp;lang=ar
@@ -1523,12 +1549,12 @@
 • Https://www.universityworldnews.com/post.php?story=20210406120310615</t>
         </is>
       </c>
-      <c r="AH5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1594,53 +1620,58 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
           <t>info@iro.cu.edu.eg</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>+20 2 35676352</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>https://cu.edu.eg</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Prof. Mohamed Sami Abdel-Sadek</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="S6" s="4" t="inlineStr">
         <is>
           <t>QS2027: 363</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="n">
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="4" t="inlineStr"/>
-      <c r="W6" s="4" t="inlineStr">
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
         <is>
           <t>• CU-CubeSat (1U student pico-satellite, Aerospace Dept. graduation project
 • Launch not confirmed)</t>
         </is>
       </c>
-      <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Y6" s="4" t="inlineStr"/>
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>• Faculty of Engineering, Department of Aerospace Engineering
 • Space System Technology Laboratory (SSTLab)
@@ -1648,31 +1679,31 @@
 • EgSA-supported educational satellite laboratory at Faculty of Engineering</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) – agreement on educational satellite laboratory (Egyptian Space Technology Educational Platform), 2022</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="n">
+      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="AC6" s="6" t="inlineStr">
+      <c r="AD6" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AE6" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>• Сайты cu.edu.eg и iro.cu.edu.eg недоступны (503/бот-защита) — контакты взяты из поисковых выдержек официальных страниц, требуют перепроверки
 • Общий e-mail канцелярии президента не найден
@@ -1680,7 +1711,7 @@
 • Собственных спутников на орбите не найдено; CU-CubeSat — учебный проект</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr">
         <is>
           <t>• Https://cu.edu.eg
 • Https://iro.cu.edu.eg/contact-us
@@ -1690,12 +1721,12 @@
 • Https://www.youm7.com/story/2026/9/6/7537608</t>
         </is>
       </c>
-      <c r="AH6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1760,87 +1791,92 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
           <t>ipso@aucegypt.edu</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>officeofthepresident@aucegypt.edu</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>+20 2 2615 1000</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>https://www.aucegypt.edu</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Prof. Ahmad S. Dallal</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>QS2027: 390</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="n">
+      <c r="U7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="4" t="inlineStr"/>
-      <c r="W7" s="4" t="inlineStr">
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr">
         <is>
           <t>• AUC CubeSat (student surface-imaging CubeSat project, 2013
 • Current status unknown)</t>
         </is>
       </c>
-      <c r="X7" s="4" t="inlineStr"/>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="Y7" s="4" t="inlineStr"/>
+      <c r="Z7" s="4" t="inlineStr">
         <is>
           <t>• Astronomical Observatory (School of Sciences and Engineering)
 • AUC CubeSat student team (2013)</t>
         </is>
       </c>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="AA7" s="4" t="inlineStr">
         <is>
           <t>Study visits of ECE department to Egyptian Space Agency (EgSA)</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="n">
+      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="AC7" s="6" t="inlineStr">
+      <c r="AD7" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD7" s="4" t="inlineStr">
+      <c r="AE7" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr">
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>• Частный американский некоммерческий вуз (аккредитация в США); представительство в Нью-Йорке: 420 Lexington Ave., Suite 1644
 • Студенческий проект AUC CubeSat (2013) — запуск не подтверждён
@@ -1848,7 +1884,7 @@
 • Менеджер по международным партнёрствам: Iman Nabil (iman.kamel@aucegypt.edu)</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
+      <c r="AH7" s="4" t="inlineStr">
         <is>
           <t>• Https://www.aucegypt.edu/about/leadership
 • Https://www.aucegypt.edu/about/leadership/president/office
@@ -1858,12 +1894,12 @@
 • Qianmu.org QS2027 list</t>
         </is>
       </c>
-      <c r="AH7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1926,46 +1962,51 @@
 Обращение: Dear Prof. Nabawy,</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>President@nriag.sci.eg</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>+20 2 25541100</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>https://www.nriag.sci.eg</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>Prof. Bassem Nabawy</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="n">
+      <c r="U8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="4" t="inlineStr"/>
       <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr">
+      <c r="X8" s="4" t="inlineStr"/>
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>Helwan Satellite Laser Ranging (SLR) station (ILRS network); Kottamia Astronomical Observatory</t>
         </is>
       </c>
-      <c r="Y8" s="4" t="inlineStr">
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <t>• Solar &amp; Space Department (Solar Lab
 • Space Lab)
@@ -1973,33 +2014,33 @@
 • Egyptian National Seismic Network</t>
         </is>
       </c>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>• Czech Technical University (FNSPE) – Helwan SLR station
 • ILRS (NASA-coordinated network)
 • Swedish embassy cooperation talks (2026)</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="n">
+      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="AC8" s="6" t="inlineStr">
+      <c r="AD8" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD8" s="4" t="inlineStr">
+      <c r="AE8" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE8" s="4" t="inlineStr">
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF8" s="4" t="inlineStr">
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>• Отдельного e-mail международного отдела нет; есть раздел «International Relation and Training»
 • Письмо направлять на President@nriag.sci.eg
@@ -2007,7 +2048,7 @@
 • Спутников не создавал; имеет станцию лазерной дальнометрии спутников в Хелуане</t>
         </is>
       </c>
-      <c r="AG8" s="4" t="inlineStr">
+      <c r="AH8" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nriag.sci.eg/
 • Https://www.nriag.sci.eg/contact-us/
@@ -2016,12 +2057,12 @@
 • Http://kfe.fjfi.cvut.cz/~blazej/en/res/prj/helwan.html</t>
         </is>
       </c>
-      <c r="AH8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -2085,97 +2126,102 @@
 Обращение: Dear Prof. Mandor,</t>
         </is>
       </c>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>President_office@suez.edu.eg</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>+20 64 3223007</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>https://suez.edu.eg</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>Prof. Naser Saeed Mandor</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr">
+      <c r="S9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="n">
+      <c r="U9" s="4" t="inlineStr"/>
+      <c r="V9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="4" t="inlineStr"/>
-      <c r="W9" s="4" t="inlineStr">
+      <c r="W9" s="4" t="inlineStr"/>
+      <c r="X9" s="4" t="inlineStr">
         <is>
           <t>Educational CubeSat supplied by EgSA (executive agreement, ~2021)</t>
         </is>
       </c>
-      <c r="X9" s="4" t="inlineStr"/>
       <c r="Y9" s="4" t="inlineStr"/>
-      <c r="Z9" s="4" t="inlineStr">
+      <c r="Z9" s="4" t="inlineStr"/>
+      <c r="AA9" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) — educational CubeSat agreement (2021)</t>
         </is>
       </c>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="n">
+      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="AC9" s="6" t="inlineStr">
+      <c r="AD9" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD9" s="4" t="inlineStr">
+      <c r="AE9" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE9" s="4" t="inlineStr">
+      <c r="AF9" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF9" s="4" t="inlineStr">
+      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>• Отдельного e-mail международного отдела на сайте не найдено — писать в офис президента (President_office@suez.edu.eg); также опубликован тел. +20 2 22621217
 • Участник программы EgSA по образовательным кубсатам (2021); запусков собственного спутника не найдено
 • В QS2027 не найден</t>
         </is>
       </c>
-      <c r="AG9" s="4" t="inlineStr">
+      <c r="AH9" s="4" t="inlineStr">
         <is>
           <t>• Https://suez.edu.eg/ar/en/
 • Https://suez.edu.eg/ar/en/contact-us/
 • Https://www.universityworldnews.com/post.php?story=20210406120310615</t>
         </is>
       </c>
-      <c r="AH9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI9"/>
+  <autoFilter ref="A1:AJ9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2186,7 +2232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI74"/>
+  <dimension ref="A1:AJ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2200,30 +2246,31 @@
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="10"/>
     <col width="36" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="45" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="45" customWidth="1" min="23" max="23"/>
     <col width="30" customWidth="1" min="24" max="24"/>
-    <col width="40" customWidth="1" min="25" max="25"/>
-    <col width="45" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="9" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="55" customWidth="1" min="32" max="32"/>
-    <col width="60" customWidth="1" min="33" max="33"/>
-    <col width="12" customWidth="1" min="34" max="34"/>
-    <col width="24" customWidth="1" min="35" max="35"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="45" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="55" customWidth="1" min="33" max="33"/>
+    <col width="60" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="24" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2284,120 +2331,125 @@
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
+          <t>Стыковка e-mail и адресата</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>E-mail (международный отдел)</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>E-mail (общий / ректорат)</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Телефон</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Ректор / президент</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Должность</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Рейтинг QS</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Рейтинг THE</t>
         </is>
       </c>
-      <c r="T1" s="3" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Национальный рейтинг</t>
         </is>
       </c>
-      <c r="U1" s="3" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Запущено КА (спутников)</t>
         </is>
       </c>
-      <c r="V1" s="3" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Названия запущенных КА (год)</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>КА в разработке</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>Наземная станция</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Космические подразделения</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Партнёрства в космической сфере</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>Космический индекс (0–100)</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>Волна рассылки</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Секретарь парткома (справочно, Китай)</t>
         </is>
@@ -2454,57 +2506,62 @@
       </c>
       <c r="J2" s="4" t="inlineStr"/>
       <c r="K2" s="4" t="inlineStr"/>
-      <c r="L2" s="4" t="inlineStr"/>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M2" s="4" t="inlineStr"/>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>+20 2 26251200</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>https://www.narss.sci.eg</t>
         </is>
       </c>
-      <c r="P2" s="4" t="inlineStr">
+      <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>Prof. Abdelaziz Ballal</t>
         </is>
       </c>
-      <c r="Q2" s="4" t="inlineStr">
+      <c r="R2" s="4" t="inlineStr">
         <is>
           <t>Acting Chairman (President)</t>
         </is>
       </c>
-      <c r="R2" s="4" t="inlineStr"/>
       <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
-      <c r="U2" s="4" t="n">
+      <c r="U2" s="4" t="inlineStr"/>
+      <c r="V2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="V2" s="4" t="inlineStr">
+      <c r="W2" s="4" t="inlineStr">
         <is>
           <t>• EgyptSat-1 (2007)
 • NARSSCube-2 (2019)
 • NARSSCube-1 (2019)</t>
         </is>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>6U agricultural monitoring CubeSat (announced 2023)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>Satellite data receiving station in Aswan (X-band; Landsat/SPOT reception)</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>Space Technology Division</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>• Egyptian Space Agency (EgSA)
 • African Space Agency (host country Egypt)
@@ -2512,22 +2569,22 @@
 • Cooperation protocols with Egyptian universities (e.g., Beni-Suef National University)</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr"/>
-      <c r="AB2" s="4" t="n">
+      <c r="AB2" s="4" t="inlineStr"/>
+      <c r="AC2" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="AC2" s="5" t="inlineStr">
+      <c r="AD2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD2" s="4" t="inlineStr"/>
-      <c r="AE2" s="4" t="inlineStr">
+      <c r="AE2" s="4" t="inlineStr"/>
+      <c r="AF2" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>• Руководитель — и.о. председателя Prof. Abdelaziz Ballal (назначен 3 июня 2026 г.; ранее — Prof. Islam Abou El-Magd)
 • Сайт narss.sci.eg недоступен (503)
@@ -2535,7 +2592,7 @@
 • EgyptSat-1 создан совместно с КБ «Южное» (Украина); EgyptSat-2 не учтён (построен РКК «Энергия», позже передан EgSA)</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>• Https://www.elwatannews.com/news/details/8295289
 • Https://spaceinafrica.com/2023/08/02/bridging-science-and-society-narsss-impact-on-egypts-development-and-technological-progress/
@@ -2544,12 +2601,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI2" s="4" t="inlineStr"/>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -2613,52 +2670,57 @@
 Обращение: Dear Dr. Ismail,</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>info@egsa.gov.eg</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>+20 2 21297950</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>https://www.egsa.gov.eg</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>Dr. Eng. Majed Ismail</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>CEO</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="4" t="inlineStr"/>
       <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="n">
+      <c r="U3" s="4" t="inlineStr"/>
+      <c r="V3" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="V3" s="4" t="inlineStr">
+      <c r="W3" s="4" t="inlineStr">
         <is>
           <t>• MisrSat-2 (2023)
 • NExSat-1 (2024)
 • SPNeX (2025)</t>
         </is>
       </c>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr"/>
+      <c r="Y3" s="4" t="inlineStr">
         <is>
           <t>EgSA ground control station at Egyptian Space City (MisrSat-2 ground segment)</t>
         </is>
       </c>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>• Satellite Assembly, Integration and Testing Center (AITC)
 • Egyptian Space City
@@ -2666,7 +2728,7 @@
 • Egyptian Universities Satellite (CubeSat) programme</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>• China (MisrSat-2 grant, AITC)
 • Berlin Space Technologies (NExSat-1)
@@ -2676,26 +2738,26 @@
 • China Meteorological Administration (talks, Sep 2026)</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="n">
+      <c r="AB3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="AC3" s="5" t="inlineStr">
+      <c r="AD3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AD3" s="4" t="inlineStr">
+      <c r="AE3" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>• Агентство, не университет; сайт egsa.gov.eg — SPA, контактные данные подгружаются из API (недоступен); адрес/e-mail/телефон с iafastro.org и WIPO TISC
 • CEO д-р инж. Маджид Исмаил назначен 19.08.2025 на 1 год; в сентябре 2026 продолжает исполнять обязанности (новости youm7/elbalad) — проверить продление
@@ -2703,7 +2765,7 @@
 • Отдельный e-mail международного отдела не найден — использовать info@egsa.gov.eg</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>• Https://www.iafastro.org/membership/all-members/egyptian-space-agency-egsa.html
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=11051
@@ -2719,12 +2781,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AH3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI3" s="4" t="inlineStr"/>
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -2790,83 +2852,88 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
           <t>international.affairs@ejust.edu.eg</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr"/>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>+20 3 4599855</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>https://www.ejust.edu.eg</t>
         </is>
       </c>
-      <c r="P4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>Prof. Ahmed El-Sabbagh</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
+      <c r="R4" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="S4" s="4" t="inlineStr"/>
+      <c r="T4" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="n">
+      <c r="U4" s="4" t="inlineStr"/>
+      <c r="V4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="4" t="inlineStr"/>
-      <c r="W4" s="4" t="inlineStr">
+      <c r="W4" s="4" t="inlineStr"/>
+      <c r="X4" s="4" t="inlineStr">
         <is>
           <t>EgSA educational satellite model (lab satellite for communication, remote sensing and space-environment applications)</t>
         </is>
       </c>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>Ground station simulation unit (educational, supplied under EgSA agreement)</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>EgSA educational satellite laboratory (satellite model, operation/testing simulators, ground-station simulator)</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>• Egyptian Space Agency (EgSA) – executive agreement on educational satellite lab, 2021
 • EgSA cooperation protocol with universities, 2021
 • JICA / Japanese partner universities consortium</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="n">
+      <c r="AB4" s="4" t="inlineStr"/>
+      <c r="AC4" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="AC4" s="6" t="inlineStr">
+      <c r="AD4" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD4" s="4" t="inlineStr">
+      <c r="AE4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>• Президент сменился: Prof. Ahmed El-Sabbagh с 1 июля 2026 г. (вместо Prof. Amr Adly)
 • Сайт ejust.edu.eg недоступен (503) — контакты Управления международных связей взяты из поисковой выдержки официальной страницы
@@ -2874,7 +2941,7 @@
 • Спутников на орбите нет; есть учебная спутниковая лаборатория EgSA</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>• Https://ejust.edu.eg/get/news/details/215
 • Https://eng.pressbee.net/show4898887.html
@@ -2882,12 +2949,12 @@
 • Https://spaceinafrica.com/2021/03/09/egsa-signs-agreement-with-egypt-japan-university-of-science-and-technology/</t>
         </is>
       </c>
-      <c r="AH4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI4" s="4" t="inlineStr"/>
+      <c r="AI4" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -2953,91 +3020,96 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
           <t>info_intoffice@bsu.edu.eg</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>info@bsu.edu.eg</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>+20 82 2356845</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>https://www.bsu.edu.eg</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr">
+      <c r="Q5" s="4" t="inlineStr">
         <is>
           <t>Prof. Tarek Ali</t>
         </is>
       </c>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="R5" s="4" t="inlineStr">
         <is>
           <t>Acting President</t>
         </is>
       </c>
-      <c r="R5" s="4" t="inlineStr">
+      <c r="S5" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1201–1400</t>
         </is>
       </c>
-      <c r="S5" s="4" t="inlineStr">
+      <c r="T5" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="n">
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="4" t="inlineStr"/>
-      <c r="W5" s="4" t="inlineStr">
+      <c r="W5" s="4" t="inlineStr"/>
+      <c r="X5" s="4" t="inlineStr">
         <is>
           <t>Educational CubeSat supplied by EgSA under 2021 executive agreement (student training)</t>
         </is>
       </c>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>AI-powered autonomous optical satellite-tracking ground station (student graduation project, telescope-based)</t>
         </is>
       </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>• Faculty of Navigation Science and Space Technology (est. 2016
 • Depts. of Space Navigation, Space Science, Space Communications)</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>• Egyptian Space Agency (EgSA) — executive agreement on educational satellite (Feb 2021)
 • NARSS (student visits)</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="n">
+      <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="AC5" s="6" t="inlineStr">
+      <c r="AD5" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD5" s="4" t="inlineStr">
+      <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>• Prof. Tarek Ali — исполняющий обязанности президента (القائم بأعمال رئيس الجامعة), не постоянный президент
 • Единственный в Египте профильный факультет навигации и космических технологий; декан — Prof. Osama Shalabiea (أسامة شلبية)
@@ -3045,7 +3117,7 @@
 • Факультет дал интервью китайскому CGTN (сен. 2026) — интерес к сотрудничеству с Китаем/БРИКС</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t>• Https://www.bsu.edu.eg/ContentSide.aspx?section_id=14&amp;cat_id=1
 • Https://www.bsu.edu.eg/NewsDetails_New.aspx?NID=167895&amp;cat_id=1&amp;lang=ar
@@ -3057,12 +3129,12 @@
 • Https://www.universityworldnews.com/post.php?story=20210406120310615</t>
         </is>
       </c>
-      <c r="AH5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI5" s="4" t="inlineStr"/>
+      <c r="AI5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -3128,53 +3200,58 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
           <t>info@iro.cu.edu.eg</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr"/>
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>+20 2 35676352</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>https://cu.edu.eg</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr">
+      <c r="Q6" s="4" t="inlineStr">
         <is>
           <t>Prof. Mohamed Sami Abdel-Sadek</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="R6" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr">
+      <c r="S6" s="4" t="inlineStr">
         <is>
           <t>QS2027: 363</t>
         </is>
       </c>
-      <c r="S6" s="4" t="inlineStr">
+      <c r="T6" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="T6" s="4" t="inlineStr"/>
-      <c r="U6" s="4" t="n">
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="4" t="inlineStr"/>
-      <c r="W6" s="4" t="inlineStr">
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
         <is>
           <t>• CU-CubeSat (1U student pico-satellite, Aerospace Dept. graduation project
 • Launch not confirmed)</t>
         </is>
       </c>
-      <c r="X6" s="4" t="inlineStr"/>
-      <c r="Y6" s="4" t="inlineStr">
+      <c r="Y6" s="4" t="inlineStr"/>
+      <c r="Z6" s="4" t="inlineStr">
         <is>
           <t>• Faculty of Engineering, Department of Aerospace Engineering
 • Space System Technology Laboratory (SSTLab)
@@ -3182,31 +3259,31 @@
 • EgSA-supported educational satellite laboratory at Faculty of Engineering</t>
         </is>
       </c>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) – agreement on educational satellite laboratory (Egyptian Space Technology Educational Platform), 2022</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="n">
+      <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="AC6" s="6" t="inlineStr">
+      <c r="AD6" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD6" s="4" t="inlineStr">
+      <c r="AE6" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>• Сайты cu.edu.eg и iro.cu.edu.eg недоступны (503/бот-защита) — контакты взяты из поисковых выдержек официальных страниц, требуют перепроверки
 • Общий e-mail канцелярии президента не найден
@@ -3214,7 +3291,7 @@
 • Собственных спутников на орбите не найдено; CU-CubeSat — учебный проект</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr">
         <is>
           <t>• Https://cu.edu.eg
 • Https://iro.cu.edu.eg/contact-us
@@ -3224,12 +3301,12 @@
 • Https://www.youm7.com/story/2026/9/6/7537608</t>
         </is>
       </c>
-      <c r="AH6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -3294,87 +3371,92 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
           <t>ipso@aucegypt.edu</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>officeofthepresident@aucegypt.edu</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>+20 2 2615 1000</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>https://www.aucegypt.edu</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr">
+      <c r="Q7" s="4" t="inlineStr">
         <is>
           <t>Prof. Ahmad S. Dallal</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="R7" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
+      <c r="S7" s="4" t="inlineStr">
         <is>
           <t>QS2027: 390</t>
         </is>
       </c>
-      <c r="S7" s="4" t="inlineStr">
+      <c r="T7" s="4" t="inlineStr">
         <is>
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="T7" s="4" t="inlineStr"/>
-      <c r="U7" s="4" t="n">
+      <c r="U7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="4" t="inlineStr"/>
-      <c r="W7" s="4" t="inlineStr">
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr">
         <is>
           <t>• AUC CubeSat (student surface-imaging CubeSat project, 2013
 • Current status unknown)</t>
         </is>
       </c>
-      <c r="X7" s="4" t="inlineStr"/>
-      <c r="Y7" s="4" t="inlineStr">
+      <c r="Y7" s="4" t="inlineStr"/>
+      <c r="Z7" s="4" t="inlineStr">
         <is>
           <t>• Astronomical Observatory (School of Sciences and Engineering)
 • AUC CubeSat student team (2013)</t>
         </is>
       </c>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="AA7" s="4" t="inlineStr">
         <is>
           <t>Study visits of ECE department to Egyptian Space Agency (EgSA)</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="n">
+      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="AC7" s="6" t="inlineStr">
+      <c r="AD7" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD7" s="4" t="inlineStr">
+      <c r="AE7" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr">
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>• Частный американский некоммерческий вуз (аккредитация в США); представительство в Нью-Йорке: 420 Lexington Ave., Suite 1644
 • Студенческий проект AUC CubeSat (2013) — запуск не подтверждён
@@ -3382,7 +3464,7 @@
 • Менеджер по международным партнёрствам: Iman Nabil (iman.kamel@aucegypt.edu)</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
+      <c r="AH7" s="4" t="inlineStr">
         <is>
           <t>• Https://www.aucegypt.edu/about/leadership
 • Https://www.aucegypt.edu/about/leadership/president/office
@@ -3392,12 +3474,12 @@
 • Qianmu.org QS2027 list</t>
         </is>
       </c>
-      <c r="AH7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -3460,46 +3542,51 @@
 Обращение: Dear Prof. Nabawy,</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr"/>
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>President@nriag.sci.eg</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>+20 2 25541100</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>https://www.nriag.sci.eg</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr">
+      <c r="Q8" s="4" t="inlineStr">
         <is>
           <t>Prof. Bassem Nabawy</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="n">
+      <c r="U8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="4" t="inlineStr"/>
       <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr">
+      <c r="X8" s="4" t="inlineStr"/>
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>Helwan Satellite Laser Ranging (SLR) station (ILRS network); Kottamia Astronomical Observatory</t>
         </is>
       </c>
-      <c r="Y8" s="4" t="inlineStr">
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <t>• Solar &amp; Space Department (Solar Lab
 • Space Lab)
@@ -3507,33 +3594,33 @@
 • Egyptian National Seismic Network</t>
         </is>
       </c>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>• Czech Technical University (FNSPE) – Helwan SLR station
 • ILRS (NASA-coordinated network)
 • Swedish embassy cooperation talks (2026)</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="n">
+      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="AC8" s="6" t="inlineStr">
+      <c r="AD8" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD8" s="4" t="inlineStr">
+      <c r="AE8" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE8" s="4" t="inlineStr">
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF8" s="4" t="inlineStr">
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>• Отдельного e-mail международного отдела нет; есть раздел «International Relation and Training»
 • Письмо направлять на President@nriag.sci.eg
@@ -3541,7 +3628,7 @@
 • Спутников не создавал; имеет станцию лазерной дальнометрии спутников в Хелуане</t>
         </is>
       </c>
-      <c r="AG8" s="4" t="inlineStr">
+      <c r="AH8" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nriag.sci.eg/
 • Https://www.nriag.sci.eg/contact-us/
@@ -3550,12 +3637,12 @@
 • Http://kfe.fjfi.cvut.cz/~blazej/en/res/prj/helwan.html</t>
         </is>
       </c>
-      <c r="AH8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -3621,74 +3708,79 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
           <t>int.affairs@nu.edu.eg</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>+20 2 3854 1734</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>https://nu.edu.eg</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr">
+      <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>Prof. Ahmed Elghazouli</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="R9" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr"/>
-      <c r="S9" s="4" t="inlineStr">
+      <c r="S9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1801–2000</t>
         </is>
       </c>
-      <c r="T9" s="4" t="inlineStr"/>
-      <c r="U9" s="4" t="n">
+      <c r="U9" s="4" t="inlineStr"/>
+      <c r="V9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="4" t="inlineStr"/>
       <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr"/>
-      <c r="Y9" s="4" t="inlineStr">
+      <c r="Y9" s="4" t="inlineStr"/>
+      <c r="Z9" s="4" t="inlineStr">
         <is>
           <t>• Wireless Intelligent Networks Center (WINC)
 • Nanoelectronics Integrated Systems Center (NISC)</t>
         </is>
       </c>
-      <c r="Z9" s="4" t="inlineStr">
+      <c r="AA9" s="4" t="inlineStr">
         <is>
           <t>MoU with Tan Kah Kee High Technology Research Institute (China-BRICS Science and Innovation Incubation Park)</t>
         </is>
       </c>
-      <c r="AA9" s="4" t="inlineStr"/>
-      <c r="AB9" s="4" t="n">
+      <c r="AB9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="AC9" s="7" t="inlineStr">
+      <c r="AD9" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD9" s="4" t="inlineStr">
+      <c r="AE9" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE9" s="4" t="inlineStr">
+      <c r="AF9" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF9" s="4" t="inlineStr">
+      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>• Первый национальный некоммерческий университет Египта (self-described)
 • Общий e-mail офиса президента не опубликован; горячая линия 16453
@@ -3697,7 +3789,7 @@
 • В QS2027 не найден</t>
         </is>
       </c>
-      <c r="AG9" s="4" t="inlineStr">
+      <c r="AH9" s="4" t="inlineStr">
         <is>
           <t>• Https://nu.edu.eg/
 • Https://nu.edu.eg/nu-president
@@ -3707,12 +3799,12 @@
 • Https://www.nu.edu.eg/news/nile-university-forges-strategic-partnership-china-brics-siip-drive-global-innovation</t>
         </is>
       </c>
-      <c r="AH9" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -3776,94 +3868,99 @@
 Обращение: Dear Prof. Mandor,</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>President_office@suez.edu.eg</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>+20 64 3223007</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>https://suez.edu.eg</t>
         </is>
       </c>
-      <c r="P10" s="4" t="inlineStr">
+      <c r="Q10" s="4" t="inlineStr">
         <is>
           <t>Prof. Naser Saeed Mandor</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="inlineStr">
+      <c r="R10" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr">
+      <c r="S10" s="4" t="inlineStr"/>
+      <c r="T10" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T10" s="4" t="inlineStr"/>
-      <c r="U10" s="4" t="n">
+      <c r="U10" s="4" t="inlineStr"/>
+      <c r="V10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="4" t="inlineStr"/>
-      <c r="W10" s="4" t="inlineStr">
+      <c r="W10" s="4" t="inlineStr"/>
+      <c r="X10" s="4" t="inlineStr">
         <is>
           <t>Educational CubeSat supplied by EgSA (executive agreement, ~2021)</t>
         </is>
       </c>
-      <c r="X10" s="4" t="inlineStr"/>
       <c r="Y10" s="4" t="inlineStr"/>
-      <c r="Z10" s="4" t="inlineStr">
+      <c r="Z10" s="4" t="inlineStr"/>
+      <c r="AA10" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) — educational CubeSat agreement (2021)</t>
         </is>
       </c>
-      <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="n">
+      <c r="AB10" s="4" t="inlineStr"/>
+      <c r="AC10" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="AC10" s="6" t="inlineStr">
+      <c r="AD10" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AD10" s="4" t="inlineStr">
+      <c r="AE10" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE10" s="4" t="inlineStr">
+      <c r="AF10" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF10" s="4" t="inlineStr">
+      <c r="AG10" s="4" t="inlineStr">
         <is>
           <t>• Отдельного e-mail международного отдела на сайте не найдено — писать в офис президента (President_office@suez.edu.eg); также опубликован тел. +20 2 22621217
 • Участник программы EgSA по образовательным кубсатам (2021); запусков собственного спутника не найдено
 • В QS2027 не найден</t>
         </is>
       </c>
-      <c r="AG10" s="4" t="inlineStr">
+      <c r="AH10" s="4" t="inlineStr">
         <is>
           <t>• Https://suez.edu.eg/ar/en/
 • Https://suez.edu.eg/ar/en/contact-us/
 • Https://www.universityworldnews.com/post.php?story=20210406120310615</t>
         </is>
       </c>
-      <c r="AH10" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI10" s="4" t="inlineStr"/>
+      <c r="AI10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -3929,89 +4026,94 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
           <t>iro@asu.edu.eg</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>President@asu.edu.eg</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>+20 2 26831231</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>https://www.asu.edu.eg</t>
         </is>
       </c>
-      <c r="P11" s="4" t="inlineStr">
+      <c r="Q11" s="4" t="inlineStr">
         <is>
           <t>Prof. Mohamed Diaa Zain El-Abedeen</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr">
+      <c r="S11" s="4" t="inlineStr">
         <is>
           <t>QS2027: 551</t>
         </is>
       </c>
-      <c r="S11" s="4" t="inlineStr">
+      <c r="T11" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="T11" s="4" t="inlineStr"/>
-      <c r="U11" s="4" t="n">
+      <c r="U11" s="4" t="inlineStr"/>
+      <c r="V11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="4" t="inlineStr"/>
       <c r="W11" s="4" t="inlineStr"/>
       <c r="X11" s="4" t="inlineStr"/>
-      <c r="Y11" s="4" t="inlineStr">
+      <c r="Y11" s="4" t="inlineStr"/>
+      <c r="Z11" s="4" t="inlineStr">
         <is>
           <t>Space innovation laboratory at Faculty of Engineering (EgSA 'Space Keys' educational satellite programme)</t>
         </is>
       </c>
-      <c r="Z11" s="4" t="inlineStr">
+      <c r="AA11" s="4" t="inlineStr">
         <is>
           <t>• Egyptian Space Agency (EgSA) — cooperation protocol
 • Space Keys educational satellite project (EgSA / ASRT)</t>
         </is>
       </c>
-      <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="n">
+      <c r="AB11" s="4" t="inlineStr"/>
+      <c r="AC11" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="AC11" s="8" t="inlineStr">
+      <c r="AD11" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD11" s="4" t="inlineStr">
+      <c r="AE11" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE11" s="4" t="inlineStr">
+      <c r="AF11" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF11" s="4" t="inlineStr">
+      <c r="AG11" s="4" t="inlineStr">
         <is>
           <t>• Руководитель Управления международных связей (IRO) указан на странице IRAC без даты — сверить актуальность
 • Международным сотрудничеством в целом руководит исполнительный директор сектора IRAC проф. Шервит Эль-Ахмади (irac@asu.edu.eg) — можно поставить в копию
 • Запущенных спутников не найдено; участвует в программе учебных спутников EgSA</t>
         </is>
       </c>
-      <c r="AG11" s="4" t="inlineStr">
+      <c r="AH11" s="4" t="inlineStr">
         <is>
           <t>• Https://www.asu.edu.eg/en/38/page/contact-us
 • Https://www.asu.edu.eg/en
@@ -4023,12 +4125,12 @@
 • Https://www.qianmu.org/ranking/1528.htm (2027 QS list, qianmu.org)</t>
         </is>
       </c>
-      <c r="AH11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -4093,81 +4195,86 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
           <t>int.office@alexu.edu.eg</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>info@alexu.edu.eg</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>+20 3 5921675</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>https://alexu.edu.eg</t>
         </is>
       </c>
-      <c r="P12" s="4" t="inlineStr">
+      <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>Prof. Ahmed Adel Abdel Hakim</t>
         </is>
       </c>
-      <c r="Q12" s="4" t="inlineStr">
+      <c r="R12" s="4" t="inlineStr">
         <is>
           <t>Acting President</t>
         </is>
       </c>
-      <c r="R12" s="4" t="inlineStr">
+      <c r="S12" s="4" t="inlineStr">
         <is>
           <t>QS2027: 801–850</t>
         </is>
       </c>
-      <c r="S12" s="4" t="inlineStr">
+      <c r="T12" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="T12" s="4" t="inlineStr"/>
-      <c r="U12" s="4" t="n">
+      <c r="U12" s="4" t="inlineStr"/>
+      <c r="V12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="4" t="inlineStr"/>
       <c r="W12" s="4" t="inlineStr"/>
       <c r="X12" s="4" t="inlineStr"/>
-      <c r="Y12" s="4" t="inlineStr">
+      <c r="Y12" s="4" t="inlineStr"/>
+      <c r="Z12" s="4" t="inlineStr">
         <is>
           <t>Educational satellite laboratory (agreement with EgSA, April 2021)</t>
         </is>
       </c>
-      <c r="Z12" s="4" t="inlineStr">
+      <c r="AA12" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) — cooperation protocol (2021), educational satellite lab</t>
         </is>
       </c>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="n">
+      <c r="AB12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="AC12" s="8" t="inlineStr">
+      <c r="AD12" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD12" s="4" t="inlineStr">
+      <c r="AE12" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE12" s="4" t="inlineStr">
+      <c r="AF12" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF12" s="4" t="inlineStr">
+      <c r="AG12" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт alexu.edu.eg выдаёт ошибку 500 (октябрь 2026); адрес/телефон/info@ взяты из справочника universitiesegypt.com — сверить
 • Президент проф. Абдель Азиз Кансуа с февраля 2026 — министр высшего образования; университет возглавляет и.о. президента проф. Ахмед Адель Абдель Хаким (сентябрь 2026)
@@ -4175,7 +4282,7 @@
 • Запущенных спутников не найдено; есть протокол с EgSA о создании учебной спутниковой лаборатории (2021)</t>
         </is>
       </c>
-      <c r="AG12" s="4" t="inlineStr">
+      <c r="AH12" s="4" t="inlineStr">
         <is>
           <t>• Https://internationaloffice.alexu.edu.eg/contact-us/
 • Https://www.elwatannews.com/news/details/8361274
@@ -4185,12 +4292,12 @@
 • Https://www.qianmu.org/ranking/1528.htm (2027 QS list, qianmu.org)</t>
         </is>
       </c>
-      <c r="AH12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -4253,87 +4360,92 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>Public.relations@aast.edu</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>+20 3 5622366; +20 3 5622388</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>https://aast.edu</t>
         </is>
       </c>
-      <c r="P13" s="4" t="inlineStr">
+      <c r="Q13" s="4" t="inlineStr">
         <is>
           <t>Prof. Ismail Abdel Ghafar Ismail Farag</t>
         </is>
       </c>
-      <c r="Q13" s="4" t="inlineStr">
+      <c r="R13" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R13" s="4" t="inlineStr">
+      <c r="S13" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1001–1200</t>
         </is>
       </c>
-      <c r="S13" s="4" t="inlineStr">
+      <c r="T13" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="T13" s="4" t="inlineStr"/>
-      <c r="U13" s="4" t="n">
+      <c r="U13" s="4" t="inlineStr"/>
+      <c r="V13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="4" t="inlineStr"/>
       <c r="W13" s="4" t="inlineStr"/>
       <c r="X13" s="4" t="inlineStr"/>
-      <c r="Y13" s="4" t="inlineStr">
+      <c r="Y13" s="4" t="inlineStr"/>
+      <c r="Z13" s="4" t="inlineStr">
         <is>
           <t>Space innovation lab with EgSA 'Space Keys' educational satellite (College of Engineering, Cairo-Sheraton branch)</t>
         </is>
       </c>
-      <c r="Z13" s="4" t="inlineStr">
+      <c r="AA13" s="4" t="inlineStr">
         <is>
           <t>• Egyptian Space Agency (EgSA) – cooperation protocol (2021), agreement to receive educational CubeSats, 'Space Keys' satellite delivered Jan 2022
 • EgSA CEO met AASTMT President on training/expertise exchange (Sep 2026)</t>
         </is>
       </c>
-      <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="n">
+      <c r="AB13" s="4" t="inlineStr"/>
+      <c r="AC13" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="AC13" s="8" t="inlineStr">
+      <c r="AD13" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD13" s="4" t="inlineStr">
+      <c r="AE13" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE13" s="4" t="inlineStr">
+      <c r="AF13" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF13" s="4" t="inlineStr">
+      <c r="AG13" s="4" t="inlineStr">
         <is>
           <t>• Общий e-mail — отдела протокола и связей с общественностью (Public.relations@aast.edu); адрес международного отдела на сайте не найден
 • Академия Лиги арабских государств, кампусы в Александрии, Каире, Порт-Саиде, Асуане, Эль-Аламейне, Латакии, Шардже
 • Сентябрь 2026: встреча главы EgSA с президентом AASTMT — удобный повод для упоминания в письме</t>
         </is>
       </c>
-      <c r="AG13" s="4" t="inlineStr">
+      <c r="AH13" s="4" t="inlineStr">
         <is>
           <t>• Https://aast.edu/en/index.php
 • Https://aast.edu/en/about/
@@ -4345,12 +4457,12 @@
 • Https://www.masrawy.com/news/news_egypt/details/2026/9/23/3052657/</t>
         </is>
       </c>
-      <c r="AH13" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI13" s="4" t="inlineStr"/>
+      <c r="AI13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -4416,87 +4528,92 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
           <t>iroffice@hq.helwan.edu.eg</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>President@capu.edu.eg</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>+20 2 28162061; +20 2 28162062</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>https://www.capu.edu.eg</t>
         </is>
       </c>
-      <c r="P14" s="4" t="inlineStr">
+      <c r="Q14" s="4" t="inlineStr">
         <is>
           <t>Prof. El-Sayed Ibrahim Kandil</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="inlineStr">
+      <c r="R14" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R14" s="4" t="inlineStr">
+      <c r="S14" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1201–1400</t>
         </is>
       </c>
-      <c r="S14" s="4" t="inlineStr">
+      <c r="T14" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1601–1800</t>
         </is>
       </c>
-      <c r="T14" s="4" t="inlineStr"/>
-      <c r="U14" s="4" t="n">
+      <c r="U14" s="4" t="inlineStr"/>
+      <c r="V14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="4" t="inlineStr"/>
       <c r="W14" s="4" t="inlineStr"/>
       <c r="X14" s="4" t="inlineStr"/>
-      <c r="Y14" s="4" t="inlineStr">
+      <c r="Y14" s="4" t="inlineStr"/>
+      <c r="Z14" s="4" t="inlineStr">
         <is>
           <t>Space innovation lab (EgSA 'Space Keys' educational satellite kit)</t>
         </is>
       </c>
-      <c r="Z14" s="4" t="inlineStr">
+      <c r="AA14" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) – cooperation protocol (2021), educational CubeSat agreement, 'Space Keys' kit delivered Jan 2022</t>
         </is>
       </c>
-      <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="n">
+      <c r="AB14" s="4" t="inlineStr"/>
+      <c r="AC14" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="AC14" s="8" t="inlineStr">
+      <c r="AD14" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD14" s="4" t="inlineStr">
+      <c r="AE14" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE14" s="4" t="inlineStr">
+      <c r="AF14" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF14" s="4" t="inlineStr">
+      <c r="AG14" s="4" t="inlineStr">
         <is>
           <t>• ДУБЛИКАТ: это тот же вуз, что и 'Helwan University' в этом списке (переименован в Capital University); отправлять одно письмо
 • Рейтинг THE2027 1601–1800 указан во входных данных для Capital University</t>
         </is>
       </c>
-      <c r="AG14" s="4" t="inlineStr">
+      <c r="AH14" s="4" t="inlineStr">
         <is>
           <t>• Https://www.capu.edu.eg/index.php/en/
 • Https://www.capu.edu.eg/index.php/en/president-leaders-en
@@ -4505,12 +4622,12 @@
 • Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/</t>
         </is>
       </c>
-      <c r="AH14" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI14" s="4" t="inlineStr"/>
+      <c r="AI14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -4574,82 +4691,87 @@
 Обращение: Dear Prof. Fakhry,</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>info@eru.edu.eg</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>+20 2 28609114</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>https://eru.edu.eg</t>
         </is>
       </c>
-      <c r="P15" s="4" t="inlineStr">
+      <c r="Q15" s="4" t="inlineStr">
         <is>
           <t>Prof. Sherif Fakhry</t>
         </is>
       </c>
-      <c r="Q15" s="4" t="inlineStr">
+      <c r="R15" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr">
+      <c r="S15" s="4" t="inlineStr"/>
+      <c r="T15" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1601–1800</t>
         </is>
       </c>
-      <c r="T15" s="4" t="inlineStr"/>
-      <c r="U15" s="4" t="n">
+      <c r="U15" s="4" t="inlineStr"/>
+      <c r="V15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="4" t="inlineStr"/>
       <c r="W15" s="4" t="inlineStr"/>
       <c r="X15" s="4" t="inlineStr"/>
-      <c r="Y15" s="4" t="inlineStr">
+      <c r="Y15" s="4" t="inlineStr"/>
+      <c r="Z15" s="4" t="inlineStr">
         <is>
           <t>Educational satellite laboratory at Faculty of Engineering (provided by EgSA)</t>
         </is>
       </c>
-      <c r="Z15" s="4" t="inlineStr">
+      <c r="AA15" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) – cooperation protocol and educational satellite lab (2021)</t>
         </is>
       </c>
-      <c r="AA15" s="4" t="inlineStr"/>
-      <c r="AB15" s="4" t="n">
+      <c r="AB15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="AC15" s="8" t="inlineStr">
+      <c r="AD15" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD15" s="4" t="inlineStr">
+      <c r="AE15" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE15" s="4" t="inlineStr">
+      <c r="AF15" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF15" s="4" t="inlineStr">
+      <c r="AG15" s="4" t="inlineStr">
         <is>
           <t>• Вуз ориентирован на сотрудничество с Россией — удобный партнёр для российской стороны
 • Есть учебная спутниковая лаборатория EgSA на инженерном факультете; собственных спутников нет
 • Отдельный e-mail международного отдела не опубликован</t>
         </is>
       </c>
-      <c r="AG15" s="4" t="inlineStr">
+      <c r="AH15" s="4" t="inlineStr">
         <is>
           <t>• Https://eru.edu.eg/
 • Https://eru.edu.eg/explore-eru/
@@ -4657,12 +4779,12 @@
 • Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/</t>
         </is>
       </c>
-      <c r="AH15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI15" s="4" t="inlineStr"/>
+      <c r="AI15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -4726,75 +4848,80 @@
 Обращение: Dear Prof. Siddiq,</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>info@azhar.edu.eg</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>+20 2 22611404</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>https://azhar.edu.eg</t>
         </is>
       </c>
-      <c r="P16" s="4" t="inlineStr">
+      <c r="Q16" s="4" t="inlineStr">
         <is>
           <t>Prof. Mahmoud Siddiq Hassan</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="inlineStr">
+      <c r="R16" s="4" t="inlineStr">
         <is>
           <t>Acting President</t>
         </is>
       </c>
-      <c r="R16" s="4" t="inlineStr">
+      <c r="S16" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1001–1200</t>
         </is>
       </c>
-      <c r="S16" s="4" t="inlineStr">
+      <c r="T16" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="T16" s="4" t="inlineStr"/>
-      <c r="U16" s="4" t="n">
+      <c r="U16" s="4" t="inlineStr"/>
+      <c r="V16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="4" t="inlineStr"/>
       <c r="W16" s="4" t="inlineStr"/>
       <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="4" t="inlineStr"/>
-      <c r="Z16" s="4" t="inlineStr">
+      <c r="Z16" s="4" t="inlineStr"/>
+      <c r="AA16" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) — cooperation protocol</t>
         </is>
       </c>
-      <c r="AA16" s="4" t="inlineStr"/>
-      <c r="AB16" s="4" t="n">
+      <c r="AB16" s="4" t="inlineStr"/>
+      <c r="AC16" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="AC16" s="8" t="inlineStr">
+      <c r="AD16" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD16" s="4" t="inlineStr">
+      <c r="AE16" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE16" s="4" t="inlineStr">
+      <c r="AF16" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF16" s="4" t="inlineStr">
+      <c r="AG16" s="4" t="inlineStr">
         <is>
           <t>• Подчиняется Аль-Азхару (Шейх аль-Азхар), а не напрямую Минвысшобразования; форма собственности — государственный
 • С 1 августа 2026 обязанности президента временно исполняет проф. Махмуд Сыддык Хасан (вице-президент по аспирантуре и науке) до назначения нового президента
@@ -4802,7 +4929,7 @@
 • Полный почтовый адрес на сайте не указан (только «Каир, Насср-Сити»)</t>
         </is>
       </c>
-      <c r="AG16" s="4" t="inlineStr">
+      <c r="AH16" s="4" t="inlineStr">
         <is>
           <t>• Https://azhar.edu.eg/
 • Https://azhar.edu.eg/2026/07/27/%d8%b4%d9%8a%d8%ae-%d8%a7%d9%84%d8%a3%d8%b2%d9%87%d8%b1-%d9%8a%d9%83%d9%84%d9%81-%d8%a7%d9%84%d8%af%d9%83%d8%aa%d9%88%d8%b1-%d9%85%d8%ad%d9%85%d9%88%d8%af-%d8%b5%d8%af%d9%8a%d9%82-%d9%86%d8%a7%d8%a6/
@@ -4811,12 +4938,12 @@
 • Https://www.qianmu.org/ranking/1528.htm (2027 QS list, qianmu.org)</t>
         </is>
       </c>
-      <c r="AH16" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI16" s="4" t="inlineStr"/>
+      <c r="AI16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -4880,81 +5007,86 @@
 Обращение: Dear Prof. Khater,</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>president@mans.edu.eg</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>+20 50 2383781; +20 50 2397055</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>https://www.mans.edu.eg</t>
         </is>
       </c>
-      <c r="P17" s="4" t="inlineStr">
+      <c r="Q17" s="4" t="inlineStr">
         <is>
           <t>Prof. Cherif Yousef Khater</t>
         </is>
       </c>
-      <c r="Q17" s="4" t="inlineStr">
+      <c r="R17" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R17" s="4" t="inlineStr">
+      <c r="S17" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1001–1200</t>
         </is>
       </c>
-      <c r="S17" s="4" t="inlineStr">
+      <c r="T17" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="T17" s="4" t="inlineStr"/>
-      <c r="U17" s="4" t="n">
+      <c r="U17" s="4" t="inlineStr"/>
+      <c r="V17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="4" t="inlineStr"/>
       <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" s="4" t="inlineStr"/>
       <c r="Y17" s="4" t="inlineStr"/>
-      <c r="Z17" s="4" t="inlineStr">
+      <c r="Z17" s="4" t="inlineStr"/>
+      <c r="AA17" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) – cooperation protocol (2021)</t>
         </is>
       </c>
-      <c r="AA17" s="4" t="inlineStr"/>
-      <c r="AB17" s="4" t="n">
+      <c r="AB17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="AC17" s="8" t="inlineStr">
+      <c r="AD17" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD17" s="4" t="inlineStr">
+      <c r="AE17" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE17" s="4" t="inlineStr">
+      <c r="AF17" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF17" s="4" t="inlineStr">
+      <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>• Сайт международного отдела (muiro.mans.edu.eg) недоступен (503) — e-mail отдела не установлен
 • Спутников не найдено (одна быстрая проверка)</t>
         </is>
       </c>
-      <c r="AG17" s="4" t="inlineStr">
+      <c r="AH17" s="4" t="inlineStr">
         <is>
           <t>• Https://www.mans.edu.eg/en
 • Https://www.mans.edu.eg/en/about/contact-info
@@ -4962,12 +5094,12 @@
 • Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/</t>
         </is>
       </c>
-      <c r="AH17" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI17" s="4" t="inlineStr"/>
+      <c r="AI17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -5030,82 +5162,87 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr"/>
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>complaints@aun.edu.eg</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>+20 88 2354130; +20 88 2354166</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>https://www.aun.edu.eg</t>
         </is>
       </c>
-      <c r="P18" s="4" t="inlineStr">
+      <c r="Q18" s="4" t="inlineStr">
         <is>
           <t>Prof. Ahmed Mohamed El-Menshawy</t>
         </is>
       </c>
-      <c r="Q18" s="4" t="inlineStr">
+      <c r="R18" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R18" s="4" t="inlineStr">
+      <c r="S18" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1001–1200</t>
         </is>
       </c>
-      <c r="S18" s="4" t="inlineStr">
+      <c r="T18" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T18" s="4" t="inlineStr"/>
-      <c r="U18" s="4" t="n">
+      <c r="U18" s="4" t="inlineStr"/>
+      <c r="V18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="4" t="inlineStr"/>
       <c r="W18" s="4" t="inlineStr"/>
       <c r="X18" s="4" t="inlineStr"/>
       <c r="Y18" s="4" t="inlineStr"/>
-      <c r="Z18" s="4" t="inlineStr">
+      <c r="Z18" s="4" t="inlineStr"/>
+      <c r="AA18" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) – cooperation protocol (2021)</t>
         </is>
       </c>
-      <c r="AA18" s="4" t="inlineStr"/>
-      <c r="AB18" s="4" t="n">
+      <c r="AB18" s="4" t="inlineStr"/>
+      <c r="AC18" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AC18" s="8" t="inlineStr">
+      <c r="AD18" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD18" s="4" t="inlineStr">
+      <c r="AE18" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE18" s="4" t="inlineStr">
+      <c r="AF18" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF18" s="4" t="inlineStr">
+      <c r="AG18" s="4" t="inlineStr">
         <is>
           <t>• Единственный общий e-mail на странице контактов — complaints@aun.edu.eg (обращения/жалобы); офис президента e-mail не публикует
 • Auiro@aun.edu.eg — это офис международных академических рейтингов, а не международных связей; e-mail отдела международных связей не найден
 • Космическая проверка не выполнена через поиск (исчерпан лимит); спутников по nanosats.csv нет</t>
         </is>
       </c>
-      <c r="AG18" s="4" t="inlineStr">
+      <c r="AH18" s="4" t="inlineStr">
         <is>
           <t>• Https://www.aun.edu.eg/main/
 • Https://www.aun.edu.eg/main/contact
@@ -5114,12 +5251,12 @@
 • Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/</t>
         </is>
       </c>
-      <c r="AH18" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI18" s="4" t="inlineStr"/>
+      <c r="AI18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -5183,78 +5320,83 @@
 Обращение: Dear Prof. Abdel Radi,</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>info@aswu.edu.eg</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>+20 97 3480901</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>https://aswu.edu.eg</t>
         </is>
       </c>
-      <c r="P19" s="4" t="inlineStr">
+      <c r="Q19" s="4" t="inlineStr">
         <is>
           <t>Prof. Ashraf Imam Abdel Radi</t>
         </is>
       </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="R19" s="4" t="inlineStr">
         <is>
           <t>Acting President</t>
         </is>
       </c>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr">
+      <c r="S19" s="4" t="inlineStr"/>
+      <c r="T19" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="T19" s="4" t="inlineStr"/>
-      <c r="U19" s="4" t="n">
+      <c r="U19" s="4" t="inlineStr"/>
+      <c r="V19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="4" t="inlineStr"/>
       <c r="W19" s="4" t="inlineStr"/>
       <c r="X19" s="4" t="inlineStr"/>
       <c r="Y19" s="4" t="inlineStr"/>
-      <c r="Z19" s="4" t="inlineStr">
+      <c r="Z19" s="4" t="inlineStr"/>
+      <c r="AA19" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) — cooperation protocol</t>
         </is>
       </c>
-      <c r="AA19" s="4" t="inlineStr"/>
-      <c r="AB19" s="4" t="n">
+      <c r="AB19" s="4" t="inlineStr"/>
+      <c r="AC19" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AC19" s="8" t="inlineStr">
+      <c r="AD19" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD19" s="4" t="inlineStr">
+      <c r="AE19" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE19" s="4" t="inlineStr">
+      <c r="AF19" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF19" s="4" t="inlineStr">
+      <c r="AG19" s="4" t="inlineStr">
         <is>
           <t>• Университет возглавляет и.о. президента проф. Ашраф Имам Абдель Ради (также вице-президент по общественной работе)
 • Адрес/телефон/info@ на официальном сайте не отображаются (подгружаются скриптом) — взяты из справочника universitiesegypt.com; отдельного e-mail международного отдела нет
 • Управление научных и культурных связей: и.о. генерального директора Махмуд Мохамед Абдель Мутталиб (e-mail не опубликован)</t>
         </is>
       </c>
-      <c r="AG19" s="4" t="inlineStr">
+      <c r="AH19" s="4" t="inlineStr">
         <is>
           <t>• Https://aswu.edu.eg/about/key-facts/leadership-team/
 • Https://www.universitiesegypt.com/aswan-university/contacts
@@ -5262,12 +5404,12 @@
 • Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/</t>
         </is>
       </c>
-      <c r="AH19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI19" s="4" t="inlineStr"/>
+      <c r="AI19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -5330,77 +5472,82 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr"/>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>info@msa.edu.eg</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>+20 2 38371113; +20 2 38371115</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>https://msa.edu.eg/msauniversity/</t>
-        </is>
-      </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
+          <t>https://msa.edu.eg/msauniversity</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
           <t>Prof. Nader Elbokle</t>
         </is>
       </c>
-      <c r="Q20" s="4" t="inlineStr">
+      <c r="R20" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R20" s="4" t="inlineStr"/>
-      <c r="S20" s="4" t="inlineStr">
+      <c r="S20" s="4" t="inlineStr"/>
+      <c r="T20" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1801–2000</t>
         </is>
       </c>
-      <c r="T20" s="4" t="inlineStr"/>
-      <c r="U20" s="4" t="n">
+      <c r="U20" s="4" t="inlineStr"/>
+      <c r="V20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="4" t="inlineStr"/>
       <c r="W20" s="4" t="inlineStr"/>
       <c r="X20" s="4" t="inlineStr"/>
       <c r="Y20" s="4" t="inlineStr"/>
-      <c r="Z20" s="4" t="inlineStr">
+      <c r="Z20" s="4" t="inlineStr"/>
+      <c r="AA20" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) – cooperation protocol (2021)</t>
         </is>
       </c>
-      <c r="AA20" s="4" t="inlineStr"/>
-      <c r="AB20" s="4" t="n">
+      <c r="AB20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AC20" s="8" t="inlineStr">
+      <c r="AD20" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD20" s="4" t="inlineStr">
+      <c r="AE20" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE20" s="4" t="inlineStr">
+      <c r="AF20" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF20" s="4" t="inlineStr">
+      <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>• Есть 'UK Quality Assurance &amp; International Partnerships Unit' (партнёрства с британскими вузами, напр. Greenwich), но отдельный e-mail не опубликован
 • Горячая линия 16672</t>
         </is>
       </c>
-      <c r="AG20" s="4" t="inlineStr">
+      <c r="AH20" s="4" t="inlineStr">
         <is>
           <t>• Https://msa.edu.eg/msauniversity/
 • Https://msa.edu.eg/msauniversity/university-president/
@@ -5408,12 +5555,12 @@
 • Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/</t>
         </is>
       </c>
-      <c r="AH20" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI20" s="4" t="inlineStr"/>
+      <c r="AI20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -5477,74 +5624,79 @@
 Обращение: Dear Prof. Saleh,</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>ПРОВЕРИТЬ: Ящик личный, имя адресата не совпадает с владельцем — уточнить владельца ящика</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>portal@psu.edu.eg</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr"/>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr"/>
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>https://psu.edu.eg</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="Q21" s="4" t="inlineStr">
         <is>
           <t>Prof. Sherif Youssef Saleh</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="inlineStr">
+      <c r="R21" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R21" s="4" t="inlineStr"/>
-      <c r="S21" s="4" t="inlineStr">
+      <c r="S21" s="4" t="inlineStr"/>
+      <c r="T21" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="T21" s="4" t="inlineStr"/>
-      <c r="U21" s="4" t="n">
+      <c r="U21" s="4" t="inlineStr"/>
+      <c r="V21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="4" t="inlineStr"/>
       <c r="W21" s="4" t="inlineStr"/>
       <c r="X21" s="4" t="inlineStr"/>
       <c r="Y21" s="4" t="inlineStr"/>
-      <c r="Z21" s="4" t="inlineStr">
+      <c r="Z21" s="4" t="inlineStr"/>
+      <c r="AA21" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) – cooperation protocol (2021)</t>
         </is>
       </c>
-      <c r="AA21" s="4" t="inlineStr"/>
-      <c r="AB21" s="4" t="n">
+      <c r="AB21" s="4" t="inlineStr"/>
+      <c r="AC21" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AC21" s="8" t="inlineStr">
+      <c r="AD21" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD21" s="4" t="inlineStr">
+      <c r="AE21" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE21" s="4" t="inlineStr">
+      <c r="AF21" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF21" s="4" t="inlineStr">
+      <c r="AG21" s="4" t="inlineStr">
         <is>
           <t>• Общий e-mail — адрес веб-портала (portal@psu.edu.eg); e-mail отдела культурных/международных связей не найден
 • Президент ранее возглавлял сектор культурных связей и командировок Минвысшобразования — релевантно для международного сотрудничества
 • Есть партнёрство с IIT Gandhinagar (Индия, БРИКС) и Ghent University</t>
         </is>
       </c>
-      <c r="AG21" s="4" t="inlineStr">
+      <c r="AH21" s="4" t="inlineStr">
         <is>
           <t>• Https://psu.edu.eg/
 • Https://psu.edu.eg/university-admin-ar/
@@ -5553,12 +5705,12 @@
 • Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/</t>
         </is>
       </c>
-      <c r="AH21" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI21" s="4" t="inlineStr"/>
+      <c r="AI21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -5622,71 +5774,76 @@
 Обращение: Dear Prof. El-Nomany,</t>
         </is>
       </c>
-      <c r="L22" s="4" t="inlineStr"/>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>president@sohag.edu.eg</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>+20 93 4570000</t>
         </is>
       </c>
-      <c r="O22" s="4" t="inlineStr">
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>https://www.sohag-univ.edu.eg</t>
         </is>
       </c>
-      <c r="P22" s="4" t="inlineStr">
+      <c r="Q22" s="4" t="inlineStr">
         <is>
           <t>Prof. Hassan El-Nomany</t>
         </is>
       </c>
-      <c r="Q22" s="4" t="inlineStr">
+      <c r="R22" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R22" s="4" t="inlineStr"/>
-      <c r="S22" s="4" t="inlineStr">
+      <c r="S22" s="4" t="inlineStr"/>
+      <c r="T22" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="T22" s="4" t="inlineStr"/>
-      <c r="U22" s="4" t="n">
+      <c r="U22" s="4" t="inlineStr"/>
+      <c r="V22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="4" t="inlineStr"/>
       <c r="W22" s="4" t="inlineStr"/>
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="4" t="inlineStr"/>
-      <c r="Z22" s="4" t="inlineStr">
+      <c r="Z22" s="4" t="inlineStr"/>
+      <c r="AA22" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) — cooperation protocol</t>
         </is>
       </c>
-      <c r="AA22" s="4" t="inlineStr"/>
-      <c r="AB22" s="4" t="n">
+      <c r="AB22" s="4" t="inlineStr"/>
+      <c r="AC22" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AC22" s="8" t="inlineStr">
+      <c r="AD22" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD22" s="4" t="inlineStr">
+      <c r="AE22" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE22" s="4" t="inlineStr">
+      <c r="AF22" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF22" s="4" t="inlineStr">
+      <c r="AG22" s="4" t="inlineStr">
         <is>
           <t>• Имя президента в латинице дано в транслитерации (حسان النعماني) — проверить написание
 • Адрес по справочнику universitiesegypt.com; телефон и e-mail совпадают с официальным сайтом
@@ -5694,19 +5851,19 @@
 • Запущенных спутников не найдено; есть протокол сотрудничества с EgSA (2021)</t>
         </is>
       </c>
-      <c r="AG22" s="4" t="inlineStr">
+      <c r="AH22" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sohag-univ.edu.eg/ar/home/
 • Https://www.universitiesegypt.com/sohag-university/contacts
 • Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/</t>
         </is>
       </c>
-      <c r="AH22" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI22" s="4" t="inlineStr"/>
+      <c r="AI22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -5759,63 +5916,68 @@
       </c>
       <c r="J23" s="4" t="inlineStr"/>
       <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4" t="inlineStr"/>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M23" s="4" t="inlineStr"/>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="N23" s="4" t="inlineStr"/>
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>17742 (hotline, Egypt only)</t>
         </is>
       </c>
-      <c r="O23" s="4" t="inlineStr">
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>https://zewailcity.edu.eg</t>
         </is>
       </c>
-      <c r="P23" s="4" t="inlineStr">
+      <c r="Q23" s="4" t="inlineStr">
         <is>
           <t>Prof. Wael Akl</t>
         </is>
       </c>
-      <c r="Q23" s="4" t="inlineStr">
+      <c r="R23" s="4" t="inlineStr">
         <is>
           <t>Acting Executive President (Zewail City); University President (UST, acting): Prof. Ibrahim El Sherbiny</t>
         </is>
       </c>
-      <c r="R23" s="4" t="inlineStr"/>
-      <c r="S23" s="4" t="inlineStr">
+      <c r="S23" s="4" t="inlineStr"/>
+      <c r="T23" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="T23" s="4" t="inlineStr"/>
-      <c r="U23" s="4" t="n">
+      <c r="U23" s="4" t="inlineStr"/>
+      <c r="V23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="4" t="inlineStr"/>
       <c r="W23" s="4" t="inlineStr"/>
       <c r="X23" s="4" t="inlineStr"/>
-      <c r="Y23" s="4" t="inlineStr">
+      <c r="Y23" s="4" t="inlineStr"/>
+      <c r="Z23" s="4" t="inlineStr">
         <is>
           <t>Aerospace Engineering programme (UST)</t>
         </is>
       </c>
-      <c r="Z23" s="4" t="inlineStr"/>
       <c r="AA23" s="4" t="inlineStr"/>
-      <c r="AB23" s="4" t="n">
+      <c r="AB23" s="4" t="inlineStr"/>
+      <c r="AC23" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AC23" s="7" t="inlineStr">
+      <c r="AD23" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AD23" s="4" t="inlineStr"/>
-      <c r="AE23" s="4" t="inlineStr">
+      <c r="AE23" s="4" t="inlineStr"/>
+      <c r="AF23" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF23" s="4" t="inlineStr">
+      <c r="AG23" s="4" t="inlineStr">
         <is>
           <t>• Руководство: и.о. исполнительного президента Prof. Wael Akl; и.о. президента университета (UST) Prof. Ibrahim El Sherbiny; председатель попечительского совета — министр высшего образования Abdelaziz Konsowa
 • На сайте не опубликованы e-mail (ни общий, ни международного отдела) — только горячая линия 17742 и форма; требуется уточнение контакта
@@ -5823,7 +5985,7 @@
 • Тип собственности: государственная некоммерческая структура по особому закону (не классический госуниверситет) — проверить формулировку</t>
         </is>
       </c>
-      <c r="AG23" s="4" t="inlineStr">
+      <c r="AH23" s="4" t="inlineStr">
         <is>
           <t>• Https://zewailcity.edu.eg/
 • Https://zewailcity.edu.eg/leadership
@@ -5831,12 +5993,12 @@
 • Https://zewailcity.edu.eg/ar</t>
         </is>
       </c>
-      <c r="AH23" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI23" s="4" t="inlineStr"/>
+      <c r="AI23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -5891,67 +6053,72 @@
 Обращение: Dear Prof. Abdel Galil,</t>
         </is>
       </c>
-      <c r="L24" s="4" t="inlineStr"/>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>info@luxor.edu.eg</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>+20 95 2287244</t>
         </is>
       </c>
-      <c r="O24" s="4" t="inlineStr">
+      <c r="P24" s="4" t="inlineStr">
         <is>
           <t>https://luxor.edu.eg</t>
         </is>
       </c>
-      <c r="P24" s="4" t="inlineStr">
+      <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>Prof. Sabreen Abdel Galil</t>
         </is>
       </c>
-      <c r="Q24" s="4" t="inlineStr">
+      <c r="R24" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R24" s="4" t="inlineStr"/>
       <c r="S24" s="4" t="inlineStr"/>
       <c r="T24" s="4" t="inlineStr"/>
-      <c r="U24" s="4" t="n">
+      <c r="U24" s="4" t="inlineStr"/>
+      <c r="V24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="4" t="inlineStr"/>
       <c r="W24" s="4" t="inlineStr"/>
       <c r="X24" s="4" t="inlineStr"/>
       <c r="Y24" s="4" t="inlineStr"/>
-      <c r="Z24" s="4" t="inlineStr">
+      <c r="Z24" s="4" t="inlineStr"/>
+      <c r="AA24" s="4" t="inlineStr">
         <is>
           <t>Beijing Institute of Technology (BIT) — cooperation visits (Jan 2026)</t>
         </is>
       </c>
-      <c r="AA24" s="4" t="inlineStr"/>
-      <c r="AB24" s="4" t="n">
+      <c r="AB24" s="4" t="inlineStr"/>
+      <c r="AC24" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC24" s="8" t="inlineStr">
+      <c r="AD24" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD24" s="4" t="inlineStr">
+      <c r="AE24" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE24" s="4" t="inlineStr">
+      <c r="AF24" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF24" s="4" t="inlineStr">
+      <c r="AG24" s="4" t="inlineStr">
         <is>
           <t>• Сайт — SPA; контакты и новости взяты из официального API сайта (luxoruniversityar.runasp.net)
 • Президент — проф. Сабрин Абдель Галиль (женщина; новость от 28.01.2026); при обращении использовать «Dear Prof. Abdel Galil»
@@ -5960,7 +6127,7 @@
 • В THE 2027 — статус Reporter (без ранга)</t>
         </is>
       </c>
-      <c r="AG24" s="4" t="inlineStr">
+      <c r="AH24" s="4" t="inlineStr">
         <is>
           <t>• Https://luxor.edu.eg/
 • Https://luxoruniversityar.runasp.net/api/v1/contacts/getall
@@ -5968,12 +6135,12 @@
 • Https://www.universitiesegypt.com/luxor-university/contacts</t>
         </is>
       </c>
-      <c r="AH24" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI24" s="4" t="inlineStr"/>
+      <c r="AI24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -6037,78 +6204,83 @@
 Обращение: Dear Prof. Sarhan,</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr"/>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>info@fue.edu.eg</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>+20 2 2618 6100</t>
         </is>
       </c>
-      <c r="O25" s="4" t="inlineStr">
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>https://www.fue.edu.eg</t>
         </is>
       </c>
-      <c r="P25" s="4" t="inlineStr">
+      <c r="Q25" s="4" t="inlineStr">
         <is>
           <t>Prof. Ebada Sarhan</t>
         </is>
       </c>
-      <c r="Q25" s="4" t="inlineStr">
+      <c r="R25" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R25" s="4" t="inlineStr">
+      <c r="S25" s="4" t="inlineStr">
         <is>
           <t>QS2027: 951–1000</t>
         </is>
       </c>
-      <c r="S25" s="4" t="inlineStr">
+      <c r="T25" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="T25" s="4" t="inlineStr"/>
-      <c r="U25" s="4" t="n">
+      <c r="U25" s="4" t="inlineStr"/>
+      <c r="V25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="4" t="inlineStr"/>
       <c r="W25" s="4" t="inlineStr"/>
       <c r="X25" s="4" t="inlineStr"/>
       <c r="Y25" s="4" t="inlineStr"/>
       <c r="Z25" s="4" t="inlineStr"/>
       <c r="AA25" s="4" t="inlineStr"/>
-      <c r="AB25" s="4" t="n">
+      <c r="AB25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC25" s="8" t="inlineStr">
+      <c r="AD25" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD25" s="4" t="inlineStr">
+      <c r="AE25" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE25" s="4" t="inlineStr">
+      <c r="AF25" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF25" s="4" t="inlineStr">
+      <c r="AG25" s="4" t="inlineStr">
         <is>
           <t>• Отдельного e-mail международного отдела не опубликовано (International Support Center обслуживает только иностранных студентов) — писать на info@fue.edu.eg
 • Горячая линия 16383; факс +20 2 2618 6111
 • Космической активности не найдено</t>
         </is>
       </c>
-      <c r="AG25" s="4" t="inlineStr">
+      <c r="AH25" s="4" t="inlineStr">
         <is>
           <t>• Https://www.fue.edu.eg/contacts
 • Https://www.fue.edu.eg/about_fue/fue_people/top_management
@@ -6116,12 +6288,12 @@
 • Qianmu.org QS2027 list</t>
         </is>
       </c>
-      <c r="AH25" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI25" s="4" t="inlineStr"/>
+      <c r="AI25" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -6186,88 +6358,93 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
           <t>culture@zu.edu.eg</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>president@zu.edu.eg</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>+20 55 2302926</t>
         </is>
       </c>
-      <c r="O26" s="4" t="inlineStr">
+      <c r="P26" s="4" t="inlineStr">
         <is>
           <t>https://www.zu.edu.eg</t>
         </is>
       </c>
-      <c r="P26" s="4" t="inlineStr">
+      <c r="Q26" s="4" t="inlineStr">
         <is>
           <t>Prof. Khaled Ali El-Derandaly</t>
         </is>
       </c>
-      <c r="Q26" s="4" t="inlineStr">
+      <c r="R26" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R26" s="4" t="inlineStr"/>
-      <c r="S26" s="4" t="inlineStr">
+      <c r="S26" s="4" t="inlineStr"/>
+      <c r="T26" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="T26" s="4" t="inlineStr"/>
-      <c r="U26" s="4" t="n">
+      <c r="U26" s="4" t="inlineStr"/>
+      <c r="V26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="4" t="inlineStr"/>
       <c r="W26" s="4" t="inlineStr"/>
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="inlineStr"/>
       <c r="Z26" s="4" t="inlineStr"/>
       <c r="AA26" s="4" t="inlineStr"/>
-      <c r="AB26" s="4" t="n">
+      <c r="AB26" s="4" t="inlineStr"/>
+      <c r="AC26" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AC26" s="8" t="inlineStr">
+      <c r="AD26" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD26" s="4" t="inlineStr">
+      <c r="AE26" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE26" s="4" t="inlineStr">
+      <c r="AF26" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF26" s="4" t="inlineStr">
+      <c r="AG26" s="4" t="inlineStr">
         <is>
           <t>• Имя президента транслитерировано с арабского (أ.د/ خالد على الدرندلى) — уточнить латинское написание
 • Culture@zu.edu.eg — ящик Управления культурных связей (конференции и международные контакты); канцелярия президента: presidency@zu.edu.eg, тел. 055 2302926
 • Спутниковой активности не найдено (1 поиск)</t>
         </is>
       </c>
-      <c r="AG26" s="4" t="inlineStr">
+      <c r="AH26" s="4" t="inlineStr">
         <is>
           <t>• Https://www.zu.edu.eg/
 • Https://www.zu.edu.eg/Contents/Index/20
 • Https://www.zu.edu.eg/Contents/Section/1086</t>
         </is>
       </c>
-      <c r="AH26" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI26" s="4" t="inlineStr"/>
+      <c r="AI26" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -6330,63 +6507,68 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr"/>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>info@buc.edu.eg</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr"/>
-      <c r="O27" s="4" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr"/>
+      <c r="P27" s="4" t="inlineStr">
         <is>
           <t>https://buc.edu.eg</t>
         </is>
       </c>
-      <c r="P27" s="4" t="inlineStr">
+      <c r="Q27" s="4" t="inlineStr">
         <is>
           <t>Prof. Ashraf Mohamed El-Shihy</t>
         </is>
       </c>
-      <c r="Q27" s="4" t="inlineStr">
+      <c r="R27" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R27" s="4" t="inlineStr"/>
-      <c r="S27" s="4" t="inlineStr">
+      <c r="S27" s="4" t="inlineStr"/>
+      <c r="T27" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="T27" s="4" t="inlineStr"/>
-      <c r="U27" s="4" t="n">
+      <c r="U27" s="4" t="inlineStr"/>
+      <c r="V27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="4" t="inlineStr"/>
       <c r="W27" s="4" t="inlineStr"/>
       <c r="X27" s="4" t="inlineStr"/>
       <c r="Y27" s="4" t="inlineStr"/>
       <c r="Z27" s="4" t="inlineStr"/>
       <c r="AA27" s="4" t="inlineStr"/>
-      <c r="AB27" s="4" t="n">
+      <c r="AB27" s="4" t="inlineStr"/>
+      <c r="AC27" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC27" s="8" t="inlineStr">
+      <c r="AD27" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD27" s="4" t="inlineStr">
+      <c r="AE27" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE27" s="4" t="inlineStr">
+      <c r="AF27" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF27" s="4" t="inlineStr">
+      <c r="AG27" s="4" t="inlineStr">
         <is>
           <t>• Президент — бывший министр высшего образования Египта
 • Телефон: только горячая линия 19592 (без кода страны)
@@ -6394,19 +6576,19 @@
 • Спутниковой активности не найдено</t>
         </is>
       </c>
-      <c r="AG27" s="4" t="inlineStr">
+      <c r="AH27" s="4" t="inlineStr">
         <is>
           <t>• Https://buc.edu.eg/
 • Https://buc.edu.eg/contact-us/
 • Https://buc.edu.eg/board-profiles/prof-dr-ashraf-mohamed-el-shihy/</t>
         </is>
       </c>
-      <c r="AH27" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI27" s="4" t="inlineStr"/>
+      <c r="AI27" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -6472,76 +6654,81 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
           <t>iro@bu.edu.eg</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>info@bu.edu.eg</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>+20 13 3231011</t>
         </is>
       </c>
-      <c r="O28" s="4" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>https://bu.edu.eg</t>
         </is>
       </c>
-      <c r="P28" s="4" t="inlineStr">
+      <c r="Q28" s="4" t="inlineStr">
         <is>
           <t>Prof. Nasser El-Gizawy</t>
         </is>
       </c>
-      <c r="Q28" s="4" t="inlineStr">
+      <c r="R28" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R28" s="4" t="inlineStr"/>
-      <c r="S28" s="4" t="inlineStr">
+      <c r="S28" s="4" t="inlineStr"/>
+      <c r="T28" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T28" s="4" t="inlineStr"/>
-      <c r="U28" s="4" t="n">
+      <c r="U28" s="4" t="inlineStr"/>
+      <c r="V28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="4" t="inlineStr"/>
       <c r="W28" s="4" t="inlineStr"/>
       <c r="X28" s="4" t="inlineStr"/>
       <c r="Y28" s="4" t="inlineStr"/>
       <c r="Z28" s="4" t="inlineStr"/>
       <c r="AA28" s="4" t="inlineStr"/>
-      <c r="AB28" s="4" t="n">
+      <c r="AB28" s="4" t="inlineStr"/>
+      <c r="AC28" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC28" s="8" t="inlineStr">
+      <c r="AD28" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD28" s="4" t="inlineStr">
+      <c r="AE28" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE28" s="4" t="inlineStr">
+      <c r="AF28" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF28" s="4" t="inlineStr">
+      <c r="AG28" s="4" t="inlineStr">
         <is>
           <t>• Президент назначен президентским указом в сентябре 2023 г
 • Международный офис: тел. +20 13 3223213 доб. 1206, индекс 13511
 • Спутниковой активности не найдено</t>
         </is>
       </c>
-      <c r="AG28" s="4" t="inlineStr">
+      <c r="AH28" s="4" t="inlineStr">
         <is>
           <t>• Https://bu.edu.eg/univ_info/president.php
 • Https://bu.edu.eg/univ_info/contact.php
@@ -6549,12 +6736,12 @@
 • Https://iro.bu.edu.eg/en/contact</t>
         </is>
       </c>
-      <c r="AH28" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI28" s="4" t="inlineStr"/>
+      <c r="AI28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -6618,85 +6805,90 @@
 Обращение: Dear Prof. Trabees,</t>
         </is>
       </c>
-      <c r="L29" s="4" t="inlineStr"/>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>info.portal@dmu.edu.eg</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>+20 45 3368069</t>
         </is>
       </c>
-      <c r="O29" s="4" t="inlineStr">
+      <c r="P29" s="4" t="inlineStr">
         <is>
           <t>https://damanhour.dmu.edu.eg</t>
         </is>
       </c>
-      <c r="P29" s="4" t="inlineStr">
+      <c r="Q29" s="4" t="inlineStr">
         <is>
           <t>Prof. Elhamy Trabees</t>
         </is>
       </c>
-      <c r="Q29" s="4" t="inlineStr">
+      <c r="R29" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R29" s="4" t="inlineStr"/>
-      <c r="S29" s="4" t="inlineStr">
+      <c r="S29" s="4" t="inlineStr"/>
+      <c r="T29" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="T29" s="4" t="inlineStr"/>
-      <c r="U29" s="4" t="n">
+      <c r="U29" s="4" t="inlineStr"/>
+      <c r="V29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="4" t="inlineStr"/>
       <c r="W29" s="4" t="inlineStr"/>
       <c r="X29" s="4" t="inlineStr"/>
       <c r="Y29" s="4" t="inlineStr"/>
       <c r="Z29" s="4" t="inlineStr"/>
       <c r="AA29" s="4" t="inlineStr"/>
-      <c r="AB29" s="4" t="n">
+      <c r="AB29" s="4" t="inlineStr"/>
+      <c r="AC29" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC29" s="8" t="inlineStr">
+      <c r="AD29" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD29" s="4" t="inlineStr">
+      <c r="AE29" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE29" s="4" t="inlineStr">
+      <c r="AF29" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF29" s="4" t="inlineStr">
+      <c r="AG29" s="4" t="inlineStr">
         <is>
           <t>• Адрес из справочника universitiesegypt.com (телефон и e-mail совпадают с официальным сайтом)
 • Отдельного e-mail международного отдела не найдено — использовать info.portal@dmu.edu.eg
 • Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет</t>
         </is>
       </c>
-      <c r="AG29" s="4" t="inlineStr">
+      <c r="AH29" s="4" t="inlineStr">
         <is>
           <t>• Https://damanhour.dmu.edu.eg/pages/default.aspx/
 • Https://www.universitiesegypt.com/damanhour-university/contacts</t>
         </is>
       </c>
-      <c r="AH29" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI29" s="4" t="inlineStr"/>
+      <c r="AI29" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -6750,67 +6942,72 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr"/>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr">
         <is>
           <t>info@du.edu.eg</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>+20 57 2412376</t>
         </is>
       </c>
-      <c r="O30" s="4" t="inlineStr">
+      <c r="P30" s="4" t="inlineStr">
         <is>
           <t>https://du.edu.eg</t>
         </is>
       </c>
-      <c r="P30" s="4" t="inlineStr">
+      <c r="Q30" s="4" t="inlineStr">
         <is>
           <t>Prof. Hamdan Rabie (أ.د. حمدان ربيع)</t>
         </is>
       </c>
-      <c r="Q30" s="4" t="inlineStr">
+      <c r="R30" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R30" s="4" t="inlineStr"/>
-      <c r="S30" s="4" t="inlineStr">
+      <c r="S30" s="4" t="inlineStr"/>
+      <c r="T30" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T30" s="4" t="inlineStr"/>
-      <c r="U30" s="4" t="n">
+      <c r="U30" s="4" t="inlineStr"/>
+      <c r="V30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="4" t="inlineStr"/>
       <c r="W30" s="4" t="inlineStr"/>
       <c r="X30" s="4" t="inlineStr"/>
       <c r="Y30" s="4" t="inlineStr"/>
       <c r="Z30" s="4" t="inlineStr"/>
       <c r="AA30" s="4" t="inlineStr"/>
-      <c r="AB30" s="4" t="n">
+      <c r="AB30" s="4" t="inlineStr"/>
+      <c r="AC30" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC30" s="8" t="inlineStr">
+      <c r="AD30" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD30" s="4" t="inlineStr">
+      <c r="AE30" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE30" s="4" t="inlineStr">
+      <c r="AF30" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF30" s="4" t="inlineStr">
+      <c r="AG30" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт du.edu.eg недоступен (503 / обрыв соединения, октябрь 2026); контакты из справочника universitiesegypt.com — требуют сверки
 • Космическая активность не проверялась поиском (лимит исчерпан); в nanosats.csv спутников нет
@@ -6818,18 +7015,18 @@
 • Перепроверка: Сайт по-прежнему недоступен; по СМИ 10.2026 добавлен президент д-р Хамдан Рабиа; контакты не перепроверены</t>
         </is>
       </c>
-      <c r="AG30" s="4" t="inlineStr">
+      <c r="AH30" s="4" t="inlineStr">
         <is>
           <t>• Https://www.universitiesegypt.com/damietta-university/contacts
 • Https://ar.wikipedia.org/wiki/جامعة_دمياط</t>
         </is>
       </c>
-      <c r="AH30" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI30" s="4" t="inlineStr"/>
+      <c r="AI30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -6893,71 +7090,76 @@
 Обращение: Dear Dr. El-Meshad,</t>
         </is>
       </c>
-      <c r="L31" s="4" t="inlineStr"/>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr">
         <is>
           <t>info@deltauniv.edu.eg</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>15955 (hotline, official site); +20 50 2770140</t>
         </is>
       </c>
-      <c r="O31" s="4" t="inlineStr">
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>https://new.deltauniv.edu.eg</t>
         </is>
       </c>
-      <c r="P31" s="4" t="inlineStr">
+      <c r="Q31" s="4" t="inlineStr">
         <is>
           <t>Dr. Yehia El-Meshad</t>
         </is>
       </c>
-      <c r="Q31" s="4" t="inlineStr">
+      <c r="R31" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R31" s="4" t="inlineStr">
+      <c r="S31" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1201–1400</t>
         </is>
       </c>
-      <c r="S31" s="4" t="inlineStr">
+      <c r="T31" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="T31" s="4" t="inlineStr"/>
-      <c r="U31" s="4" t="n">
+      <c r="U31" s="4" t="inlineStr"/>
+      <c r="V31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="4" t="inlineStr"/>
       <c r="W31" s="4" t="inlineStr"/>
       <c r="X31" s="4" t="inlineStr"/>
       <c r="Y31" s="4" t="inlineStr"/>
       <c r="Z31" s="4" t="inlineStr"/>
       <c r="AA31" s="4" t="inlineStr"/>
-      <c r="AB31" s="4" t="n">
+      <c r="AB31" s="4" t="inlineStr"/>
+      <c r="AC31" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC31" s="8" t="inlineStr">
+      <c r="AD31" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD31" s="4" t="inlineStr">
+      <c r="AE31" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE31" s="4" t="inlineStr">
+      <c r="AF31" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF31" s="4" t="inlineStr">
+      <c r="AG31" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт new.deltauniv.edu.eg рендерится через JavaScript (навигация через JS, страница «президент» отсутствует) — руководство и международный отдел на сайте проверить не удалось; info@deltauniv.edu.eg и горячая линия 15955 подтверждены на сайте 04.10.2026
 • Президент (Dr. Yehia El-Meshad / يحيى المشد) подтверждён только СМИ (июнь 2026); председатель совета попечителей — Dr. Mohamed Rabie
@@ -6967,7 +7169,7 @@
 • Перепроверка: Общий e-mail и горячая линия подтверждены на официальном сайте 04.10.2026; президент — по СМИ 06.2026, на сайте не найден</t>
         </is>
       </c>
-      <c r="AG31" s="4" t="inlineStr">
+      <c r="AH31" s="4" t="inlineStr">
         <is>
           <t>• Https://new.deltauniv.edu.eg/EN/aboutdu/index
 • Https://www.egyptianeducation.com/delta-university-science-technology/contacts
@@ -6975,12 +7177,12 @@
 • Qianmu.org QS2027 list</t>
         </is>
       </c>
-      <c r="AH31" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI31" s="4" t="inlineStr"/>
+      <c r="AI31" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -7044,67 +7246,72 @@
 Обращение: Dear Prof. El-Attar,</t>
         </is>
       </c>
-      <c r="L32" s="4" t="inlineStr"/>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr"/>
+      <c r="N32" s="4" t="inlineStr">
         <is>
           <t>presd@fayoum.edu.eg</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>+20 84 2114087</t>
         </is>
       </c>
-      <c r="O32" s="4" t="inlineStr">
+      <c r="P32" s="4" t="inlineStr">
         <is>
           <t>https://www.fayoum.edu.eg</t>
         </is>
       </c>
-      <c r="P32" s="4" t="inlineStr">
+      <c r="Q32" s="4" t="inlineStr">
         <is>
           <t>Prof. Sherif Mohamed Sabry El-Attar</t>
         </is>
       </c>
-      <c r="Q32" s="4" t="inlineStr">
+      <c r="R32" s="4" t="inlineStr">
         <is>
           <t>Acting President</t>
         </is>
       </c>
-      <c r="R32" s="4" t="inlineStr"/>
-      <c r="S32" s="4" t="inlineStr">
+      <c r="S32" s="4" t="inlineStr"/>
+      <c r="T32" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T32" s="4" t="inlineStr"/>
-      <c r="U32" s="4" t="n">
+      <c r="U32" s="4" t="inlineStr"/>
+      <c r="V32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="4" t="inlineStr"/>
       <c r="W32" s="4" t="inlineStr"/>
       <c r="X32" s="4" t="inlineStr"/>
       <c r="Y32" s="4" t="inlineStr"/>
       <c r="Z32" s="4" t="inlineStr"/>
       <c r="AA32" s="4" t="inlineStr"/>
-      <c r="AB32" s="4" t="n">
+      <c r="AB32" s="4" t="inlineStr"/>
+      <c r="AC32" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC32" s="8" t="inlineStr">
+      <c r="AD32" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD32" s="4" t="inlineStr">
+      <c r="AE32" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE32" s="4" t="inlineStr">
+      <c r="AF32" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF32" s="4" t="inlineStr">
+      <c r="AG32" s="4" t="inlineStr">
         <is>
           <t>• Prof. Sherif El-Attar — исполняющий обязанности президента (с 01.08.2026), специальность — архитектура; личный e-mail sma00@fayoum.edu.eg
 • Presd@fayoum.edu.eg — ящик офиса президента; факс +20 84 2114095
@@ -7112,19 +7319,19 @@
 • В QS2027 не найден; космической активности не найдено</t>
         </is>
       </c>
-      <c r="AG32" s="4" t="inlineStr">
+      <c r="AH32" s="4" t="inlineStr">
         <is>
           <t>• Https://www.fayoum.edu.eg/en/EnterpriseSettings/UniversityPresident
 • Https://www.fayoum.edu.eg/en/EnterpriseSettings/presidentoffice
 • Https://www.fayoum.edu.eg/en/Faculty/TabContent/5095</t>
         </is>
       </c>
-      <c r="AH32" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI32" s="4" t="inlineStr"/>
+      <c r="AI32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -7177,55 +7384,60 @@
       </c>
       <c r="J33" s="4" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr"/>
-      <c r="L33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M33" s="4" t="inlineStr"/>
       <c r="N33" s="4" t="inlineStr"/>
-      <c r="O33" s="4" t="inlineStr">
+      <c r="O33" s="4" t="inlineStr"/>
+      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>https://www.gu.edu.eg</t>
         </is>
       </c>
-      <c r="P33" s="4" t="inlineStr">
+      <c r="Q33" s="4" t="inlineStr">
         <is>
           <t>Prof. Dr. Mohamed El-Shinawi</t>
         </is>
       </c>
-      <c r="Q33" s="4" t="inlineStr">
+      <c r="R33" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R33" s="4" t="inlineStr"/>
-      <c r="S33" s="4" t="inlineStr">
+      <c r="S33" s="4" t="inlineStr"/>
+      <c r="T33" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="T33" s="4" t="inlineStr"/>
-      <c r="U33" s="4" t="n">
+      <c r="U33" s="4" t="inlineStr"/>
+      <c r="V33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="4" t="inlineStr"/>
       <c r="W33" s="4" t="inlineStr"/>
       <c r="X33" s="4" t="inlineStr"/>
       <c r="Y33" s="4" t="inlineStr"/>
       <c r="Z33" s="4" t="inlineStr"/>
       <c r="AA33" s="4" t="inlineStr"/>
-      <c r="AB33" s="4" t="n">
+      <c r="AB33" s="4" t="inlineStr"/>
+      <c r="AC33" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC33" s="8" t="inlineStr">
+      <c r="AD33" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD33" s="4" t="inlineStr"/>
-      <c r="AE33" s="4" t="inlineStr">
+      <c r="AE33" s="4" t="inlineStr"/>
+      <c r="AF33" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF33" s="4" t="inlineStr">
+      <c r="AG33" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт gu.edu.eg недоступен из нашей сети (503 / ошибка TLS, повторно 04.10.2026) — контакты не верифицированы; требуется ручная проверка
 • Президент Prof. Dr. Mohamed El-Shinawi (проф. хирургии Ain Shams) — по официальным новостям gu.edu.eg 2026 г., видимым в поисковой выдаче
@@ -7233,19 +7445,19 @@
 • Перепроверка: Президент проф. Mohamed El-Shinawi подтверждается официальными новостями gu.edu.eg (06.2026) по поисковой выдаче; сайт по-прежнему недоступен — контакты не найдены</t>
         </is>
       </c>
-      <c r="AG33" s="4" t="inlineStr">
+      <c r="AH33" s="4" t="inlineStr">
         <is>
           <t>• Https://www.timeshighereducation.com/world-university-rankings/galala-university
 • Https://en.wikipedia.org/wiki/Galala_University
 • Https://www.gu.edu.eg/2026/06/galala-university-president-speaks-at-international-conference-in-madrid-on-strengthening-public-private-collaboration-in-higher-education (snippet)</t>
         </is>
       </c>
-      <c r="AH33" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI33" s="4" t="inlineStr"/>
+      <c r="AI33" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -7310,76 +7522,81 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
+          <t>личный, совпало</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
           <t>frank.gunzer@guc.edu.eg</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>yasser.higazi@guc.edu.eg</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>+20 2 27589990</t>
         </is>
       </c>
-      <c r="O34" s="4" t="inlineStr">
+      <c r="P34" s="4" t="inlineStr">
         <is>
           <t>https://www.guc.edu.eg</t>
         </is>
       </c>
-      <c r="P34" s="4" t="inlineStr">
+      <c r="Q34" s="4" t="inlineStr">
         <is>
           <t>Prof. Dr. Yasser Hegazy</t>
         </is>
       </c>
-      <c r="Q34" s="4" t="inlineStr">
+      <c r="R34" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R34" s="4" t="inlineStr">
+      <c r="S34" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1401+</t>
         </is>
       </c>
-      <c r="S34" s="4" t="inlineStr"/>
       <c r="T34" s="4" t="inlineStr"/>
-      <c r="U34" s="4" t="n">
+      <c r="U34" s="4" t="inlineStr"/>
+      <c r="V34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="4" t="inlineStr"/>
       <c r="W34" s="4" t="inlineStr"/>
       <c r="X34" s="4" t="inlineStr"/>
       <c r="Y34" s="4" t="inlineStr"/>
       <c r="Z34" s="4" t="inlineStr"/>
       <c r="AA34" s="4" t="inlineStr"/>
-      <c r="AB34" s="4" t="n">
+      <c r="AB34" s="4" t="inlineStr"/>
+      <c r="AC34" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC34" s="8" t="inlineStr">
+      <c r="AD34" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD34" s="4" t="inlineStr">
+      <c r="AE34" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE34" s="4" t="inlineStr">
+      <c r="AF34" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF34" s="4" t="inlineStr">
+      <c r="AG34" s="4" t="inlineStr">
         <is>
           <t>• Ящик международного направления — персональный адрес вице-президента по международным делам проф. Франка Гюнцера
 • У президента два варианта адреса на странице (yasser.higazi@ и yasser.higazy@guc.edu.eg); в поле указан первый, отображаемый под его именем
 • Горячая линия 16482; космическая активность поиском не проверялась (лимит поиска исчерпан), в nanosats.csv спутников нет</t>
         </is>
       </c>
-      <c r="AG34" s="4" t="inlineStr">
+      <c r="AH34" s="4" t="inlineStr">
         <is>
           <t>• Https://guc.edu.eg/
 • Https://guc.edu.eg/en/about_guc/trustees_council_deans/president_cabinet.aspx
@@ -7387,12 +7604,12 @@
 • Https://www.qianmu.org/ranking/1528.htm (2027 QS list, qianmu.org)</t>
         </is>
       </c>
-      <c r="AH34" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI34" s="4" t="inlineStr"/>
+      <c r="AI34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -7455,86 +7672,91 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr"/>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr">
         <is>
           <t>info@horus.edu.eg</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>+20 11 44455582; +20 57 392000</t>
         </is>
       </c>
-      <c r="O35" s="4" t="inlineStr">
+      <c r="P35" s="4" t="inlineStr">
         <is>
           <t>https://horus.edu.eg</t>
         </is>
       </c>
-      <c r="P35" s="4" t="inlineStr">
+      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>Prof. El Said Abdel Hady</t>
         </is>
       </c>
-      <c r="Q35" s="4" t="inlineStr">
+      <c r="R35" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R35" s="4" t="inlineStr"/>
-      <c r="S35" s="4" t="inlineStr">
+      <c r="S35" s="4" t="inlineStr"/>
+      <c r="T35" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T35" s="4" t="inlineStr"/>
-      <c r="U35" s="4" t="n">
+      <c r="U35" s="4" t="inlineStr"/>
+      <c r="V35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="4" t="inlineStr"/>
       <c r="W35" s="4" t="inlineStr"/>
       <c r="X35" s="4" t="inlineStr"/>
       <c r="Y35" s="4" t="inlineStr"/>
       <c r="Z35" s="4" t="inlineStr"/>
       <c r="AA35" s="4" t="inlineStr"/>
-      <c r="AB35" s="4" t="n">
+      <c r="AB35" s="4" t="inlineStr"/>
+      <c r="AC35" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC35" s="8" t="inlineStr">
+      <c r="AD35" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD35" s="4" t="inlineStr">
+      <c r="AE35" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE35" s="4" t="inlineStr">
+      <c r="AF35" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF35" s="4" t="inlineStr">
+      <c r="AG35" s="4" t="inlineStr">
         <is>
           <t>• Есть Управление международных связей (IRO-HUE), но отдельный e-mail и руководитель не опубликованы — используется info@horus.edu.eg
 • Председатель попечительского совета — Prof. Ibrahim Saber
 • Спутников нет (проверка по сайту и nanosats.csv; веб-поиск исчерпан)</t>
         </is>
       </c>
-      <c r="AG35" s="4" t="inlineStr">
+      <c r="AH35" s="4" t="inlineStr">
         <is>
           <t>• Https://horus.edu.eg/
 • Https://horus.edu.eg/contact-us/
 • Https://horus.edu.eg/international-relations-office-iro-hue/</t>
         </is>
       </c>
-      <c r="AH35" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI35" s="4" t="inlineStr"/>
+      <c r="AI35" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -7587,55 +7809,60 @@
       </c>
       <c r="J36" s="4" t="inlineStr"/>
       <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="4" t="inlineStr"/>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M36" s="4" t="inlineStr"/>
       <c r="N36" s="4" t="inlineStr"/>
-      <c r="O36" s="4" t="inlineStr">
+      <c r="O36" s="4" t="inlineStr"/>
+      <c r="P36" s="4" t="inlineStr">
         <is>
           <t>https://www.menofia.edu.eg</t>
         </is>
       </c>
-      <c r="P36" s="4" t="inlineStr">
+      <c r="Q36" s="4" t="inlineStr">
         <is>
           <t>Prof. Ahmed Farag El-Kased</t>
         </is>
       </c>
-      <c r="Q36" s="4" t="inlineStr">
+      <c r="R36" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R36" s="4" t="inlineStr"/>
-      <c r="S36" s="4" t="inlineStr">
+      <c r="S36" s="4" t="inlineStr"/>
+      <c r="T36" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="T36" s="4" t="inlineStr"/>
-      <c r="U36" s="4" t="n">
+      <c r="U36" s="4" t="inlineStr"/>
+      <c r="V36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="4" t="inlineStr"/>
       <c r="W36" s="4" t="inlineStr"/>
       <c r="X36" s="4" t="inlineStr"/>
       <c r="Y36" s="4" t="inlineStr"/>
       <c r="Z36" s="4" t="inlineStr"/>
       <c r="AA36" s="4" t="inlineStr"/>
-      <c r="AB36" s="4" t="n">
+      <c r="AB36" s="4" t="inlineStr"/>
+      <c r="AC36" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC36" s="8" t="inlineStr">
+      <c r="AD36" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD36" s="4" t="inlineStr"/>
-      <c r="AE36" s="4" t="inlineStr">
+      <c r="AE36" s="4" t="inlineStr"/>
+      <c r="AF36" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF36" s="4" t="inlineStr">
+      <c r="AG36" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт menofia.edu.eg недоступен из среды (блокировка прокси/DNS) — контакты не проверены
 • ВАЖНО: в сент. 2026 Высший совет университетов объявил конкурс на пост президента (приём заявок с 10.10.2026) — руководитель может смениться в ближайшие месяцы; проверить перед отправкой
@@ -7645,19 +7872,19 @@
 • Перепроверка: 04.10.2026: menofia.edu.eg недоступен (503/сброс), портал Высшего совета университетов scu.eg не отдаёт данные без JS — данные не изменены</t>
         </is>
       </c>
-      <c r="AG36" s="4" t="inlineStr">
+      <c r="AH36" s="4" t="inlineStr">
         <is>
           <t>• Https://alkhabaralyoum.com/2026/09/26/ (news)
 • Https://www.cairomubasher.com/235786
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=12548</t>
         </is>
       </c>
-      <c r="AH36" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI36" s="4" t="inlineStr"/>
+      <c r="AI36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -7721,63 +7948,68 @@
 Обращение: Dear Prof. Farhat,</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr"/>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr"/>
+      <c r="N37" s="4" t="inlineStr">
         <is>
           <t>president@mu.edu.eg</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr"/>
-      <c r="O37" s="4" t="inlineStr">
+      <c r="O37" s="4" t="inlineStr"/>
+      <c r="P37" s="4" t="inlineStr">
         <is>
           <t>https://www.minia.edu.eg</t>
         </is>
       </c>
-      <c r="P37" s="4" t="inlineStr">
+      <c r="Q37" s="4" t="inlineStr">
         <is>
           <t>Prof. Essam El-Din Sadek Farhat</t>
         </is>
       </c>
-      <c r="Q37" s="4" t="inlineStr">
+      <c r="R37" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R37" s="4" t="inlineStr"/>
-      <c r="S37" s="4" t="inlineStr">
+      <c r="S37" s="4" t="inlineStr"/>
+      <c r="T37" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="T37" s="4" t="inlineStr"/>
-      <c r="U37" s="4" t="n">
+      <c r="U37" s="4" t="inlineStr"/>
+      <c r="V37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="4" t="inlineStr"/>
       <c r="W37" s="4" t="inlineStr"/>
       <c r="X37" s="4" t="inlineStr"/>
       <c r="Y37" s="4" t="inlineStr"/>
       <c r="Z37" s="4" t="inlineStr"/>
       <c r="AA37" s="4" t="inlineStr"/>
-      <c r="AB37" s="4" t="n">
+      <c r="AB37" s="4" t="inlineStr"/>
+      <c r="AC37" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC37" s="8" t="inlineStr">
+      <c r="AD37" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD37" s="4" t="inlineStr">
+      <c r="AE37" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE37" s="4" t="inlineStr">
+      <c r="AF37" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF37" s="4" t="inlineStr">
+      <c r="AG37" s="4" t="inlineStr">
         <is>
           <t>• Сайт minia.edu.eg недоступен (DNS) — e-mail президента (president@mu.edu.eg, также presid.office@mu.edu.eg) взят из поисковой выдержки официальной страницы
 • Почтовый индекс и телефон не подтверждены
@@ -7785,19 +8017,19 @@
 • Спутниковой активности не найдено</t>
         </is>
       </c>
-      <c r="AG37" s="4" t="inlineStr">
+      <c r="AH37" s="4" t="inlineStr">
         <is>
           <t>• Https://www.minia.edu.eg/minia/Engmail.aspx
 • Https://www.minia.edu.eg/Minia/Econtact.aspx
 • Https://www.maspero.eg/our-reporters/2026/09/20/990867/</t>
         </is>
       </c>
-      <c r="AH37" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI37" s="4" t="inlineStr"/>
+      <c r="AI37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -7861,63 +8093,68 @@
 Обращение: Dear Prof. El-Menoufy,</t>
         </is>
       </c>
-      <c r="L38" s="4" t="inlineStr"/>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr"/>
+      <c r="N38" s="4" t="inlineStr">
         <is>
           <t>info@must.edu.eg</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr"/>
-      <c r="O38" s="4" t="inlineStr">
+      <c r="O38" s="4" t="inlineStr"/>
+      <c r="P38" s="4" t="inlineStr">
         <is>
           <t>https://must.edu.eg</t>
         </is>
       </c>
-      <c r="P38" s="4" t="inlineStr">
+      <c r="Q38" s="4" t="inlineStr">
         <is>
           <t>Prof. Hala El-Menoufy</t>
         </is>
       </c>
-      <c r="Q38" s="4" t="inlineStr">
+      <c r="R38" s="4" t="inlineStr">
         <is>
           <t>Acting President</t>
         </is>
       </c>
-      <c r="R38" s="4" t="inlineStr"/>
-      <c r="S38" s="4" t="inlineStr">
+      <c r="S38" s="4" t="inlineStr"/>
+      <c r="T38" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1801–2000</t>
         </is>
       </c>
-      <c r="T38" s="4" t="inlineStr"/>
-      <c r="U38" s="4" t="n">
+      <c r="U38" s="4" t="inlineStr"/>
+      <c r="V38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V38" s="4" t="inlineStr"/>
       <c r="W38" s="4" t="inlineStr"/>
       <c r="X38" s="4" t="inlineStr"/>
       <c r="Y38" s="4" t="inlineStr"/>
       <c r="Z38" s="4" t="inlineStr"/>
       <c r="AA38" s="4" t="inlineStr"/>
-      <c r="AB38" s="4" t="n">
+      <c r="AB38" s="4" t="inlineStr"/>
+      <c r="AC38" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC38" s="8" t="inlineStr">
+      <c r="AD38" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD38" s="4" t="inlineStr">
+      <c r="AE38" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE38" s="4" t="inlineStr">
+      <c r="AF38" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF38" s="4" t="inlineStr">
+      <c r="AG38" s="4" t="inlineStr">
         <is>
           <t>• Prof. Hala El-Menoufy — исполняющая обязанности президента (Acting President)
 • Опубликован только короткий номер 16878; полного телефона с +20 на сайте нет
@@ -7926,7 +8163,7 @@
 • В QS2027 не найден</t>
         </is>
       </c>
-      <c r="AG38" s="4" t="inlineStr">
+      <c r="AH38" s="4" t="inlineStr">
         <is>
           <t>• Https://must.edu.eg/
 • Https://must.edu.eg/about-must/president/
@@ -7934,12 +8171,12 @@
 • Https://must.edu.eg/sectors/international-students-affairs-sector/</t>
         </is>
       </c>
-      <c r="AH38" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI38" s="4" t="inlineStr"/>
+      <c r="AI38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -7992,78 +8229,83 @@
       </c>
       <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="4" t="inlineStr"/>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M39" s="4" t="inlineStr"/>
-      <c r="N39" s="4" t="inlineStr">
+      <c r="N39" s="4" t="inlineStr"/>
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>+20 92 7602010</t>
         </is>
       </c>
-      <c r="O39" s="4" t="inlineStr">
+      <c r="P39" s="4" t="inlineStr">
         <is>
           <t>https://nvu.edu.eg</t>
         </is>
       </c>
-      <c r="P39" s="4" t="inlineStr">
+      <c r="Q39" s="4" t="inlineStr">
         <is>
           <t>Prof. Abdelaziz Tantawi</t>
         </is>
       </c>
-      <c r="Q39" s="4" t="inlineStr">
+      <c r="R39" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R39" s="4" t="inlineStr"/>
-      <c r="S39" s="4" t="inlineStr">
+      <c r="S39" s="4" t="inlineStr"/>
+      <c r="T39" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T39" s="4" t="inlineStr"/>
-      <c r="U39" s="4" t="n">
+      <c r="U39" s="4" t="inlineStr"/>
+      <c r="V39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V39" s="4" t="inlineStr"/>
       <c r="W39" s="4" t="inlineStr"/>
       <c r="X39" s="4" t="inlineStr"/>
       <c r="Y39" s="4" t="inlineStr"/>
       <c r="Z39" s="4" t="inlineStr"/>
       <c r="AA39" s="4" t="inlineStr"/>
-      <c r="AB39" s="4" t="n">
+      <c r="AB39" s="4" t="inlineStr"/>
+      <c r="AC39" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC39" s="8" t="inlineStr">
+      <c r="AD39" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD39" s="4" t="inlineStr"/>
-      <c r="AE39" s="4" t="inlineStr">
+      <c r="AE39" s="4" t="inlineStr"/>
+      <c r="AF39" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF39" s="4" t="inlineStr">
+      <c r="AG39" s="4" t="inlineStr">
         <is>
           <t>• Сайт nvu.edu.eg недоступен — официальный общий и международный e-mail не подтверждены (в агрегаторах встречается portal@nvu.edu.eg)
 • В СМИ сообщалось о судебном разбирательстве с участием президента университета (дело об исполнении судебного решения) — учесть при обращении
 • Спутниковой активности не найдено</t>
         </is>
       </c>
-      <c r="AG39" s="4" t="inlineStr">
+      <c r="AH39" s="4" t="inlineStr">
         <is>
           <t>• Https://www.youm7.com/story/2026/9/16/7548695
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=11058
 • Https://nvu.edu.eg/leaderstop.php</t>
         </is>
       </c>
-      <c r="AH39" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI39" s="4" t="inlineStr"/>
+      <c r="AI39" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -8128,76 +8370,81 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
           <t>ilca@o6u.edu.eg</t>
         </is>
       </c>
-      <c r="M40" s="4" t="inlineStr">
+      <c r="N40" s="4" t="inlineStr">
         <is>
           <t>President-office@o6u.edu.eg</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>+20 2 38355275</t>
         </is>
       </c>
-      <c r="O40" s="4" t="inlineStr">
+      <c r="P40" s="4" t="inlineStr">
         <is>
           <t>https://o6u.edu.eg</t>
         </is>
       </c>
-      <c r="P40" s="4" t="inlineStr">
+      <c r="Q40" s="4" t="inlineStr">
         <is>
           <t>Prof. Gamal Samy</t>
         </is>
       </c>
-      <c r="Q40" s="4" t="inlineStr">
+      <c r="R40" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R40" s="4" t="inlineStr"/>
-      <c r="S40" s="4" t="inlineStr">
+      <c r="S40" s="4" t="inlineStr"/>
+      <c r="T40" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T40" s="4" t="inlineStr"/>
-      <c r="U40" s="4" t="n">
+      <c r="U40" s="4" t="inlineStr"/>
+      <c r="V40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V40" s="4" t="inlineStr"/>
       <c r="W40" s="4" t="inlineStr"/>
       <c r="X40" s="4" t="inlineStr"/>
       <c r="Y40" s="4" t="inlineStr"/>
       <c r="Z40" s="4" t="inlineStr"/>
       <c r="AA40" s="4" t="inlineStr"/>
-      <c r="AB40" s="4" t="n">
+      <c r="AB40" s="4" t="inlineStr"/>
+      <c r="AC40" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC40" s="8" t="inlineStr">
+      <c r="AD40" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD40" s="4" t="inlineStr">
+      <c r="AE40" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE40" s="4" t="inlineStr">
+      <c r="AF40" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF40" s="4" t="inlineStr">
+      <c r="AG40" s="4" t="inlineStr">
         <is>
           <t>• Имя президента (проф. Гамаль Сами) подтверждено новостью сайта 2024 г. и Википедией; подтверждения 2025–2026 не найдено — сверить
 • Ilca@o6u.edu.eg — Управление международных и местных культурных связей (Admin of International &amp; Local Cultural Affairs); руководитель не указан
 • Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет</t>
         </is>
       </c>
-      <c r="AG40" s="4" t="inlineStr">
+      <c r="AH40" s="4" t="inlineStr">
         <is>
           <t>• Https://o6u.edu.eg/dpagesuni.aspx?FactId=0&amp;id=935
 • Https://o6u.edu.eg/default.aspx?id=70
@@ -8205,12 +8452,12 @@
 • Https://en.wikipedia.org/wiki/October_6_University</t>
         </is>
       </c>
-      <c r="AH40" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI40" s="4" t="inlineStr"/>
+      <c r="AI40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -8273,67 +8520,72 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr"/>
-      <c r="M41" s="4" t="inlineStr">
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr"/>
+      <c r="N41" s="4" t="inlineStr">
         <is>
           <t>info@pua.edu.eg</t>
         </is>
       </c>
-      <c r="N41" s="4" t="inlineStr">
+      <c r="O41" s="4" t="inlineStr">
         <is>
           <t>+20 3 3877700</t>
         </is>
       </c>
-      <c r="O41" s="4" t="inlineStr">
+      <c r="P41" s="4" t="inlineStr">
         <is>
           <t>https://www.pua.edu.eg</t>
         </is>
       </c>
-      <c r="P41" s="4" t="inlineStr">
+      <c r="Q41" s="4" t="inlineStr">
         <is>
           <t>Prof. Mahmoud Mohy El-Din</t>
         </is>
       </c>
-      <c r="Q41" s="4" t="inlineStr">
+      <c r="R41" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R41" s="4" t="inlineStr"/>
-      <c r="S41" s="4" t="inlineStr">
+      <c r="S41" s="4" t="inlineStr"/>
+      <c r="T41" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1601–1800</t>
         </is>
       </c>
-      <c r="T41" s="4" t="inlineStr"/>
-      <c r="U41" s="4" t="n">
+      <c r="U41" s="4" t="inlineStr"/>
+      <c r="V41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V41" s="4" t="inlineStr"/>
       <c r="W41" s="4" t="inlineStr"/>
       <c r="X41" s="4" t="inlineStr"/>
       <c r="Y41" s="4" t="inlineStr"/>
       <c r="Z41" s="4" t="inlineStr"/>
       <c r="AA41" s="4" t="inlineStr"/>
-      <c r="AB41" s="4" t="n">
+      <c r="AB41" s="4" t="inlineStr"/>
+      <c r="AC41" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC41" s="8" t="inlineStr">
+      <c r="AD41" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD41" s="4" t="inlineStr">
+      <c r="AE41" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE41" s="4" t="inlineStr">
+      <c r="AF41" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF41" s="4" t="inlineStr">
+      <c r="AG41" s="4" t="inlineStr">
         <is>
           <t>• Сайт pua.edu.eg снова доступен (04.10.2026): президент, общий e-mail, телефон и адрес подтверждены; прежний номер +20 3 3877000 из справочника был неверным — исправлен на +20 3 3877700
 • На сайте есть ящик International.Students@pua.edu.eg (тел. +20 3 3877872 / 3877886) — офис регистрации иностранных студентов, не отдел партнёрств; отдельный e-mail международного отдела не найден
@@ -8341,19 +8593,19 @@
 • Перепроверка: Президент проф. Махмуд Мохи Эль-Дин, info@pua.edu.eg, телефон и адрес подтверждены на pua.edu.eg 04.10.2026; телефон исправлен</t>
         </is>
       </c>
-      <c r="AG41" s="4" t="inlineStr">
+      <c r="AH41" s="4" t="inlineStr">
         <is>
           <t>• Https://www.pua.edu.eg/
 • Https://www.pua.edu.eg/about-pua/message-from-the-president-of-pharos-university/
 • Https://en.wikipedia.org/wiki/Pharos_University_in_Alexandria</t>
         </is>
       </c>
-      <c r="AH41" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI41" s="4" t="inlineStr"/>
+      <c r="AI41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -8416,67 +8668,72 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L42" s="4" t="inlineStr"/>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr"/>
+      <c r="N42" s="4" t="inlineStr">
         <is>
           <t>info@svu.edu.eg</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>+20 96 5211279</t>
         </is>
       </c>
-      <c r="O42" s="4" t="inlineStr">
+      <c r="P42" s="4" t="inlineStr">
         <is>
           <t>https://www.svu.edu.eg</t>
         </is>
       </c>
-      <c r="P42" s="4" t="inlineStr">
+      <c r="Q42" s="4" t="inlineStr">
         <is>
           <t>Prof. Ahmed Akkawy</t>
         </is>
       </c>
-      <c r="Q42" s="4" t="inlineStr">
+      <c r="R42" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R42" s="4" t="inlineStr"/>
-      <c r="S42" s="4" t="inlineStr">
+      <c r="S42" s="4" t="inlineStr"/>
+      <c r="T42" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="T42" s="4" t="inlineStr"/>
-      <c r="U42" s="4" t="n">
+      <c r="U42" s="4" t="inlineStr"/>
+      <c r="V42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="4" t="inlineStr"/>
       <c r="W42" s="4" t="inlineStr"/>
       <c r="X42" s="4" t="inlineStr"/>
       <c r="Y42" s="4" t="inlineStr"/>
       <c r="Z42" s="4" t="inlineStr"/>
       <c r="AA42" s="4" t="inlineStr"/>
-      <c r="AB42" s="4" t="n">
+      <c r="AB42" s="4" t="inlineStr"/>
+      <c r="AC42" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC42" s="8" t="inlineStr">
+      <c r="AD42" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD42" s="4" t="inlineStr">
+      <c r="AE42" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE42" s="4" t="inlineStr">
+      <c r="AF42" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF42" s="4" t="inlineStr">
+      <c r="AG42" s="4" t="inlineStr">
         <is>
           <t>• Qena University — новое название South Valley University (جامعة جنوب الوادي); в списке также есть строка «South Valley University» — это ДУБЛЬ одного и того же вуза, отправлять одно письмо
 • Адрес, телефон и info@svu.edu.eg взяты из справочников/поисковых выдержек, на официальной странице не подтверждены
@@ -8484,7 +8741,7 @@
 • Спутниковой активности не найдено</t>
         </is>
       </c>
-      <c r="AG42" s="4" t="inlineStr">
+      <c r="AH42" s="4" t="inlineStr">
         <is>
           <t>• Https://www.svu.edu.eg/en/
 • Https://www.youm7.com/story/2026/6/4/7437439
@@ -8492,12 +8749,12 @@
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=10024</t>
         </is>
       </c>
-      <c r="AH42" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI42" s="4" t="inlineStr"/>
+      <c r="AI42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -8550,51 +8807,56 @@
       </c>
       <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M43" s="4" t="inlineStr"/>
       <c r="N43" s="4" t="inlineStr"/>
-      <c r="O43" s="4" t="inlineStr">
+      <c r="O43" s="4" t="inlineStr"/>
+      <c r="P43" s="4" t="inlineStr">
         <is>
           <t>https://www.suezuni.edu.eg</t>
         </is>
       </c>
-      <c r="P43" s="4" t="inlineStr"/>
-      <c r="Q43" s="4" t="inlineStr">
+      <c r="Q43" s="4" t="inlineStr"/>
+      <c r="R43" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R43" s="4" t="inlineStr"/>
-      <c r="S43" s="4" t="inlineStr">
+      <c r="S43" s="4" t="inlineStr"/>
+      <c r="T43" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="T43" s="4" t="inlineStr"/>
-      <c r="U43" s="4" t="n">
+      <c r="U43" s="4" t="inlineStr"/>
+      <c r="V43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="4" t="inlineStr"/>
       <c r="W43" s="4" t="inlineStr"/>
       <c r="X43" s="4" t="inlineStr"/>
       <c r="Y43" s="4" t="inlineStr"/>
       <c r="Z43" s="4" t="inlineStr"/>
       <c r="AA43" s="4" t="inlineStr"/>
-      <c r="AB43" s="4" t="n">
+      <c r="AB43" s="4" t="inlineStr"/>
+      <c r="AC43" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC43" s="8" t="inlineStr">
+      <c r="AD43" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD43" s="4" t="inlineStr"/>
-      <c r="AE43" s="4" t="inlineStr">
+      <c r="AE43" s="4" t="inlineStr"/>
+      <c r="AF43" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF43" s="4" t="inlineStr">
+      <c r="AG43" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт недоступен из нашей сети (503/таймаут), поиск исчерпан — контакты и руководитель не верифицированы; требуется ручная проверка
 • По Википедии (не верифицировано) президент — Abdul Azim Al-Sharkawy
@@ -8602,18 +8864,18 @@
 • Перепроверка: 04.10.2026: сайт suezuni.edu.eg по-прежнему недоступен (curl — нет соединения, WebFetch — 503); данные не изменены</t>
         </is>
       </c>
-      <c r="AG43" s="4" t="inlineStr">
+      <c r="AH43" s="4" t="inlineStr">
         <is>
           <t>• Https://www.timeshighereducation.com/world-university-rankings/suez-university
 • Https://en.wikipedia.org/wiki/Suez_University</t>
         </is>
       </c>
-      <c r="AH43" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI43" s="4" t="inlineStr"/>
+      <c r="AI43" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -8677,78 +8939,83 @@
 Обращение: Dear Prof. Mahmoud,</t>
         </is>
       </c>
-      <c r="L44" s="4" t="inlineStr"/>
-      <c r="M44" s="4" t="inlineStr">
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>ПРОВЕРИТЬ: Ящик личный, имя адресата не совпадает с владельцем — уточнить владельца ящика</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr"/>
+      <c r="N44" s="4" t="inlineStr">
         <is>
           <t>tanta_unv@unv.tanta.edu.eg</t>
         </is>
       </c>
-      <c r="N44" s="4" t="inlineStr">
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>+20 40 3317928</t>
         </is>
       </c>
-      <c r="O44" s="4" t="inlineStr">
+      <c r="P44" s="4" t="inlineStr">
         <is>
           <t>https://tanta.edu.eg</t>
         </is>
       </c>
-      <c r="P44" s="4" t="inlineStr">
+      <c r="Q44" s="4" t="inlineStr">
         <is>
           <t>Prof. Mohamed Hussein Mahmoud</t>
         </is>
       </c>
-      <c r="Q44" s="4" t="inlineStr">
+      <c r="R44" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R44" s="4" t="inlineStr">
+      <c r="S44" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1401+</t>
         </is>
       </c>
-      <c r="S44" s="4" t="inlineStr">
+      <c r="T44" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="T44" s="4" t="inlineStr"/>
-      <c r="U44" s="4" t="n">
+      <c r="U44" s="4" t="inlineStr"/>
+      <c r="V44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="4" t="inlineStr"/>
       <c r="W44" s="4" t="inlineStr"/>
       <c r="X44" s="4" t="inlineStr"/>
       <c r="Y44" s="4" t="inlineStr"/>
       <c r="Z44" s="4" t="inlineStr"/>
       <c r="AA44" s="4" t="inlineStr"/>
-      <c r="AB44" s="4" t="n">
+      <c r="AB44" s="4" t="inlineStr"/>
+      <c r="AC44" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC44" s="8" t="inlineStr">
+      <c r="AD44" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD44" s="4" t="inlineStr">
+      <c r="AE44" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE44" s="4" t="inlineStr">
+      <c r="AF44" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF44" s="4" t="inlineStr">
+      <c r="AG44" s="4" t="inlineStr">
         <is>
           <t>• Президент проф. Мохамед Хусейн Махмуд назначен президентским указом с 26.03.2025
 • Есть только ящик офиса иностранных студентов international_std@unv.tanta.edu.eg (приём студентов) — можно поставить в копию; отдельного ящика по международному сотрудничеству не найдено
 • Запущенных спутников не найдено (быстрая проверка)</t>
         </is>
       </c>
-      <c r="AG44" s="4" t="inlineStr">
+      <c r="AH44" s="4" t="inlineStr">
         <is>
           <t>• Https://tanta.edu.eg/
 • Https://tanta.edu.eg/President.aspx
@@ -8756,12 +9023,12 @@
 • Https://www.qianmu.org/ranking/1528.htm (2027 QS list, qianmu.org)</t>
         </is>
       </c>
-      <c r="AH44" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI44" s="4" t="inlineStr"/>
+      <c r="AI44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -8825,71 +9092,76 @@
 Обращение: Dear Prof. Loutfi,</t>
         </is>
       </c>
-      <c r="L45" s="4" t="inlineStr"/>
-      <c r="M45" s="4" t="inlineStr">
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr"/>
+      <c r="N45" s="4" t="inlineStr">
         <is>
           <t>info@bue.edu.eg</t>
         </is>
       </c>
-      <c r="N45" s="4" t="inlineStr">
+      <c r="O45" s="4" t="inlineStr">
         <is>
           <t>+20 19283</t>
         </is>
       </c>
-      <c r="O45" s="4" t="inlineStr">
+      <c r="P45" s="4" t="inlineStr">
         <is>
           <t>https://www.bue.edu.eg</t>
         </is>
       </c>
-      <c r="P45" s="4" t="inlineStr">
+      <c r="Q45" s="4" t="inlineStr">
         <is>
           <t>Prof. Mohamed Loutfi</t>
         </is>
       </c>
-      <c r="Q45" s="4" t="inlineStr">
+      <c r="R45" s="4" t="inlineStr">
         <is>
           <t>President and Vice-Chancellor</t>
         </is>
       </c>
-      <c r="R45" s="4" t="inlineStr">
+      <c r="S45" s="4" t="inlineStr">
         <is>
           <t>QS2027: 1201–1400</t>
         </is>
       </c>
-      <c r="S45" s="4" t="inlineStr">
+      <c r="T45" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="T45" s="4" t="inlineStr"/>
-      <c r="U45" s="4" t="n">
+      <c r="U45" s="4" t="inlineStr"/>
+      <c r="V45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="4" t="inlineStr"/>
       <c r="W45" s="4" t="inlineStr"/>
       <c r="X45" s="4" t="inlineStr"/>
       <c r="Y45" s="4" t="inlineStr"/>
       <c r="Z45" s="4" t="inlineStr"/>
       <c r="AA45" s="4" t="inlineStr"/>
-      <c r="AB45" s="4" t="n">
+      <c r="AB45" s="4" t="inlineStr"/>
+      <c r="AC45" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC45" s="8" t="inlineStr">
+      <c r="AD45" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD45" s="4" t="inlineStr">
+      <c r="AE45" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE45" s="4" t="inlineStr">
+      <c r="AF45" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF45" s="4" t="inlineStr">
+      <c r="AG45" s="4" t="inlineStr">
         <is>
           <t>• Некоммерческий частный вуз, созданный по межправительственному соглашению Египта и Великобритании; дипломы валидируются британскими вузами
 • Отдельного международного офиса/e-mail нет; отдел «Students Recruitment and Partnerships» (studentrecruitment@bue.edu.eg) ориентирован на абитуриентов — писать на info@bue.edu.eg
@@ -8898,7 +9170,7 @@
 • Космической активности на сайте не найдено (поисковая проверка не выполнена — исчерпана квота поиска)</t>
         </is>
       </c>
-      <c r="AG45" s="4" t="inlineStr">
+      <c r="AH45" s="4" t="inlineStr">
         <is>
           <t>• Https://www.bue.edu.eg/
 • Https://www.bue.edu.eg/leadership-structure
@@ -8907,12 +9179,12 @@
 • Qianmu.org QS2027 list</t>
         </is>
       </c>
-      <c r="AH45" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI45" s="4" t="inlineStr"/>
+      <c r="AI45" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -8976,67 +9248,72 @@
 Обращение: Dear Prof. Abdel-Bary,</t>
         </is>
       </c>
-      <c r="L46" s="4" t="inlineStr"/>
-      <c r="M46" s="4" t="inlineStr">
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr"/>
+      <c r="N46" s="4" t="inlineStr">
         <is>
           <t>info@usc.edu.eg</t>
         </is>
       </c>
-      <c r="N46" s="4" t="inlineStr">
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>+20 48 2603205</t>
         </is>
       </c>
-      <c r="O46" s="4" t="inlineStr">
+      <c r="P46" s="4" t="inlineStr">
         <is>
           <t>https://usc.edu.eg</t>
         </is>
       </c>
-      <c r="P46" s="4" t="inlineStr">
+      <c r="Q46" s="4" t="inlineStr">
         <is>
           <t>Prof. Nasser Abdel-Bary</t>
         </is>
       </c>
-      <c r="Q46" s="4" t="inlineStr">
+      <c r="R46" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R46" s="4" t="inlineStr"/>
-      <c r="S46" s="4" t="inlineStr">
+      <c r="S46" s="4" t="inlineStr"/>
+      <c r="T46" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="T46" s="4" t="inlineStr"/>
-      <c r="U46" s="4" t="n">
+      <c r="U46" s="4" t="inlineStr"/>
+      <c r="V46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="4" t="inlineStr"/>
       <c r="W46" s="4" t="inlineStr"/>
       <c r="X46" s="4" t="inlineStr"/>
       <c r="Y46" s="4" t="inlineStr"/>
       <c r="Z46" s="4" t="inlineStr"/>
       <c r="AA46" s="4" t="inlineStr"/>
-      <c r="AB46" s="4" t="n">
+      <c r="AB46" s="4" t="inlineStr"/>
+      <c r="AC46" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AC46" s="8" t="inlineStr">
+      <c r="AD46" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD46" s="4" t="inlineStr">
+      <c r="AE46" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE46" s="4" t="inlineStr">
+      <c r="AF46" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF46" s="4" t="inlineStr">
+      <c r="AG46" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт usc.edu.eg недоступен (блокировка прокси / DNS) — данные из WHED, справочника и СМИ
 • Президент Dr. Nasser Abdel-Bary (ناصر عبد الباري) подтверждён СМИ за сен. 2026; в WHED указан устаревший и.о. Ahmed Azab; учёное звание Prof. не проверено
@@ -9047,7 +9324,7 @@
 • Перепроверка: Сайт usc.edu.eg по-прежнему недоступен (curl/WebFetch 503); на сайте Минвысобразования найдено, что в авг. 2025 президентом была д-р Шаден Муавия — текущий президент Nasser Abdel-Bary (СМИ 2026) официально не подтверждён; контакты не изменены</t>
         </is>
       </c>
-      <c r="AG46" s="4" t="inlineStr">
+      <c r="AH46" s="4" t="inlineStr">
         <is>
           <t>• Https://whed.net/institutions/IAU-020464
 • Https://www.universitiesegypt.com/university-sadat-city/contacts
@@ -9055,12 +9332,12 @@
 • Https://www.youm7.com/story/2026/2/26/7320365</t>
         </is>
       </c>
-      <c r="AH46" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI46" s="4" t="inlineStr"/>
+      <c r="AI46" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -9123,63 +9400,68 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L47" s="4" t="inlineStr"/>
-      <c r="M47" s="4" t="inlineStr">
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr"/>
+      <c r="N47" s="4" t="inlineStr">
         <is>
           <t>info@acu.edu.eg</t>
         </is>
       </c>
-      <c r="N47" s="4" t="inlineStr">
+      <c r="O47" s="4" t="inlineStr">
         <is>
           <t>19228 (hotline, Egypt)</t>
         </is>
       </c>
-      <c r="O47" s="4" t="inlineStr">
+      <c r="P47" s="4" t="inlineStr">
         <is>
           <t>https://acu.edu.eg</t>
         </is>
       </c>
-      <c r="P47" s="4" t="inlineStr">
+      <c r="Q47" s="4" t="inlineStr">
         <is>
           <t>Prof. Ahmed Mohamed Anani (أ.د. أحمد محمد عناني)</t>
         </is>
       </c>
-      <c r="Q47" s="4" t="inlineStr">
+      <c r="R47" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R47" s="4" t="inlineStr"/>
       <c r="S47" s="4" t="inlineStr"/>
       <c r="T47" s="4" t="inlineStr"/>
-      <c r="U47" s="4" t="n">
+      <c r="U47" s="4" t="inlineStr"/>
+      <c r="V47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="4" t="inlineStr"/>
       <c r="W47" s="4" t="inlineStr"/>
       <c r="X47" s="4" t="inlineStr"/>
       <c r="Y47" s="4" t="inlineStr"/>
       <c r="Z47" s="4" t="inlineStr"/>
       <c r="AA47" s="4" t="inlineStr"/>
-      <c r="AB47" s="4" t="n">
+      <c r="AB47" s="4" t="inlineStr"/>
+      <c r="AC47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC47" s="8" t="inlineStr">
+      <c r="AD47" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD47" s="4" t="inlineStr">
+      <c r="AE47" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE47" s="4" t="inlineStr">
+      <c r="AF47" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF47" s="4" t="inlineStr">
+      <c r="AG47" s="4" t="inlineStr">
         <is>
           <t>• THE2027: только статус Reporter (без ранга)
 • Сайт www.acu.edu.eg отдаёт 403, но acu.edu.eg (без www) доступен
@@ -9189,7 +9471,7 @@
 • Перепроверка: Сайт открылся по адресу без www (acu.edu.eg) 04.10.2026: президент — проф. Ахмед Мохамед Анани (страница руководства + новость 19.07.2026), прежнее имя Amal Fawzy Ahmed исправлено; адрес, info@acu.edu.eg и горячая линия 19228 подтверждены на странице контактов</t>
         </is>
       </c>
-      <c r="AG47" s="4" t="inlineStr">
+      <c r="AH47" s="4" t="inlineStr">
         <is>
           <t>• Https://acu.edu.eg/about-the-council/university-leaders
 • Https://acu.edu.eg/en/contact-us
@@ -9197,12 +9479,12 @@
 • Https://english.ahram.org.eg/NewsContent/1/2/569449/Egypt/Society/Ahram-Canadian-University-achieves-new-milestone-i.aspx</t>
         </is>
       </c>
-      <c r="AH47" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI47" s="4" t="inlineStr"/>
+      <c r="AI47" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -9255,47 +9537,52 @@
       </c>
       <c r="J48" s="4" t="inlineStr"/>
       <c r="K48" s="4" t="inlineStr"/>
-      <c r="L48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M48" s="4" t="inlineStr"/>
       <c r="N48" s="4" t="inlineStr"/>
-      <c r="O48" s="4" t="inlineStr">
+      <c r="O48" s="4" t="inlineStr"/>
+      <c r="P48" s="4" t="inlineStr">
         <is>
           <t>https://aiu.edu.eg</t>
         </is>
       </c>
-      <c r="P48" s="4" t="inlineStr"/>
-      <c r="Q48" s="4" t="inlineStr">
+      <c r="Q48" s="4" t="inlineStr"/>
+      <c r="R48" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R48" s="4" t="inlineStr"/>
       <c r="S48" s="4" t="inlineStr"/>
       <c r="T48" s="4" t="inlineStr"/>
-      <c r="U48" s="4" t="n">
+      <c r="U48" s="4" t="inlineStr"/>
+      <c r="V48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="4" t="inlineStr"/>
       <c r="W48" s="4" t="inlineStr"/>
       <c r="X48" s="4" t="inlineStr"/>
       <c r="Y48" s="4" t="inlineStr"/>
       <c r="Z48" s="4" t="inlineStr"/>
       <c r="AA48" s="4" t="inlineStr"/>
-      <c r="AB48" s="4" t="n">
+      <c r="AB48" s="4" t="inlineStr"/>
+      <c r="AC48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC48" s="8" t="inlineStr">
+      <c r="AD48" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD48" s="4" t="inlineStr"/>
-      <c r="AE48" s="4" t="inlineStr">
+      <c r="AE48" s="4" t="inlineStr"/>
+      <c r="AF48" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF48" s="4" t="inlineStr">
+      <c r="AG48" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт aiu.edu.eg (http/https, www) по-прежнему недоступен из нашей сети (503/таймаут, в т.ч. через WebFetch) — контакты и руководитель не верифицированы; требуется ручная проверка
 • По Википедии и поисковой выдаче (без даты/официального источника) президент — Prof. Dr. Essam Elkordi (عصام الكردي); председатель совета — Dr. Ahmed Mahmoud — не подтверждено, в поля не внесено
@@ -9304,18 +9591,18 @@
 • Перепроверка: Сайт недоступен; данные не изменены (президент Essam Elkordi — только по вторичным источникам)</t>
         </is>
       </c>
-      <c r="AG48" s="4" t="inlineStr">
+      <c r="AH48" s="4" t="inlineStr">
         <is>
           <t>• Https://www.timeshighereducation.com/world-university-rankings/alamein-international-university
 • Https://en.wikipedia.org/wiki/Alamein_International_University</t>
         </is>
       </c>
-      <c r="AH48" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI48" s="4" t="inlineStr"/>
+      <c r="AI48" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -9378,63 +9665,68 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L49" s="4" t="inlineStr"/>
-      <c r="M49" s="4" t="inlineStr">
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="inlineStr"/>
+      <c r="N49" s="4" t="inlineStr">
         <is>
           <t>info@anu.edu.eg</t>
         </is>
       </c>
-      <c r="N49" s="4" t="inlineStr">
+      <c r="O49" s="4" t="inlineStr">
         <is>
           <t>+20 122 885 8407</t>
         </is>
       </c>
-      <c r="O49" s="4" t="inlineStr">
+      <c r="P49" s="4" t="inlineStr">
         <is>
           <t>https://anu.edu.eg</t>
         </is>
       </c>
-      <c r="P49" s="4" t="inlineStr">
+      <c r="Q49" s="4" t="inlineStr">
         <is>
           <t>Prof. Ahmed Adel Abdel Hakim</t>
         </is>
       </c>
-      <c r="Q49" s="4" t="inlineStr">
+      <c r="R49" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R49" s="4" t="inlineStr"/>
       <c r="S49" s="4" t="inlineStr"/>
       <c r="T49" s="4" t="inlineStr"/>
-      <c r="U49" s="4" t="n">
+      <c r="U49" s="4" t="inlineStr"/>
+      <c r="V49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V49" s="4" t="inlineStr"/>
       <c r="W49" s="4" t="inlineStr"/>
       <c r="X49" s="4" t="inlineStr"/>
       <c r="Y49" s="4" t="inlineStr"/>
       <c r="Z49" s="4" t="inlineStr"/>
       <c r="AA49" s="4" t="inlineStr"/>
-      <c r="AB49" s="4" t="n">
+      <c r="AB49" s="4" t="inlineStr"/>
+      <c r="AC49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC49" s="8" t="inlineStr">
+      <c r="AD49" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD49" s="4" t="inlineStr">
+      <c r="AE49" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE49" s="4" t="inlineStr">
+      <c r="AF49" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF49" s="4" t="inlineStr">
+      <c r="AG49" s="4" t="inlineStr">
         <is>
           <t>• Национальный (ахлия) университет при Alexandria University; руководство — и.о. (Ahmed Adel Abdel Hakim, он же и.о. президента Alexandria University по данным СМИ, сентябрь 2026)
 • Спутниковой активности не найдено
@@ -9442,7 +9734,7 @@
 • Перепроверка: Сайт открылся 04.10.2026: президент, адрес, e-mail info@anu.edu.eg подтверждены, добавлен телефон +20 122 885 8407 (страницы без даты)</t>
         </is>
       </c>
-      <c r="AG49" s="4" t="inlineStr">
+      <c r="AH49" s="4" t="inlineStr">
         <is>
           <t>• Https://anu.edu.eg/en/contact
 • Https://www.dostor.org/5708804
@@ -9451,12 +9743,12 @@
 • Https://anu.edu.eg/en/contact</t>
         </is>
       </c>
-      <c r="AH49" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI49" s="4" t="inlineStr"/>
+      <c r="AI49" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -9511,63 +9803,68 @@
 Обращение: Dear Prof. El-Shebeiny,</t>
         </is>
       </c>
-      <c r="L50" s="4" t="inlineStr"/>
-      <c r="M50" s="4" t="inlineStr">
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr"/>
+      <c r="N50" s="4" t="inlineStr">
         <is>
           <t>info@aru.edu.eg</t>
         </is>
       </c>
-      <c r="N50" s="4" t="inlineStr">
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>+20 68 3320523</t>
         </is>
       </c>
-      <c r="O50" s="4" t="inlineStr">
+      <c r="P50" s="4" t="inlineStr">
         <is>
           <t>https://aru.edu.eg</t>
         </is>
       </c>
-      <c r="P50" s="4" t="inlineStr">
+      <c r="Q50" s="4" t="inlineStr">
         <is>
           <t>Prof. Ayman Abdel Meguid El-Shebeiny</t>
         </is>
       </c>
-      <c r="Q50" s="4" t="inlineStr">
+      <c r="R50" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R50" s="4" t="inlineStr"/>
       <c r="S50" s="4" t="inlineStr"/>
       <c r="T50" s="4" t="inlineStr"/>
-      <c r="U50" s="4" t="n">
+      <c r="U50" s="4" t="inlineStr"/>
+      <c r="V50" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V50" s="4" t="inlineStr"/>
       <c r="W50" s="4" t="inlineStr"/>
       <c r="X50" s="4" t="inlineStr"/>
       <c r="Y50" s="4" t="inlineStr"/>
       <c r="Z50" s="4" t="inlineStr"/>
       <c r="AA50" s="4" t="inlineStr"/>
-      <c r="AB50" s="4" t="n">
+      <c r="AB50" s="4" t="inlineStr"/>
+      <c r="AC50" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC50" s="8" t="inlineStr">
+      <c r="AD50" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD50" s="4" t="inlineStr">
+      <c r="AE50" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE50" s="4" t="inlineStr">
+      <c r="AF50" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF50" s="4" t="inlineStr">
+      <c r="AG50" s="4" t="inlineStr">
         <is>
           <t>• Имя президента (أيمن عبد المجيد الشبيني) — со страницы «Слово президента» без даты; латинская транслитерация условная — сверить
 • Полный почтовый адрес на сайте не указан (только «Эль-Ариш, Северный Синай»); отдельного e-mail международного отдела нет
@@ -9575,19 +9872,19 @@
 • В THE 2027 — статус Reporter (без ранга)</t>
         </is>
       </c>
-      <c r="AG50" s="4" t="inlineStr">
+      <c r="AH50" s="4" t="inlineStr">
         <is>
           <t>• Https://aru.edu.eg/ar
 • Https://aru.edu.eg/ar/contact
 • Https://aru.edu.eg/ar/page/head-word</t>
         </is>
       </c>
-      <c r="AH50" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI50" s="4" t="inlineStr"/>
+      <c r="AI50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -9651,67 +9948,72 @@
 Обращение: Dear Prof. Mahmoud,</t>
         </is>
       </c>
-      <c r="L51" s="4" t="inlineStr"/>
-      <c r="M51" s="4" t="inlineStr">
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="inlineStr"/>
+      <c r="N51" s="4" t="inlineStr">
         <is>
           <t>info@bnu.edu.eg</t>
         </is>
       </c>
-      <c r="N51" s="4" t="inlineStr">
+      <c r="O51" s="4" t="inlineStr">
         <is>
           <t>+20 120 522 3222</t>
         </is>
       </c>
-      <c r="O51" s="4" t="inlineStr">
+      <c r="P51" s="4" t="inlineStr">
         <is>
           <t>https://bnu.edu.eg</t>
         </is>
       </c>
-      <c r="P51" s="4" t="inlineStr">
+      <c r="Q51" s="4" t="inlineStr">
         <is>
           <t>Prof. Tamer Samir Mahmoud</t>
         </is>
       </c>
-      <c r="Q51" s="4" t="inlineStr">
+      <c r="R51" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R51" s="4" t="inlineStr"/>
-      <c r="S51" s="4" t="inlineStr">
+      <c r="S51" s="4" t="inlineStr"/>
+      <c r="T51" s="4" t="inlineStr">
         <is>
           <t>THE2027 Reporter (unranked)</t>
         </is>
       </c>
-      <c r="T51" s="4" t="inlineStr"/>
-      <c r="U51" s="4" t="n">
+      <c r="U51" s="4" t="inlineStr"/>
+      <c r="V51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="4" t="inlineStr"/>
       <c r="W51" s="4" t="inlineStr"/>
       <c r="X51" s="4" t="inlineStr"/>
       <c r="Y51" s="4" t="inlineStr"/>
       <c r="Z51" s="4" t="inlineStr"/>
       <c r="AA51" s="4" t="inlineStr"/>
-      <c r="AB51" s="4" t="n">
+      <c r="AB51" s="4" t="inlineStr"/>
+      <c r="AC51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC51" s="8" t="inlineStr">
+      <c r="AD51" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD51" s="4" t="inlineStr">
+      <c r="AE51" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE51" s="4" t="inlineStr">
+      <c r="AF51" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF51" s="4" t="inlineStr">
+      <c r="AG51" s="4" t="inlineStr">
         <is>
           <t>• Национальный (ахлия) некоммерческий университет при Benha University, создан указом президента №369 от 2022 г.; 10 факультетов
 • В THE2027 только в статусе Reporter (без ранга)
@@ -9719,19 +10021,19 @@
 • Космической активности на сайте не найдено (поисковая проверка не выполнена — исчерпана квота поиска)</t>
         </is>
       </c>
-      <c r="AG51" s="4" t="inlineStr">
+      <c r="AH51" s="4" t="inlineStr">
         <is>
           <t>• Https://bnu.edu.eg/page/about
 • Https://bnu.edu.eg/en/page/academic_leaders
 • Https://bnu.edu.eg/page/contact</t>
         </is>
       </c>
-      <c r="AH51" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI51" s="4" t="inlineStr"/>
+      <c r="AI51" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -9782,59 +10084,64 @@
 Обращение: Dear Professor El-Gohary,</t>
         </is>
       </c>
-      <c r="L52" s="4" t="inlineStr"/>
-      <c r="M52" s="4" t="inlineStr">
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="inlineStr"/>
+      <c r="N52" s="4" t="inlineStr">
         <is>
           <t>contact@batechu.com</t>
         </is>
       </c>
-      <c r="N52" s="4" t="inlineStr"/>
-      <c r="O52" s="4" t="inlineStr">
+      <c r="O52" s="4" t="inlineStr"/>
+      <c r="P52" s="4" t="inlineStr">
         <is>
           <t>https://batechu.com</t>
         </is>
       </c>
-      <c r="P52" s="4" t="inlineStr">
+      <c r="Q52" s="4" t="inlineStr">
         <is>
           <t>Prof. Dr. Mohamed Morsi El-Gohary (محمد مرسي الجوهري)</t>
         </is>
       </c>
-      <c r="Q52" s="4" t="inlineStr">
+      <c r="R52" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R52" s="4" t="inlineStr"/>
       <c r="S52" s="4" t="inlineStr"/>
       <c r="T52" s="4" t="inlineStr"/>
-      <c r="U52" s="4" t="n">
+      <c r="U52" s="4" t="inlineStr"/>
+      <c r="V52" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V52" s="4" t="inlineStr"/>
       <c r="W52" s="4" t="inlineStr"/>
       <c r="X52" s="4" t="inlineStr"/>
       <c r="Y52" s="4" t="inlineStr"/>
       <c r="Z52" s="4" t="inlineStr"/>
       <c r="AA52" s="4" t="inlineStr"/>
-      <c r="AB52" s="4" t="n">
+      <c r="AB52" s="4" t="inlineStr"/>
+      <c r="AC52" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC52" s="8" t="inlineStr">
+      <c r="AD52" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD52" s="4" t="inlineStr">
+      <c r="AE52" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE52" s="4" t="inlineStr">
+      <c r="AF52" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF52" s="4" t="inlineStr">
+      <c r="AG52" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт batechu.com (не в зоне .edu.eg); e-mail contact@batechu.com подтверждён на странице Contact Us; телефон и полный почтовый адрес на сайте не опубликованы
 • Президент проф. д-р Мохамед Мурси аль-Гохари — по обращению президента на главной странице официального сайта (подвал © 2026); дата назначения не указана
@@ -9843,19 +10150,19 @@
 • Перепроверка: 04.10.2026: президент и e-mail подтверждены на официальном сайте batechu.com; телефон и адрес не опубликованы</t>
         </is>
       </c>
-      <c r="AG52" s="4" t="inlineStr">
+      <c r="AH52" s="4" t="inlineStr">
         <is>
           <t>• Https://batechu.com/
 • Https://batechu.com/contact-us
 • Https://en.wikipedia.org/wiki/Borg_El_Arab_Technological_University</t>
         </is>
       </c>
-      <c r="AH52" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI52" s="4" t="inlineStr"/>
+      <c r="AI52" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -9915,69 +10222,74 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="inlineStr">
+        <is>
           <t>Socialmedia@cic-cairo.com</t>
         </is>
       </c>
-      <c r="M53" s="4" t="inlineStr">
+      <c r="N53" s="4" t="inlineStr">
         <is>
           <t>Info@cic-cairo.com</t>
         </is>
       </c>
-      <c r="N53" s="4" t="inlineStr">
+      <c r="O53" s="4" t="inlineStr">
         <is>
           <t>16242 (hotline)</t>
         </is>
       </c>
-      <c r="O53" s="4" t="inlineStr">
+      <c r="P53" s="4" t="inlineStr">
         <is>
           <t>https://www.cic-cairo.edu.eg</t>
         </is>
       </c>
-      <c r="P53" s="4" t="inlineStr">
+      <c r="Q53" s="4" t="inlineStr">
         <is>
           <t>Prof. Mamdouh Elkady</t>
         </is>
       </c>
-      <c r="Q53" s="4" t="inlineStr">
+      <c r="R53" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R53" s="4" t="inlineStr"/>
-      <c r="S53" s="4" t="inlineStr">
+      <c r="S53" s="4" t="inlineStr"/>
+      <c r="T53" s="4" t="inlineStr">
         <is>
           <t>THE2027 Reporter (unranked)</t>
         </is>
       </c>
-      <c r="T53" s="4" t="inlineStr"/>
-      <c r="U53" s="4" t="n">
+      <c r="U53" s="4" t="inlineStr"/>
+      <c r="V53" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="4" t="inlineStr"/>
       <c r="W53" s="4" t="inlineStr"/>
       <c r="X53" s="4" t="inlineStr"/>
       <c r="Y53" s="4" t="inlineStr"/>
       <c r="Z53" s="4" t="inlineStr"/>
       <c r="AA53" s="4" t="inlineStr"/>
-      <c r="AB53" s="4" t="n">
+      <c r="AB53" s="4" t="inlineStr"/>
+      <c r="AC53" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC53" s="8" t="inlineStr">
+      <c r="AD53" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD53" s="4" t="inlineStr">
+      <c r="AE53" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE53" s="4" t="inlineStr">
+      <c r="AF53" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF53" s="4" t="inlineStr">
+      <c r="AG53" s="4" t="inlineStr">
         <is>
           <t>• Info@ помечен на сайте как контакт для новых студентов; Socialmedia@cic-cairo.com — указан как контакт 'Collaborations' (сотрудничество)
 • Частный колледж (не университет) с канадскими дипломами Cape Breton University; второй кампус — Sheikh Zayed
@@ -9985,19 +10297,19 @@
 • Profile_type условный (инженерия/ИТ/бизнес)</t>
         </is>
       </c>
-      <c r="AG53" s="4" t="inlineStr">
+      <c r="AH53" s="4" t="inlineStr">
         <is>
           <t>• Https://www.cic-cairo.edu.eg/
 • Https://www.cic-cairo.edu.eg/about/
 • Https://www.timeshighereducation.com/world-university-rankings/canadian-international-college-cairo-campus-cape-breton-university-canada</t>
         </is>
       </c>
-      <c r="AH53" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI53" s="4" t="inlineStr"/>
+      <c r="AI53" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -10058,63 +10370,68 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L54" s="4" t="inlineStr"/>
-      <c r="M54" s="4" t="inlineStr">
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="inlineStr"/>
+      <c r="N54" s="4" t="inlineStr">
         <is>
           <t>student.admission@deraya.edu.eg</t>
         </is>
       </c>
-      <c r="N54" s="4" t="inlineStr">
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>+20 86 2110026</t>
         </is>
       </c>
-      <c r="O54" s="4" t="inlineStr">
+      <c r="P54" s="4" t="inlineStr">
         <is>
           <t>https://deraya.edu.eg</t>
         </is>
       </c>
-      <c r="P54" s="4" t="inlineStr">
+      <c r="Q54" s="4" t="inlineStr">
         <is>
           <t>Prof. Sherif Refaat</t>
         </is>
       </c>
-      <c r="Q54" s="4" t="inlineStr">
+      <c r="R54" s="4" t="inlineStr">
         <is>
           <t>Acting President</t>
         </is>
       </c>
-      <c r="R54" s="4" t="inlineStr"/>
       <c r="S54" s="4" t="inlineStr"/>
       <c r="T54" s="4" t="inlineStr"/>
-      <c r="U54" s="4" t="n">
+      <c r="U54" s="4" t="inlineStr"/>
+      <c r="V54" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V54" s="4" t="inlineStr"/>
       <c r="W54" s="4" t="inlineStr"/>
       <c r="X54" s="4" t="inlineStr"/>
       <c r="Y54" s="4" t="inlineStr"/>
       <c r="Z54" s="4" t="inlineStr"/>
       <c r="AA54" s="4" t="inlineStr"/>
-      <c r="AB54" s="4" t="n">
+      <c r="AB54" s="4" t="inlineStr"/>
+      <c r="AC54" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC54" s="8" t="inlineStr">
+      <c r="AD54" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD54" s="4" t="inlineStr">
+      <c r="AE54" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE54" s="4" t="inlineStr">
+      <c r="AF54" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF54" s="4" t="inlineStr">
+      <c r="AG54" s="4" t="inlineStr">
         <is>
           <t>• THE2027: только статус Reporter (без ранга)
 • Общий e-mail не опубликован — указан e-mail приёмной комиссии (student.admission@); есть также registrar@deraya.edu.eg; горячая линия 16283
@@ -10122,19 +10439,19 @@
 • Профиль медицинский/фармацевтический — низкая релевантность для спутниковой программы</t>
         </is>
       </c>
-      <c r="AG54" s="4" t="inlineStr">
+      <c r="AH54" s="4" t="inlineStr">
         <is>
           <t>• Https://deraya.edu.eg/
 • Https://deraya.edu.eg/?page_id=1853
 • Https://deraya.edu.eg/contact/</t>
         </is>
       </c>
-      <c r="AH54" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI54" s="4" t="inlineStr"/>
+      <c r="AI54" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -10174,43 +10491,48 @@
       <c r="I55" s="4" t="inlineStr"/>
       <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr"/>
-      <c r="L55" s="4" t="inlineStr"/>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M55" s="4" t="inlineStr"/>
       <c r="N55" s="4" t="inlineStr"/>
       <c r="O55" s="4" t="inlineStr"/>
       <c r="P55" s="4" t="inlineStr"/>
-      <c r="Q55" s="4" t="inlineStr">
+      <c r="Q55" s="4" t="inlineStr"/>
+      <c r="R55" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R55" s="4" t="inlineStr"/>
       <c r="S55" s="4" t="inlineStr"/>
       <c r="T55" s="4" t="inlineStr"/>
-      <c r="U55" s="4" t="n">
+      <c r="U55" s="4" t="inlineStr"/>
+      <c r="V55" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="4" t="inlineStr"/>
       <c r="W55" s="4" t="inlineStr"/>
       <c r="X55" s="4" t="inlineStr"/>
       <c r="Y55" s="4" t="inlineStr"/>
       <c r="Z55" s="4" t="inlineStr"/>
       <c r="AA55" s="4" t="inlineStr"/>
-      <c r="AB55" s="4" t="n">
+      <c r="AB55" s="4" t="inlineStr"/>
+      <c r="AC55" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC55" s="8" t="inlineStr">
+      <c r="AD55" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD55" s="4" t="inlineStr"/>
-      <c r="AE55" s="4" t="inlineStr">
+      <c r="AE55" s="4" t="inlineStr"/>
+      <c r="AF55" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF55" s="4" t="inlineStr">
+      <c r="AG55" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт не найден (epsnu.edu.eg недоступен), лимит веб-поиска исчерпан — все контактные поля требуют ручного заполнения
 • Национальный (ахлия) университет, созданный при государственном Порт-Саидском университете (по арабской Википедии)
@@ -10218,17 +10540,17 @@
 • Перепроверка: Домены epsnu.edu.eg недоступны (04.10.2026); на сайте Порт-Саидского университета (psu.edu.eg) ссылки на национальный университет не найдено; данные не изменены</t>
         </is>
       </c>
-      <c r="AG55" s="4" t="inlineStr">
+      <c r="AH55" s="4" t="inlineStr">
         <is>
           <t>Https://ar.wikipedia.org/wiki/جامعة_شرق_بورسعيد_الأهلية</t>
         </is>
       </c>
-      <c r="AH55" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI55" s="4" t="inlineStr"/>
+      <c r="AI55" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -10291,67 +10613,72 @@
 Обращение: Dear Prof. Hamad,</t>
         </is>
       </c>
-      <c r="L56" s="4" t="inlineStr"/>
-      <c r="M56" s="4" t="inlineStr">
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="inlineStr"/>
+      <c r="N56" s="4" t="inlineStr">
         <is>
           <t>contact@eui.edu.eg</t>
         </is>
       </c>
-      <c r="N56" s="4" t="inlineStr">
+      <c r="O56" s="4" t="inlineStr">
         <is>
           <t>+20 103 008 0940</t>
         </is>
       </c>
-      <c r="O56" s="4" t="inlineStr">
+      <c r="P56" s="4" t="inlineStr">
         <is>
           <t>https://eui.edu.eg</t>
         </is>
       </c>
-      <c r="P56" s="4" t="inlineStr">
+      <c r="Q56" s="4" t="inlineStr">
         <is>
           <t>Prof. Ahmed Mohamed Hamad</t>
         </is>
       </c>
-      <c r="Q56" s="4" t="inlineStr">
+      <c r="R56" s="4" t="inlineStr">
         <is>
           <t>Acting President</t>
         </is>
       </c>
-      <c r="R56" s="4" t="inlineStr"/>
-      <c r="S56" s="4" t="inlineStr">
+      <c r="S56" s="4" t="inlineStr"/>
+      <c r="T56" s="4" t="inlineStr">
         <is>
           <t>THE2027 Reporter (unranked)</t>
         </is>
       </c>
-      <c r="T56" s="4" t="inlineStr"/>
-      <c r="U56" s="4" t="n">
+      <c r="U56" s="4" t="inlineStr"/>
+      <c r="V56" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V56" s="4" t="inlineStr"/>
       <c r="W56" s="4" t="inlineStr"/>
       <c r="X56" s="4" t="inlineStr"/>
       <c r="Y56" s="4" t="inlineStr"/>
       <c r="Z56" s="4" t="inlineStr"/>
       <c r="AA56" s="4" t="inlineStr"/>
-      <c r="AB56" s="4" t="n">
+      <c r="AB56" s="4" t="inlineStr"/>
+      <c r="AC56" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC56" s="8" t="inlineStr">
+      <c r="AD56" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD56" s="4" t="inlineStr">
+      <c r="AE56" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE56" s="4" t="inlineStr">
+      <c r="AF56" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF56" s="4" t="inlineStr">
+      <c r="AG56" s="4" t="inlineStr">
         <is>
           <t>• Создан Министерством связи и ИТ совместно с Минвысшобразования (начал работу в 2021/22); форма собственности указана как национальный некоммерческий — уточнить
 • Prof. Ahmed Mohamed Hamad — исполняющий обязанности президента; основатель-президент — Prof. Reem Bahgat
@@ -10360,7 +10687,7 @@
 • Космической активности на сайте не найдено (поисковая проверка не выполнена — исчерпана квота поиска)</t>
         </is>
       </c>
-      <c r="AG56" s="4" t="inlineStr">
+      <c r="AH56" s="4" t="inlineStr">
         <is>
           <t>• Https://eui.edu.eg/
 • Https://eui.edu.eg/who-we-are
@@ -10368,12 +10695,12 @@
 • Https://eui.edu.eg/contact-us</t>
         </is>
       </c>
-      <c r="AH56" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI56" s="4" t="inlineStr"/>
+      <c r="AI56" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -10424,51 +10751,56 @@
       </c>
       <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr"/>
-      <c r="L57" s="4" t="inlineStr"/>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M57" s="4" t="inlineStr"/>
       <c r="N57" s="4" t="inlineStr"/>
-      <c r="O57" s="4" t="inlineStr">
+      <c r="O57" s="4" t="inlineStr"/>
+      <c r="P57" s="4" t="inlineStr">
         <is>
           <t>https://www.ecu.edu.eg</t>
         </is>
       </c>
-      <c r="P57" s="4" t="inlineStr">
+      <c r="Q57" s="4" t="inlineStr">
         <is>
           <t>Prof. Dr. Rasha El-Kholy</t>
         </is>
       </c>
-      <c r="Q57" s="4" t="inlineStr">
+      <c r="R57" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R57" s="4" t="inlineStr"/>
       <c r="S57" s="4" t="inlineStr"/>
       <c r="T57" s="4" t="inlineStr"/>
-      <c r="U57" s="4" t="n">
+      <c r="U57" s="4" t="inlineStr"/>
+      <c r="V57" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="4" t="inlineStr"/>
       <c r="W57" s="4" t="inlineStr"/>
       <c r="X57" s="4" t="inlineStr"/>
       <c r="Y57" s="4" t="inlineStr"/>
       <c r="Z57" s="4" t="inlineStr"/>
       <c r="AA57" s="4" t="inlineStr"/>
-      <c r="AB57" s="4" t="n">
+      <c r="AB57" s="4" t="inlineStr"/>
+      <c r="AC57" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC57" s="8" t="inlineStr">
+      <c r="AD57" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD57" s="4" t="inlineStr"/>
-      <c r="AE57" s="4" t="inlineStr">
+      <c r="AE57" s="4" t="inlineStr"/>
+      <c r="AF57" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF57" s="4" t="inlineStr">
+      <c r="AG57" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт ecu.edu.eg блокирует автоматический доступ (403, Cloudflare, повторно 04.10.2026); e-mail и телефон не найдены — найти вручную
 • Президент Prof. Dr. Rasha El-Kholy — по поисковой выдаче официальных страниц ECU (University President’s Message) и интервью на портале Belt and Road; дата назначения не установлена (предыдущий президент Ashraf El-Shihy, 2017–2023) — перепроверить
@@ -10478,18 +10810,18 @@
 • Перепроверка: Сайт ecu.edu.eg по-прежнему 403 (Cloudflare); президент проф. Rasha El-Kholy внесена по выдаче официальных страниц ECU и портала Belt and Road (дата не установлена) — контакты не найдены</t>
         </is>
       </c>
-      <c r="AG57" s="4" t="inlineStr">
+      <c r="AH57" s="4" t="inlineStr">
         <is>
           <t>• Https://ar.wikipedia.org/wiki/الجامعة_المصرية_الصينية
 • Https://ecu.edu.eg/about-ecu/university-presidents-message/ (snippet)</t>
         </is>
       </c>
-      <c r="AH57" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI57" s="4" t="inlineStr"/>
+      <c r="AI57" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -10546,86 +10878,91 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L58" s="4" t="inlineStr"/>
-      <c r="M58" s="4" t="inlineStr">
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="inlineStr"/>
+      <c r="N58" s="4" t="inlineStr">
         <is>
           <t>info@sut.edu.eg</t>
         </is>
       </c>
-      <c r="N58" s="4" t="inlineStr">
+      <c r="O58" s="4" t="inlineStr">
         <is>
           <t>+20 10 70919636; +20 10 70966547 (hotline 15755)</t>
         </is>
       </c>
-      <c r="O58" s="4" t="inlineStr">
+      <c r="P58" s="4" t="inlineStr">
         <is>
           <t>https://sut.edu.eg</t>
         </is>
       </c>
-      <c r="P58" s="4" t="inlineStr">
+      <c r="Q58" s="4" t="inlineStr">
         <is>
           <t>Dr. Ahmed Hassan Yousef</t>
         </is>
       </c>
-      <c r="Q58" s="4" t="inlineStr">
+      <c r="R58" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R58" s="4" t="inlineStr"/>
-      <c r="S58" s="4" t="inlineStr">
+      <c r="S58" s="4" t="inlineStr"/>
+      <c r="T58" s="4" t="inlineStr">
         <is>
           <t>THE2027 Reporter (unranked)</t>
         </is>
       </c>
-      <c r="T58" s="4" t="inlineStr"/>
-      <c r="U58" s="4" t="n">
+      <c r="U58" s="4" t="inlineStr"/>
+      <c r="V58" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V58" s="4" t="inlineStr"/>
       <c r="W58" s="4" t="inlineStr"/>
       <c r="X58" s="4" t="inlineStr"/>
       <c r="Y58" s="4" t="inlineStr"/>
       <c r="Z58" s="4" t="inlineStr"/>
       <c r="AA58" s="4" t="inlineStr"/>
-      <c r="AB58" s="4" t="n">
+      <c r="AB58" s="4" t="inlineStr"/>
+      <c r="AC58" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC58" s="8" t="inlineStr">
+      <c r="AD58" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD58" s="4" t="inlineStr">
+      <c r="AE58" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE58" s="4" t="inlineStr">
+      <c r="AF58" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF58" s="4" t="inlineStr">
+      <c r="AG58" s="4" t="inlineStr">
         <is>
           <t>• Первый политехнический университет Египта (B.Tech), связан с группой Elsewedy Electric
 • Арабское официальное название на сайте не найдено
 • Спутников не найдено</t>
         </is>
       </c>
-      <c r="AG58" s="4" t="inlineStr">
+      <c r="AH58" s="4" t="inlineStr">
         <is>
           <t>• Https://sut.edu.eg/
 • Https://sut.edu.eg/about-sutech/president/
 • Https://sut.edu.eg/contact-us/</t>
         </is>
       </c>
-      <c r="AH58" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI58" s="4" t="inlineStr"/>
+      <c r="AI58" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -10686,65 +11023,70 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
           <t>iro@hu.edu.eg</t>
         </is>
       </c>
-      <c r="M59" s="4" t="inlineStr">
+      <c r="N59" s="4" t="inlineStr">
         <is>
           <t>admission@hu.edu.eg</t>
         </is>
       </c>
-      <c r="N59" s="4" t="inlineStr">
+      <c r="O59" s="4" t="inlineStr">
         <is>
           <t>16418 (hotline)</t>
         </is>
       </c>
-      <c r="O59" s="4" t="inlineStr">
+      <c r="P59" s="4" t="inlineStr">
         <is>
           <t>https://hu.edu.eg</t>
         </is>
       </c>
-      <c r="P59" s="4" t="inlineStr">
+      <c r="Q59" s="4" t="inlineStr">
         <is>
           <t>Prof. Dr. Gouda Helal</t>
         </is>
       </c>
-      <c r="Q59" s="4" t="inlineStr">
+      <c r="R59" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R59" s="4" t="inlineStr"/>
       <c r="S59" s="4" t="inlineStr"/>
       <c r="T59" s="4" t="inlineStr"/>
-      <c r="U59" s="4" t="n">
+      <c r="U59" s="4" t="inlineStr"/>
+      <c r="V59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V59" s="4" t="inlineStr"/>
       <c r="W59" s="4" t="inlineStr"/>
       <c r="X59" s="4" t="inlineStr"/>
       <c r="Y59" s="4" t="inlineStr"/>
       <c r="Z59" s="4" t="inlineStr"/>
       <c r="AA59" s="4" t="inlineStr"/>
-      <c r="AB59" s="4" t="n">
+      <c r="AB59" s="4" t="inlineStr"/>
+      <c r="AC59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC59" s="8" t="inlineStr">
+      <c r="AD59" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD59" s="4" t="inlineStr">
+      <c r="AE59" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE59" s="4" t="inlineStr">
+      <c r="AF59" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF59" s="4" t="inlineStr">
+      <c r="AG59" s="4" t="inlineStr">
         <is>
           <t>• Частный университет устойчивого развития (основан при SEKEM, председатель попечительского совета — Хельми Абулейш)
 • Общий ящик опубликован только для приёма (admission@hu.edu.eg) — иного общего адреса нет; телефон — короткая горячая линия 16418
@@ -10752,19 +11094,19 @@
 • Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет</t>
         </is>
       </c>
-      <c r="AG59" s="4" t="inlineStr">
+      <c r="AH59" s="4" t="inlineStr">
         <is>
           <t>• Https://hu.edu.eg/
 • Https://hu.edu.eg/about-us/
 • Https://hu.edu.eg/heliopolis-university-international-relations/</t>
         </is>
       </c>
-      <c r="AH59" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI59" s="4" t="inlineStr"/>
+      <c r="AI59" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -10808,47 +11150,52 @@
       </c>
       <c r="J60" s="4" t="inlineStr"/>
       <c r="K60" s="4" t="inlineStr"/>
-      <c r="L60" s="4" t="inlineStr"/>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M60" s="4" t="inlineStr"/>
       <c r="N60" s="4" t="inlineStr"/>
-      <c r="O60" s="4" t="inlineStr">
+      <c r="O60" s="4" t="inlineStr"/>
+      <c r="P60" s="4" t="inlineStr">
         <is>
           <t>https://hnu.edu.eg</t>
         </is>
       </c>
-      <c r="P60" s="4" t="inlineStr"/>
-      <c r="Q60" s="4" t="inlineStr">
+      <c r="Q60" s="4" t="inlineStr"/>
+      <c r="R60" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R60" s="4" t="inlineStr"/>
       <c r="S60" s="4" t="inlineStr"/>
       <c r="T60" s="4" t="inlineStr"/>
-      <c r="U60" s="4" t="n">
+      <c r="U60" s="4" t="inlineStr"/>
+      <c r="V60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V60" s="4" t="inlineStr"/>
       <c r="W60" s="4" t="inlineStr"/>
       <c r="X60" s="4" t="inlineStr"/>
       <c r="Y60" s="4" t="inlineStr"/>
       <c r="Z60" s="4" t="inlineStr"/>
       <c r="AA60" s="4" t="inlineStr"/>
-      <c r="AB60" s="4" t="n">
+      <c r="AB60" s="4" t="inlineStr"/>
+      <c r="AC60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC60" s="8" t="inlineStr">
+      <c r="AD60" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD60" s="4" t="inlineStr"/>
-      <c r="AE60" s="4" t="inlineStr">
+      <c r="AE60" s="4" t="inlineStr"/>
+      <c r="AF60" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF60" s="4" t="inlineStr">
+      <c r="AG60" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт hnu.edu.eg недоступен (503 / сброс соединения, проверка 04.10.2026) — руководство и контакты HNU НЕ проверены
 • Национальный (ахлия) некоммерческий университет, выделен из Helwan University; материнский вуз переименован в Capital University (جامعة العاصمة, capu.edu.eg). На capu.edu.eg (новость 30.09.2026) подтверждено: президент Capital University — проф. Эль-Сайед Кандиль, он курирует проекты HNU (учебная больница HNU); генеральный секретарь (أمين) HNU — Сайед Атта. Имя президента HNU не найдено
@@ -10857,7 +11204,7 @@
 • Перепроверка: Сайт hnu.edu.eg недоступен; по capu.edu.eg уточнены связь с Capital University и контакты его международного офиса, руководитель HNU не найден</t>
         </is>
       </c>
-      <c r="AG60" s="4" t="inlineStr">
+      <c r="AH60" s="4" t="inlineStr">
         <is>
           <t>• Https://www.wikidata.org/wiki/Q105600196
 • Https://ar.wikipedia.org/wiki/جامعة_حلوان_الأهلية
@@ -10865,12 +11212,12 @@
 • Https://capu.edu.eg/index.php/ar/about-ar/agreements-and-partnerships/office-of-international-relations</t>
         </is>
       </c>
-      <c r="AH60" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI60" s="4" t="inlineStr"/>
+      <c r="AI60" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -10910,60 +11257,65 @@
       <c r="I61" s="4" t="inlineStr"/>
       <c r="J61" s="4" t="inlineStr"/>
       <c r="K61" s="4" t="inlineStr"/>
-      <c r="L61" s="4" t="inlineStr"/>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M61" s="4" t="inlineStr"/>
       <c r="N61" s="4" t="inlineStr"/>
       <c r="O61" s="4" t="inlineStr"/>
       <c r="P61" s="4" t="inlineStr"/>
-      <c r="Q61" s="4" t="inlineStr">
+      <c r="Q61" s="4" t="inlineStr"/>
+      <c r="R61" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R61" s="4" t="inlineStr"/>
       <c r="S61" s="4" t="inlineStr"/>
       <c r="T61" s="4" t="inlineStr"/>
-      <c r="U61" s="4" t="n">
+      <c r="U61" s="4" t="inlineStr"/>
+      <c r="V61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="4" t="inlineStr"/>
       <c r="W61" s="4" t="inlineStr"/>
       <c r="X61" s="4" t="inlineStr"/>
       <c r="Y61" s="4" t="inlineStr"/>
       <c r="Z61" s="4" t="inlineStr"/>
       <c r="AA61" s="4" t="inlineStr"/>
-      <c r="AB61" s="4" t="n">
+      <c r="AB61" s="4" t="inlineStr"/>
+      <c r="AC61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC61" s="8" t="inlineStr">
+      <c r="AD61" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD61" s="4" t="inlineStr"/>
-      <c r="AE61" s="4" t="inlineStr">
+      <c r="AE61" s="4" t="inlineStr"/>
+      <c r="AF61" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF61" s="4" t="inlineStr">
+      <c r="AG61" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт не найден/недоступен; веб-поиск исчерпан — все контакты требуют ручной проверки
 • Создан в 2020–2021 на базе филиала South Valley University в Хургаде (по арабской Википедии)
 • Перепроверка: Официальный домен не найден (варианты hurghada.edu.eg, hurghadauniv.edu.eg и др. недоступны); сайт Минвысобразования (mohesr.gov.eg, 30.08.2025) подтверждает существование вуза (утверждение фирменного стиля Хургадского университета Высшим советом университетов), но руководителя и контактов не даёт; данные не изменены</t>
         </is>
       </c>
-      <c r="AG61" s="4" t="inlineStr">
+      <c r="AH61" s="4" t="inlineStr">
         <is>
           <t>Https://ar.wikipedia.org/wiki/جامعة_الغردقة</t>
         </is>
       </c>
-      <c r="AH61" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI61" s="4" t="inlineStr"/>
+      <c r="AI61" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -11027,70 +11379,75 @@
 Обращение: Dear Prof. Eid,</t>
         </is>
       </c>
-      <c r="L62" s="4" t="inlineStr"/>
-      <c r="M62" s="4" t="inlineStr">
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M62" s="4" t="inlineStr"/>
+      <c r="N62" s="4" t="inlineStr">
         <is>
           <t>president@kfs.edu.eg</t>
         </is>
       </c>
-      <c r="N62" s="4" t="inlineStr">
+      <c r="O62" s="4" t="inlineStr">
         <is>
           <t>+20 47 3109590; +20 47 3109591</t>
         </is>
       </c>
-      <c r="O62" s="4" t="inlineStr">
+      <c r="P62" s="4" t="inlineStr">
         <is>
           <t>https://www.kfs.edu.eg</t>
         </is>
       </c>
-      <c r="P62" s="4" t="inlineStr">
+      <c r="Q62" s="4" t="inlineStr">
         <is>
           <t>Prof. Yehia Zakaria Ahmed Eid</t>
         </is>
       </c>
-      <c r="Q62" s="4" t="inlineStr">
+      <c r="R62" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R62" s="4" t="inlineStr"/>
       <c r="S62" s="4" t="inlineStr"/>
       <c r="T62" s="4" t="inlineStr"/>
-      <c r="U62" s="4" t="n">
+      <c r="U62" s="4" t="inlineStr"/>
+      <c r="V62" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="4" t="inlineStr"/>
       <c r="W62" s="4" t="inlineStr"/>
       <c r="X62" s="4" t="inlineStr"/>
       <c r="Y62" s="4" t="inlineStr"/>
       <c r="Z62" s="4" t="inlineStr"/>
       <c r="AA62" s="4" t="inlineStr"/>
-      <c r="AB62" s="4" t="n">
+      <c r="AB62" s="4" t="inlineStr"/>
+      <c r="AC62" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC62" s="8" t="inlineStr">
+      <c r="AD62" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD62" s="4" t="inlineStr">
+      <c r="AE62" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE62" s="4" t="inlineStr">
+      <c r="AF62" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF62" s="4" t="inlineStr">
+      <c r="AG62" s="4" t="inlineStr">
         <is>
           <t>• Отдельного e-mail международного офиса нет; президентский e-mail указан как основной контакт
 • Директор Управления международных связей — Prof. Reda Abdel-Monsef Ahmed (أ.د. رضا عبدالمنصف أحمد), дата страницы не указана — можно поставить в копию через президента
 • Main_fields — по типичному профилю; на сайте детальный список факультетов не сверялся</t>
         </is>
       </c>
-      <c r="AG62" s="4" t="inlineStr">
+      <c r="AH62" s="4" t="inlineStr">
         <is>
           <t>• Https://www.kfs.edu.eg/
 • Http://www.kfs.edu.eg/interoffice/
@@ -11098,12 +11455,12 @@
 • Https://www.timeshighereducation.com/world-university-rankings/kafrelsheikh-university</t>
         </is>
       </c>
-      <c r="AH62" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI62" s="4" t="inlineStr"/>
+      <c r="AI62" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -11166,59 +11523,64 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L63" s="4" t="inlineStr"/>
-      <c r="M63" s="4" t="inlineStr">
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M63" s="4" t="inlineStr"/>
+      <c r="N63" s="4" t="inlineStr">
         <is>
           <t>info@ksiu.edu.eg</t>
         </is>
       </c>
-      <c r="N63" s="4" t="inlineStr"/>
-      <c r="O63" s="4" t="inlineStr">
+      <c r="O63" s="4" t="inlineStr"/>
+      <c r="P63" s="4" t="inlineStr">
         <is>
           <t>https://ksiu.edu.eg</t>
         </is>
       </c>
-      <c r="P63" s="4" t="inlineStr">
+      <c r="Q63" s="4" t="inlineStr">
         <is>
           <t>Prof. Ashraf S. Hussein</t>
         </is>
       </c>
-      <c r="Q63" s="4" t="inlineStr">
+      <c r="R63" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R63" s="4" t="inlineStr"/>
       <c r="S63" s="4" t="inlineStr"/>
       <c r="T63" s="4" t="inlineStr"/>
-      <c r="U63" s="4" t="n">
+      <c r="U63" s="4" t="inlineStr"/>
+      <c r="V63" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="4" t="inlineStr"/>
       <c r="W63" s="4" t="inlineStr"/>
       <c r="X63" s="4" t="inlineStr"/>
       <c r="Y63" s="4" t="inlineStr"/>
       <c r="Z63" s="4" t="inlineStr"/>
       <c r="AA63" s="4" t="inlineStr"/>
-      <c r="AB63" s="4" t="n">
+      <c r="AB63" s="4" t="inlineStr"/>
+      <c r="AC63" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC63" s="8" t="inlineStr">
+      <c r="AD63" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD63" s="4" t="inlineStr">
+      <c r="AE63" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE63" s="4" t="inlineStr">
+      <c r="AF63" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF63" s="4" t="inlineStr">
+      <c r="AG63" s="4" t="inlineStr">
         <is>
           <t>• THE2027: только статус Reporter (без ранга)
 • Сайт ksiu.edu.eg недоступен (503); данные из поисковых выдержек официального сайта, дата не подтверждена
@@ -11227,19 +11589,19 @@
 • Перепроверка: 04.10.2026: ksiu.edu.eg недоступен (ошибка TLS-цепочки, en.-поддомен — 502); по поиску президент проф. Ashraf Hussein указан на сайте — данные не изменены</t>
         </is>
       </c>
-      <c r="AG63" s="4" t="inlineStr">
+      <c r="AH63" s="4" t="inlineStr">
         <is>
           <t>• Https://ksiu.edu.eg/
 • Https://ksiu.edu.eg/contact/
 • Https://ksiu.edu.eg/teams/prof-ashraf-s-hussein/</t>
         </is>
       </c>
-      <c r="AH63" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI63" s="4" t="inlineStr"/>
+      <c r="AI63" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -11291,51 +11653,56 @@
       </c>
       <c r="J64" s="4" t="inlineStr"/>
       <c r="K64" s="4" t="inlineStr"/>
-      <c r="L64" s="4" t="inlineStr"/>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M64" s="4" t="inlineStr"/>
       <c r="N64" s="4" t="inlineStr"/>
-      <c r="O64" s="4" t="inlineStr">
+      <c r="O64" s="4" t="inlineStr"/>
+      <c r="P64" s="4" t="inlineStr">
         <is>
           <t>https://www.mansnu.edu.eg</t>
         </is>
       </c>
-      <c r="P64" s="4" t="inlineStr"/>
-      <c r="Q64" s="4" t="inlineStr">
+      <c r="Q64" s="4" t="inlineStr"/>
+      <c r="R64" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R64" s="4" t="inlineStr"/>
-      <c r="S64" s="4" t="inlineStr">
+      <c r="S64" s="4" t="inlineStr"/>
+      <c r="T64" s="4" t="inlineStr">
         <is>
           <t>THE2027 Reporter (unranked)</t>
         </is>
       </c>
-      <c r="T64" s="4" t="inlineStr"/>
-      <c r="U64" s="4" t="n">
+      <c r="U64" s="4" t="inlineStr"/>
+      <c r="V64" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V64" s="4" t="inlineStr"/>
       <c r="W64" s="4" t="inlineStr"/>
       <c r="X64" s="4" t="inlineStr"/>
       <c r="Y64" s="4" t="inlineStr"/>
       <c r="Z64" s="4" t="inlineStr"/>
       <c r="AA64" s="4" t="inlineStr"/>
-      <c r="AB64" s="4" t="n">
+      <c r="AB64" s="4" t="inlineStr"/>
+      <c r="AC64" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC64" s="8" t="inlineStr">
+      <c r="AD64" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD64" s="4" t="inlineStr"/>
-      <c r="AE64" s="4" t="inlineStr">
+      <c r="AE64" s="4" t="inlineStr"/>
+      <c r="AF64" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF64" s="4" t="inlineStr">
+      <c r="AG64" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт mansnu.edu.eg недоступен (503 / блокировка прокси); поисковая квота исчерпана — руководство и контакты НЕ проверены
 • Национальный (ахлия) некоммерческий университет при Mansoura University (кампус 42 федданa в Новой Мансуре); обычно возглавляется президентом Mansoura University — уточнить
@@ -11344,18 +11711,18 @@
 • Перепроверка: Сайт mansnu.edu.eg (www и без www) недоступен — таймаут через curl и reader-сервис 04.10.2026; данные не изменены</t>
         </is>
       </c>
-      <c r="AG64" s="4" t="inlineStr">
+      <c r="AH64" s="4" t="inlineStr">
         <is>
           <t>• Https://www.wikidata.org/wiki/Q114817413
 • Https://ar.wikipedia.org/wiki/جامعة_المنصورة_الأهلية</t>
         </is>
       </c>
-      <c r="AH64" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI64" s="4" t="inlineStr"/>
+      <c r="AI64" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -11408,55 +11775,60 @@
       </c>
       <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr"/>
-      <c r="L65" s="4" t="inlineStr"/>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M65" s="4" t="inlineStr"/>
-      <c r="N65" s="4" t="inlineStr">
+      <c r="N65" s="4" t="inlineStr"/>
+      <c r="O65" s="4" t="inlineStr">
         <is>
           <t>+20 46 4948489</t>
         </is>
       </c>
-      <c r="O65" s="4" t="inlineStr">
+      <c r="P65" s="4" t="inlineStr">
         <is>
           <t>https://www.mau.edu.eg</t>
         </is>
       </c>
-      <c r="P65" s="4" t="inlineStr">
+      <c r="Q65" s="4" t="inlineStr">
         <is>
           <t>Prof. Amr Ahmed El-Masry</t>
         </is>
       </c>
-      <c r="Q65" s="4" t="inlineStr">
+      <c r="R65" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R65" s="4" t="inlineStr"/>
       <c r="S65" s="4" t="inlineStr"/>
       <c r="T65" s="4" t="inlineStr"/>
-      <c r="U65" s="4" t="n">
+      <c r="U65" s="4" t="inlineStr"/>
+      <c r="V65" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="4" t="inlineStr"/>
       <c r="W65" s="4" t="inlineStr"/>
       <c r="X65" s="4" t="inlineStr"/>
       <c r="Y65" s="4" t="inlineStr"/>
       <c r="Z65" s="4" t="inlineStr"/>
       <c r="AA65" s="4" t="inlineStr"/>
-      <c r="AB65" s="4" t="n">
+      <c r="AB65" s="4" t="inlineStr"/>
+      <c r="AC65" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC65" s="8" t="inlineStr">
+      <c r="AD65" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD65" s="4" t="inlineStr"/>
-      <c r="AE65" s="4" t="inlineStr">
+      <c r="AE65" s="4" t="inlineStr"/>
+      <c r="AF65" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF65" s="4" t="inlineStr">
+      <c r="AG65" s="4" t="inlineStr">
         <is>
           <t>• Сайт mau.edu.eg (Blazor, рендер JS) открыт через reader-сервис 04.10.2026: на сайте нет e-mail и телефонов (в т.ч. на странице International Relations) — официальный общий и международный e-mail не найдены (в каталоге WIPO только личный адрес сотрудника)
 • Президент назван «President» (новость 01.10.2026) и «Acting President» (сентябрь 2025/2026) — статус и.о. мог измениться после конкурса (собеседования ноябрь 2025)
@@ -11465,18 +11837,18 @@
 • Перепроверка: Президент Prof. Amr Ahmed El-Masry и адрес кампуса (Km 9) подтверждены на mau.edu.eg 04.10.2026 (новость от 01.10.2026); e-mail на сайте не опубликован; адрес исправлен (было «Km 4»)</t>
         </is>
       </c>
-      <c r="AG65" s="4" t="inlineStr">
+      <c r="AH65" s="4" t="inlineStr">
         <is>
           <t>• Https://www.maspero.eg/our-reporters/2026/09/17/990072/
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=11055</t>
         </is>
       </c>
-      <c r="AH65" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI65" s="4" t="inlineStr"/>
+      <c r="AI65" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -11516,51 +11888,56 @@
       </c>
       <c r="J66" s="4" t="inlineStr"/>
       <c r="K66" s="4" t="inlineStr"/>
-      <c r="L66" s="4" t="inlineStr"/>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M66" s="4" t="inlineStr"/>
       <c r="N66" s="4" t="inlineStr"/>
-      <c r="O66" s="4" t="inlineStr">
-        <is>
-          <t>https://mnu.menofia.education/</t>
-        </is>
-      </c>
-      <c r="P66" s="4" t="inlineStr"/>
-      <c r="Q66" s="4" t="inlineStr">
+      <c r="O66" s="4" t="inlineStr"/>
+      <c r="P66" s="4" t="inlineStr">
+        <is>
+          <t>https://mnu.menofia.education</t>
+        </is>
+      </c>
+      <c r="Q66" s="4" t="inlineStr"/>
+      <c r="R66" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R66" s="4" t="inlineStr"/>
-      <c r="S66" s="4" t="inlineStr">
+      <c r="S66" s="4" t="inlineStr"/>
+      <c r="T66" s="4" t="inlineStr">
         <is>
           <t>THE2027 Reporter (unranked)</t>
         </is>
       </c>
-      <c r="T66" s="4" t="inlineStr"/>
-      <c r="U66" s="4" t="n">
+      <c r="U66" s="4" t="inlineStr"/>
+      <c r="V66" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V66" s="4" t="inlineStr"/>
       <c r="W66" s="4" t="inlineStr"/>
       <c r="X66" s="4" t="inlineStr"/>
       <c r="Y66" s="4" t="inlineStr"/>
       <c r="Z66" s="4" t="inlineStr"/>
       <c r="AA66" s="4" t="inlineStr"/>
-      <c r="AB66" s="4" t="n">
+      <c r="AB66" s="4" t="inlineStr"/>
+      <c r="AC66" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC66" s="8" t="inlineStr">
+      <c r="AD66" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD66" s="4" t="inlineStr"/>
-      <c r="AE66" s="4" t="inlineStr">
+      <c r="AE66" s="4" t="inlineStr"/>
+      <c r="AF66" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF66" s="4" t="inlineStr">
+      <c r="AG66" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт недоступен из нашей сети (503/таймаут), поиск исчерпан — контакты и руководитель не верифицированы; требуется ручная проверка
 • Описание в профиле THE скопировано с государственного Menoufia University — не использовать его для профиля
@@ -11568,17 +11945,17 @@
 • Перепроверка: Сайты mnu.menofia.education, mnu.edu.eg и menofia.edu.eg недоступны (04.10.2026, сброс соединения); данные не изменены</t>
         </is>
       </c>
-      <c r="AG66" s="4" t="inlineStr">
+      <c r="AH66" s="4" t="inlineStr">
         <is>
           <t>Https://www.timeshighereducation.com/world-university-rankings/menoufia-national-university</t>
         </is>
       </c>
-      <c r="AH66" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI66" s="4" t="inlineStr"/>
+      <c r="AI66" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -11641,59 +12018,64 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L67" s="4" t="inlineStr"/>
-      <c r="M67" s="4" t="inlineStr">
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="inlineStr"/>
+      <c r="N67" s="4" t="inlineStr">
         <is>
           <t>miu@miuegypt.edu.eg</t>
         </is>
       </c>
-      <c r="N67" s="4" t="inlineStr"/>
-      <c r="O67" s="4" t="inlineStr">
+      <c r="O67" s="4" t="inlineStr"/>
+      <c r="P67" s="4" t="inlineStr">
         <is>
           <t>https://www.miuegypt.edu.eg</t>
         </is>
       </c>
-      <c r="P67" s="4" t="inlineStr">
+      <c r="Q67" s="4" t="inlineStr">
         <is>
           <t>Prof. Mahasen Farghaly</t>
         </is>
       </c>
-      <c r="Q67" s="4" t="inlineStr">
+      <c r="R67" s="4" t="inlineStr">
         <is>
           <t>Acting President</t>
         </is>
       </c>
-      <c r="R67" s="4" t="inlineStr"/>
       <c r="S67" s="4" t="inlineStr"/>
       <c r="T67" s="4" t="inlineStr"/>
-      <c r="U67" s="4" t="n">
+      <c r="U67" s="4" t="inlineStr"/>
+      <c r="V67" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="4" t="inlineStr"/>
       <c r="W67" s="4" t="inlineStr"/>
       <c r="X67" s="4" t="inlineStr"/>
       <c r="Y67" s="4" t="inlineStr"/>
       <c r="Z67" s="4" t="inlineStr"/>
       <c r="AA67" s="4" t="inlineStr"/>
-      <c r="AB67" s="4" t="n">
+      <c r="AB67" s="4" t="inlineStr"/>
+      <c r="AC67" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC67" s="8" t="inlineStr">
+      <c r="AD67" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD67" s="4" t="inlineStr">
+      <c r="AE67" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE67" s="4" t="inlineStr">
+      <c r="AF67" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AF67" s="4" t="inlineStr">
+      <c r="AG67" s="4" t="inlineStr">
         <is>
           <t>• THE2027: только статус Reporter (без ранга)
 • Руководитель — и.о. президента (июль 2026); председатель попечительского совета — Mohamed El Rashidi
@@ -11701,7 +12083,7 @@
 • Спутниковой активности не найдено</t>
         </is>
       </c>
-      <c r="AG67" s="4" t="inlineStr">
+      <c r="AH67" s="4" t="inlineStr">
         <is>
           <t>• Https://www.miuegypt.edu.eg/
 • Https://www.miuegypt.edu.eg/contact-us/
@@ -11709,12 +12091,12 @@
 • Https://www.miuegypt.edu.eg/computer-science-graduation-projects-expo-2026/</t>
         </is>
       </c>
-      <c r="AH67" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI67" s="4" t="inlineStr"/>
+      <c r="AI67" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -11777,59 +12159,64 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L68" s="4" t="inlineStr"/>
-      <c r="M68" s="4" t="inlineStr">
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="inlineStr"/>
+      <c r="N68" s="4" t="inlineStr">
         <is>
           <t>Info@mti.edu.eg</t>
         </is>
       </c>
-      <c r="N68" s="4" t="inlineStr"/>
-      <c r="O68" s="4" t="inlineStr">
+      <c r="O68" s="4" t="inlineStr"/>
+      <c r="P68" s="4" t="inlineStr">
         <is>
           <t>https://www.mti.edu.eg</t>
         </is>
       </c>
-      <c r="P68" s="4" t="inlineStr">
+      <c r="Q68" s="4" t="inlineStr">
         <is>
           <t>Prof. Olfat Kamel</t>
         </is>
       </c>
-      <c r="Q68" s="4" t="inlineStr">
+      <c r="R68" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R68" s="4" t="inlineStr"/>
       <c r="S68" s="4" t="inlineStr"/>
       <c r="T68" s="4" t="inlineStr"/>
-      <c r="U68" s="4" t="n">
+      <c r="U68" s="4" t="inlineStr"/>
+      <c r="V68" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="4" t="inlineStr"/>
       <c r="W68" s="4" t="inlineStr"/>
       <c r="X68" s="4" t="inlineStr"/>
       <c r="Y68" s="4" t="inlineStr"/>
       <c r="Z68" s="4" t="inlineStr"/>
       <c r="AA68" s="4" t="inlineStr"/>
-      <c r="AB68" s="4" t="n">
+      <c r="AB68" s="4" t="inlineStr"/>
+      <c r="AC68" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC68" s="8" t="inlineStr">
+      <c r="AD68" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD68" s="4" t="inlineStr">
+      <c r="AE68" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE68" s="4" t="inlineStr">
+      <c r="AF68" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF68" s="4" t="inlineStr">
+      <c r="AG68" s="4" t="inlineStr">
         <is>
           <t>• Президент указан на текущем арабском портале (послание президента), но англ. страница датирована 2015 г. — актуальность желательно подтвердить
 • Телефон: только горячая линия 19041
@@ -11837,7 +12224,7 @@
 • Спутниковой активности не найдено</t>
         </is>
       </c>
-      <c r="AG68" s="4" t="inlineStr">
+      <c r="AH68" s="4" t="inlineStr">
         <is>
           <t>• Https://mti.edu.eg/default1.aspx
 • Https://mti.edu.eg/629748
@@ -11845,12 +12232,12 @@
 • Https://ar.mti.edu.eg/default.aspx</t>
         </is>
       </c>
-      <c r="AH68" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI68" s="4" t="inlineStr"/>
+      <c r="AI68" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -11903,55 +12290,60 @@
       </c>
       <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr"/>
-      <c r="L69" s="4" t="inlineStr"/>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M69" s="4" t="inlineStr"/>
-      <c r="N69" s="4" t="inlineStr">
+      <c r="N69" s="4" t="inlineStr"/>
+      <c r="O69" s="4" t="inlineStr">
         <is>
           <t>+20 19206</t>
         </is>
       </c>
-      <c r="O69" s="4" t="inlineStr">
+      <c r="P69" s="4" t="inlineStr">
         <is>
           <t>https://www.nub.edu.eg</t>
         </is>
       </c>
-      <c r="P69" s="4" t="inlineStr">
+      <c r="Q69" s="4" t="inlineStr">
         <is>
           <t>Prof. Hossam El-Malahy</t>
         </is>
       </c>
-      <c r="Q69" s="4" t="inlineStr">
+      <c r="R69" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R69" s="4" t="inlineStr"/>
       <c r="S69" s="4" t="inlineStr"/>
       <c r="T69" s="4" t="inlineStr"/>
-      <c r="U69" s="4" t="n">
+      <c r="U69" s="4" t="inlineStr"/>
+      <c r="V69" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="4" t="inlineStr"/>
       <c r="W69" s="4" t="inlineStr"/>
       <c r="X69" s="4" t="inlineStr"/>
       <c r="Y69" s="4" t="inlineStr"/>
       <c r="Z69" s="4" t="inlineStr"/>
       <c r="AA69" s="4" t="inlineStr"/>
-      <c r="AB69" s="4" t="n">
+      <c r="AB69" s="4" t="inlineStr"/>
+      <c r="AC69" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC69" s="8" t="inlineStr">
+      <c r="AD69" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD69" s="4" t="inlineStr"/>
-      <c r="AE69" s="4" t="inlineStr">
+      <c r="AE69" s="4" t="inlineStr"/>
+      <c r="AF69" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF69" s="4" t="inlineStr">
+      <c r="AG69" s="4" t="inlineStr">
         <is>
           <t>• E-mail на сайте не опубликован (только веб-форма); телефон — короткий номер 19206, факс +20 82 2284688
 • Президент Prof. Hossam El-Malahy — советник Президента Египта по высшему образованию и науке, член Сената; одновременно президент Badya University — влиятельный адресат
@@ -11959,19 +12351,19 @@
 • Арабское название (جامعة النهضة) не подтверждено на сайте</t>
         </is>
       </c>
-      <c r="AG69" s="4" t="inlineStr">
+      <c r="AH69" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nub.edu.eg/
 • Https://www.nub.edu.eg/about/office-of-the-president/
 • Https://www.nub.edu.eg/contact/</t>
         </is>
       </c>
-      <c r="AH69" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI69" s="4" t="inlineStr"/>
+      <c r="AI69" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -12019,51 +12411,56 @@
       </c>
       <c r="J70" s="4" t="inlineStr"/>
       <c r="K70" s="4" t="inlineStr"/>
-      <c r="L70" s="4" t="inlineStr"/>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
+        </is>
+      </c>
       <c r="M70" s="4" t="inlineStr"/>
       <c r="N70" s="4" t="inlineStr"/>
-      <c r="O70" s="4" t="inlineStr">
+      <c r="O70" s="4" t="inlineStr"/>
+      <c r="P70" s="4" t="inlineStr">
         <is>
           <t>https://nctu.edu.eg</t>
         </is>
       </c>
-      <c r="P70" s="4" t="inlineStr">
+      <c r="Q70" s="4" t="inlineStr">
         <is>
           <t>Dr. Tarek Abdel Malak (د. طارق عبد الملاك)</t>
         </is>
       </c>
-      <c r="Q70" s="4" t="inlineStr">
+      <c r="R70" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R70" s="4" t="inlineStr"/>
       <c r="S70" s="4" t="inlineStr"/>
       <c r="T70" s="4" t="inlineStr"/>
-      <c r="U70" s="4" t="n">
+      <c r="U70" s="4" t="inlineStr"/>
+      <c r="V70" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V70" s="4" t="inlineStr"/>
       <c r="W70" s="4" t="inlineStr"/>
       <c r="X70" s="4" t="inlineStr"/>
       <c r="Y70" s="4" t="inlineStr"/>
       <c r="Z70" s="4" t="inlineStr"/>
       <c r="AA70" s="4" t="inlineStr"/>
-      <c r="AB70" s="4" t="n">
+      <c r="AB70" s="4" t="inlineStr"/>
+      <c r="AC70" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC70" s="8" t="inlineStr">
+      <c r="AD70" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD70" s="4" t="inlineStr"/>
-      <c r="AE70" s="4" t="inlineStr">
+      <c r="AE70" s="4" t="inlineStr"/>
+      <c r="AF70" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF70" s="4" t="inlineStr">
+      <c r="AG70" s="4" t="inlineStr">
         <is>
           <t>• Государственный технологический университет (прикладное технологическое образование); подтверждён только факультет технологий промышленности и энергетики (по арабской Википедии)
 • Космической активности не проверено
@@ -12072,18 +12469,18 @@
 • Перепроверка: Сайт недоступен; по СМИ 09.2026 добавлен президент д-р Тарек Абдель Малак; контактов по-прежнему нет</t>
         </is>
       </c>
-      <c r="AG70" s="4" t="inlineStr">
+      <c r="AH70" s="4" t="inlineStr">
         <is>
           <t>• Https://www.wikidata.org/wiki/Q100257877
 • Https://ar.wikipedia.org/wiki/جامعة_القاهرة_الجديدة_التكنولوجية</t>
         </is>
       </c>
-      <c r="AH70" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI70" s="4" t="inlineStr"/>
+      <c r="AI70" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -12147,63 +12544,68 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L71" s="4" t="inlineStr"/>
-      <c r="M71" s="4" t="inlineStr">
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="inlineStr"/>
+      <c r="N71" s="4" t="inlineStr">
         <is>
           <t>enrollment@ngu.edu.eg</t>
         </is>
       </c>
-      <c r="N71" s="4" t="inlineStr">
+      <c r="O71" s="4" t="inlineStr">
         <is>
           <t>+20 106 829 4242</t>
         </is>
       </c>
-      <c r="O71" s="4" t="inlineStr">
+      <c r="P71" s="4" t="inlineStr">
         <is>
           <t>https://ngu.edu.eg</t>
         </is>
       </c>
-      <c r="P71" s="4" t="inlineStr">
+      <c r="Q71" s="4" t="inlineStr">
         <is>
           <t>Prof. A. Sameh Farid</t>
         </is>
       </c>
-      <c r="Q71" s="4" t="inlineStr">
+      <c r="R71" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R71" s="4" t="inlineStr"/>
       <c r="S71" s="4" t="inlineStr"/>
       <c r="T71" s="4" t="inlineStr"/>
-      <c r="U71" s="4" t="n">
+      <c r="U71" s="4" t="inlineStr"/>
+      <c r="V71" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V71" s="4" t="inlineStr"/>
       <c r="W71" s="4" t="inlineStr"/>
       <c r="X71" s="4" t="inlineStr"/>
       <c r="Y71" s="4" t="inlineStr"/>
       <c r="Z71" s="4" t="inlineStr"/>
       <c r="AA71" s="4" t="inlineStr"/>
-      <c r="AB71" s="4" t="n">
+      <c r="AB71" s="4" t="inlineStr"/>
+      <c r="AC71" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC71" s="8" t="inlineStr">
+      <c r="AD71" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD71" s="4" t="inlineStr">
+      <c r="AE71" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE71" s="4" t="inlineStr">
+      <c r="AF71" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF71" s="4" t="inlineStr">
+      <c r="AG71" s="4" t="inlineStr">
         <is>
           <t>• Общего e-mail / e-mail офиса президента нет; указан ящик приёмной комиссии enrollment@ngu.edu.eg (единственный, кроме careers@) — лучше дополнительно связаться по телефону
 • Президент-основатель Prof. A. Sameh Farid — бывший министр здравоохранения Египта (2011)
@@ -12213,19 +12615,19 @@
 • Арабское название (جامعة نيو جيزة) не подтверждено на сайте</t>
         </is>
       </c>
-      <c r="AG71" s="4" t="inlineStr">
+      <c r="AH71" s="4" t="inlineStr">
         <is>
           <t>• Https://ngu.edu.eg/
 • Https://ngu.edu.eg/about-ngu/
 • Https://ngu.edu.eg/contact</t>
         </is>
       </c>
-      <c r="AH71" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI71" s="4" t="inlineStr"/>
+      <c r="AI71" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -12283,63 +12685,68 @@
 Обращение: Dear Prof. El-Domany,</t>
         </is>
       </c>
-      <c r="L72" s="4" t="inlineStr"/>
-      <c r="M72" s="4" t="inlineStr">
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>ящик общий</t>
+        </is>
+      </c>
+      <c r="M72" s="4" t="inlineStr"/>
+      <c r="N72" s="4" t="inlineStr">
         <is>
           <t>info@oust.edu.eg</t>
         </is>
       </c>
-      <c r="N72" s="4" t="inlineStr">
+      <c r="O72" s="4" t="inlineStr">
         <is>
           <t>16308 (hotline)</t>
         </is>
       </c>
-      <c r="O72" s="4" t="inlineStr">
+      <c r="P72" s="4" t="inlineStr">
         <is>
           <t>https://oust.edu.eg</t>
         </is>
       </c>
-      <c r="P72" s="4" t="inlineStr">
+      <c r="Q72" s="4" t="inlineStr">
         <is>
           <t>Prof. Ramadan El-Domany</t>
         </is>
       </c>
-      <c r="Q72" s="4" t="inlineStr">
+      <c r="R72" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R72" s="4" t="inlineStr"/>
       <c r="S72" s="4" t="inlineStr"/>
       <c r="T72" s="4" t="inlineStr"/>
-      <c r="U72" s="4" t="n">
+      <c r="U72" s="4" t="inlineStr"/>
+      <c r="V72" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V72" s="4" t="inlineStr"/>
       <c r="W72" s="4" t="inlineStr"/>
       <c r="X72" s="4" t="inlineStr"/>
       <c r="Y72" s="4" t="inlineStr"/>
       <c r="Z72" s="4" t="inlineStr"/>
       <c r="AA72" s="4" t="inlineStr"/>
-      <c r="AB72" s="4" t="n">
+      <c r="AB72" s="4" t="inlineStr"/>
+      <c r="AC72" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC72" s="8" t="inlineStr">
+      <c r="AD72" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD72" s="4" t="inlineStr">
+      <c r="AE72" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE72" s="4" t="inlineStr">
+      <c r="AF72" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF72" s="4" t="inlineStr">
+      <c r="AG72" s="4" t="inlineStr">
         <is>
           <t>• Форма собственности на сайте не указана (вероятно частный — не подтверждено), поле оставлено пустым
 • На сайте указан только короткий номер горячей линии 16308 (без +20) и адрес «Rd. 21 Cairo-Belbeis» (вероятно, 21-й км шоссе Каир–Бильбейс)
@@ -12347,19 +12754,19 @@
 • В THE 2027 — статус Reporter (без ранга)</t>
         </is>
       </c>
-      <c r="AG72" s="4" t="inlineStr">
+      <c r="AH72" s="4" t="inlineStr">
         <is>
           <t>• Https://oust.edu.eg/en
 • Https://oust.edu.eg/en/pages/about-oust
 • Https://oust.edu.eg/en/posts/prof-dr-ramadan-el-domany-university-president-joined-a-tour-with-the-student-welfare-department-to-follow-up-on-student-activities-and-interact-with-students</t>
         </is>
       </c>
-      <c r="AH72" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI72" s="4" t="inlineStr"/>
+      <c r="AI72" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -12418,66 +12825,71 @@
 Обращение: Dear Director of International Relations,</t>
         </is>
       </c>
-      <c r="L73" s="4" t="inlineStr"/>
-      <c r="M73" s="4" t="inlineStr">
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="inlineStr"/>
+      <c r="N73" s="4" t="inlineStr">
         <is>
           <t>Info@su.edu.eg</t>
         </is>
       </c>
-      <c r="N73" s="4" t="inlineStr"/>
-      <c r="O73" s="4" t="inlineStr">
+      <c r="O73" s="4" t="inlineStr"/>
+      <c r="P73" s="4" t="inlineStr">
         <is>
           <t>https://www.su.edu.eg</t>
         </is>
       </c>
-      <c r="P73" s="4" t="inlineStr">
+      <c r="Q73" s="4" t="inlineStr">
         <is>
           <t>Prof. Gehan Fekry</t>
         </is>
       </c>
-      <c r="Q73" s="4" t="inlineStr">
+      <c r="R73" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R73" s="4" t="inlineStr"/>
       <c r="S73" s="4" t="inlineStr"/>
       <c r="T73" s="4" t="inlineStr"/>
-      <c r="U73" s="4" t="n">
+      <c r="U73" s="4" t="inlineStr"/>
+      <c r="V73" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V73" s="4" t="inlineStr"/>
       <c r="W73" s="4" t="inlineStr"/>
       <c r="X73" s="4" t="inlineStr"/>
       <c r="Y73" s="4" t="inlineStr"/>
       <c r="Z73" s="4" t="inlineStr"/>
       <c r="AA73" s="4" t="inlineStr"/>
-      <c r="AB73" s="4" t="n">
+      <c r="AB73" s="4" t="inlineStr"/>
+      <c r="AC73" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC73" s="8" t="inlineStr">
+      <c r="AD73" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD73" s="4" t="inlineStr">
+      <c r="AE73" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE73" s="4" t="inlineStr">
+      <c r="AF73" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AF73" s="4" t="inlineStr">
+      <c r="AG73" s="4" t="inlineStr">
         <is>
           <t>• Есть Centre for International Cooperation and Foreign Relations (ICFR), но его e-mail/руководитель не найдены
 • Два кампуса: Эль-Ариш и Эль-Кантара (Восточная)
 • Арабское официальное название на сайте не сверено</t>
         </is>
       </c>
-      <c r="AG73" s="4" t="inlineStr">
+      <c r="AH73" s="4" t="inlineStr">
         <is>
           <t>• Https://www.su.edu.eg/
 • Https://www.su.edu.eg/su_glance/
@@ -12485,12 +12897,12 @@
 • Https://www.timeshighereducation.com/world-university-rankings/sinai-university</t>
         </is>
       </c>
-      <c r="AH73" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI73" s="4" t="inlineStr"/>
+      <c r="AI73" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -12552,63 +12964,68 @@
 Обращение: Dear President,</t>
         </is>
       </c>
-      <c r="L74" s="4" t="inlineStr"/>
-      <c r="M74" s="4" t="inlineStr">
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>нет имени: Письмо с нейтральным обращением; имя найти при проверке сайта</t>
+        </is>
+      </c>
+      <c r="M74" s="4" t="inlineStr"/>
+      <c r="N74" s="4" t="inlineStr">
         <is>
           <t>Info@Sphinx.edu.eg</t>
         </is>
       </c>
-      <c r="N74" s="4" t="inlineStr">
+      <c r="O74" s="4" t="inlineStr">
         <is>
           <t>17090 (короткий номер, Египет)</t>
         </is>
       </c>
-      <c r="O74" s="4" t="inlineStr">
+      <c r="P74" s="4" t="inlineStr">
         <is>
           <t>https://sphinx.edu.eg</t>
         </is>
       </c>
-      <c r="P74" s="4" t="inlineStr"/>
-      <c r="Q74" s="4" t="inlineStr">
+      <c r="Q74" s="4" t="inlineStr"/>
+      <c r="R74" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="R74" s="4" t="inlineStr"/>
-      <c r="S74" s="4" t="inlineStr">
+      <c r="S74" s="4" t="inlineStr"/>
+      <c r="T74" s="4" t="inlineStr">
         <is>
           <t>THE2027 Reporter (unranked)</t>
         </is>
       </c>
-      <c r="T74" s="4" t="inlineStr"/>
-      <c r="U74" s="4" t="n">
+      <c r="U74" s="4" t="inlineStr"/>
+      <c r="V74" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="4" t="inlineStr"/>
       <c r="W74" s="4" t="inlineStr"/>
       <c r="X74" s="4" t="inlineStr"/>
       <c r="Y74" s="4" t="inlineStr"/>
       <c r="Z74" s="4" t="inlineStr"/>
       <c r="AA74" s="4" t="inlineStr"/>
-      <c r="AB74" s="4" t="n">
+      <c r="AB74" s="4" t="inlineStr"/>
+      <c r="AC74" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AC74" s="8" t="inlineStr">
+      <c r="AD74" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AD74" s="4" t="inlineStr">
+      <c r="AE74" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AE74" s="4" t="inlineStr">
+      <c r="AF74" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AF74" s="4" t="inlineStr">
+      <c r="AG74" s="4" t="inlineStr">
         <is>
           <t>• Частный университет в Новом Асьюте, создан указом президента №36 от 2019 г
 • Сайт почти пустой (JS, без страниц руководства/контактов) — президент не установлен; поисковая проверка невозможна (исчерпана квота поиска)
@@ -12619,22 +13036,22 @@
 • Перепроверка: Сайт открылся 04.10.2026: подтверждены только Info@Sphinx.edu.eg, номер 17090 и адрес «Regional service zone, New Assiut»; президент на сайте не указан</t>
         </is>
       </c>
-      <c r="AG74" s="4" t="inlineStr">
+      <c r="AH74" s="4" t="inlineStr">
         <is>
           <t>• Https://sphinx.edu.eg/en/home/index
 • Https://ar.wikipedia.org/wiki/جامعة_سفنكس
 • Https://sphinx.edu.eg/en/home/index</t>
         </is>
       </c>
-      <c r="AH74" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AI74" s="4" t="inlineStr"/>
+      <c r="AI74" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AJ74" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI74"/>
+  <autoFilter ref="A1:AJ74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/research/brics_universities/output/BRICS_universities_egypt.xlsx
+++ b/research/brics_universities/output/BRICS_universities_egypt.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Египет" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AJ$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Египет'!$A$1:$AJ$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Волна 1'!$A$1:$AK$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Египет'!$A$1:$AK$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -558,10 +558,10 @@
         <v>63</v>
       </c>
       <c r="G5" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ9"/>
+  <dimension ref="A1:AK9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -676,21 +676,22 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="45" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="45" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="45" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="9" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="55" customWidth="1" min="33" max="33"/>
-    <col width="60" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="24" customWidth="1" min="36" max="36"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="40" customWidth="1" min="27" max="27"/>
+    <col width="45" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="55" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="24" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -801,75 +802,80 @@
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
+          <t>Рейтинг Webometrics (мир)</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
           <t>Запущено КА (спутников)</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Названия запущенных КА (год)</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>КА в разработке</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Наземная станция</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Космические подразделения</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>Партнёрства в космической сфере</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>Космический индекс (0–100)</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>Волна рассылки</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="AJ1" s="3" t="inlineStr">
+      <c r="AK1" s="3" t="inlineStr">
         <is>
           <t>Секретарь парткома (справочно, Китай)</t>
         </is>
@@ -953,35 +959,44 @@
           <t>Acting Chairman (President)</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
+      <c r="V2" s="4" t="inlineStr"/>
+      <c r="W2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>• EgyptSat-1 (2007)
 • NARSSCube-2 (2019)
 • NARSSCube-1 (2019)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>6U agricultural monitoring CubeSat (announced 2023)</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>Satellite data receiving station in Aswan (X-band; Landsat/SPOT reception)</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>Space Technology Division</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr">
+      <c r="AB2" s="4" t="inlineStr">
         <is>
           <t>• Egyptian Space Agency (EgSA)
 • African Space Agency (host country Egypt)
@@ -989,30 +1004,31 @@
 • Cooperation protocols with Egyptian universities (e.g., Beni-Suef National University)</t>
         </is>
       </c>
-      <c r="AB2" s="4" t="inlineStr"/>
-      <c r="AC2" s="4" t="n">
+      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AD2" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="AD2" s="5" t="inlineStr">
+      <c r="AE2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE2" s="4" t="inlineStr"/>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr"/>
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>• Руководитель — и.о. председателя Prof. Abdelaziz Ballal (назначен 3 июня 2026 г.; ранее — Prof. Islam Abou El-Magd)
 • Сайт narss.sci.eg недоступен (503)
 • Официальный общий/международный e-mail не найден (в каталоге WIPO указан только личный адрес сотрудника)
-• EgyptSat-1 создан совместно с КБ «Южное» (Украина); EgyptSat-2 не учтён (построен РКК «Энергия», позже передан EgSA)</t>
-        </is>
-      </c>
-      <c r="AH2" s="4" t="inlineStr">
+• EgyptSat-1 создан совместно с КБ «Южное» (Украина); EgyptSat-2 не учтён (построен РКК «Энергия», позже передан EgSA)
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="inlineStr">
         <is>
           <t>• Https://www.elwatannews.com/news/details/8295289
 • Https://spaceinafrica.com/2023/08/02/bridging-science-and-society-narsss-impact-on-egypts-development-and-technological-progress/
@@ -1021,12 +1037,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI2" s="4" t="inlineStr">
+      <c r="AJ2" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ2" s="4" t="inlineStr"/>
+      <c r="AK2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -1121,26 +1137,43 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="n">
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>• MisrSat-2 (2023)
 • NExSat-1 (2024)
 • SPNeX (2025)</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr"/>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>EgSA ground control station at Egyptian Space City (MisrSat-2 ground segment)</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>• Satellite Assembly, Integration and Testing Center (AITC)
 • Egyptian Space City
@@ -1148,7 +1181,7 @@
 • Egyptian Universities Satellite (CubeSat) programme</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr">
+      <c r="AB3" s="4" t="inlineStr">
         <is>
           <t>• China (MisrSat-2 grant, AITC)
 • Berlin Space Technologies (NExSat-1)
@@ -1158,34 +1191,35 @@
 • China Meteorological Administration (talks, Sep 2026)</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="n">
+      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AD3" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="AD3" s="5" t="inlineStr">
+      <c r="AE3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>• Агентство, не университет; сайт egsa.gov.eg — SPA, контактные данные подгружаются из API (недоступен); адрес/e-mail/телефон с iafastro.org и WIPO TISC
 • CEO д-р инж. Маджид Исмаил назначен 19.08.2025 на 1 год; в сентябре 2026 продолжает исполнять обязанности (новости youm7/elbalad) — проверить продление
 • В подсчёт включены спутники, созданные/собранные EgSA: MisrSat-2 (совместно с Китаем, сборка в AITC), NExSat-1 (с Berlin Space Technologies), SPNeX (6U, полностью египетский). Horus-1/2 (2023), EgyptSat-A, TIBA-1 и др. — закупленные/иностранного производства, не учтены
-• Отдельный e-mail международного отдела не найден — использовать info@egsa.gov.eg</t>
-        </is>
-      </c>
-      <c r="AH3" s="4" t="inlineStr">
+• Отдельный e-mail международного отдела не найден — использовать info@egsa.gov.eg
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="inlineStr">
         <is>
           <t>• Https://www.iafastro.org/membership/all-members/egyptian-space-agency-egsa.html
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=11051
@@ -1201,12 +1235,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI3" s="4" t="inlineStr">
+      <c r="AJ3" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1301,80 +1335,96 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: 801–850</t>
+        </is>
+      </c>
       <c r="T4" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr"/>
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>EgSA educational satellite model (lab satellite for communication, remote sensing and space-environment applications)</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>Ground station simulation unit (educational, supplied under EgSA agreement)</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>EgSA educational satellite laboratory (satellite model, operation/testing simulators, ground-station simulator)</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AB4" s="4" t="inlineStr">
         <is>
           <t>• Egyptian Space Agency (EgSA) – executive agreement on educational satellite lab, 2021
 • EgSA cooperation protocol with universities, 2021
 • JICA / Japanese partner universities consortium</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="n">
+      <c r="AC4" s="4" t="inlineStr"/>
+      <c r="AD4" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="AD4" s="6" t="inlineStr">
+      <c r="AE4" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>• Президент сменился: Prof. Ahmed El-Sabbagh с 1 июля 2026 г. (вместо Prof. Amr Adly)
 • Сайт ejust.edu.eg недоступен (503) — контакты Управления международных связей взяты из поисковой выдержки официальной страницы
 • Также опубликован адрес overseas@ejust.edu.eg
-• Спутников на орбите нет; есть учебная спутниковая лаборатория EgSA</t>
-        </is>
-      </c>
-      <c r="AH4" s="4" t="inlineStr">
+• Спутников на орбите нет; есть учебная спутниковая лаборатория EgSA
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI4" s="4" t="inlineStr">
         <is>
           <t>• Https://ejust.edu.eg/get/news/details/215
 • Https://eng.pressbee.net/show4898887.html
 • Https://www.ejust.edu.eg/regional-international-affairs
-• Https://spaceinafrica.com/2021/03/09/egsa-signs-agreement-with-egypt-japan-university-of-science-and-technology/</t>
-        </is>
-      </c>
-      <c r="AI4" s="4" t="inlineStr">
+• Https://spaceinafrica.com/2021/03/09/egsa-signs-agreement-with-egypt-japan-university-of-science-and-technology/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1483,61 +1533,71 @@
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="n">
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr"/>
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>Educational CubeSat supplied by EgSA under 2021 executive agreement (student training)</t>
         </is>
       </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>AI-powered autonomous optical satellite-tracking ground station (student graduation project, telescope-based)</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>• Faculty of Navigation Science and Space Technology (est. 2016
 • Depts. of Space Navigation, Space Science, Space Communications)</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="AB5" s="4" t="inlineStr">
         <is>
           <t>• Egyptian Space Agency (EgSA) — executive agreement on educational satellite (Feb 2021)
 • NARSS (student visits)</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="n">
+      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AD5" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="AD5" s="6" t="inlineStr">
+      <c r="AE5" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t>• Prof. Tarek Ali — исполняющий обязанности президента (القائم بأعمال رئيس الجامعة), не постоянный президент
 • Единственный в Египте профильный факультет навигации и космических технологий; декан — Prof. Osama Shalabiea (أسامة شلبية)
 • Международный ящик принадлежит Администрации иностранных студентов; профиль партнёрств может быть ограничен
-• Факультет дал интервью китайскому CGTN (сен. 2026) — интерес к сотрудничеству с Китаем/БРИКС</t>
-        </is>
-      </c>
-      <c r="AH5" s="4" t="inlineStr">
+• Факультет дал интервью китайскому CGTN (сен. 2026) — интерес к сотрудничеству с Китаем/БРИКС
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI5" s="4" t="inlineStr">
         <is>
           <t>• Https://www.bsu.edu.eg/ContentSide.aspx?section_id=14&amp;cat_id=1
 • Https://www.bsu.edu.eg/NewsDetails_New.aspx?NID=167895&amp;cat_id=1&amp;lang=ar
@@ -1546,15 +1606,17 @@
 • Https://www.spacescien.bsu.edu.eg/
 • Https://spaceinafrica.com/2021/02/26/egsa-agreement-beni-suef-university-educational-satellite/
 • Https://www.bsu.edu.eg/NewsDetails_New.aspx?NID=167508&amp;cat_id=1&amp;lang=en
-• Https://www.universityworldnews.com/post.php?story=20210406120310615</t>
-        </is>
-      </c>
-      <c r="AI5" s="4" t="inlineStr">
+• Https://www.universityworldnews.com/post.php?story=20210406120310615
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1660,18 +1722,19 @@
         </is>
       </c>
       <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
+      <c r="V6" s="4" t="inlineStr"/>
+      <c r="W6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="X6" s="4" t="inlineStr"/>
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <t>• CU-CubeSat (1U student pico-satellite, Aerospace Dept. graduation project
 • Launch not confirmed)</t>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr"/>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="Z6" s="4" t="inlineStr"/>
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>• Faculty of Engineering, Department of Aerospace Engineering
 • Space System Technology Laboratory (SSTLab)
@@ -1679,39 +1742,40 @@
 • EgSA-supported educational satellite laboratory at Faculty of Engineering</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr">
+      <c r="AB6" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) – agreement on educational satellite laboratory (Egyptian Space Technology Educational Platform), 2022</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="n">
+      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AD6" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="AD6" s="6" t="inlineStr">
+      <c r="AE6" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr">
         <is>
           <t>• Сайты cu.edu.eg и iro.cu.edu.eg недоступны (503/бот-защита) — контакты взяты из поисковых выдержек официальных страниц, требуют перепроверки
 • Общий e-mail канцелярии президента не найден
 • Директор Управления международных связей (Heidi Bayoumy) указан на странице IRO без даты — актуальность на 2026 г. не подтверждена
-• Собственных спутников на орбите не найдено; CU-CubeSat — учебный проект</t>
-        </is>
-      </c>
-      <c r="AH6" s="4" t="inlineStr">
+• Собственных спутников на орбите не найдено; CU-CubeSat — учебный проект
+• Ручная проверка: Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI6" s="4" t="inlineStr">
         <is>
           <t>• Https://cu.edu.eg
 • Https://iro.cu.edu.eg/contact-us
@@ -1721,12 +1785,12 @@
 • Https://www.youm7.com/story/2026/9/6/7537608</t>
         </is>
       </c>
-      <c r="AI6" s="4" t="inlineStr">
+      <c r="AJ6" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1826,7 +1890,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 390</t>
+          <t>QS2027: =390</t>
         </is>
       </c>
       <c r="T7" s="4" t="inlineStr">
@@ -1834,72 +1898,85 @@
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="n">
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr">
+      <c r="X7" s="4" t="inlineStr"/>
+      <c r="Y7" s="4" t="inlineStr">
         <is>
           <t>• AUC CubeSat (student surface-imaging CubeSat project, 2013
 • Current status unknown)</t>
         </is>
       </c>
-      <c r="Y7" s="4" t="inlineStr"/>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="Z7" s="4" t="inlineStr"/>
+      <c r="AA7" s="4" t="inlineStr">
         <is>
           <t>• Astronomical Observatory (School of Sciences and Engineering)
 • AUC CubeSat student team (2013)</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr">
+      <c r="AB7" s="4" t="inlineStr">
         <is>
           <t>Study visits of ECE department to Egyptian Space Agency (EgSA)</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="n">
+      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AD7" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="AD7" s="6" t="inlineStr">
+      <c r="AE7" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr">
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
+      <c r="AH7" s="4" t="inlineStr">
         <is>
           <t>• Частный американский некоммерческий вуз (аккредитация в США); представительство в Нью-Йорке: 420 Lexington Ave., Suite 1644
 • Студенческий проект AUC CubeSat (2013) — запуск не подтверждён
 • Офис президента: Executive Director Enas Fallal (enas.fallal@aucegypt.edu)
-• Менеджер по международным партнёрствам: Iman Nabil (iman.kamel@aucegypt.edu)</t>
-        </is>
-      </c>
-      <c r="AH7" s="4" t="inlineStr">
+• Менеджер по международным партнёрствам: Iman Nabil (iman.kamel@aucegypt.edu)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI7" s="4" t="inlineStr">
         <is>
           <t>• Https://www.aucegypt.edu/about/leadership
 • Https://www.aucegypt.edu/about/leadership/president/office
 • Https://www.aucegypt.edu/academics/international-programs-and-services-office
 • Https://amsat-uk.org/2013/05/26/the-american-university-in-cairo-auc-cubesat/
 • Https://sse.aucegypt.edu/news/visit-egyptian-space-agency-egsa
-• Qianmu.org QS2027 list</t>
-        </is>
-      </c>
-      <c r="AI7" s="4" t="inlineStr">
+• Qianmu.org QS2027 list
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1993,20 +2070,37 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr">
+      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <t>Helwan Satellite Laser Ranging (SLR) station (ILRS network); Kottamia Astronomical Observatory</t>
         </is>
       </c>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>• Solar &amp; Space Department (Solar Lab
 • Space Lab)
@@ -2014,41 +2108,42 @@
 • Egyptian National Seismic Network</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr">
+      <c r="AB8" s="4" t="inlineStr">
         <is>
           <t>• Czech Technical University (FNSPE) – Helwan SLR station
 • ILRS (NASA-coordinated network)
 • Swedish embassy cooperation talks (2026)</t>
         </is>
       </c>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="n">
+      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AD8" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="AD8" s="6" t="inlineStr">
+      <c r="AE8" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE8" s="4" t="inlineStr">
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF8" s="4" t="inlineStr">
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG8" s="4" t="inlineStr">
+      <c r="AH8" s="4" t="inlineStr">
         <is>
           <t>• Отдельного e-mail международного отдела нет; есть раздел «International Relation and Training»
 • Письмо направлять на President@nriag.sci.eg
 • На сайте NRIAG обнаружены спам-ссылки (вероятно, сайт скомпрометирован) — на контакты это не влияет
-• Спутников не создавал; имеет станцию лазерной дальнометрии спутников в Хелуане</t>
-        </is>
-      </c>
-      <c r="AH8" s="4" t="inlineStr">
+• Спутников не создавал; имеет станцию лазерной дальнометрии спутников в Хелуане
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI8" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nriag.sci.eg/
 • Https://www.nriag.sci.eg/contact-us/
@@ -2057,12 +2152,12 @@
 • Http://kfe.fjfi.cvut.cz/~blazej/en/res/prj/helwan.html</t>
         </is>
       </c>
-      <c r="AI8" s="4" t="inlineStr">
+      <c r="AJ8" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -2157,71 +2252,86 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T9" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="n">
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W9" s="4" t="inlineStr"/>
-      <c r="X9" s="4" t="inlineStr">
+      <c r="X9" s="4" t="inlineStr"/>
+      <c r="Y9" s="4" t="inlineStr">
         <is>
           <t>Educational CubeSat supplied by EgSA (executive agreement, ~2021)</t>
         </is>
       </c>
-      <c r="Y9" s="4" t="inlineStr"/>
       <c r="Z9" s="4" t="inlineStr"/>
-      <c r="AA9" s="4" t="inlineStr">
+      <c r="AA9" s="4" t="inlineStr"/>
+      <c r="AB9" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) — educational CubeSat agreement (2021)</t>
         </is>
       </c>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="n">
+      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AD9" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="AD9" s="6" t="inlineStr">
+      <c r="AE9" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE9" s="4" t="inlineStr">
+      <c r="AF9" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF9" s="4" t="inlineStr">
+      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG9" s="4" t="inlineStr">
+      <c r="AH9" s="4" t="inlineStr">
         <is>
           <t>• Отдельного e-mail международного отдела на сайте не найдено — писать в офис президента (President_office@suez.edu.eg); также опубликован тел. +20 2 22621217
 • Участник программы EgSA по образовательным кубсатам (2021); запусков собственного спутника не найдено
-• В QS2027 не найден</t>
-        </is>
-      </c>
-      <c r="AH9" s="4" t="inlineStr">
+• В QS2027 не найден
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI9" s="4" t="inlineStr">
         <is>
           <t>• Https://suez.edu.eg/ar/en/
 • Https://suez.edu.eg/ar/en/contact-us/
-• Https://www.universityworldnews.com/post.php?story=20210406120310615</t>
-        </is>
-      </c>
-      <c r="AI9" s="4" t="inlineStr">
+• Https://www.universityworldnews.com/post.php?story=20210406120310615
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ9"/>
+  <autoFilter ref="A1:AK9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2232,7 +2342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ74"/>
+  <dimension ref="A1:AK74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2256,21 +2366,22 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="13" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="45" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="45" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="45" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="9" customWidth="1" min="30" max="30"/>
-    <col width="12" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="55" customWidth="1" min="33" max="33"/>
-    <col width="60" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
-    <col width="24" customWidth="1" min="36" max="36"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="40" customWidth="1" min="27" max="27"/>
+    <col width="45" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="12" customWidth="1" min="32" max="32"/>
+    <col width="11" customWidth="1" min="33" max="33"/>
+    <col width="55" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="24" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2381,75 +2492,80 @@
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
+          <t>Рейтинг Webometrics (мир)</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
           <t>Запущено КА (спутников)</t>
         </is>
       </c>
-      <c r="W1" s="3" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Названия запущенных КА (год)</t>
         </is>
       </c>
-      <c r="X1" s="3" t="inlineStr">
+      <c r="Y1" s="3" t="inlineStr">
         <is>
           <t>КА в разработке</t>
         </is>
       </c>
-      <c r="Y1" s="3" t="inlineStr">
+      <c r="Z1" s="3" t="inlineStr">
         <is>
           <t>Наземная станция</t>
         </is>
       </c>
-      <c r="Z1" s="3" t="inlineStr">
+      <c r="AA1" s="3" t="inlineStr">
         <is>
           <t>Космические подразделения</t>
         </is>
       </c>
-      <c r="AA1" s="3" t="inlineStr">
+      <c r="AB1" s="3" t="inlineStr">
         <is>
           <t>Партнёрства в космической сфере</t>
         </is>
       </c>
-      <c r="AB1" s="3" t="inlineStr">
+      <c r="AC1" s="3" t="inlineStr">
         <is>
           <t>Санкционные / ограничительные списки (США)</t>
         </is>
       </c>
-      <c r="AC1" s="3" t="inlineStr">
+      <c r="AD1" s="3" t="inlineStr">
         <is>
           <t>Космический индекс (0–100)</t>
         </is>
       </c>
-      <c r="AD1" s="3" t="inlineStr">
+      <c r="AE1" s="3" t="inlineStr">
         <is>
           <t>Волна рассылки</t>
         </is>
       </c>
-      <c r="AE1" s="3" t="inlineStr">
+      <c r="AF1" s="3" t="inlineStr">
         <is>
           <t>Проверка домена e-mail (MX)</t>
         </is>
       </c>
-      <c r="AF1" s="3" t="inlineStr">
+      <c r="AG1" s="3" t="inlineStr">
         <is>
           <t>Достоверность</t>
         </is>
       </c>
-      <c r="AG1" s="3" t="inlineStr">
+      <c r="AH1" s="3" t="inlineStr">
         <is>
           <t>Примечания</t>
         </is>
       </c>
-      <c r="AH1" s="3" t="inlineStr">
+      <c r="AI1" s="3" t="inlineStr">
         <is>
           <t>Источники</t>
         </is>
       </c>
-      <c r="AI1" s="3" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Дата проверки</t>
         </is>
       </c>
-      <c r="AJ1" s="3" t="inlineStr">
+      <c r="AK1" s="3" t="inlineStr">
         <is>
           <t>Секретарь парткома (справочно, Китай)</t>
         </is>
@@ -2533,35 +2649,44 @@
           <t>Acting Chairman (President)</t>
         </is>
       </c>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="n">
+      <c r="V2" s="4" t="inlineStr"/>
+      <c r="W2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W2" s="4" t="inlineStr">
+      <c r="X2" s="4" t="inlineStr">
         <is>
           <t>• EgyptSat-1 (2007)
 • NARSSCube-2 (2019)
 • NARSSCube-1 (2019)</t>
         </is>
       </c>
-      <c r="X2" s="4" t="inlineStr">
+      <c r="Y2" s="4" t="inlineStr">
         <is>
           <t>6U agricultural monitoring CubeSat (announced 2023)</t>
         </is>
       </c>
-      <c r="Y2" s="4" t="inlineStr">
+      <c r="Z2" s="4" t="inlineStr">
         <is>
           <t>Satellite data receiving station in Aswan (X-band; Landsat/SPOT reception)</t>
         </is>
       </c>
-      <c r="Z2" s="4" t="inlineStr">
+      <c r="AA2" s="4" t="inlineStr">
         <is>
           <t>Space Technology Division</t>
         </is>
       </c>
-      <c r="AA2" s="4" t="inlineStr">
+      <c r="AB2" s="4" t="inlineStr">
         <is>
           <t>• Egyptian Space Agency (EgSA)
 • African Space Agency (host country Egypt)
@@ -2569,30 +2694,31 @@
 • Cooperation protocols with Egyptian universities (e.g., Beni-Suef National University)</t>
         </is>
       </c>
-      <c r="AB2" s="4" t="inlineStr"/>
-      <c r="AC2" s="4" t="n">
+      <c r="AC2" s="4" t="inlineStr"/>
+      <c r="AD2" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="AD2" s="5" t="inlineStr">
+      <c r="AE2" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE2" s="4" t="inlineStr"/>
-      <c r="AF2" s="4" t="inlineStr">
+      <c r="AF2" s="4" t="inlineStr"/>
+      <c r="AG2" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG2" s="4" t="inlineStr">
+      <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>• Руководитель — и.о. председателя Prof. Abdelaziz Ballal (назначен 3 июня 2026 г.; ранее — Prof. Islam Abou El-Magd)
 • Сайт narss.sci.eg недоступен (503)
 • Официальный общий/международный e-mail не найден (в каталоге WIPO указан только личный адрес сотрудника)
-• EgyptSat-1 создан совместно с КБ «Южное» (Украина); EgyptSat-2 не учтён (построен РКК «Энергия», позже передан EgSA)</t>
-        </is>
-      </c>
-      <c r="AH2" s="4" t="inlineStr">
+• EgyptSat-1 создан совместно с КБ «Южное» (Украина); EgyptSat-2 не учтён (построен РКК «Энергия», позже передан EgSA)
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="inlineStr">
         <is>
           <t>• Https://www.elwatannews.com/news/details/8295289
 • Https://spaceinafrica.com/2023/08/02/bridging-science-and-society-narsss-impact-on-egypts-development-and-technological-progress/
@@ -2601,12 +2727,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI2" s="4" t="inlineStr">
+      <c r="AJ2" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ2" s="4" t="inlineStr"/>
+      <c r="AK2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -2701,26 +2827,43 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr"/>
-      <c r="U3" s="4" t="inlineStr"/>
-      <c r="V3" s="4" t="n">
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W3" s="4" t="inlineStr">
+      <c r="X3" s="4" t="inlineStr">
         <is>
           <t>• MisrSat-2 (2023)
 • NExSat-1 (2024)
 • SPNeX (2025)</t>
         </is>
       </c>
-      <c r="X3" s="4" t="inlineStr"/>
-      <c r="Y3" s="4" t="inlineStr">
+      <c r="Y3" s="4" t="inlineStr"/>
+      <c r="Z3" s="4" t="inlineStr">
         <is>
           <t>EgSA ground control station at Egyptian Space City (MisrSat-2 ground segment)</t>
         </is>
       </c>
-      <c r="Z3" s="4" t="inlineStr">
+      <c r="AA3" s="4" t="inlineStr">
         <is>
           <t>• Satellite Assembly, Integration and Testing Center (AITC)
 • Egyptian Space City
@@ -2728,7 +2871,7 @@
 • Egyptian Universities Satellite (CubeSat) programme</t>
         </is>
       </c>
-      <c r="AA3" s="4" t="inlineStr">
+      <c r="AB3" s="4" t="inlineStr">
         <is>
           <t>• China (MisrSat-2 grant, AITC)
 • Berlin Space Technologies (NExSat-1)
@@ -2738,34 +2881,35 @@
 • China Meteorological Administration (talks, Sep 2026)</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="n">
+      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AD3" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="AD3" s="5" t="inlineStr">
+      <c r="AE3" s="5" t="inlineStr">
         <is>
           <t>1A</t>
         </is>
       </c>
-      <c r="AE3" s="4" t="inlineStr">
+      <c r="AF3" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF3" s="4" t="inlineStr">
+      <c r="AG3" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG3" s="4" t="inlineStr">
+      <c r="AH3" s="4" t="inlineStr">
         <is>
           <t>• Агентство, не университет; сайт egsa.gov.eg — SPA, контактные данные подгружаются из API (недоступен); адрес/e-mail/телефон с iafastro.org и WIPO TISC
 • CEO д-р инж. Маджид Исмаил назначен 19.08.2025 на 1 год; в сентябре 2026 продолжает исполнять обязанности (новости youm7/elbalad) — проверить продление
 • В подсчёт включены спутники, созданные/собранные EgSA: MisrSat-2 (совместно с Китаем, сборка в AITC), NExSat-1 (с Berlin Space Technologies), SPNeX (6U, полностью египетский). Horus-1/2 (2023), EgyptSat-A, TIBA-1 и др. — закупленные/иностранного производства, не учтены
-• Отдельный e-mail международного отдела не найден — использовать info@egsa.gov.eg</t>
-        </is>
-      </c>
-      <c r="AH3" s="4" t="inlineStr">
+• Отдельный e-mail международного отдела не найден — использовать info@egsa.gov.eg
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="inlineStr">
         <is>
           <t>• Https://www.iafastro.org/membership/all-members/egyptian-space-agency-egsa.html
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=11051
@@ -2781,12 +2925,12 @@
 • Nanosats.csv</t>
         </is>
       </c>
-      <c r="AI3" s="4" t="inlineStr">
+      <c r="AJ3" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ3" s="4" t="inlineStr"/>
+      <c r="AK3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -2881,80 +3025,96 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S4" s="4" t="inlineStr"/>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: 801–850</t>
+        </is>
+      </c>
       <c r="T4" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr"/>
-      <c r="V4" s="4" t="n">
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
+      <c r="X4" s="4" t="inlineStr"/>
+      <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>EgSA educational satellite model (lab satellite for communication, remote sensing and space-environment applications)</t>
         </is>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="Z4" s="4" t="inlineStr">
         <is>
           <t>Ground station simulation unit (educational, supplied under EgSA agreement)</t>
         </is>
       </c>
-      <c r="Z4" s="4" t="inlineStr">
+      <c r="AA4" s="4" t="inlineStr">
         <is>
           <t>EgSA educational satellite laboratory (satellite model, operation/testing simulators, ground-station simulator)</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AB4" s="4" t="inlineStr">
         <is>
           <t>• Egyptian Space Agency (EgSA) – executive agreement on educational satellite lab, 2021
 • EgSA cooperation protocol with universities, 2021
 • JICA / Japanese partner universities consortium</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="n">
+      <c r="AC4" s="4" t="inlineStr"/>
+      <c r="AD4" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="AD4" s="6" t="inlineStr">
+      <c r="AE4" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE4" s="4" t="inlineStr">
+      <c r="AF4" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG4" s="4" t="inlineStr">
+      <c r="AH4" s="4" t="inlineStr">
         <is>
           <t>• Президент сменился: Prof. Ahmed El-Sabbagh с 1 июля 2026 г. (вместо Prof. Amr Adly)
 • Сайт ejust.edu.eg недоступен (503) — контакты Управления международных связей взяты из поисковой выдержки официальной страницы
 • Также опубликован адрес overseas@ejust.edu.eg
-• Спутников на орбите нет; есть учебная спутниковая лаборатория EgSA</t>
-        </is>
-      </c>
-      <c r="AH4" s="4" t="inlineStr">
+• Спутников на орбите нет; есть учебная спутниковая лаборатория EgSA
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI4" s="4" t="inlineStr">
         <is>
           <t>• Https://ejust.edu.eg/get/news/details/215
 • Https://eng.pressbee.net/show4898887.html
 • Https://www.ejust.edu.eg/regional-international-affairs
-• Https://spaceinafrica.com/2021/03/09/egsa-signs-agreement-with-egypt-japan-university-of-science-and-technology/</t>
-        </is>
-      </c>
-      <c r="AI4" s="4" t="inlineStr">
+• Https://spaceinafrica.com/2021/03/09/egsa-signs-agreement-with-egypt-japan-university-of-science-and-technology/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ4" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ4" s="4" t="inlineStr"/>
+      <c r="AK4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -3063,61 +3223,71 @@
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="U5" s="4" t="inlineStr"/>
-      <c r="V5" s="4" t="n">
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
+      <c r="X5" s="4" t="inlineStr"/>
+      <c r="Y5" s="4" t="inlineStr">
         <is>
           <t>Educational CubeSat supplied by EgSA under 2021 executive agreement (student training)</t>
         </is>
       </c>
-      <c r="Y5" s="4" t="inlineStr">
+      <c r="Z5" s="4" t="inlineStr">
         <is>
           <t>AI-powered autonomous optical satellite-tracking ground station (student graduation project, telescope-based)</t>
         </is>
       </c>
-      <c r="Z5" s="4" t="inlineStr">
+      <c r="AA5" s="4" t="inlineStr">
         <is>
           <t>• Faculty of Navigation Science and Space Technology (est. 2016
 • Depts. of Space Navigation, Space Science, Space Communications)</t>
         </is>
       </c>
-      <c r="AA5" s="4" t="inlineStr">
+      <c r="AB5" s="4" t="inlineStr">
         <is>
           <t>• Egyptian Space Agency (EgSA) — executive agreement on educational satellite (Feb 2021)
 • NARSS (student visits)</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="n">
+      <c r="AC5" s="4" t="inlineStr"/>
+      <c r="AD5" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="AD5" s="6" t="inlineStr">
+      <c r="AE5" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE5" s="4" t="inlineStr">
+      <c r="AF5" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF5" s="4" t="inlineStr">
+      <c r="AG5" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG5" s="4" t="inlineStr">
+      <c r="AH5" s="4" t="inlineStr">
         <is>
           <t>• Prof. Tarek Ali — исполняющий обязанности президента (القائم بأعمال رئيس الجامعة), не постоянный президент
 • Единственный в Египте профильный факультет навигации и космических технологий; декан — Prof. Osama Shalabiea (أسامة شلبية)
 • Международный ящик принадлежит Администрации иностранных студентов; профиль партнёрств может быть ограничен
-• Факультет дал интервью китайскому CGTN (сен. 2026) — интерес к сотрудничеству с Китаем/БРИКС</t>
-        </is>
-      </c>
-      <c r="AH5" s="4" t="inlineStr">
+• Факультет дал интервью китайскому CGTN (сен. 2026) — интерес к сотрудничеству с Китаем/БРИКС
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI5" s="4" t="inlineStr">
         <is>
           <t>• Https://www.bsu.edu.eg/ContentSide.aspx?section_id=14&amp;cat_id=1
 • Https://www.bsu.edu.eg/NewsDetails_New.aspx?NID=167895&amp;cat_id=1&amp;lang=ar
@@ -3126,15 +3296,17 @@
 • Https://www.spacescien.bsu.edu.eg/
 • Https://spaceinafrica.com/2021/02/26/egsa-agreement-beni-suef-university-educational-satellite/
 • Https://www.bsu.edu.eg/NewsDetails_New.aspx?NID=167508&amp;cat_id=1&amp;lang=en
-• Https://www.universityworldnews.com/post.php?story=20210406120310615</t>
-        </is>
-      </c>
-      <c r="AI5" s="4" t="inlineStr">
+• Https://www.universityworldnews.com/post.php?story=20210406120310615
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ5" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ5" s="4" t="inlineStr"/>
+      <c r="AK5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -3240,18 +3412,19 @@
         </is>
       </c>
       <c r="U6" s="4" t="inlineStr"/>
-      <c r="V6" s="4" t="n">
+      <c r="V6" s="4" t="inlineStr"/>
+      <c r="W6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
+      <c r="X6" s="4" t="inlineStr"/>
+      <c r="Y6" s="4" t="inlineStr">
         <is>
           <t>• CU-CubeSat (1U student pico-satellite, Aerospace Dept. graduation project
 • Launch not confirmed)</t>
         </is>
       </c>
-      <c r="Y6" s="4" t="inlineStr"/>
-      <c r="Z6" s="4" t="inlineStr">
+      <c r="Z6" s="4" t="inlineStr"/>
+      <c r="AA6" s="4" t="inlineStr">
         <is>
           <t>• Faculty of Engineering, Department of Aerospace Engineering
 • Space System Technology Laboratory (SSTLab)
@@ -3259,39 +3432,40 @@
 • EgSA-supported educational satellite laboratory at Faculty of Engineering</t>
         </is>
       </c>
-      <c r="AA6" s="4" t="inlineStr">
+      <c r="AB6" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) – agreement on educational satellite laboratory (Egyptian Space Technology Educational Platform), 2022</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="n">
+      <c r="AC6" s="4" t="inlineStr"/>
+      <c r="AD6" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="AD6" s="6" t="inlineStr">
+      <c r="AE6" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE6" s="4" t="inlineStr">
+      <c r="AF6" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF6" s="4" t="inlineStr">
+      <c r="AG6" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG6" s="4" t="inlineStr">
+      <c r="AH6" s="4" t="inlineStr">
         <is>
           <t>• Сайты cu.edu.eg и iro.cu.edu.eg недоступны (503/бот-защита) — контакты взяты из поисковых выдержек официальных страниц, требуют перепроверки
 • Общий e-mail канцелярии президента не найден
 • Директор Управления международных связей (Heidi Bayoumy) указан на странице IRO без даты — актуальность на 2026 г. не подтверждена
-• Собственных спутников на орбите не найдено; CU-CubeSat — учебный проект</t>
-        </is>
-      </c>
-      <c r="AH6" s="4" t="inlineStr">
+• Собственных спутников на орбите не найдено; CU-CubeSat — учебный проект
+• Ручная проверка: Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI6" s="4" t="inlineStr">
         <is>
           <t>• Https://cu.edu.eg
 • Https://iro.cu.edu.eg/contact-us
@@ -3301,12 +3475,12 @@
 • Https://www.youm7.com/story/2026/9/6/7537608</t>
         </is>
       </c>
-      <c r="AI6" s="4" t="inlineStr">
+      <c r="AJ6" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -3406,7 +3580,7 @@
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 390</t>
+          <t>QS2027: =390</t>
         </is>
       </c>
       <c r="T7" s="4" t="inlineStr">
@@ -3414,72 +3588,85 @@
           <t>THE2027: 701–800</t>
         </is>
       </c>
-      <c r="U7" s="4" t="inlineStr"/>
-      <c r="V7" s="4" t="n">
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr">
+      <c r="X7" s="4" t="inlineStr"/>
+      <c r="Y7" s="4" t="inlineStr">
         <is>
           <t>• AUC CubeSat (student surface-imaging CubeSat project, 2013
 • Current status unknown)</t>
         </is>
       </c>
-      <c r="Y7" s="4" t="inlineStr"/>
-      <c r="Z7" s="4" t="inlineStr">
+      <c r="Z7" s="4" t="inlineStr"/>
+      <c r="AA7" s="4" t="inlineStr">
         <is>
           <t>• Astronomical Observatory (School of Sciences and Engineering)
 • AUC CubeSat student team (2013)</t>
         </is>
       </c>
-      <c r="AA7" s="4" t="inlineStr">
+      <c r="AB7" s="4" t="inlineStr">
         <is>
           <t>Study visits of ECE department to Egyptian Space Agency (EgSA)</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="n">
+      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AD7" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="AD7" s="6" t="inlineStr">
+      <c r="AE7" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE7" s="4" t="inlineStr">
+      <c r="AF7" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF7" s="4" t="inlineStr">
+      <c r="AG7" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG7" s="4" t="inlineStr">
+      <c r="AH7" s="4" t="inlineStr">
         <is>
           <t>• Частный американский некоммерческий вуз (аккредитация в США); представительство в Нью-Йорке: 420 Lexington Ave., Suite 1644
 • Студенческий проект AUC CubeSat (2013) — запуск не подтверждён
 • Офис президента: Executive Director Enas Fallal (enas.fallal@aucegypt.edu)
-• Менеджер по международным партнёрствам: Iman Nabil (iman.kamel@aucegypt.edu)</t>
-        </is>
-      </c>
-      <c r="AH7" s="4" t="inlineStr">
+• Менеджер по международным партнёрствам: Iman Nabil (iman.kamel@aucegypt.edu)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI7" s="4" t="inlineStr">
         <is>
           <t>• Https://www.aucegypt.edu/about/leadership
 • Https://www.aucegypt.edu/about/leadership/president/office
 • Https://www.aucegypt.edu/academics/international-programs-and-services-office
 • Https://amsat-uk.org/2013/05/26/the-american-university-in-cairo-auc-cubesat/
 • Https://sse.aucegypt.edu/news/visit-egyptian-space-agency-egsa
-• Qianmu.org QS2027 list</t>
-        </is>
-      </c>
-      <c r="AI7" s="4" t="inlineStr">
+• Qianmu.org QS2027 list
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ7" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -3573,20 +3760,37 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr"/>
-      <c r="V8" s="4" t="n">
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr"/>
-      <c r="Y8" s="4" t="inlineStr">
+      <c r="Y8" s="4" t="inlineStr"/>
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <t>Helwan Satellite Laser Ranging (SLR) station (ILRS network); Kottamia Astronomical Observatory</t>
         </is>
       </c>
-      <c r="Z8" s="4" t="inlineStr">
+      <c r="AA8" s="4" t="inlineStr">
         <is>
           <t>• Solar &amp; Space Department (Solar Lab
 • Space Lab)
@@ -3594,41 +3798,42 @@
 • Egyptian National Seismic Network</t>
         </is>
       </c>
-      <c r="AA8" s="4" t="inlineStr">
+      <c r="AB8" s="4" t="inlineStr">
         <is>
           <t>• Czech Technical University (FNSPE) – Helwan SLR station
 • ILRS (NASA-coordinated network)
 • Swedish embassy cooperation talks (2026)</t>
         </is>
       </c>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="n">
+      <c r="AC8" s="4" t="inlineStr"/>
+      <c r="AD8" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="AD8" s="6" t="inlineStr">
+      <c r="AE8" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE8" s="4" t="inlineStr">
+      <c r="AF8" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF8" s="4" t="inlineStr">
+      <c r="AG8" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG8" s="4" t="inlineStr">
+      <c r="AH8" s="4" t="inlineStr">
         <is>
           <t>• Отдельного e-mail международного отдела нет; есть раздел «International Relation and Training»
 • Письмо направлять на President@nriag.sci.eg
 • На сайте NRIAG обнаружены спам-ссылки (вероятно, сайт скомпрометирован) — на контакты это не влияет
-• Спутников не создавал; имеет станцию лазерной дальнометрии спутников в Хелуане</t>
-        </is>
-      </c>
-      <c r="AH8" s="4" t="inlineStr">
+• Спутников не создавал; имеет станцию лазерной дальнометрии спутников в Хелуане
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI8" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nriag.sci.eg/
 • Https://www.nriag.sci.eg/contact-us/
@@ -3637,12 +3842,12 @@
 • Http://kfe.fjfi.cvut.cz/~blazej/en/res/prj/helwan.html</t>
         </is>
       </c>
-      <c r="AI8" s="4" t="inlineStr">
+      <c r="AJ8" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -3737,74 +3942,89 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T9" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1801–2000</t>
         </is>
       </c>
-      <c r="U9" s="4" t="inlineStr"/>
-      <c r="V9" s="4" t="n">
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W9" s="4" t="inlineStr"/>
       <c r="X9" s="4" t="inlineStr"/>
       <c r="Y9" s="4" t="inlineStr"/>
-      <c r="Z9" s="4" t="inlineStr">
+      <c r="Z9" s="4" t="inlineStr"/>
+      <c r="AA9" s="4" t="inlineStr">
         <is>
           <t>• Wireless Intelligent Networks Center (WINC)
 • Nanoelectronics Integrated Systems Center (NISC)</t>
         </is>
       </c>
-      <c r="AA9" s="4" t="inlineStr">
+      <c r="AB9" s="4" t="inlineStr">
         <is>
           <t>MoU with Tan Kah Kee High Technology Research Institute (China-BRICS Science and Innovation Incubation Park)</t>
         </is>
       </c>
-      <c r="AB9" s="4" t="inlineStr"/>
-      <c r="AC9" s="4" t="n">
+      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AD9" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="AD9" s="7" t="inlineStr">
+      <c r="AE9" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AE9" s="4" t="inlineStr">
+      <c r="AF9" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF9" s="4" t="inlineStr">
+      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG9" s="4" t="inlineStr">
+      <c r="AH9" s="4" t="inlineStr">
         <is>
           <t>• Первый национальный некоммерческий университет Египта (self-described)
 • Общий e-mail офиса президента не опубликован; горячая линия 16453
 • Космических проектов (спутники, наземная станция) не найдено
 • Есть партнёрство с China-BRICS SIIP — удобная зацепка для БРИКС-приглашения
-• В QS2027 не найден</t>
-        </is>
-      </c>
-      <c r="AH9" s="4" t="inlineStr">
+• В QS2027 не найден
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI9" s="4" t="inlineStr">
         <is>
           <t>• Https://nu.edu.eg/
 • Https://nu.edu.eg/nu-president
 • Https://nu.edu.eg/office-international-affairs
 • Https://nu.edu.eg/contact-us
 • Https://nu.edu.eg/about/nu-glance
-• Https://www.nu.edu.eg/news/nile-university-forges-strategic-partnership-china-brics-siip-drive-global-innovation</t>
-        </is>
-      </c>
-      <c r="AI9" s="4" t="inlineStr">
+• Https://www.nu.edu.eg/news/nile-university-forges-strategic-partnership-china-brics-siip-drive-global-innovation
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ9" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -3899,68 +4119,83 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T10" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="U10" s="4" t="inlineStr"/>
-      <c r="V10" s="4" t="n">
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr">
+      <c r="X10" s="4" t="inlineStr"/>
+      <c r="Y10" s="4" t="inlineStr">
         <is>
           <t>Educational CubeSat supplied by EgSA (executive agreement, ~2021)</t>
         </is>
       </c>
-      <c r="Y10" s="4" t="inlineStr"/>
       <c r="Z10" s="4" t="inlineStr"/>
-      <c r="AA10" s="4" t="inlineStr">
+      <c r="AA10" s="4" t="inlineStr"/>
+      <c r="AB10" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) — educational CubeSat agreement (2021)</t>
         </is>
       </c>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="n">
+      <c r="AC10" s="4" t="inlineStr"/>
+      <c r="AD10" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="AD10" s="6" t="inlineStr">
+      <c r="AE10" s="6" t="inlineStr">
         <is>
           <t>1B</t>
         </is>
       </c>
-      <c r="AE10" s="4" t="inlineStr">
+      <c r="AF10" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF10" s="4" t="inlineStr">
+      <c r="AG10" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG10" s="4" t="inlineStr">
+      <c r="AH10" s="4" t="inlineStr">
         <is>
           <t>• Отдельного e-mail международного отдела на сайте не найдено — писать в офис президента (President_office@suez.edu.eg); также опубликован тел. +20 2 22621217
 • Участник программы EgSA по образовательным кубсатам (2021); запусков собственного спутника не найдено
-• В QS2027 не найден</t>
-        </is>
-      </c>
-      <c r="AH10" s="4" t="inlineStr">
+• В QS2027 не найден
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI10" s="4" t="inlineStr">
         <is>
           <t>• Https://suez.edu.eg/ar/en/
 • Https://suez.edu.eg/ar/en/contact-us/
-• Https://www.universityworldnews.com/post.php?story=20210406120310615</t>
-        </is>
-      </c>
-      <c r="AI10" s="4" t="inlineStr">
+• Https://www.universityworldnews.com/post.php?story=20210406120310615
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ10" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ10" s="4" t="inlineStr"/>
+      <c r="AK10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -4061,7 +4296,7 @@
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>QS2027: 551</t>
+          <t>QS2027: =551</t>
         </is>
       </c>
       <c r="T11" s="4" t="inlineStr">
@@ -4069,51 +4304,61 @@
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="U11" s="4" t="inlineStr"/>
-      <c r="V11" s="4" t="n">
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W11" s="4" t="inlineStr"/>
       <c r="X11" s="4" t="inlineStr"/>
       <c r="Y11" s="4" t="inlineStr"/>
-      <c r="Z11" s="4" t="inlineStr">
+      <c r="Z11" s="4" t="inlineStr"/>
+      <c r="AA11" s="4" t="inlineStr">
         <is>
           <t>Space innovation laboratory at Faculty of Engineering (EgSA 'Space Keys' educational satellite programme)</t>
         </is>
       </c>
-      <c r="AA11" s="4" t="inlineStr">
+      <c r="AB11" s="4" t="inlineStr">
         <is>
           <t>• Egyptian Space Agency (EgSA) — cooperation protocol
 • Space Keys educational satellite project (EgSA / ASRT)</t>
         </is>
       </c>
-      <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="n">
+      <c r="AC11" s="4" t="inlineStr"/>
+      <c r="AD11" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="AD11" s="8" t="inlineStr">
+      <c r="AE11" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE11" s="4" t="inlineStr">
+      <c r="AF11" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF11" s="4" t="inlineStr">
+      <c r="AG11" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG11" s="4" t="inlineStr">
+      <c r="AH11" s="4" t="inlineStr">
         <is>
           <t>• Руководитель Управления международных связей (IRO) указан на странице IRAC без даты — сверить актуальность
 • Международным сотрудничеством в целом руководит исполнительный директор сектора IRAC проф. Шервит Эль-Ахмади (irac@asu.edu.eg) — можно поставить в копию
-• Запущенных спутников не найдено; участвует в программе учебных спутников EgSA</t>
-        </is>
-      </c>
-      <c r="AH11" s="4" t="inlineStr">
+• Запущенных спутников не найдено; участвует в программе учебных спутников EgSA
+• Рейтинги: QS: в таблице как «Ain Shams University in Cairo (ASU, Cairo)»; Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI11" s="4" t="inlineStr">
         <is>
           <t>• Https://www.asu.edu.eg/en/38/page/contact-us
 • Https://www.asu.edu.eg/en
@@ -4122,15 +4367,17 @@
 • Http://iroms.asu.edu.eg/
 • Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/
 • Https://spaceinafrica.com/2022/01/04/egsa-celebrates-the-delivery-of-the-first-three-educational-satellites-to-the-egyptian-universities/
-• Https://www.qianmu.org/ranking/1528.htm (2027 QS list, qianmu.org)</t>
-        </is>
-      </c>
-      <c r="AI11" s="4" t="inlineStr">
+• Https://www.qianmu.org/ranking/1528.htm (2027 QS list, qianmu.org)
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ11" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -4238,66 +4485,79 @@
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="U12" s="4" t="inlineStr"/>
-      <c r="V12" s="4" t="n">
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W12" s="4" t="inlineStr"/>
       <c r="X12" s="4" t="inlineStr"/>
       <c r="Y12" s="4" t="inlineStr"/>
-      <c r="Z12" s="4" t="inlineStr">
+      <c r="Z12" s="4" t="inlineStr"/>
+      <c r="AA12" s="4" t="inlineStr">
         <is>
           <t>Educational satellite laboratory (agreement with EgSA, April 2021)</t>
         </is>
       </c>
-      <c r="AA12" s="4" t="inlineStr">
+      <c r="AB12" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) — cooperation protocol (2021), educational satellite lab</t>
         </is>
       </c>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="n">
+      <c r="AC12" s="4" t="inlineStr"/>
+      <c r="AD12" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="AD12" s="8" t="inlineStr">
+      <c r="AE12" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE12" s="4" t="inlineStr">
+      <c r="AF12" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF12" s="4" t="inlineStr">
+      <c r="AG12" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG12" s="4" t="inlineStr">
+      <c r="AH12" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт alexu.edu.eg выдаёт ошибку 500 (октябрь 2026); адрес/телефон/info@ взяты из справочника universitiesegypt.com — сверить
 • Президент проф. Абдель Азиз Кансуа с февраля 2026 — министр высшего образования; университет возглавляет и.о. президента проф. Ахмед Адель Абдель Хаким (сентябрь 2026)
 • В поисковой выдаче официального сайта фигурирует president@alexu.edu.eg (страницу открыть не удалось) — можно поставить в копию
-• Запущенных спутников не найдено; есть протокол с EgSA о создании учебной спутниковой лаборатории (2021)</t>
-        </is>
-      </c>
-      <c r="AH12" s="4" t="inlineStr">
+• Запущенных спутников не найдено; есть протокол с EgSA о создании учебной спутниковой лаборатории (2021)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI12" s="4" t="inlineStr">
         <is>
           <t>• Https://internationaloffice.alexu.edu.eg/contact-us/
 • Https://www.elwatannews.com/news/details/8361274
 • Https://en.wikipedia.org/wiki/Abdul_Aziz_Qansouh
 • Https://www.universitiesegypt.com/alexandria-university/contacts
 • Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/
-• Https://www.qianmu.org/ranking/1528.htm (2027 QS list, qianmu.org)</t>
-        </is>
-      </c>
-      <c r="AI12" s="4" t="inlineStr">
+• Https://www.qianmu.org/ranking/1528.htm (2027 QS list, qianmu.org)
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ12" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ12" s="4" t="inlineStr"/>
+      <c r="AK12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -4401,51 +4661,61 @@
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr"/>
-      <c r="V13" s="4" t="n">
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="4" t="inlineStr"/>
       <c r="X13" s="4" t="inlineStr"/>
       <c r="Y13" s="4" t="inlineStr"/>
-      <c r="Z13" s="4" t="inlineStr">
+      <c r="Z13" s="4" t="inlineStr"/>
+      <c r="AA13" s="4" t="inlineStr">
         <is>
           <t>Space innovation lab with EgSA 'Space Keys' educational satellite (College of Engineering, Cairo-Sheraton branch)</t>
         </is>
       </c>
-      <c r="AA13" s="4" t="inlineStr">
+      <c r="AB13" s="4" t="inlineStr">
         <is>
           <t>• Egyptian Space Agency (EgSA) – cooperation protocol (2021), agreement to receive educational CubeSats, 'Space Keys' satellite delivered Jan 2022
 • EgSA CEO met AASTMT President on training/expertise exchange (Sep 2026)</t>
         </is>
       </c>
-      <c r="AB13" s="4" t="inlineStr"/>
-      <c r="AC13" s="4" t="n">
+      <c r="AC13" s="4" t="inlineStr"/>
+      <c r="AD13" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="AD13" s="8" t="inlineStr">
+      <c r="AE13" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE13" s="4" t="inlineStr">
+      <c r="AF13" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF13" s="4" t="inlineStr">
+      <c r="AG13" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG13" s="4" t="inlineStr">
+      <c r="AH13" s="4" t="inlineStr">
         <is>
           <t>• Общий e-mail — отдела протокола и связей с общественностью (Public.relations@aast.edu); адрес международного отдела на сайте не найден
 • Академия Лиги арабских государств, кампусы в Александрии, Каире, Порт-Саиде, Асуане, Эль-Аламейне, Латакии, Шардже
-• Сентябрь 2026: встреча главы EgSA с президентом AASTMT — удобный повод для упоминания в письме</t>
-        </is>
-      </c>
-      <c r="AH13" s="4" t="inlineStr">
+• Сентябрь 2026: встреча главы EgSA с президентом AASTMT — удобный повод для упоминания в письме
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI13" s="4" t="inlineStr">
         <is>
           <t>• Https://aast.edu/en/index.php
 • Https://aast.edu/en/about/
@@ -4454,15 +4724,17 @@
 • Https://www.universityworldnews.com/post.php?story=20210406120310615
 • Https://satelliteprome.com/news/egsa-produces-educational-satellites-for-egyptian-universities/
 • Https://ahlmasrnews.com/news/egypt-news/12898084/
-• Https://www.masrawy.com/news/news_egypt/details/2026/9/23/3052657/</t>
-        </is>
-      </c>
-      <c r="AI13" s="4" t="inlineStr">
+• Https://www.masrawy.com/news/news_egypt/details/2026/9/23/3052657/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ13" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ13" s="4" t="inlineStr"/>
+      <c r="AK13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -4571,63 +4843,75 @@
           <t>THE2027: 1601–1800</t>
         </is>
       </c>
-      <c r="U14" s="4" t="inlineStr"/>
-      <c r="V14" s="4" t="n">
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="4" t="inlineStr"/>
       <c r="X14" s="4" t="inlineStr"/>
       <c r="Y14" s="4" t="inlineStr"/>
-      <c r="Z14" s="4" t="inlineStr">
+      <c r="Z14" s="4" t="inlineStr"/>
+      <c r="AA14" s="4" t="inlineStr">
         <is>
           <t>Space innovation lab (EgSA 'Space Keys' educational satellite kit)</t>
         </is>
       </c>
-      <c r="AA14" s="4" t="inlineStr">
+      <c r="AB14" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) – cooperation protocol (2021), educational CubeSat agreement, 'Space Keys' kit delivered Jan 2022</t>
         </is>
       </c>
-      <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="n">
+      <c r="AC14" s="4" t="inlineStr"/>
+      <c r="AD14" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="AD14" s="8" t="inlineStr">
+      <c r="AE14" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE14" s="4" t="inlineStr">
+      <c r="AF14" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF14" s="4" t="inlineStr">
+      <c r="AG14" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG14" s="4" t="inlineStr">
+      <c r="AH14" s="4" t="inlineStr">
         <is>
           <t>• ДУБЛИКАТ: это тот же вуз, что и 'Helwan University' в этом списке (переименован в Capital University); отправлять одно письмо
-• Рейтинг THE2027 1601–1800 указан во входных данных для Capital University</t>
-        </is>
-      </c>
-      <c r="AH14" s="4" t="inlineStr">
+• Рейтинг THE2027 1601–1800 указан во входных данных для Capital University
+• Рейтинги: QS: в таблице как «Capital University – Egypt»; Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI14" s="4" t="inlineStr">
         <is>
           <t>• Https://www.capu.edu.eg/index.php/en/
 • Https://www.capu.edu.eg/index.php/en/president-leaders-en
 • Https://www.capu.edu.eg/index.php/en/contact-en
 • Https://www.capu.edu.eg/index.php/en/about-en/agreements-and-partnerships/international-relations-office
-• Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/</t>
-        </is>
-      </c>
-      <c r="AI14" s="4" t="inlineStr">
+• Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ14" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ14" s="4" t="inlineStr"/>
+      <c r="AK14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -4722,69 +5006,84 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S15" s="4" t="inlineStr"/>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T15" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1601–1800</t>
         </is>
       </c>
-      <c r="U15" s="4" t="inlineStr"/>
-      <c r="V15" s="4" t="n">
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W15" s="4" t="inlineStr"/>
       <c r="X15" s="4" t="inlineStr"/>
       <c r="Y15" s="4" t="inlineStr"/>
-      <c r="Z15" s="4" t="inlineStr">
+      <c r="Z15" s="4" t="inlineStr"/>
+      <c r="AA15" s="4" t="inlineStr">
         <is>
           <t>Educational satellite laboratory at Faculty of Engineering (provided by EgSA)</t>
         </is>
       </c>
-      <c r="AA15" s="4" t="inlineStr">
+      <c r="AB15" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) – cooperation protocol and educational satellite lab (2021)</t>
         </is>
       </c>
-      <c r="AB15" s="4" t="inlineStr"/>
-      <c r="AC15" s="4" t="n">
+      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AD15" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="AD15" s="8" t="inlineStr">
+      <c r="AE15" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE15" s="4" t="inlineStr">
+      <c r="AF15" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF15" s="4" t="inlineStr">
+      <c r="AG15" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG15" s="4" t="inlineStr">
+      <c r="AH15" s="4" t="inlineStr">
         <is>
           <t>• Вуз ориентирован на сотрудничество с Россией — удобный партнёр для российской стороны
 • Есть учебная спутниковая лаборатория EgSA на инженерном факультете; собственных спутников нет
-• Отдельный e-mail международного отдела не опубликован</t>
-        </is>
-      </c>
-      <c r="AH15" s="4" t="inlineStr">
+• Отдельный e-mail международного отдела не опубликован
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI15" s="4" t="inlineStr">
         <is>
           <t>• Https://eru.edu.eg/
 • Https://eru.edu.eg/explore-eru/
 • Https://eru.edu.eg/inauguration-of-a-satellite-laboratory-at-the-egyptian-russian-university/
-• Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/</t>
-        </is>
-      </c>
-      <c r="AI15" s="4" t="inlineStr">
+• Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ15" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ15" s="4" t="inlineStr"/>
+      <c r="AK15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -4889,61 +5188,74 @@
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="U16" s="4" t="inlineStr"/>
-      <c r="V16" s="4" t="n">
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>1180</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W16" s="4" t="inlineStr"/>
       <c r="X16" s="4" t="inlineStr"/>
       <c r="Y16" s="4" t="inlineStr"/>
       <c r="Z16" s="4" t="inlineStr"/>
-      <c r="AA16" s="4" t="inlineStr">
+      <c r="AA16" s="4" t="inlineStr"/>
+      <c r="AB16" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) — cooperation protocol</t>
         </is>
       </c>
-      <c r="AB16" s="4" t="inlineStr"/>
-      <c r="AC16" s="4" t="n">
+      <c r="AC16" s="4" t="inlineStr"/>
+      <c r="AD16" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="AD16" s="8" t="inlineStr">
+      <c r="AE16" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE16" s="4" t="inlineStr">
+      <c r="AF16" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF16" s="4" t="inlineStr">
+      <c r="AG16" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG16" s="4" t="inlineStr">
+      <c r="AH16" s="4" t="inlineStr">
         <is>
           <t>• Подчиняется Аль-Азхару (Шейх аль-Азхар), а не напрямую Минвысшобразования; форма собственности — государственный
 • С 1 августа 2026 обязанности президента временно исполняет проф. Махмуд Сыддык Хасан (вице-президент по аспирантуре и науке) до назначения нового президента
 • Сайт международного отдела international.azu.edu.eg — только JS-приложение регистрации; e-mail международного отдела не найден — использовать info@azhar.edu.eg
-• Полный почтовый адрес на сайте не указан (только «Каир, Насср-Сити»)</t>
-        </is>
-      </c>
-      <c r="AH16" s="4" t="inlineStr">
+• Полный почтовый адрес на сайте не указан (только «Каир, Насср-Сити»)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI16" s="4" t="inlineStr">
         <is>
           <t>• Https://azhar.edu.eg/
 • Https://azhar.edu.eg/2026/07/27/%d8%b4%d9%8a%d8%ae-%d8%a7%d9%84%d8%a3%d8%b2%d9%87%d8%b1-%d9%8a%d9%83%d9%84%d9%81-%d8%a7%d9%84%d8%af%d9%83%d8%aa%d9%88%d8%b1-%d9%85%d8%ad%d9%85%d9%88%d8%af-%d8%b5%d8%af%d9%8a%d9%82-%d9%86%d8%a7%d8%a6/
 • Https://www.youm7.com/story/2026/9/13/x/7544963
 • Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/
-• Https://www.qianmu.org/ranking/1528.htm (2027 QS list, qianmu.org)</t>
-        </is>
-      </c>
-      <c r="AI16" s="4" t="inlineStr">
+• Https://www.qianmu.org/ranking/1528.htm (2027 QS list, qianmu.org)
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ16" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ16" s="4" t="inlineStr"/>
+      <c r="AK16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -5048,58 +5360,71 @@
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="U17" s="4" t="inlineStr"/>
-      <c r="V17" s="4" t="n">
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>797</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" s="4" t="inlineStr"/>
       <c r="Y17" s="4" t="inlineStr"/>
       <c r="Z17" s="4" t="inlineStr"/>
-      <c r="AA17" s="4" t="inlineStr">
+      <c r="AA17" s="4" t="inlineStr"/>
+      <c r="AB17" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) – cooperation protocol (2021)</t>
         </is>
       </c>
-      <c r="AB17" s="4" t="inlineStr"/>
-      <c r="AC17" s="4" t="n">
+      <c r="AC17" s="4" t="inlineStr"/>
+      <c r="AD17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="AD17" s="8" t="inlineStr">
+      <c r="AE17" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE17" s="4" t="inlineStr">
+      <c r="AF17" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF17" s="4" t="inlineStr">
+      <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG17" s="4" t="inlineStr">
+      <c r="AH17" s="4" t="inlineStr">
         <is>
           <t>• Сайт международного отдела (muiro.mans.edu.eg) недоступен (503) — e-mail отдела не установлен
-• Спутников не найдено (одна быстрая проверка)</t>
-        </is>
-      </c>
-      <c r="AH17" s="4" t="inlineStr">
+• Спутников не найдено (одна быстрая проверка)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI17" s="4" t="inlineStr">
         <is>
           <t>• Https://www.mans.edu.eg/en
 • Https://www.mans.edu.eg/en/about/contact-info
 • Https://www.mans.edu.eg/en/about/history-and-facts/president-s-speech
-• Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/</t>
-        </is>
-      </c>
-      <c r="AI17" s="4" t="inlineStr">
+• Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ17" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ17" s="4" t="inlineStr"/>
+      <c r="AK17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -5203,60 +5528,73 @@
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="U18" s="4" t="inlineStr"/>
-      <c r="V18" s="4" t="n">
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>1149</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W18" s="4" t="inlineStr"/>
       <c r="X18" s="4" t="inlineStr"/>
       <c r="Y18" s="4" t="inlineStr"/>
       <c r="Z18" s="4" t="inlineStr"/>
-      <c r="AA18" s="4" t="inlineStr">
+      <c r="AA18" s="4" t="inlineStr"/>
+      <c r="AB18" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) – cooperation protocol (2021)</t>
         </is>
       </c>
-      <c r="AB18" s="4" t="inlineStr"/>
-      <c r="AC18" s="4" t="n">
+      <c r="AC18" s="4" t="inlineStr"/>
+      <c r="AD18" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AD18" s="8" t="inlineStr">
+      <c r="AE18" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE18" s="4" t="inlineStr">
+      <c r="AF18" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF18" s="4" t="inlineStr">
+      <c r="AG18" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG18" s="4" t="inlineStr">
+      <c r="AH18" s="4" t="inlineStr">
         <is>
           <t>• Единственный общий e-mail на странице контактов — complaints@aun.edu.eg (обращения/жалобы); офис президента e-mail не публикует
 • Auiro@aun.edu.eg — это офис международных академических рейтингов, а не международных связей; e-mail отдела международных связей не найден
-• Космическая проверка не выполнена через поиск (исчерпан лимит); спутников по nanosats.csv нет</t>
-        </is>
-      </c>
-      <c r="AH18" s="4" t="inlineStr">
+• Космическая проверка не выполнена через поиск (исчерпан лимит); спутников по nanosats.csv нет
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI18" s="4" t="inlineStr">
         <is>
           <t>• Https://www.aun.edu.eg/main/
 • Https://www.aun.edu.eg/main/contact
 • Https://www.aun.edu.eg/main/node/85606
 • Https://www.aun.edu.eg/AUIRO/ar/Office-Team
-• Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/</t>
-        </is>
-      </c>
-      <c r="AI18" s="4" t="inlineStr">
+• Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ18" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ18" s="4" t="inlineStr"/>
+      <c r="AK18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -5351,65 +5689,80 @@
           <t>Acting President</t>
         </is>
       </c>
-      <c r="S19" s="4" t="inlineStr"/>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T19" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="U19" s="4" t="inlineStr"/>
-      <c r="V19" s="4" t="n">
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W19" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W19" s="4" t="inlineStr"/>
       <c r="X19" s="4" t="inlineStr"/>
       <c r="Y19" s="4" t="inlineStr"/>
       <c r="Z19" s="4" t="inlineStr"/>
-      <c r="AA19" s="4" t="inlineStr">
+      <c r="AA19" s="4" t="inlineStr"/>
+      <c r="AB19" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) — cooperation protocol</t>
         </is>
       </c>
-      <c r="AB19" s="4" t="inlineStr"/>
-      <c r="AC19" s="4" t="n">
+      <c r="AC19" s="4" t="inlineStr"/>
+      <c r="AD19" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AD19" s="8" t="inlineStr">
+      <c r="AE19" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE19" s="4" t="inlineStr">
+      <c r="AF19" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF19" s="4" t="inlineStr">
+      <c r="AG19" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG19" s="4" t="inlineStr">
+      <c r="AH19" s="4" t="inlineStr">
         <is>
           <t>• Университет возглавляет и.о. президента проф. Ашраф Имам Абдель Ради (также вице-президент по общественной работе)
 • Адрес/телефон/info@ на официальном сайте не отображаются (подгружаются скриптом) — взяты из справочника universitiesegypt.com; отдельного e-mail международного отдела нет
-• Управление научных и культурных связей: и.о. генерального директора Махмуд Мохамед Абдель Мутталиб (e-mail не опубликован)</t>
-        </is>
-      </c>
-      <c r="AH19" s="4" t="inlineStr">
+• Управление научных и культурных связей: и.о. генерального директора Махмуд Мохамед Абдель Мутталиб (e-mail не опубликован)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI19" s="4" t="inlineStr">
         <is>
           <t>• Https://aswu.edu.eg/about/key-facts/leadership-team/
 • Https://www.universitiesegypt.com/aswan-university/contacts
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=10034
-• Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/</t>
-        </is>
-      </c>
-      <c r="AI19" s="4" t="inlineStr">
+• Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ19" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ19" s="4" t="inlineStr"/>
+      <c r="AK19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -5503,64 +5856,79 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S20" s="4" t="inlineStr"/>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T20" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1801–2000</t>
         </is>
       </c>
-      <c r="U20" s="4" t="inlineStr"/>
-      <c r="V20" s="4" t="n">
+      <c r="U20" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W20" s="4" t="inlineStr"/>
       <c r="X20" s="4" t="inlineStr"/>
       <c r="Y20" s="4" t="inlineStr"/>
       <c r="Z20" s="4" t="inlineStr"/>
-      <c r="AA20" s="4" t="inlineStr">
+      <c r="AA20" s="4" t="inlineStr"/>
+      <c r="AB20" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) – cooperation protocol (2021)</t>
         </is>
       </c>
-      <c r="AB20" s="4" t="inlineStr"/>
-      <c r="AC20" s="4" t="n">
+      <c r="AC20" s="4" t="inlineStr"/>
+      <c r="AD20" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AD20" s="8" t="inlineStr">
+      <c r="AE20" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE20" s="4" t="inlineStr">
+      <c r="AF20" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF20" s="4" t="inlineStr">
+      <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG20" s="4" t="inlineStr">
+      <c r="AH20" s="4" t="inlineStr">
         <is>
           <t>• Есть 'UK Quality Assurance &amp; International Partnerships Unit' (партнёрства с британскими вузами, напр. Greenwich), но отдельный e-mail не опубликован
-• Горячая линия 16672</t>
-        </is>
-      </c>
-      <c r="AH20" s="4" t="inlineStr">
+• Горячая линия 16672
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI20" s="4" t="inlineStr">
         <is>
           <t>• Https://msa.edu.eg/msauniversity/
 • Https://msa.edu.eg/msauniversity/university-president/
 • Https://msa.edu.eg/msauniversity/contact/
-• Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/</t>
-        </is>
-      </c>
-      <c r="AI20" s="4" t="inlineStr">
+• Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ20" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ20" s="4" t="inlineStr"/>
+      <c r="AK20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -5651,66 +6019,81 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S21" s="4" t="inlineStr"/>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T21" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="U21" s="4" t="inlineStr"/>
-      <c r="V21" s="4" t="n">
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W21" s="4" t="inlineStr"/>
       <c r="X21" s="4" t="inlineStr"/>
       <c r="Y21" s="4" t="inlineStr"/>
       <c r="Z21" s="4" t="inlineStr"/>
-      <c r="AA21" s="4" t="inlineStr">
+      <c r="AA21" s="4" t="inlineStr"/>
+      <c r="AB21" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) – cooperation protocol (2021)</t>
         </is>
       </c>
-      <c r="AB21" s="4" t="inlineStr"/>
-      <c r="AC21" s="4" t="n">
+      <c r="AC21" s="4" t="inlineStr"/>
+      <c r="AD21" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AD21" s="8" t="inlineStr">
+      <c r="AE21" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE21" s="4" t="inlineStr">
+      <c r="AF21" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF21" s="4" t="inlineStr">
+      <c r="AG21" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG21" s="4" t="inlineStr">
+      <c r="AH21" s="4" t="inlineStr">
         <is>
           <t>• Общий e-mail — адрес веб-портала (portal@psu.edu.eg); e-mail отдела культурных/международных связей не найден
 • Президент ранее возглавлял сектор культурных связей и командировок Минвысшобразования — релевантно для международного сотрудничества
-• Есть партнёрство с IIT Gandhinagar (Индия, БРИКС) и Ghent University</t>
-        </is>
-      </c>
-      <c r="AH21" s="4" t="inlineStr">
+• Есть партнёрство с IIT Gandhinagar (Индия, БРИКС) и Ghent University
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI21" s="4" t="inlineStr">
         <is>
           <t>• Https://psu.edu.eg/
 • Https://psu.edu.eg/university-admin-ar/
 • Https://psu.edu.eg/about-ar/
 • Https://psu.edu.eg/en/home-en/
-• Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/</t>
-        </is>
-      </c>
-      <c r="AI21" s="4" t="inlineStr">
+• Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ21" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ21" s="4" t="inlineStr"/>
+      <c r="AK21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -5805,65 +6188,80 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S22" s="4" t="inlineStr"/>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T22" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="U22" s="4" t="inlineStr"/>
-      <c r="V22" s="4" t="n">
+      <c r="U22" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W22" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W22" s="4" t="inlineStr"/>
       <c r="X22" s="4" t="inlineStr"/>
       <c r="Y22" s="4" t="inlineStr"/>
       <c r="Z22" s="4" t="inlineStr"/>
-      <c r="AA22" s="4" t="inlineStr">
+      <c r="AA22" s="4" t="inlineStr"/>
+      <c r="AB22" s="4" t="inlineStr">
         <is>
           <t>Egyptian Space Agency (EgSA) — cooperation protocol</t>
         </is>
       </c>
-      <c r="AB22" s="4" t="inlineStr"/>
-      <c r="AC22" s="4" t="n">
+      <c r="AC22" s="4" t="inlineStr"/>
+      <c r="AD22" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AD22" s="8" t="inlineStr">
+      <c r="AE22" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE22" s="4" t="inlineStr">
+      <c r="AF22" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF22" s="4" t="inlineStr">
+      <c r="AG22" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG22" s="4" t="inlineStr">
+      <c r="AH22" s="4" t="inlineStr">
         <is>
           <t>• Имя президента в латинице дано в транслитерации (حسان النعماني) — проверить написание
 • Адрес по справочнику universitiesegypt.com; телефон и e-mail совпадают с официальным сайтом
 • Отдельного e-mail международного отдела не найдено — используется ящик президента
-• Запущенных спутников не найдено; есть протокол сотрудничества с EgSA (2021)</t>
-        </is>
-      </c>
-      <c r="AH22" s="4" t="inlineStr">
+• Запущенных спутников не найдено; есть протокол сотрудничества с EgSA (2021)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI22" s="4" t="inlineStr">
         <is>
           <t>• Https://www.sohag-univ.edu.eg/ar/home/
 • Https://www.universitiesegypt.com/sohag-university/contacts
-• Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/</t>
-        </is>
-      </c>
-      <c r="AI22" s="4" t="inlineStr">
+• Https://spaceinafrica.com/2021/09/29/egypt-space-agency-enters-cooperation-protocol-with-local-universities/
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ22" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ22" s="4" t="inlineStr"/>
+      <c r="AK22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -5943,62 +6341,77 @@
           <t>Acting Executive President (Zewail City); University President (UST, acting): Prof. Ibrahim El Sherbiny</t>
         </is>
       </c>
-      <c r="S23" s="4" t="inlineStr"/>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T23" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="U23" s="4" t="inlineStr"/>
-      <c r="V23" s="4" t="n">
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W23" s="4" t="inlineStr"/>
       <c r="X23" s="4" t="inlineStr"/>
       <c r="Y23" s="4" t="inlineStr"/>
-      <c r="Z23" s="4" t="inlineStr">
+      <c r="Z23" s="4" t="inlineStr"/>
+      <c r="AA23" s="4" t="inlineStr">
         <is>
           <t>Aerospace Engineering programme (UST)</t>
         </is>
       </c>
-      <c r="AA23" s="4" t="inlineStr"/>
       <c r="AB23" s="4" t="inlineStr"/>
-      <c r="AC23" s="4" t="n">
+      <c r="AC23" s="4" t="inlineStr"/>
+      <c r="AD23" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="AD23" s="7" t="inlineStr">
+      <c r="AE23" s="7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AE23" s="4" t="inlineStr"/>
-      <c r="AF23" s="4" t="inlineStr">
+      <c r="AF23" s="4" t="inlineStr"/>
+      <c r="AG23" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG23" s="4" t="inlineStr">
+      <c r="AH23" s="4" t="inlineStr">
         <is>
           <t>• Руководство: и.о. исполнительного президента Prof. Wael Akl; и.о. президента университета (UST) Prof. Ibrahim El Sherbiny; председатель попечительского совета — министр высшего образования Abdelaziz Konsowa
 • На сайте не опубликованы e-mail (ни общий, ни международного отдела) — только горячая линия 17742 и форма; требуется уточнение контакта
 • Собственных спутников не найдено; есть программа аэрокосмической инженерии; Zewail City посещали астронавты ОАЭ (MBRSC) — формального соглашения не найдено
-• Тип собственности: государственная некоммерческая структура по особому закону (не классический госуниверситет) — проверить формулировку</t>
-        </is>
-      </c>
-      <c r="AH23" s="4" t="inlineStr">
+• Тип собственности: государственная некоммерческая структура по особому закону (не классический госуниверситет) — проверить формулировку
+• Рейтинги: THE: в таблице как «Zewail City of Science and Technology»; Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI23" s="4" t="inlineStr">
         <is>
           <t>• Https://zewailcity.edu.eg/
 • Https://zewailcity.edu.eg/leadership
 • Https://zewailcity.edu.eg/contact-us
-• Https://zewailcity.edu.eg/ar</t>
-        </is>
-      </c>
-      <c r="AI23" s="4" t="inlineStr">
+• Https://zewailcity.edu.eg/ar
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ23" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ23" s="4" t="inlineStr"/>
+      <c r="AK23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -6084,63 +6497,82 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S24" s="4" t="inlineStr"/>
-      <c r="T24" s="4" t="inlineStr"/>
-      <c r="U24" s="4" t="inlineStr"/>
-      <c r="V24" s="4" t="n">
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W24" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W24" s="4" t="inlineStr"/>
       <c r="X24" s="4" t="inlineStr"/>
       <c r="Y24" s="4" t="inlineStr"/>
       <c r="Z24" s="4" t="inlineStr"/>
-      <c r="AA24" s="4" t="inlineStr">
+      <c r="AA24" s="4" t="inlineStr"/>
+      <c r="AB24" s="4" t="inlineStr">
         <is>
           <t>Beijing Institute of Technology (BIT) — cooperation visits (Jan 2026)</t>
         </is>
       </c>
-      <c r="AB24" s="4" t="inlineStr"/>
-      <c r="AC24" s="4" t="n">
+      <c r="AC24" s="4" t="inlineStr"/>
+      <c r="AD24" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AD24" s="8" t="inlineStr">
+      <c r="AE24" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE24" s="4" t="inlineStr">
+      <c r="AF24" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF24" s="4" t="inlineStr">
+      <c r="AG24" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG24" s="4" t="inlineStr">
+      <c r="AH24" s="4" t="inlineStr">
         <is>
           <t>• Сайт — SPA; контакты и новости взяты из официального API сайта (luxoruniversityar.runasp.net)
 • Президент — проф. Сабрин Абдель Галиль (женщина; новость от 28.01.2026); при обращении использовать «Dear Prof. Abdel Galil»
 • В январе 2026 принимала делегацию Пекинского технологического института (BIT) — возможная точка входа для космической тематики
 • Отдельного e-mail международного отдела нет; космическая активность поиском не проверялась (лимит поиска исчерпан)
-• В THE 2027 — статус Reporter (без ранга)</t>
-        </is>
-      </c>
-      <c r="AH24" s="4" t="inlineStr">
+• В THE 2027 — статус Reporter (без ранга)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI24" s="4" t="inlineStr">
         <is>
           <t>• Https://luxor.edu.eg/
 • Https://luxoruniversityar.runasp.net/api/v1/contacts/getall
 • Https://luxoruniversityar.runasp.net/api/v1/posts/getall
-• Https://www.universitiesegypt.com/luxor-university/contacts</t>
-        </is>
-      </c>
-      <c r="AI24" s="4" t="inlineStr">
+• Https://www.universitiesegypt.com/luxor-university/contacts
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ24" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ24" s="4" t="inlineStr"/>
+      <c r="AK24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -6245,55 +6677,68 @@
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="U25" s="4" t="inlineStr"/>
-      <c r="V25" s="4" t="n">
+      <c r="U25" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V25" s="4" t="inlineStr">
+        <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="W25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W25" s="4" t="inlineStr"/>
       <c r="X25" s="4" t="inlineStr"/>
       <c r="Y25" s="4" t="inlineStr"/>
       <c r="Z25" s="4" t="inlineStr"/>
       <c r="AA25" s="4" t="inlineStr"/>
       <c r="AB25" s="4" t="inlineStr"/>
-      <c r="AC25" s="4" t="n">
+      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AD25" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD25" s="8" t="inlineStr">
+      <c r="AE25" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE25" s="4" t="inlineStr">
+      <c r="AF25" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF25" s="4" t="inlineStr">
+      <c r="AG25" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG25" s="4" t="inlineStr">
+      <c r="AH25" s="4" t="inlineStr">
         <is>
           <t>• Отдельного e-mail международного отдела не опубликовано (International Support Center обслуживает только иностранных студентов) — писать на info@fue.edu.eg
 • Горячая линия 16383; факс +20 2 2618 6111
-• Космической активности не найдено</t>
-        </is>
-      </c>
-      <c r="AH25" s="4" t="inlineStr">
+• Космической активности не найдено
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI25" s="4" t="inlineStr">
         <is>
           <t>• Https://www.fue.edu.eg/contacts
 • Https://www.fue.edu.eg/about_fue/fue_people/top_management
 • Https://www.fue.edu.eg/international_support_center
-• Qianmu.org QS2027 list</t>
-        </is>
-      </c>
-      <c r="AI25" s="4" t="inlineStr">
+• Qianmu.org QS2027 list
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ25" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ25" s="4" t="inlineStr"/>
+      <c r="AK25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -6391,60 +6836,77 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S26" s="4" t="inlineStr"/>
+      <c r="S26" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: 1201–1400</t>
+        </is>
+      </c>
       <c r="T26" s="4" t="inlineStr">
         <is>
           <t>THE2027: 801–1000</t>
         </is>
       </c>
-      <c r="U26" s="4" t="inlineStr"/>
-      <c r="V26" s="4" t="n">
+      <c r="U26" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="W26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W26" s="4" t="inlineStr"/>
       <c r="X26" s="4" t="inlineStr"/>
       <c r="Y26" s="4" t="inlineStr"/>
       <c r="Z26" s="4" t="inlineStr"/>
       <c r="AA26" s="4" t="inlineStr"/>
       <c r="AB26" s="4" t="inlineStr"/>
-      <c r="AC26" s="4" t="n">
+      <c r="AC26" s="4" t="inlineStr"/>
+      <c r="AD26" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="AD26" s="8" t="inlineStr">
+      <c r="AE26" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE26" s="4" t="inlineStr">
+      <c r="AF26" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF26" s="4" t="inlineStr">
+      <c r="AG26" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG26" s="4" t="inlineStr">
+      <c r="AH26" s="4" t="inlineStr">
         <is>
           <t>• Имя президента транслитерировано с арабского (أ.د/ خالد على الدرندلى) — уточнить латинское написание
 • Culture@zu.edu.eg — ящик Управления культурных связей (конференции и международные контакты); канцелярия президента: presidency@zu.edu.eg, тел. 055 2302926
-• Спутниковой активности не найдено (1 поиск)</t>
-        </is>
-      </c>
-      <c r="AH26" s="4" t="inlineStr">
+• Спутниковой активности не найдено (1 поиск)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI26" s="4" t="inlineStr">
         <is>
           <t>• Https://www.zu.edu.eg/
 • Https://www.zu.edu.eg/Contents/Index/20
-• Https://www.zu.edu.eg/Contents/Section/1086</t>
-        </is>
-      </c>
-      <c r="AI26" s="4" t="inlineStr">
+• Https://www.zu.edu.eg/Contents/Section/1086
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ26" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ26" s="4" t="inlineStr"/>
+      <c r="AK26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -6534,61 +6996,76 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S27" s="4" t="inlineStr"/>
+      <c r="S27" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T27" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="U27" s="4" t="inlineStr"/>
-      <c r="V27" s="4" t="n">
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W27" s="4" t="inlineStr"/>
       <c r="X27" s="4" t="inlineStr"/>
       <c r="Y27" s="4" t="inlineStr"/>
       <c r="Z27" s="4" t="inlineStr"/>
       <c r="AA27" s="4" t="inlineStr"/>
       <c r="AB27" s="4" t="inlineStr"/>
-      <c r="AC27" s="4" t="n">
+      <c r="AC27" s="4" t="inlineStr"/>
+      <c r="AD27" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD27" s="8" t="inlineStr">
+      <c r="AE27" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE27" s="4" t="inlineStr">
+      <c r="AF27" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF27" s="4" t="inlineStr">
+      <c r="AG27" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG27" s="4" t="inlineStr">
+      <c r="AH27" s="4" t="inlineStr">
         <is>
           <t>• Президент — бывший министр высшего образования Египта
 • Телефон: только горячая линия 19592 (без кода страны)
 • E-mail международного отдела не опубликован; использовать info@buc.edu.eg
-• Спутниковой активности не найдено</t>
-        </is>
-      </c>
-      <c r="AH27" s="4" t="inlineStr">
+• Спутниковой активности не найдено
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI27" s="4" t="inlineStr">
         <is>
           <t>• Https://buc.edu.eg/
 • Https://buc.edu.eg/contact-us/
-• Https://buc.edu.eg/board-profiles/prof-dr-ashraf-mohamed-el-shihy/</t>
-        </is>
-      </c>
-      <c r="AI27" s="4" t="inlineStr">
+• Https://buc.edu.eg/board-profiles/prof-dr-ashraf-mohamed-el-shihy/
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ27" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ27" s="4" t="inlineStr"/>
+      <c r="AK27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -6687,61 +7164,77 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S28" s="4" t="inlineStr"/>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: 1401+</t>
+        </is>
+      </c>
       <c r="T28" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="U28" s="4" t="inlineStr"/>
-      <c r="V28" s="4" t="n">
+      <c r="U28" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W28" s="4" t="inlineStr"/>
       <c r="X28" s="4" t="inlineStr"/>
       <c r="Y28" s="4" t="inlineStr"/>
       <c r="Z28" s="4" t="inlineStr"/>
       <c r="AA28" s="4" t="inlineStr"/>
       <c r="AB28" s="4" t="inlineStr"/>
-      <c r="AC28" s="4" t="n">
+      <c r="AC28" s="4" t="inlineStr"/>
+      <c r="AD28" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD28" s="8" t="inlineStr">
+      <c r="AE28" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE28" s="4" t="inlineStr">
+      <c r="AF28" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF28" s="4" t="inlineStr">
+      <c r="AG28" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG28" s="4" t="inlineStr">
+      <c r="AH28" s="4" t="inlineStr">
         <is>
           <t>• Президент назначен президентским указом в сентябре 2023 г
 • Международный офис: тел. +20 13 3223213 доб. 1206, индекс 13511
-• Спутниковой активности не найдено</t>
-        </is>
-      </c>
-      <c r="AH28" s="4" t="inlineStr">
+• Спутниковой активности не найдено
+• Рейтинги: QS: в таблице как «Benha University - Egypt»; Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI28" s="4" t="inlineStr">
         <is>
           <t>• Https://bu.edu.eg/univ_info/president.php
 • Https://bu.edu.eg/univ_info/contact.php
 • Https://iro.bu.edu.eg/en/team
-• Https://iro.bu.edu.eg/en/contact</t>
-        </is>
-      </c>
-      <c r="AI28" s="4" t="inlineStr">
+• Https://iro.bu.edu.eg/en/contact
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ28" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ28" s="4" t="inlineStr"/>
+      <c r="AK28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -6836,59 +7329,74 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S29" s="4" t="inlineStr"/>
+      <c r="S29" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T29" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="U29" s="4" t="inlineStr"/>
-      <c r="V29" s="4" t="n">
+      <c r="U29" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W29" s="4" t="inlineStr"/>
       <c r="X29" s="4" t="inlineStr"/>
       <c r="Y29" s="4" t="inlineStr"/>
       <c r="Z29" s="4" t="inlineStr"/>
       <c r="AA29" s="4" t="inlineStr"/>
       <c r="AB29" s="4" t="inlineStr"/>
-      <c r="AC29" s="4" t="n">
+      <c r="AC29" s="4" t="inlineStr"/>
+      <c r="AD29" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD29" s="8" t="inlineStr">
+      <c r="AE29" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE29" s="4" t="inlineStr">
+      <c r="AF29" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF29" s="4" t="inlineStr">
+      <c r="AG29" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG29" s="4" t="inlineStr">
+      <c r="AH29" s="4" t="inlineStr">
         <is>
           <t>• Адрес из справочника universitiesegypt.com (телефон и e-mail совпадают с официальным сайтом)
 • Отдельного e-mail международного отдела не найдено — использовать info.portal@dmu.edu.eg
-• Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет</t>
-        </is>
-      </c>
-      <c r="AH29" s="4" t="inlineStr">
+• Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI29" s="4" t="inlineStr">
         <is>
           <t>• Https://damanhour.dmu.edu.eg/pages/default.aspx/
-• Https://www.universitiesegypt.com/damanhour-university/contacts</t>
-        </is>
-      </c>
-      <c r="AI29" s="4" t="inlineStr">
+• Https://www.universitiesegypt.com/damanhour-university/contacts
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ29" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ29" s="4" t="inlineStr"/>
+      <c r="AK29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -6973,60 +7481,66 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S30" s="4" t="inlineStr"/>
+      <c r="S30" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T30" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
       <c r="U30" s="4" t="inlineStr"/>
-      <c r="V30" s="4" t="n">
+      <c r="V30" s="4" t="inlineStr"/>
+      <c r="W30" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="4" t="inlineStr"/>
       <c r="X30" s="4" t="inlineStr"/>
       <c r="Y30" s="4" t="inlineStr"/>
       <c r="Z30" s="4" t="inlineStr"/>
       <c r="AA30" s="4" t="inlineStr"/>
       <c r="AB30" s="4" t="inlineStr"/>
-      <c r="AC30" s="4" t="n">
+      <c r="AC30" s="4" t="inlineStr"/>
+      <c r="AD30" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD30" s="8" t="inlineStr">
+      <c r="AE30" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE30" s="4" t="inlineStr">
+      <c r="AF30" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF30" s="4" t="inlineStr">
+      <c r="AG30" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG30" s="4" t="inlineStr">
+      <c r="AH30" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт du.edu.eg недоступен (503 / обрыв соединения, октябрь 2026); контакты из справочника universitiesegypt.com — требуют сверки
 • Космическая активность не проверялась поиском (лимит исчерпан); в nanosats.csv спутников нет
 • Президент д-р Хамдан Рабиа (حمدان ربيع) — подтверждён публикациями СМИ сентября–октября 2026 г. (Sada El-Omma, Al-Dostor); на официальном сайте не проверен (du.edu.eg и med.du.edu.eg недоступны 04.10.2026)
-• Перепроверка: Сайт по-прежнему недоступен; по СМИ 10.2026 добавлен президент д-р Хамдан Рабиа; контакты не перепроверены</t>
-        </is>
-      </c>
-      <c r="AH30" s="4" t="inlineStr">
+• Перепроверка: Сайт по-прежнему недоступен; по СМИ 10.2026 добавлен президент д-р Хамдан Рабиа; контакты не перепроверены
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026. Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI30" s="4" t="inlineStr">
         <is>
           <t>• Https://www.universitiesegypt.com/damietta-university/contacts
 • Https://ar.wikipedia.org/wiki/جامعة_دمياط</t>
         </is>
       </c>
-      <c r="AI30" s="4" t="inlineStr">
+      <c r="AJ30" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ30" s="4" t="inlineStr"/>
+      <c r="AK30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -7131,58 +7645,70 @@
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="U31" s="4" t="inlineStr"/>
-      <c r="V31" s="4" t="n">
+      <c r="U31" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W31" s="4" t="inlineStr"/>
       <c r="X31" s="4" t="inlineStr"/>
       <c r="Y31" s="4" t="inlineStr"/>
       <c r="Z31" s="4" t="inlineStr"/>
       <c r="AA31" s="4" t="inlineStr"/>
       <c r="AB31" s="4" t="inlineStr"/>
-      <c r="AC31" s="4" t="n">
+      <c r="AC31" s="4" t="inlineStr"/>
+      <c r="AD31" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD31" s="8" t="inlineStr">
+      <c r="AE31" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE31" s="4" t="inlineStr">
+      <c r="AF31" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF31" s="4" t="inlineStr">
+      <c r="AG31" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG31" s="4" t="inlineStr">
+      <c r="AH31" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт new.deltauniv.edu.eg рендерится через JavaScript (навигация через JS, страница «президент» отсутствует) — руководство и международный отдел на сайте проверить не удалось; info@deltauniv.edu.eg и горячая линия 15955 подтверждены на сайте 04.10.2026
 • Президент (Dr. Yehia El-Meshad / يحيى المشد) подтверждён только СМИ (июнь 2026); председатель совета попечителей — Dr. Mohamed Rabie
 • Телефон +20 50 2770140 и адрес — со стороннего справочника egyptianeducation.com
 • Не путать с Delta Technological University (جامعة الدلتا التكنولوجية)
 • Отдельного международного e-mail не найдено
-• Перепроверка: Общий e-mail и горячая линия подтверждены на официальном сайте 04.10.2026; президент — по СМИ 06.2026, на сайте не найден</t>
-        </is>
-      </c>
-      <c r="AH31" s="4" t="inlineStr">
+• Перепроверка: Общий e-mail и горячая линия подтверждены на официальном сайте 04.10.2026; президент — по СМИ 06.2026, на сайте не найден
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI31" s="4" t="inlineStr">
         <is>
           <t>• Https://new.deltauniv.edu.eg/EN/aboutdu/index
 • Https://www.egyptianeducation.com/delta-university-science-technology/contacts
 • Https://taleemalyoum.com/ (news 2026-06-08)
-• Qianmu.org QS2027 list</t>
-        </is>
-      </c>
-      <c r="AI31" s="4" t="inlineStr">
+• Qianmu.org QS2027 list
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ31" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ31" s="4" t="inlineStr"/>
+      <c r="AK31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -7277,61 +7803,76 @@
           <t>Acting President</t>
         </is>
       </c>
-      <c r="S32" s="4" t="inlineStr"/>
+      <c r="S32" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="U32" s="4" t="inlineStr"/>
-      <c r="V32" s="4" t="n">
+      <c r="U32" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W32" s="4" t="inlineStr"/>
       <c r="X32" s="4" t="inlineStr"/>
       <c r="Y32" s="4" t="inlineStr"/>
       <c r="Z32" s="4" t="inlineStr"/>
       <c r="AA32" s="4" t="inlineStr"/>
       <c r="AB32" s="4" t="inlineStr"/>
-      <c r="AC32" s="4" t="n">
+      <c r="AC32" s="4" t="inlineStr"/>
+      <c r="AD32" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD32" s="8" t="inlineStr">
+      <c r="AE32" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE32" s="4" t="inlineStr">
+      <c r="AF32" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF32" s="4" t="inlineStr">
+      <c r="AG32" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG32" s="4" t="inlineStr">
+      <c r="AH32" s="4" t="inlineStr">
         <is>
           <t>• Prof. Sherif El-Attar — исполняющий обязанности президента (с 01.08.2026), специальность — архитектура; личный e-mail sma00@fayoum.edu.eg
 • Presd@fayoum.edu.eg — ящик офиса президента; факс +20 84 2114095
 • Управление международных связей (International Relations Office, создано 2022) существует, но его e-mail на открытых страницах не опубликован (в поисковике фигурирует iro@fayoum.edu.eg — не проверено); тел. офиса +20 84 2114059
-• В QS2027 не найден; космической активности не найдено</t>
-        </is>
-      </c>
-      <c r="AH32" s="4" t="inlineStr">
+• В QS2027 не найден; космической активности не найдено
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI32" s="4" t="inlineStr">
         <is>
           <t>• Https://www.fayoum.edu.eg/en/EnterpriseSettings/UniversityPresident
 • Https://www.fayoum.edu.eg/en/EnterpriseSettings/presidentoffice
-• Https://www.fayoum.edu.eg/en/Faculty/TabContent/5095</t>
-        </is>
-      </c>
-      <c r="AI32" s="4" t="inlineStr">
+• Https://www.fayoum.edu.eg/en/Faculty/TabContent/5095
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ32" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ32" s="4" t="inlineStr"/>
+      <c r="AK32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -7379,19 +7920,36 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Galala City, Galala Plateau, Suez Governorate, Egypt</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr"/>
+          <t>Galala Plateau, Attaka, Suez, Egypt</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>info@gu.edu.eg</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>ФИО не найдено
+Обращение: Dear Director of International Relations,</t>
+        </is>
+      </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
           <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr"/>
-      <c r="N33" s="4" t="inlineStr"/>
-      <c r="O33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>info@gu.edu.eg</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>15888 (горячая линия, внутри Египта)</t>
+        </is>
+      </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
           <t>https://www.gu.edu.eg</t>
@@ -7407,57 +7965,70 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S33" s="4" t="inlineStr"/>
+      <c r="S33" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T33" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
       <c r="U33" s="4" t="inlineStr"/>
-      <c r="V33" s="4" t="n">
+      <c r="V33" s="4" t="inlineStr"/>
+      <c r="W33" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W33" s="4" t="inlineStr"/>
       <c r="X33" s="4" t="inlineStr"/>
       <c r="Y33" s="4" t="inlineStr"/>
       <c r="Z33" s="4" t="inlineStr"/>
       <c r="AA33" s="4" t="inlineStr"/>
       <c r="AB33" s="4" t="inlineStr"/>
-      <c r="AC33" s="4" t="n">
+      <c r="AC33" s="4" t="inlineStr"/>
+      <c r="AD33" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD33" s="8" t="inlineStr">
+      <c r="AE33" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE33" s="4" t="inlineStr"/>
       <c r="AF33" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>да</t>
         </is>
       </c>
       <c r="AG33" s="4" t="inlineStr">
+        <is>
+          <t>высокая</t>
+        </is>
+      </c>
+      <c r="AH33" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт gu.edu.eg недоступен из нашей сети (503 / ошибка TLS, повторно 04.10.2026) — контакты не верифицированы; требуется ручная проверка
 • Президент Prof. Dr. Mohamed El-Shinawi (проф. хирургии Ain Shams) — по официальным новостям gu.edu.eg 2026 г., видимым в поисковой выдаче
 • Партнёрство с Arizona State University (двойные дипломы); спутниковых проектов не найдено
-• Перепроверка: Президент проф. Mohamed El-Shinawi подтверждается официальными новостями gu.edu.eg (06.2026) по поисковой выдаче; сайт по-прежнему недоступен — контакты не найдены</t>
-        </is>
-      </c>
-      <c r="AH33" s="4" t="inlineStr">
+• Перепроверка: Президент проф. Mohamed El-Shinawi подтверждается официальными новостями gu.edu.eg (06.2026) по поисковой выдаче; сайт по-прежнему недоступен — контакты не найдены
+• Ручная проверка: Контакты прочитаны на официальном сайте 05.10.2026 (сессия с агентами). Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026. Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI33" s="4" t="inlineStr">
         <is>
           <t>• Https://www.timeshighereducation.com/world-university-rankings/galala-university
 • Https://en.wikipedia.org/wiki/Galala_University
-• Https://www.gu.edu.eg/2026/06/galala-university-president-speaks-at-international-conference-in-madrid-on-strengthening-public-private-collaboration-in-higher-education (snippet)</t>
-        </is>
-      </c>
-      <c r="AI33" s="4" t="inlineStr">
+• Https://www.gu.edu.eg/2026/06/galala-university-president-speaks-at-international-conference-in-madrid-on-strengthening-public-private-collaboration-in-higher-education (snippet)
+https://www.gu.edu.eg/contact/
+• Https://www.gu.edu.eg/president/
+• Https://www.gu.edu.eg/international-students/</t>
+        </is>
+      </c>
+      <c r="AJ33" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ33" s="4" t="inlineStr"/>
+      <c r="AK33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -7560,56 +8131,71 @@
           <t>QS2027: 1401+</t>
         </is>
       </c>
-      <c r="T34" s="4" t="inlineStr"/>
-      <c r="U34" s="4" t="inlineStr"/>
-      <c r="V34" s="4" t="n">
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U34" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W34" s="4" t="inlineStr"/>
       <c r="X34" s="4" t="inlineStr"/>
       <c r="Y34" s="4" t="inlineStr"/>
       <c r="Z34" s="4" t="inlineStr"/>
       <c r="AA34" s="4" t="inlineStr"/>
       <c r="AB34" s="4" t="inlineStr"/>
-      <c r="AC34" s="4" t="n">
+      <c r="AC34" s="4" t="inlineStr"/>
+      <c r="AD34" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD34" s="8" t="inlineStr">
+      <c r="AE34" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE34" s="4" t="inlineStr">
+      <c r="AF34" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF34" s="4" t="inlineStr">
+      <c r="AG34" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG34" s="4" t="inlineStr">
+      <c r="AH34" s="4" t="inlineStr">
         <is>
           <t>• Ящик международного направления — персональный адрес вице-президента по международным делам проф. Франка Гюнцера
 • У президента два варианта адреса на странице (yasser.higazi@ и yasser.higazy@guc.edu.eg); в поле указан первый, отображаемый под его именем
-• Горячая линия 16482; космическая активность поиском не проверялась (лимит поиска исчерпан), в nanosats.csv спутников нет</t>
-        </is>
-      </c>
-      <c r="AH34" s="4" t="inlineStr">
+• Горячая линия 16482; космическая активность поиском не проверялась (лимит поиска исчерпан), в nanosats.csv спутников нет
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI34" s="4" t="inlineStr">
         <is>
           <t>• Https://guc.edu.eg/
 • Https://guc.edu.eg/en/about_guc/trustees_council_deans/president_cabinet.aspx
 • Https://guc.edu.eg/en/contact.aspx
-• Https://www.qianmu.org/ranking/1528.htm (2027 QS list, qianmu.org)</t>
-        </is>
-      </c>
-      <c r="AI34" s="4" t="inlineStr">
+• Https://www.qianmu.org/ranking/1528.htm (2027 QS list, qianmu.org)
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)</t>
+        </is>
+      </c>
+      <c r="AJ34" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ34" s="4" t="inlineStr"/>
+      <c r="AK34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -7703,60 +8289,75 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S35" s="4" t="inlineStr"/>
+      <c r="S35" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T35" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="U35" s="4" t="inlineStr"/>
-      <c r="V35" s="4" t="n">
+      <c r="U35" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V35" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W35" s="4" t="inlineStr"/>
       <c r="X35" s="4" t="inlineStr"/>
       <c r="Y35" s="4" t="inlineStr"/>
       <c r="Z35" s="4" t="inlineStr"/>
       <c r="AA35" s="4" t="inlineStr"/>
       <c r="AB35" s="4" t="inlineStr"/>
-      <c r="AC35" s="4" t="n">
+      <c r="AC35" s="4" t="inlineStr"/>
+      <c r="AD35" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD35" s="8" t="inlineStr">
+      <c r="AE35" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE35" s="4" t="inlineStr">
+      <c r="AF35" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF35" s="4" t="inlineStr">
+      <c r="AG35" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG35" s="4" t="inlineStr">
+      <c r="AH35" s="4" t="inlineStr">
         <is>
           <t>• Есть Управление международных связей (IRO-HUE), но отдельный e-mail и руководитель не опубликованы — используется info@horus.edu.eg
 • Председатель попечительского совета — Prof. Ibrahim Saber
-• Спутников нет (проверка по сайту и nanosats.csv; веб-поиск исчерпан)</t>
-        </is>
-      </c>
-      <c r="AH35" s="4" t="inlineStr">
+• Спутников нет (проверка по сайту и nanosats.csv; веб-поиск исчерпан)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI35" s="4" t="inlineStr">
         <is>
           <t>• Https://horus.edu.eg/
 • Https://horus.edu.eg/contact-us/
-• Https://horus.edu.eg/international-relations-office-iro-hue/</t>
-        </is>
-      </c>
-      <c r="AI35" s="4" t="inlineStr">
+• Https://horus.edu.eg/international-relations-office-iro-hue/
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ35" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ35" s="4" t="inlineStr"/>
+      <c r="AK35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -7832,59 +8433,65 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S36" s="4" t="inlineStr"/>
+      <c r="S36" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T36" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
       <c r="U36" s="4" t="inlineStr"/>
-      <c r="V36" s="4" t="n">
+      <c r="V36" s="4" t="inlineStr"/>
+      <c r="W36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="4" t="inlineStr"/>
       <c r="X36" s="4" t="inlineStr"/>
       <c r="Y36" s="4" t="inlineStr"/>
       <c r="Z36" s="4" t="inlineStr"/>
       <c r="AA36" s="4" t="inlineStr"/>
       <c r="AB36" s="4" t="inlineStr"/>
-      <c r="AC36" s="4" t="n">
+      <c r="AC36" s="4" t="inlineStr"/>
+      <c r="AD36" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD36" s="8" t="inlineStr">
+      <c r="AE36" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE36" s="4" t="inlineStr"/>
-      <c r="AF36" s="4" t="inlineStr">
+      <c r="AF36" s="4" t="inlineStr"/>
+      <c r="AG36" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG36" s="4" t="inlineStr">
+      <c r="AH36" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт menofia.edu.eg недоступен из среды (блокировка прокси/DNS) — контакты не проверены
 • ВАЖНО: в сент. 2026 Высший совет университетов объявил конкурс на пост президента (приём заявок с 10.10.2026) — руководитель может смениться в ближайшие месяцы; проверить перед отправкой
 • Непроверенные (из поисковой выдачи) адреса: president@menofia.edu.eg, menofia@menofia.edu.eg; телефоны из справочников: +20 48 2224216 (edarabia), +20 48 232 9094 (WIPO TISC)
 • Адрес — по справочнику WIPO TISC
 • В QS2027 не найден; космической активности не найдено
-• Перепроверка: 04.10.2026: menofia.edu.eg недоступен (503/сброс), портал Высшего совета университетов scu.eg не отдаёт данные без JS — данные не изменены</t>
-        </is>
-      </c>
-      <c r="AH36" s="4" t="inlineStr">
+• Перепроверка: 04.10.2026: menofia.edu.eg недоступен (503/сброс), портал Высшего совета университетов scu.eg не отдаёт данные без JS — данные не изменены
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026. Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI36" s="4" t="inlineStr">
         <is>
           <t>• Https://alkhabaralyoum.com/2026/09/26/ (news)
 • Https://www.cairomubasher.com/235786
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=12548</t>
         </is>
       </c>
-      <c r="AI36" s="4" t="inlineStr">
+      <c r="AJ36" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ36" s="4" t="inlineStr"/>
+      <c r="AK36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -7975,61 +8582,67 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S37" s="4" t="inlineStr"/>
+      <c r="S37" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T37" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
       <c r="U37" s="4" t="inlineStr"/>
-      <c r="V37" s="4" t="n">
+      <c r="V37" s="4" t="inlineStr"/>
+      <c r="W37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W37" s="4" t="inlineStr"/>
       <c r="X37" s="4" t="inlineStr"/>
       <c r="Y37" s="4" t="inlineStr"/>
       <c r="Z37" s="4" t="inlineStr"/>
       <c r="AA37" s="4" t="inlineStr"/>
       <c r="AB37" s="4" t="inlineStr"/>
-      <c r="AC37" s="4" t="n">
+      <c r="AC37" s="4" t="inlineStr"/>
+      <c r="AD37" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD37" s="8" t="inlineStr">
+      <c r="AE37" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE37" s="4" t="inlineStr">
+      <c r="AF37" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF37" s="4" t="inlineStr">
+      <c r="AG37" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG37" s="4" t="inlineStr">
+      <c r="AH37" s="4" t="inlineStr">
         <is>
           <t>• Сайт minia.edu.eg недоступен (DNS) — e-mail президента (president@mu.edu.eg, также presid.office@mu.edu.eg) взят из поисковой выдержки официальной страницы
 • Почтовый индекс и телефон не подтверждены
 • E-mail международного отдела не найден
-• Спутниковой активности не найдено</t>
-        </is>
-      </c>
-      <c r="AH37" s="4" t="inlineStr">
+• Спутниковой активности не найдено
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026. Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI37" s="4" t="inlineStr">
         <is>
           <t>• Https://www.minia.edu.eg/minia/Engmail.aspx
 • Https://www.minia.edu.eg/Minia/Econtact.aspx
 • Https://www.maspero.eg/our-reporters/2026/09/20/990867/</t>
         </is>
       </c>
-      <c r="AI37" s="4" t="inlineStr">
+      <c r="AJ37" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ37" s="4" t="inlineStr"/>
+      <c r="AK37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -8120,63 +8733,78 @@
           <t>Acting President</t>
         </is>
       </c>
-      <c r="S38" s="4" t="inlineStr"/>
+      <c r="S38" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T38" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1801–2000</t>
         </is>
       </c>
-      <c r="U38" s="4" t="inlineStr"/>
-      <c r="V38" s="4" t="n">
+      <c r="U38" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W38" s="4" t="inlineStr"/>
       <c r="X38" s="4" t="inlineStr"/>
       <c r="Y38" s="4" t="inlineStr"/>
       <c r="Z38" s="4" t="inlineStr"/>
       <c r="AA38" s="4" t="inlineStr"/>
       <c r="AB38" s="4" t="inlineStr"/>
-      <c r="AC38" s="4" t="n">
+      <c r="AC38" s="4" t="inlineStr"/>
+      <c r="AD38" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD38" s="8" t="inlineStr">
+      <c r="AE38" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE38" s="4" t="inlineStr">
+      <c r="AF38" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF38" s="4" t="inlineStr">
+      <c r="AG38" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG38" s="4" t="inlineStr">
+      <c r="AH38" s="4" t="inlineStr">
         <is>
           <t>• Prof. Hala El-Menoufy — исполняющая обязанности президента (Acting President)
 • Опубликован только короткий номер 16878; полного телефона с +20 на сайте нет
 • Есть сектор по делам иностранных студентов (International Students Affairs Sector), но отдельного e-mail нет — писать на info@must.edu.eg
 • Профиль преимущественно медико-фармацевтический; космической активности на сайте не найдено (поисковая проверка не выполнена — исчерпана квота поиска)
-• В QS2027 не найден</t>
-        </is>
-      </c>
-      <c r="AH38" s="4" t="inlineStr">
+• В QS2027 не найден
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI38" s="4" t="inlineStr">
         <is>
           <t>• Https://must.edu.eg/
 • Https://must.edu.eg/about-must/president/
 • Https://must.edu.eg/contact/
-• Https://must.edu.eg/sectors/international-students-affairs-sector/</t>
-        </is>
-      </c>
-      <c r="AI38" s="4" t="inlineStr">
+• Https://must.edu.eg/sectors/international-students-affairs-sector/
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ38" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ38" s="4" t="inlineStr"/>
+      <c r="AK38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -8256,56 +8884,62 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S39" s="4" t="inlineStr"/>
+      <c r="S39" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T39" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
       <c r="U39" s="4" t="inlineStr"/>
-      <c r="V39" s="4" t="n">
+      <c r="V39" s="4" t="inlineStr"/>
+      <c r="W39" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W39" s="4" t="inlineStr"/>
       <c r="X39" s="4" t="inlineStr"/>
       <c r="Y39" s="4" t="inlineStr"/>
       <c r="Z39" s="4" t="inlineStr"/>
       <c r="AA39" s="4" t="inlineStr"/>
       <c r="AB39" s="4" t="inlineStr"/>
-      <c r="AC39" s="4" t="n">
+      <c r="AC39" s="4" t="inlineStr"/>
+      <c r="AD39" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD39" s="8" t="inlineStr">
+      <c r="AE39" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE39" s="4" t="inlineStr"/>
-      <c r="AF39" s="4" t="inlineStr">
+      <c r="AF39" s="4" t="inlineStr"/>
+      <c r="AG39" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG39" s="4" t="inlineStr">
+      <c r="AH39" s="4" t="inlineStr">
         <is>
           <t>• Сайт nvu.edu.eg недоступен — официальный общий и международный e-mail не подтверждены (в агрегаторах встречается portal@nvu.edu.eg)
 • В СМИ сообщалось о судебном разбирательстве с участием президента университета (дело об исполнении судебного решения) — учесть при обращении
-• Спутниковой активности не найдено</t>
-        </is>
-      </c>
-      <c r="AH39" s="4" t="inlineStr">
+• Спутниковой активности не найдено
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026. Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI39" s="4" t="inlineStr">
         <is>
           <t>• Https://www.youm7.com/story/2026/9/16/7548695
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=11058
 • Https://nvu.edu.eg/leaderstop.php</t>
         </is>
       </c>
-      <c r="AI39" s="4" t="inlineStr">
+      <c r="AJ39" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ39" s="4" t="inlineStr"/>
+      <c r="AK39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -8403,61 +9037,76 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S40" s="4" t="inlineStr"/>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T40" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
-      <c r="U40" s="4" t="inlineStr"/>
-      <c r="V40" s="4" t="n">
+      <c r="U40" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V40" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W40" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W40" s="4" t="inlineStr"/>
       <c r="X40" s="4" t="inlineStr"/>
       <c r="Y40" s="4" t="inlineStr"/>
       <c r="Z40" s="4" t="inlineStr"/>
       <c r="AA40" s="4" t="inlineStr"/>
       <c r="AB40" s="4" t="inlineStr"/>
-      <c r="AC40" s="4" t="n">
+      <c r="AC40" s="4" t="inlineStr"/>
+      <c r="AD40" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD40" s="8" t="inlineStr">
+      <c r="AE40" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE40" s="4" t="inlineStr">
+      <c r="AF40" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF40" s="4" t="inlineStr">
+      <c r="AG40" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG40" s="4" t="inlineStr">
+      <c r="AH40" s="4" t="inlineStr">
         <is>
           <t>• Имя президента (проф. Гамаль Сами) подтверждено новостью сайта 2024 г. и Википедией; подтверждения 2025–2026 не найдено — сверить
 • Ilca@o6u.edu.eg — Управление международных и местных культурных связей (Admin of International &amp; Local Cultural Affairs); руководитель не указан
-• Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет</t>
-        </is>
-      </c>
-      <c r="AH40" s="4" t="inlineStr">
+• Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI40" s="4" t="inlineStr">
         <is>
           <t>• Https://o6u.edu.eg/dpagesuni.aspx?FactId=0&amp;id=935
 • Https://o6u.edu.eg/default.aspx?id=70
 • Https://o6u.edu.eg/UniversityNewsDetailes.aspx?FactId=0&amp;News=22067
-• Https://en.wikipedia.org/wiki/October_6_University</t>
-        </is>
-      </c>
-      <c r="AI40" s="4" t="inlineStr">
+• Https://en.wikipedia.org/wiki/October_6_University
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ40" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ40" s="4" t="inlineStr"/>
+      <c r="AK40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -8551,61 +9200,76 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S41" s="4" t="inlineStr"/>
+      <c r="S41" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T41" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1601–1800</t>
         </is>
       </c>
-      <c r="U41" s="4" t="inlineStr"/>
-      <c r="V41" s="4" t="n">
+      <c r="U41" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V41" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W41" s="4" t="inlineStr"/>
       <c r="X41" s="4" t="inlineStr"/>
       <c r="Y41" s="4" t="inlineStr"/>
       <c r="Z41" s="4" t="inlineStr"/>
       <c r="AA41" s="4" t="inlineStr"/>
       <c r="AB41" s="4" t="inlineStr"/>
-      <c r="AC41" s="4" t="n">
+      <c r="AC41" s="4" t="inlineStr"/>
+      <c r="AD41" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD41" s="8" t="inlineStr">
+      <c r="AE41" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE41" s="4" t="inlineStr">
+      <c r="AF41" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF41" s="4" t="inlineStr">
+      <c r="AG41" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG41" s="4" t="inlineStr">
+      <c r="AH41" s="4" t="inlineStr">
         <is>
           <t>• Сайт pua.edu.eg снова доступен (04.10.2026): президент, общий e-mail, телефон и адрес подтверждены; прежний номер +20 3 3877000 из справочника был неверным — исправлен на +20 3 3877700
 • На сайте есть ящик International.Students@pua.edu.eg (тел. +20 3 3877872 / 3877886) — офис регистрации иностранных студентов, не отдел партнёрств; отдельный e-mail международного отдела не найден
 • Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет
-• Перепроверка: Президент проф. Махмуд Мохи Эль-Дин, info@pua.edu.eg, телефон и адрес подтверждены на pua.edu.eg 04.10.2026; телефон исправлен</t>
-        </is>
-      </c>
-      <c r="AH41" s="4" t="inlineStr">
+• Перепроверка: Президент проф. Махмуд Мохи Эль-Дин, info@pua.edu.eg, телефон и адрес подтверждены на pua.edu.eg 04.10.2026; телефон исправлен
+• Рейтинги: THE: в таблице как «Pharos University»; Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI41" s="4" t="inlineStr">
         <is>
           <t>• Https://www.pua.edu.eg/
 • Https://www.pua.edu.eg/about-pua/message-from-the-president-of-pharos-university/
-• Https://en.wikipedia.org/wiki/Pharos_University_in_Alexandria</t>
-        </is>
-      </c>
-      <c r="AI41" s="4" t="inlineStr">
+• Https://en.wikipedia.org/wiki/Pharos_University_in_Alexandria
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ41" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ41" s="4" t="inlineStr"/>
+      <c r="AK41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -8699,62 +9363,77 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S42" s="4" t="inlineStr"/>
+      <c r="S42" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T42" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="U42" s="4" t="inlineStr"/>
-      <c r="V42" s="4" t="n">
+      <c r="U42" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V42" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W42" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W42" s="4" t="inlineStr"/>
       <c r="X42" s="4" t="inlineStr"/>
       <c r="Y42" s="4" t="inlineStr"/>
       <c r="Z42" s="4" t="inlineStr"/>
       <c r="AA42" s="4" t="inlineStr"/>
       <c r="AB42" s="4" t="inlineStr"/>
-      <c r="AC42" s="4" t="n">
+      <c r="AC42" s="4" t="inlineStr"/>
+      <c r="AD42" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD42" s="8" t="inlineStr">
+      <c r="AE42" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE42" s="4" t="inlineStr">
+      <c r="AF42" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF42" s="4" t="inlineStr">
+      <c r="AG42" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG42" s="4" t="inlineStr">
+      <c r="AH42" s="4" t="inlineStr">
         <is>
           <t>• Qena University — новое название South Valley University (جامعة جنوب الوادي); в списке также есть строка «South Valley University» — это ДУБЛЬ одного и того же вуза, отправлять одно письмо
 • Адрес, телефон и info@svu.edu.eg взяты из справочников/поисковых выдержек, на официальной странице не подтверждены
 • E-mail международного отдела не найден
-• Спутниковой активности не найдено</t>
-        </is>
-      </c>
-      <c r="AH42" s="4" t="inlineStr">
+• Спутниковой активности не найдено
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI42" s="4" t="inlineStr">
         <is>
           <t>• Https://www.svu.edu.eg/en/
 • Https://www.youm7.com/story/2026/6/4/7437439
 • Https://en.wikipedia.org/wiki/Qena_University
-• Https://www.wipo.int/tisc/en/search/details.jsp?id=10024</t>
-        </is>
-      </c>
-      <c r="AI42" s="4" t="inlineStr">
+• Https://www.wipo.int/tisc/en/search/details.jsp?id=10024
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ42" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ42" s="4" t="inlineStr"/>
+      <c r="AK42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -8826,56 +9505,62 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S43" s="4" t="inlineStr"/>
+      <c r="S43" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T43" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1201–1400</t>
         </is>
       </c>
       <c r="U43" s="4" t="inlineStr"/>
-      <c r="V43" s="4" t="n">
+      <c r="V43" s="4" t="inlineStr"/>
+      <c r="W43" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W43" s="4" t="inlineStr"/>
       <c r="X43" s="4" t="inlineStr"/>
       <c r="Y43" s="4" t="inlineStr"/>
       <c r="Z43" s="4" t="inlineStr"/>
       <c r="AA43" s="4" t="inlineStr"/>
       <c r="AB43" s="4" t="inlineStr"/>
-      <c r="AC43" s="4" t="n">
+      <c r="AC43" s="4" t="inlineStr"/>
+      <c r="AD43" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD43" s="8" t="inlineStr">
+      <c r="AE43" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE43" s="4" t="inlineStr"/>
-      <c r="AF43" s="4" t="inlineStr">
+      <c r="AF43" s="4" t="inlineStr"/>
+      <c r="AG43" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG43" s="4" t="inlineStr">
+      <c r="AH43" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт недоступен из нашей сети (503/таймаут), поиск исчерпан — контакты и руководитель не верифицированы; требуется ручная проверка
 • По Википедии (не верифицировано) президент — Abdul Azim Al-Sharkawy
 • Не путать с Suez Canal University (Исмаилия), которая подписала протокол с EgSA в 2021 г
-• Перепроверка: 04.10.2026: сайт suezuni.edu.eg по-прежнему недоступен (curl — нет соединения, WebFetch — 503); данные не изменены</t>
-        </is>
-      </c>
-      <c r="AH43" s="4" t="inlineStr">
+• Перепроверка: 04.10.2026: сайт suezuni.edu.eg по-прежнему недоступен (curl — нет соединения, WebFetch — 503); данные не изменены
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026. Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI43" s="4" t="inlineStr">
         <is>
           <t>• Https://www.timeshighereducation.com/world-university-rankings/suez-university
 • Https://en.wikipedia.org/wiki/Suez_University</t>
         </is>
       </c>
-      <c r="AI43" s="4" t="inlineStr">
+      <c r="AJ43" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ43" s="4" t="inlineStr"/>
+      <c r="AK43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -8980,55 +9665,68 @@
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
-      <c r="U44" s="4" t="inlineStr"/>
-      <c r="V44" s="4" t="n">
+      <c r="U44" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V44" s="4" t="inlineStr">
+        <is>
+          <t>1175</t>
+        </is>
+      </c>
+      <c r="W44" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W44" s="4" t="inlineStr"/>
       <c r="X44" s="4" t="inlineStr"/>
       <c r="Y44" s="4" t="inlineStr"/>
       <c r="Z44" s="4" t="inlineStr"/>
       <c r="AA44" s="4" t="inlineStr"/>
       <c r="AB44" s="4" t="inlineStr"/>
-      <c r="AC44" s="4" t="n">
+      <c r="AC44" s="4" t="inlineStr"/>
+      <c r="AD44" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD44" s="8" t="inlineStr">
+      <c r="AE44" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE44" s="4" t="inlineStr">
+      <c r="AF44" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF44" s="4" t="inlineStr">
+      <c r="AG44" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG44" s="4" t="inlineStr">
+      <c r="AH44" s="4" t="inlineStr">
         <is>
           <t>• Президент проф. Мохамед Хусейн Махмуд назначен президентским указом с 26.03.2025
 • Есть только ящик офиса иностранных студентов international_std@unv.tanta.edu.eg (приём студентов) — можно поставить в копию; отдельного ящика по международному сотрудничеству не найдено
-• Запущенных спутников не найдено (быстрая проверка)</t>
-        </is>
-      </c>
-      <c r="AH44" s="4" t="inlineStr">
+• Запущенных спутников не найдено (быстрая проверка)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI44" s="4" t="inlineStr">
         <is>
           <t>• Https://tanta.edu.eg/
 • Https://tanta.edu.eg/President.aspx
 • Https://international-students.tanta.edu.eg/
-• Https://www.qianmu.org/ranking/1528.htm (2027 QS list, qianmu.org)</t>
-        </is>
-      </c>
-      <c r="AI44" s="4" t="inlineStr">
+• Https://www.qianmu.org/ranking/1528.htm (2027 QS list, qianmu.org)
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ44" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ44" s="4" t="inlineStr"/>
+      <c r="AK44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -9133,58 +9831,70 @@
           <t>THE2027: 1401–1600</t>
         </is>
       </c>
-      <c r="U45" s="4" t="inlineStr"/>
-      <c r="V45" s="4" t="n">
+      <c r="U45" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V45" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W45" s="4" t="inlineStr"/>
       <c r="X45" s="4" t="inlineStr"/>
       <c r="Y45" s="4" t="inlineStr"/>
       <c r="Z45" s="4" t="inlineStr"/>
       <c r="AA45" s="4" t="inlineStr"/>
       <c r="AB45" s="4" t="inlineStr"/>
-      <c r="AC45" s="4" t="n">
+      <c r="AC45" s="4" t="inlineStr"/>
+      <c r="AD45" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD45" s="8" t="inlineStr">
+      <c r="AE45" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE45" s="4" t="inlineStr">
+      <c r="AF45" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF45" s="4" t="inlineStr">
+      <c r="AG45" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG45" s="4" t="inlineStr">
+      <c r="AH45" s="4" t="inlineStr">
         <is>
           <t>• Некоммерческий частный вуз, созданный по межправительственному соглашению Египта и Великобритании; дипломы валидируются британскими вузами
 • Отдельного международного офиса/e-mail нет; отдел «Students Recruitment and Partnerships» (studentrecruitment@bue.edu.eg) ориентирован на абитуриентов — писать на info@bue.edu.eg
 • Телефон 19283 — горячая линия (короткий номер)
 • Председатель совета попечителей — Ms Farida Mohamed Farid Khamis
-• Космической активности на сайте не найдено (поисковая проверка не выполнена — исчерпана квота поиска)</t>
-        </is>
-      </c>
-      <c r="AH45" s="4" t="inlineStr">
+• Космической активности на сайте не найдено (поисковая проверка не выполнена — исчерпана квота поиска)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI45" s="4" t="inlineStr">
         <is>
           <t>• Https://www.bue.edu.eg/
 • Https://www.bue.edu.eg/leadership-structure
 • Https://www.bue.edu.eg/contact-us
 • Https://www.bue.edu.eg/administrative-departments/the-students-recruitment-and-partnerships-bue
-• Qianmu.org QS2027 list</t>
-        </is>
-      </c>
-      <c r="AI45" s="4" t="inlineStr">
+• Qianmu.org QS2027 list
+https://www.topuniversities.com/world-university-rankings (QS WUR 2027)
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ45" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ45" s="4" t="inlineStr"/>
+      <c r="AK45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -9279,41 +9989,46 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S46" s="4" t="inlineStr"/>
+      <c r="S46" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T46" s="4" t="inlineStr">
         <is>
           <t>THE2027: 1001–1200</t>
         </is>
       </c>
       <c r="U46" s="4" t="inlineStr"/>
-      <c r="V46" s="4" t="n">
+      <c r="V46" s="4" t="inlineStr"/>
+      <c r="W46" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W46" s="4" t="inlineStr"/>
       <c r="X46" s="4" t="inlineStr"/>
       <c r="Y46" s="4" t="inlineStr"/>
       <c r="Z46" s="4" t="inlineStr"/>
       <c r="AA46" s="4" t="inlineStr"/>
       <c r="AB46" s="4" t="inlineStr"/>
-      <c r="AC46" s="4" t="n">
+      <c r="AC46" s="4" t="inlineStr"/>
+      <c r="AD46" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="AD46" s="8" t="inlineStr">
+      <c r="AE46" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE46" s="4" t="inlineStr">
+      <c r="AF46" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF46" s="4" t="inlineStr">
+      <c r="AG46" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG46" s="4" t="inlineStr">
+      <c r="AH46" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт usc.edu.eg недоступен (блокировка прокси / DNS) — данные из WHED, справочника и СМИ
 • Президент Dr. Nasser Abdel-Bary (ناصر عبد الباري) подтверждён СМИ за сен. 2026; в WHED указан устаревший и.о. Ahmed Azab; учёное звание Prof. не проверено
@@ -9321,10 +10036,11 @@
 • E-mail info@usc.edu.eg и телефон — со стороннего справочника universitiesegypt.com
 • В QS2027 не найден
 • Сайт Минвысобразования Египта (mohesr.gov.eg, 30.08.2025) называл президентом д-р Шаден Муавия (شادن معاوية); СМИ фев. и сен. 2026 — Nasser Abdel-Bary, т.е. вероятна смена руководителя; официального решения о назначении не найдено
-• Перепроверка: Сайт usc.edu.eg по-прежнему недоступен (curl/WebFetch 503); на сайте Минвысобразования найдено, что в авг. 2025 президентом была д-р Шаден Муавия — текущий президент Nasser Abdel-Bary (СМИ 2026) официально не подтверждён; контакты не изменены</t>
-        </is>
-      </c>
-      <c r="AH46" s="4" t="inlineStr">
+• Перепроверка: Сайт usc.edu.eg по-прежнему недоступен (curl/WebFetch 503); на сайте Минвысобразования найдено, что в авг. 2025 президентом была д-р Шаден Муавия — текущий президент Nasser Abdel-Bary (СМИ 2026) официально не подтверждён; контакты не изменены
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026. Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI46" s="4" t="inlineStr">
         <is>
           <t>• Https://whed.net/institutions/IAU-020464
 • Https://www.universitiesegypt.com/university-sadat-city/contacts
@@ -9332,12 +10048,12 @@
 • Https://www.youm7.com/story/2026/2/26/7320365</t>
         </is>
       </c>
-      <c r="AI46" s="4" t="inlineStr">
+      <c r="AJ46" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ46" s="4" t="inlineStr"/>
+      <c r="AK46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -9431,60 +10147,79 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S47" s="4" t="inlineStr"/>
-      <c r="T47" s="4" t="inlineStr"/>
-      <c r="U47" s="4" t="inlineStr"/>
-      <c r="V47" s="4" t="n">
+      <c r="S47" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T47" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U47" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V47" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W47" s="4" t="inlineStr"/>
       <c r="X47" s="4" t="inlineStr"/>
       <c r="Y47" s="4" t="inlineStr"/>
       <c r="Z47" s="4" t="inlineStr"/>
       <c r="AA47" s="4" t="inlineStr"/>
       <c r="AB47" s="4" t="inlineStr"/>
-      <c r="AC47" s="4" t="n">
+      <c r="AC47" s="4" t="inlineStr"/>
+      <c r="AD47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD47" s="8" t="inlineStr">
+      <c r="AE47" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE47" s="4" t="inlineStr">
+      <c r="AF47" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF47" s="4" t="inlineStr">
+      <c r="AG47" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG47" s="4" t="inlineStr">
+      <c r="AH47" s="4" t="inlineStr">
         <is>
           <t>• THE2027: только статус Reporter (без ранга)
 • Сайт www.acu.edu.eg отдаёт 403, но acu.edu.eg (без www) доступен
 • Ранее указанный телефон +20 2 38333078 на официальном сайте не найден — заменён горячей линией 19228; отдельный e-mail международного отдела не опубликован (есть раздел «Международные партнёрства»)
 • Председатель совета попечителей — проф. Мохамед Фаиз Фархат (глава Al-Ahram)
 • Спутниковой активности не найдено
-• Перепроверка: Сайт открылся по адресу без www (acu.edu.eg) 04.10.2026: президент — проф. Ахмед Мохамед Анани (страница руководства + новость 19.07.2026), прежнее имя Amal Fawzy Ahmed исправлено; адрес, info@acu.edu.eg и горячая линия 19228 подтверждены на странице контактов</t>
-        </is>
-      </c>
-      <c r="AH47" s="4" t="inlineStr">
+• Перепроверка: Сайт открылся по адресу без www (acu.edu.eg) 04.10.2026: президент — проф. Ахмед Мохамед Анани (страница руководства + новость 19.07.2026), прежнее имя Amal Fawzy Ahmed исправлено; адрес, info@acu.edu.eg и горячая линия 19228 подтверждены на странице контактов
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI47" s="4" t="inlineStr">
         <is>
           <t>• Https://acu.edu.eg/about-the-council/university-leaders
 • Https://acu.edu.eg/en/contact-us
 • Https://acu.edu.eg/news
-• Https://english.ahram.org.eg/NewsContent/1/2/569449/Egypt/Society/Ahram-Canadian-University-achieves-new-milestone-i.aspx</t>
-        </is>
-      </c>
-      <c r="AI47" s="4" t="inlineStr">
+• Https://english.ahram.org.eg/NewsContent/1/2/569449/Egypt/Society/Ahram-Canadian-University-achieves-new-milestone-i.aspx
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ47" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ47" s="4" t="inlineStr"/>
+      <c r="AK47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -9532,77 +10267,112 @@
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>New Alamein City, Matrouh Governorate, Egypt</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr"/>
-      <c r="K48" s="4" t="inlineStr"/>
+          <t>District ED1 on the C4B Road, Southern Eastern Region, New Alamein City, Matrouh Governorate, Egypt</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>info@Aiu.edu.eg</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Essam ElKordi
+President
+Обращение: Dear Prof. ElKordi,</t>
+        </is>
+      </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
           <t>нет ящика: Найти e-mail международного отдела или канцелярии</t>
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr"/>
-      <c r="N48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>info@Aiu.edu.eg</t>
+        </is>
+      </c>
       <c r="O48" s="4" t="inlineStr"/>
       <c r="P48" s="4" t="inlineStr">
         <is>
           <t>https://aiu.edu.eg</t>
         </is>
       </c>
-      <c r="Q48" s="4" t="inlineStr"/>
+      <c r="Q48" s="4" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Essam Ahmed ElKordi</t>
+        </is>
+      </c>
       <c r="R48" s="4" t="inlineStr">
         <is>
           <t>President</t>
         </is>
       </c>
-      <c r="S48" s="4" t="inlineStr"/>
-      <c r="T48" s="4" t="inlineStr"/>
+      <c r="S48" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T48" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="U48" s="4" t="inlineStr"/>
-      <c r="V48" s="4" t="n">
+      <c r="V48" s="4" t="inlineStr"/>
+      <c r="W48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W48" s="4" t="inlineStr"/>
       <c r="X48" s="4" t="inlineStr"/>
       <c r="Y48" s="4" t="inlineStr"/>
       <c r="Z48" s="4" t="inlineStr"/>
       <c r="AA48" s="4" t="inlineStr"/>
       <c r="AB48" s="4" t="inlineStr"/>
-      <c r="AC48" s="4" t="n">
+      <c r="AC48" s="4" t="inlineStr"/>
+      <c r="AD48" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD48" s="8" t="inlineStr">
+      <c r="AE48" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE48" s="4" t="inlineStr"/>
       <c r="AF48" s="4" t="inlineStr">
         <is>
-          <t>низкая</t>
+          <t>да</t>
         </is>
       </c>
       <c r="AG48" s="4" t="inlineStr">
+        <is>
+          <t>высокая</t>
+        </is>
+      </c>
+      <c r="AH48" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт aiu.edu.eg (http/https, www) по-прежнему недоступен из нашей сети (503/таймаут, в т.ч. через WebFetch) — контакты и руководитель не верифицированы; требуется ручная проверка
 • По Википедии и поисковой выдаче (без даты/официального источника) президент — Prof. Dr. Essam Elkordi (عصام الكردي); председатель совета — Dr. Ahmed Mahmoud — не подтверждено, в поля не внесено
 • Вуз активен в международной работе (участие в EAIE 2026, Глазго — по СМИ)
 • Арабское название не сверено с официальным сайтом
-• Перепроверка: Сайт недоступен; данные не изменены (президент Essam Elkordi — только по вторичным источникам)</t>
-        </is>
-      </c>
-      <c r="AH48" s="4" t="inlineStr">
+• Перепроверка: Сайт недоступен; данные не изменены (президент Essam Elkordi — только по вторичным источникам)
+• Ручная проверка: Контакты прочитаны на официальном сайте 05.10.2026 (сессия с агентами). Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI48" s="4" t="inlineStr">
         <is>
           <t>• Https://www.timeshighereducation.com/world-university-rankings/alamein-international-university
-• Https://en.wikipedia.org/wiki/Alamein_International_University</t>
-        </is>
-      </c>
-      <c r="AI48" s="4" t="inlineStr">
+• Https://en.wikipedia.org/wiki/Alamein_International_University
+https://aiu.edu.eg/aiu-president/
+• Https://aiu.edu.eg/contact-us/
+• Https://aiu.edu.eg/international-collaboration/</t>
+        </is>
+      </c>
+      <c r="AJ48" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ48" s="4" t="inlineStr"/>
+      <c r="AK48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -9696,45 +10466,63 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S49" s="4" t="inlineStr"/>
-      <c r="T49" s="4" t="inlineStr"/>
-      <c r="U49" s="4" t="inlineStr"/>
-      <c r="V49" s="4" t="n">
+      <c r="S49" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T49" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U49" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V49" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W49" s="4" t="inlineStr"/>
       <c r="X49" s="4" t="inlineStr"/>
       <c r="Y49" s="4" t="inlineStr"/>
       <c r="Z49" s="4" t="inlineStr"/>
       <c r="AA49" s="4" t="inlineStr"/>
       <c r="AB49" s="4" t="inlineStr"/>
-      <c r="AC49" s="4" t="n">
+      <c r="AC49" s="4" t="inlineStr"/>
+      <c r="AD49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD49" s="8" t="inlineStr">
+      <c r="AE49" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE49" s="4" t="inlineStr">
+      <c r="AF49" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF49" s="4" t="inlineStr">
+      <c r="AG49" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG49" s="4" t="inlineStr">
+      <c r="AH49" s="4" t="inlineStr">
         <is>
           <t>• Национальный (ахлия) университет при Alexandria University; руководство — и.о. (Ahmed Adel Abdel Hakim, он же и.о. президента Alexandria University по данным СМИ, сентябрь 2026)
 • Спутниковой активности не найдено
 • Сайт anu.edu.eg доступен (04.10.2026): страница «Meet The President» называет Prof. Dr. Ahmed Adel Abdel Hakim президентом; контакты (адрес, info@anu.edu.eg, +201228858407) — на странице Contact; страницы без даты
-• Перепроверка: Сайт открылся 04.10.2026: президент, адрес, e-mail info@anu.edu.eg подтверждены, добавлен телефон +20 122 885 8407 (страницы без даты)</t>
-        </is>
-      </c>
-      <c r="AH49" s="4" t="inlineStr">
+• Перепроверка: Сайт открылся 04.10.2026: президент, адрес, e-mail info@anu.edu.eg подтверждены, добавлен телефон +20 122 885 8407 (страницы без даты)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI49" s="4" t="inlineStr">
         <is>
           <t>• Https://anu.edu.eg/en/contact
 • Https://www.dostor.org/5708804
@@ -9743,12 +10531,12 @@
 • Https://anu.edu.eg/en/contact</t>
         </is>
       </c>
-      <c r="AI49" s="4" t="inlineStr">
+      <c r="AJ49" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ49" s="4" t="inlineStr"/>
+      <c r="AK49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -9834,57 +10622,76 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S50" s="4" t="inlineStr"/>
-      <c r="T50" s="4" t="inlineStr"/>
-      <c r="U50" s="4" t="inlineStr"/>
-      <c r="V50" s="4" t="n">
+      <c r="S50" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T50" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U50" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V50" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W50" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W50" s="4" t="inlineStr"/>
       <c r="X50" s="4" t="inlineStr"/>
       <c r="Y50" s="4" t="inlineStr"/>
       <c r="Z50" s="4" t="inlineStr"/>
       <c r="AA50" s="4" t="inlineStr"/>
       <c r="AB50" s="4" t="inlineStr"/>
-      <c r="AC50" s="4" t="n">
+      <c r="AC50" s="4" t="inlineStr"/>
+      <c r="AD50" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD50" s="8" t="inlineStr">
+      <c r="AE50" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE50" s="4" t="inlineStr">
+      <c r="AF50" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF50" s="4" t="inlineStr">
+      <c r="AG50" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG50" s="4" t="inlineStr">
+      <c r="AH50" s="4" t="inlineStr">
         <is>
           <t>• Имя президента (أيمن عبد المجيد الشبيني) — со страницы «Слово президента» без даты; латинская транслитерация условная — сверить
 • Полный почтовый адрес на сайте не указан (только «Эль-Ариш, Северный Синай»); отдельного e-mail международного отдела нет
 • Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет
-• В THE 2027 — статус Reporter (без ранга)</t>
-        </is>
-      </c>
-      <c r="AH50" s="4" t="inlineStr">
+• В THE 2027 — статус Reporter (без ранга)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI50" s="4" t="inlineStr">
         <is>
           <t>• Https://aru.edu.eg/ar
 • Https://aru.edu.eg/ar/contact
-• Https://aru.edu.eg/ar/page/head-word</t>
-        </is>
-      </c>
-      <c r="AI50" s="4" t="inlineStr">
+• Https://aru.edu.eg/ar/page/head-word
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ50" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ50" s="4" t="inlineStr"/>
+      <c r="AK50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -9979,61 +10786,76 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S51" s="4" t="inlineStr"/>
+      <c r="S51" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T51" s="4" t="inlineStr">
         <is>
-          <t>THE2027 Reporter (unranked)</t>
-        </is>
-      </c>
-      <c r="U51" s="4" t="inlineStr"/>
-      <c r="V51" s="4" t="n">
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U51" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V51" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W51" s="4" t="inlineStr"/>
       <c r="X51" s="4" t="inlineStr"/>
       <c r="Y51" s="4" t="inlineStr"/>
       <c r="Z51" s="4" t="inlineStr"/>
       <c r="AA51" s="4" t="inlineStr"/>
       <c r="AB51" s="4" t="inlineStr"/>
-      <c r="AC51" s="4" t="n">
+      <c r="AC51" s="4" t="inlineStr"/>
+      <c r="AD51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD51" s="8" t="inlineStr">
+      <c r="AE51" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE51" s="4" t="inlineStr">
+      <c r="AF51" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF51" s="4" t="inlineStr">
+      <c r="AG51" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG51" s="4" t="inlineStr">
+      <c r="AH51" s="4" t="inlineStr">
         <is>
           <t>• Национальный (ахлия) некоммерческий университет при Benha University, создан указом президента №369 от 2022 г.; 10 факультетов
 • В THE2027 только в статусе Reporter (без ранга)
 • Опубликован только мобильный номер; международного отдела/e-mail нет — писать на info@bnu.edu.eg
-• Космической активности на сайте не найдено (поисковая проверка не выполнена — исчерпана квота поиска)</t>
-        </is>
-      </c>
-      <c r="AH51" s="4" t="inlineStr">
+• Космической активности на сайте не найдено (поисковая проверка не выполнена — исчерпана квота поиска)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI51" s="4" t="inlineStr">
         <is>
           <t>• Https://bnu.edu.eg/page/about
 • Https://bnu.edu.eg/en/page/academic_leaders
-• Https://bnu.edu.eg/page/contact</t>
-        </is>
-      </c>
-      <c r="AI51" s="4" t="inlineStr">
+• Https://bnu.edu.eg/page/contact
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ51" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ51" s="4" t="inlineStr"/>
+      <c r="AK51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -10111,58 +10933,76 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S52" s="4" t="inlineStr"/>
-      <c r="T52" s="4" t="inlineStr"/>
-      <c r="U52" s="4" t="inlineStr"/>
-      <c r="V52" s="4" t="n">
+      <c r="S52" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T52" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U52" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V52" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W52" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W52" s="4" t="inlineStr"/>
       <c r="X52" s="4" t="inlineStr"/>
       <c r="Y52" s="4" t="inlineStr"/>
       <c r="Z52" s="4" t="inlineStr"/>
       <c r="AA52" s="4" t="inlineStr"/>
       <c r="AB52" s="4" t="inlineStr"/>
-      <c r="AC52" s="4" t="n">
+      <c r="AC52" s="4" t="inlineStr"/>
+      <c r="AD52" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD52" s="8" t="inlineStr">
+      <c r="AE52" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE52" s="4" t="inlineStr">
+      <c r="AF52" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF52" s="4" t="inlineStr">
+      <c r="AG52" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG52" s="4" t="inlineStr">
+      <c r="AH52" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт batechu.com (не в зоне .edu.eg); e-mail contact@batechu.com подтверждён на странице Contact Us; телефон и полный почтовый адрес на сайте не опубликованы
 • Президент проф. д-р Мохамед Мурси аль-Гохари — по обращению президента на главной странице официального сайта (подвал © 2026); дата назначения не указана
 • Форма собственности не подтверждена (технологический университет; в Википедии — «National university»)
 • Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет
-• Перепроверка: 04.10.2026: президент и e-mail подтверждены на официальном сайте batechu.com; телефон и адрес не опубликованы</t>
-        </is>
-      </c>
-      <c r="AH52" s="4" t="inlineStr">
+• Перепроверка: 04.10.2026: президент и e-mail подтверждены на официальном сайте batechu.com; телефон и адрес не опубликованы
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI52" s="4" t="inlineStr">
         <is>
           <t>• Https://batechu.com/
 • Https://batechu.com/contact-us
 • Https://en.wikipedia.org/wiki/Borg_El_Arab_Technological_University</t>
         </is>
       </c>
-      <c r="AI52" s="4" t="inlineStr">
+      <c r="AJ52" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ52" s="4" t="inlineStr"/>
+      <c r="AK52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -10255,61 +11095,76 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S53" s="4" t="inlineStr"/>
+      <c r="S53" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T53" s="4" t="inlineStr">
         <is>
-          <t>THE2027 Reporter (unranked)</t>
-        </is>
-      </c>
-      <c r="U53" s="4" t="inlineStr"/>
-      <c r="V53" s="4" t="n">
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U53" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V53" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W53" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W53" s="4" t="inlineStr"/>
       <c r="X53" s="4" t="inlineStr"/>
       <c r="Y53" s="4" t="inlineStr"/>
       <c r="Z53" s="4" t="inlineStr"/>
       <c r="AA53" s="4" t="inlineStr"/>
       <c r="AB53" s="4" t="inlineStr"/>
-      <c r="AC53" s="4" t="n">
+      <c r="AC53" s="4" t="inlineStr"/>
+      <c r="AD53" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD53" s="8" t="inlineStr">
+      <c r="AE53" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE53" s="4" t="inlineStr">
+      <c r="AF53" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF53" s="4" t="inlineStr">
+      <c r="AG53" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG53" s="4" t="inlineStr">
+      <c r="AH53" s="4" t="inlineStr">
         <is>
           <t>• Info@ помечен на сайте как контакт для новых студентов; Socialmedia@cic-cairo.com — указан как контакт 'Collaborations' (сотрудничество)
 • Частный колледж (не университет) с канадскими дипломами Cape Breton University; второй кампус — Sheikh Zayed
 • Официальное арабское название на сайте не найдено (встречается 'المعهد الكندى العالى' — возможно, другое юрлицо)
-• Profile_type условный (инженерия/ИТ/бизнес)</t>
-        </is>
-      </c>
-      <c r="AH53" s="4" t="inlineStr">
+• Profile_type условный (инженерия/ИТ/бизнес)
+• Рейтинги: THE: в таблице как «Canadian International College – Cairo Campus of Cape Breton University Canada»; Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI53" s="4" t="inlineStr">
         <is>
           <t>• Https://www.cic-cairo.edu.eg/
 • Https://www.cic-cairo.edu.eg/about/
-• Https://www.timeshighereducation.com/world-university-rankings/canadian-international-college-cairo-campus-cape-breton-university-canada</t>
-        </is>
-      </c>
-      <c r="AI53" s="4" t="inlineStr">
+• Https://www.timeshighereducation.com/world-university-rankings/canadian-international-college-cairo-campus-cape-breton-university-canada
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ53" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ53" s="4" t="inlineStr"/>
+      <c r="AK53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -10401,57 +11256,76 @@
           <t>Acting President</t>
         </is>
       </c>
-      <c r="S54" s="4" t="inlineStr"/>
-      <c r="T54" s="4" t="inlineStr"/>
-      <c r="U54" s="4" t="inlineStr"/>
-      <c r="V54" s="4" t="n">
+      <c r="S54" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T54" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U54" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V54" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W54" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W54" s="4" t="inlineStr"/>
       <c r="X54" s="4" t="inlineStr"/>
       <c r="Y54" s="4" t="inlineStr"/>
       <c r="Z54" s="4" t="inlineStr"/>
       <c r="AA54" s="4" t="inlineStr"/>
       <c r="AB54" s="4" t="inlineStr"/>
-      <c r="AC54" s="4" t="n">
+      <c r="AC54" s="4" t="inlineStr"/>
+      <c r="AD54" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD54" s="8" t="inlineStr">
+      <c r="AE54" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE54" s="4" t="inlineStr">
+      <c r="AF54" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF54" s="4" t="inlineStr">
+      <c r="AG54" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG54" s="4" t="inlineStr">
+      <c r="AH54" s="4" t="inlineStr">
         <is>
           <t>• THE2027: только статус Reporter (без ранга)
 • Общий e-mail не опубликован — указан e-mail приёмной комиссии (student.admission@); есть также registrar@deraya.edu.eg; горячая линия 16283
 • Руководитель — исполняющий обязанности президента
-• Профиль медицинский/фармацевтический — низкая релевантность для спутниковой программы</t>
-        </is>
-      </c>
-      <c r="AH54" s="4" t="inlineStr">
+• Профиль медицинский/фармацевтический — низкая релевантность для спутниковой программы
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI54" s="4" t="inlineStr">
         <is>
           <t>• Https://deraya.edu.eg/
 • Https://deraya.edu.eg/?page_id=1853
-• Https://deraya.edu.eg/contact/</t>
-        </is>
-      </c>
-      <c r="AI54" s="4" t="inlineStr">
+• Https://deraya.edu.eg/contact/
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ54" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ54" s="4" t="inlineStr"/>
+      <c r="AK54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -10506,51 +11380,61 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S55" s="4" t="inlineStr"/>
-      <c r="T55" s="4" t="inlineStr"/>
+      <c r="S55" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T55" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="U55" s="4" t="inlineStr"/>
-      <c r="V55" s="4" t="n">
+      <c r="V55" s="4" t="inlineStr"/>
+      <c r="W55" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W55" s="4" t="inlineStr"/>
       <c r="X55" s="4" t="inlineStr"/>
       <c r="Y55" s="4" t="inlineStr"/>
       <c r="Z55" s="4" t="inlineStr"/>
       <c r="AA55" s="4" t="inlineStr"/>
       <c r="AB55" s="4" t="inlineStr"/>
-      <c r="AC55" s="4" t="n">
+      <c r="AC55" s="4" t="inlineStr"/>
+      <c r="AD55" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD55" s="8" t="inlineStr">
+      <c r="AE55" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE55" s="4" t="inlineStr"/>
-      <c r="AF55" s="4" t="inlineStr">
+      <c r="AF55" s="4" t="inlineStr"/>
+      <c r="AG55" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG55" s="4" t="inlineStr">
+      <c r="AH55" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт не найден (epsnu.edu.eg недоступен), лимит веб-поиска исчерпан — все контактные поля требуют ручного заполнения
 • Национальный (ахлия) университет, созданный при государственном Порт-Саидском университете (по арабской Википедии)
 • Космическая активность не проверялась; в nanosats.csv спутников нет
-• Перепроверка: Домены epsnu.edu.eg недоступны (04.10.2026); на сайте Порт-Саидского университета (psu.edu.eg) ссылки на национальный университет не найдено; данные не изменены</t>
-        </is>
-      </c>
-      <c r="AH55" s="4" t="inlineStr">
+• Перепроверка: Домены epsnu.edu.eg недоступны (04.10.2026); на сайте Порт-Саидского университета (psu.edu.eg) ссылки на национальный университет не найдено; данные не изменены
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI55" s="4" t="inlineStr">
         <is>
           <t>Https://ar.wikipedia.org/wiki/جامعة_شرق_بورسعيد_الأهلية</t>
         </is>
       </c>
-      <c r="AI55" s="4" t="inlineStr">
+      <c r="AJ55" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ55" s="4" t="inlineStr"/>
+      <c r="AK55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -10644,63 +11528,78 @@
           <t>Acting President</t>
         </is>
       </c>
-      <c r="S56" s="4" t="inlineStr"/>
+      <c r="S56" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T56" s="4" t="inlineStr">
         <is>
-          <t>THE2027 Reporter (unranked)</t>
-        </is>
-      </c>
-      <c r="U56" s="4" t="inlineStr"/>
-      <c r="V56" s="4" t="n">
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U56" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V56" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W56" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W56" s="4" t="inlineStr"/>
       <c r="X56" s="4" t="inlineStr"/>
       <c r="Y56" s="4" t="inlineStr"/>
       <c r="Z56" s="4" t="inlineStr"/>
       <c r="AA56" s="4" t="inlineStr"/>
       <c r="AB56" s="4" t="inlineStr"/>
-      <c r="AC56" s="4" t="n">
+      <c r="AC56" s="4" t="inlineStr"/>
+      <c r="AD56" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD56" s="8" t="inlineStr">
+      <c r="AE56" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE56" s="4" t="inlineStr">
+      <c r="AF56" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF56" s="4" t="inlineStr">
+      <c r="AG56" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG56" s="4" t="inlineStr">
+      <c r="AH56" s="4" t="inlineStr">
         <is>
           <t>• Создан Министерством связи и ИТ совместно с Минвысшобразования (начал работу в 2021/22); форма собственности указана как национальный некоммерческий — уточнить
 • Prof. Ahmed Mohamed Hamad — исполняющий обязанности президента; основатель-президент — Prof. Reem Bahgat
 • Опубликованы только телефоны приёмной комиссии (+20 103 008 0940 / +20 103 009 0509)
 • Раздел International Relations есть, но отдельного e-mail нет — писать на contact@eui.edu.eg
-• Космической активности на сайте не найдено (поисковая проверка не выполнена — исчерпана квота поиска)</t>
-        </is>
-      </c>
-      <c r="AH56" s="4" t="inlineStr">
+• Космической активности на сайте не найдено (поисковая проверка не выполнена — исчерпана квота поиска)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI56" s="4" t="inlineStr">
         <is>
           <t>• Https://eui.edu.eg/
 • Https://eui.edu.eg/who-we-are
 • Https://eui.edu.eg/top-management
-• Https://eui.edu.eg/contact-us</t>
-        </is>
-      </c>
-      <c r="AI56" s="4" t="inlineStr">
+• Https://eui.edu.eg/contact-us
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ56" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ56" s="4" t="inlineStr"/>
+      <c r="AK56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -10774,54 +11673,64 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S57" s="4" t="inlineStr"/>
-      <c r="T57" s="4" t="inlineStr"/>
+      <c r="S57" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T57" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter (в списке, без места)</t>
+        </is>
+      </c>
       <c r="U57" s="4" t="inlineStr"/>
-      <c r="V57" s="4" t="n">
+      <c r="V57" s="4" t="inlineStr"/>
+      <c r="W57" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W57" s="4" t="inlineStr"/>
       <c r="X57" s="4" t="inlineStr"/>
       <c r="Y57" s="4" t="inlineStr"/>
       <c r="Z57" s="4" t="inlineStr"/>
       <c r="AA57" s="4" t="inlineStr"/>
       <c r="AB57" s="4" t="inlineStr"/>
-      <c r="AC57" s="4" t="n">
+      <c r="AC57" s="4" t="inlineStr"/>
+      <c r="AD57" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD57" s="8" t="inlineStr">
+      <c r="AE57" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE57" s="4" t="inlineStr"/>
-      <c r="AF57" s="4" t="inlineStr">
+      <c r="AF57" s="4" t="inlineStr"/>
+      <c r="AG57" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG57" s="4" t="inlineStr">
+      <c r="AH57" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт ecu.edu.eg блокирует автоматический доступ (403, Cloudflare, повторно 04.10.2026); e-mail и телефон не найдены — найти вручную
 • Президент Prof. Dr. Rasha El-Kholy — по поисковой выдаче официальных страниц ECU (University President’s Message) и интервью на портале Belt and Road; дата назначения не установлена (предыдущий президент Ashraf El-Shihy, 2017–2023) — перепроверить
 • Адрес и профиль — только по арабской Википедии
 • Космическая активность поиском не проверялась; в nanosats.csv спутников нет
 • В THE 2027 — статус Reporter (без ранга)
-• Перепроверка: Сайт ecu.edu.eg по-прежнему 403 (Cloudflare); президент проф. Rasha El-Kholy внесена по выдаче официальных страниц ECU и портала Belt and Road (дата не установлена) — контакты не найдены</t>
-        </is>
-      </c>
-      <c r="AH57" s="4" t="inlineStr">
+• Перепроверка: Сайт ecu.edu.eg по-прежнему 403 (Cloudflare); президент проф. Rasha El-Kholy внесена по выдаче официальных страниц ECU и портала Belt and Road (дата не установлена) — контакты не найдены
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI57" s="4" t="inlineStr">
         <is>
           <t>• Https://ar.wikipedia.org/wiki/الجامعة_المصرية_الصينية
 • Https://ecu.edu.eg/about-ecu/university-presidents-message/ (snippet)</t>
         </is>
       </c>
-      <c r="AI57" s="4" t="inlineStr">
+      <c r="AJ57" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ57" s="4" t="inlineStr"/>
+      <c r="AK57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -10909,60 +11818,75 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S58" s="4" t="inlineStr"/>
+      <c r="S58" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T58" s="4" t="inlineStr">
         <is>
-          <t>THE2027 Reporter (unranked)</t>
-        </is>
-      </c>
-      <c r="U58" s="4" t="inlineStr"/>
-      <c r="V58" s="4" t="n">
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U58" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V58" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W58" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W58" s="4" t="inlineStr"/>
       <c r="X58" s="4" t="inlineStr"/>
       <c r="Y58" s="4" t="inlineStr"/>
       <c r="Z58" s="4" t="inlineStr"/>
       <c r="AA58" s="4" t="inlineStr"/>
       <c r="AB58" s="4" t="inlineStr"/>
-      <c r="AC58" s="4" t="n">
+      <c r="AC58" s="4" t="inlineStr"/>
+      <c r="AD58" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD58" s="8" t="inlineStr">
+      <c r="AE58" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE58" s="4" t="inlineStr">
+      <c r="AF58" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF58" s="4" t="inlineStr">
+      <c r="AG58" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG58" s="4" t="inlineStr">
+      <c r="AH58" s="4" t="inlineStr">
         <is>
           <t>• Первый политехнический университет Египта (B.Tech), связан с группой Elsewedy Electric
 • Арабское официальное название на сайте не найдено
-• Спутников не найдено</t>
-        </is>
-      </c>
-      <c r="AH58" s="4" t="inlineStr">
+• Спутников не найдено
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI58" s="4" t="inlineStr">
         <is>
           <t>• Https://sut.edu.eg/
 • Https://sut.edu.eg/about-sutech/president/
-• Https://sut.edu.eg/contact-us/</t>
-        </is>
-      </c>
-      <c r="AI58" s="4" t="inlineStr">
+• Https://sut.edu.eg/contact-us/
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ58" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ58" s="4" t="inlineStr"/>
+      <c r="AK58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -11056,57 +11980,75 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S59" s="4" t="inlineStr"/>
-      <c r="T59" s="4" t="inlineStr"/>
-      <c r="U59" s="4" t="inlineStr"/>
-      <c r="V59" s="4" t="n">
+      <c r="S59" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T59" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U59" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V59" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W59" s="4" t="inlineStr"/>
       <c r="X59" s="4" t="inlineStr"/>
       <c r="Y59" s="4" t="inlineStr"/>
       <c r="Z59" s="4" t="inlineStr"/>
       <c r="AA59" s="4" t="inlineStr"/>
       <c r="AB59" s="4" t="inlineStr"/>
-      <c r="AC59" s="4" t="n">
+      <c r="AC59" s="4" t="inlineStr"/>
+      <c r="AD59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD59" s="8" t="inlineStr">
+      <c r="AE59" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE59" s="4" t="inlineStr">
+      <c r="AF59" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF59" s="4" t="inlineStr">
+      <c r="AG59" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG59" s="4" t="inlineStr">
+      <c r="AH59" s="4" t="inlineStr">
         <is>
           <t>• Частный университет устойчивого развития (основан при SEKEM, председатель попечительского совета — Хельми Абулейш)
 • Общий ящик опубликован только для приёма (admission@hu.edu.eg) — иного общего адреса нет; телефон — короткая горячая линия 16418
 • Почтовый адрес на сайте не найден; руководитель международного отдела (IRO) не указан
-• Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет</t>
-        </is>
-      </c>
-      <c r="AH59" s="4" t="inlineStr">
+• Космическая активность поиском не проверялась (лимит поиска исчерпан); в nanosats.csv спутников нет
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI59" s="4" t="inlineStr">
         <is>
           <t>• Https://hu.edu.eg/
 • Https://hu.edu.eg/about-us/
 • Https://hu.edu.eg/heliopolis-university-international-relations/</t>
         </is>
       </c>
-      <c r="AI59" s="4" t="inlineStr">
+      <c r="AJ59" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ59" s="4" t="inlineStr"/>
+      <c r="AK59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -11169,42 +12111,52 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S60" s="4" t="inlineStr"/>
-      <c r="T60" s="4" t="inlineStr"/>
+      <c r="S60" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T60" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="U60" s="4" t="inlineStr"/>
-      <c r="V60" s="4" t="n">
+      <c r="V60" s="4" t="inlineStr"/>
+      <c r="W60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W60" s="4" t="inlineStr"/>
       <c r="X60" s="4" t="inlineStr"/>
       <c r="Y60" s="4" t="inlineStr"/>
       <c r="Z60" s="4" t="inlineStr"/>
       <c r="AA60" s="4" t="inlineStr"/>
       <c r="AB60" s="4" t="inlineStr"/>
-      <c r="AC60" s="4" t="n">
+      <c r="AC60" s="4" t="inlineStr"/>
+      <c r="AD60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD60" s="8" t="inlineStr">
+      <c r="AE60" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE60" s="4" t="inlineStr"/>
-      <c r="AF60" s="4" t="inlineStr">
+      <c r="AF60" s="4" t="inlineStr"/>
+      <c r="AG60" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG60" s="4" t="inlineStr">
+      <c r="AH60" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт hnu.edu.eg недоступен (503 / сброс соединения, проверка 04.10.2026) — руководство и контакты HNU НЕ проверены
 • Национальный (ахлия) некоммерческий университет, выделен из Helwan University; материнский вуз переименован в Capital University (جامعة العاصمة, capu.edu.eg). На capu.edu.eg (новость 30.09.2026) подтверждено: президент Capital University — проф. Эль-Сайед Кандиль, он курирует проекты HNU (учебная больница HNU); генеральный секретарь (أمين) HNU — Сайед Атта. Имя президента HNU не найдено
 • Возможный канал связи — Офис международных отношений Capital University (capu.edu.eg): директор проф. Мохамед Шими, iroffice@hq.helwan.edu.eg, тел. +20 2 2556 9067 / +20 2 2555 5021 (это контакты материнского вуза, не HNU)
 • Космической активности не проверено
-• Перепроверка: Сайт hnu.edu.eg недоступен; по capu.edu.eg уточнены связь с Capital University и контакты его международного офиса, руководитель HNU не найден</t>
-        </is>
-      </c>
-      <c r="AH60" s="4" t="inlineStr">
+• Перепроверка: Сайт hnu.edu.eg недоступен; по capu.edu.eg уточнены связь с Capital University и контакты его международного офиса, руководитель HNU не найден
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI60" s="4" t="inlineStr">
         <is>
           <t>• Https://www.wikidata.org/wiki/Q105600196
 • Https://ar.wikipedia.org/wiki/جامعة_حلوان_الأهلية
@@ -11212,12 +12164,12 @@
 • Https://capu.edu.eg/index.php/ar/about-ar/agreements-and-partnerships/office-of-international-relations</t>
         </is>
       </c>
-      <c r="AI60" s="4" t="inlineStr">
+      <c r="AJ60" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ60" s="4" t="inlineStr"/>
+      <c r="AK60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -11272,50 +12224,60 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S61" s="4" t="inlineStr"/>
-      <c r="T61" s="4" t="inlineStr"/>
+      <c r="S61" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T61" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="U61" s="4" t="inlineStr"/>
-      <c r="V61" s="4" t="n">
+      <c r="V61" s="4" t="inlineStr"/>
+      <c r="W61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W61" s="4" t="inlineStr"/>
       <c r="X61" s="4" t="inlineStr"/>
       <c r="Y61" s="4" t="inlineStr"/>
       <c r="Z61" s="4" t="inlineStr"/>
       <c r="AA61" s="4" t="inlineStr"/>
       <c r="AB61" s="4" t="inlineStr"/>
-      <c r="AC61" s="4" t="n">
+      <c r="AC61" s="4" t="inlineStr"/>
+      <c r="AD61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD61" s="8" t="inlineStr">
+      <c r="AE61" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE61" s="4" t="inlineStr"/>
-      <c r="AF61" s="4" t="inlineStr">
+      <c r="AF61" s="4" t="inlineStr"/>
+      <c r="AG61" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG61" s="4" t="inlineStr">
+      <c r="AH61" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт не найден/недоступен; веб-поиск исчерпан — все контакты требуют ручной проверки
 • Создан в 2020–2021 на базе филиала South Valley University в Хургаде (по арабской Википедии)
-• Перепроверка: Официальный домен не найден (варианты hurghada.edu.eg, hurghadauniv.edu.eg и др. недоступны); сайт Минвысобразования (mohesr.gov.eg, 30.08.2025) подтверждает существование вуза (утверждение фирменного стиля Хургадского университета Высшим советом университетов), но руководителя и контактов не даёт; данные не изменены</t>
-        </is>
-      </c>
-      <c r="AH61" s="4" t="inlineStr">
+• Перепроверка: Официальный домен не найден (варианты hurghada.edu.eg, hurghadauniv.edu.eg и др. недоступны); сайт Минвысобразования (mohesr.gov.eg, 30.08.2025) подтверждает существование вуза (утверждение фирменного стиля Хургадского университета Высшим советом университетов), но руководителя и контактов не даёт; данные не изменены
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI61" s="4" t="inlineStr">
         <is>
           <t>Https://ar.wikipedia.org/wiki/جامعة_الغردقة</t>
         </is>
       </c>
-      <c r="AI61" s="4" t="inlineStr">
+      <c r="AJ61" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ61" s="4" t="inlineStr"/>
+      <c r="AK61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -11410,57 +12372,76 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S62" s="4" t="inlineStr"/>
-      <c r="T62" s="4" t="inlineStr"/>
-      <c r="U62" s="4" t="inlineStr"/>
-      <c r="V62" s="4" t="n">
+      <c r="S62" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T62" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U62" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V62" s="4" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="W62" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W62" s="4" t="inlineStr"/>
       <c r="X62" s="4" t="inlineStr"/>
       <c r="Y62" s="4" t="inlineStr"/>
       <c r="Z62" s="4" t="inlineStr"/>
       <c r="AA62" s="4" t="inlineStr"/>
       <c r="AB62" s="4" t="inlineStr"/>
-      <c r="AC62" s="4" t="n">
+      <c r="AC62" s="4" t="inlineStr"/>
+      <c r="AD62" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD62" s="8" t="inlineStr">
+      <c r="AE62" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE62" s="4" t="inlineStr">
+      <c r="AF62" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF62" s="4" t="inlineStr">
+      <c r="AG62" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG62" s="4" t="inlineStr">
+      <c r="AH62" s="4" t="inlineStr">
         <is>
           <t>• Отдельного e-mail международного офиса нет; президентский e-mail указан как основной контакт
 • Директор Управления международных связей — Prof. Reda Abdel-Monsef Ahmed (أ.د. رضا عبدالمنصف أحمد), дата страницы не указана — можно поставить в копию через президента
-• Main_fields — по типичному профилю; на сайте детальный список факультетов не сверялся</t>
-        </is>
-      </c>
-      <c r="AH62" s="4" t="inlineStr">
+• Main_fields — по типичному профилю; на сайте детальный список факультетов не сверялся
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI62" s="4" t="inlineStr">
         <is>
           <t>• Https://www.kfs.edu.eg/
 • Http://www.kfs.edu.eg/interoffice/
 • Http://www.kfs.edu.eg/interoffice/display.aspx?topic=100438
-• Https://www.timeshighereducation.com/world-university-rankings/kafrelsheikh-university</t>
-        </is>
-      </c>
-      <c r="AI62" s="4" t="inlineStr">
+• Https://www.timeshighereducation.com/world-university-rankings/kafrelsheikh-university
+https://figshare.com/articles/preprint/Ranking_Web_of_Universities_webometrics_info_July_2026_edition/33062150</t>
+        </is>
+      </c>
+      <c r="AJ62" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ62" s="4" t="inlineStr"/>
+      <c r="AK62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -11534,7 +12515,11 @@
           <t>info@ksiu.edu.eg</t>
         </is>
       </c>
-      <c r="O63" s="4" t="inlineStr"/>
+      <c r="O63" s="4" t="inlineStr">
+        <is>
+          <t>+20 16949 (hotline)</t>
+        </is>
+      </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
           <t>https://ksiu.edu.eg</t>
@@ -11550,58 +12535,70 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S63" s="4" t="inlineStr"/>
-      <c r="T63" s="4" t="inlineStr"/>
+      <c r="S63" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T63" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter (в списке, без места)</t>
+        </is>
+      </c>
       <c r="U63" s="4" t="inlineStr"/>
-      <c r="V63" s="4" t="n">
+      <c r="V63" s="4" t="inlineStr"/>
+      <c r="W63" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W63" s="4" t="inlineStr"/>
       <c r="X63" s="4" t="inlineStr"/>
       <c r="Y63" s="4" t="inlineStr"/>
       <c r="Z63" s="4" t="inlineStr"/>
       <c r="AA63" s="4" t="inlineStr"/>
       <c r="AB63" s="4" t="inlineStr"/>
-      <c r="AC63" s="4" t="n">
+      <c r="AC63" s="4" t="inlineStr"/>
+      <c r="AD63" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD63" s="8" t="inlineStr">
+      <c r="AE63" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE63" s="4" t="inlineStr">
+      <c r="AF63" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF63" s="4" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
       <c r="AG63" s="4" t="inlineStr">
+        <is>
+          <t>высокая</t>
+        </is>
+      </c>
+      <c r="AH63" s="4" t="inlineStr">
         <is>
           <t>• THE2027: только статус Reporter (без ранга)
 • Сайт ksiu.edu.eg недоступен (503); данные из поисковых выдержек официального сайта, дата не подтверждена
 • Персональный e-mail президента по выдержке: ashraf@ksiu.edu.eg; горячая линия 16949
 • Спутниковой активности не найдено
-• Перепроверка: 04.10.2026: ksiu.edu.eg недоступен (ошибка TLS-цепочки, en.-поддомен — 502); по поиску президент проф. Ashraf Hussein указан на сайте — данные не изменены</t>
-        </is>
-      </c>
-      <c r="AH63" s="4" t="inlineStr">
+• Перепроверка: 04.10.2026: ksiu.edu.eg недоступен (ошибка TLS-цепочки, en.-поддомен — 502); по поиску президент проф. Ashraf Hussein указан на сайте — данные не изменены
+• Ручная проверка: Контакты прочитаны на официальном сайте 05.10.2026 (сессия с агентами). Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI63" s="4" t="inlineStr">
         <is>
           <t>• Https://ksiu.edu.eg/
 • Https://ksiu.edu.eg/contact/
-• Https://ksiu.edu.eg/teams/prof-ashraf-s-hussein/</t>
-        </is>
-      </c>
-      <c r="AI63" s="4" t="inlineStr">
+• Https://ksiu.edu.eg/teams/prof-ashraf-s-hussein/
+https://ksiu.edu.eg/contact-information/
+• Https://ksiu.edu.eg/about-university/</t>
+        </is>
+      </c>
+      <c r="AJ63" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ63" s="4" t="inlineStr"/>
+      <c r="AK63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -11672,57 +12669,63 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S64" s="4" t="inlineStr"/>
+      <c r="S64" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T64" s="4" t="inlineStr">
         <is>
           <t>THE2027 Reporter (unranked)</t>
         </is>
       </c>
       <c r="U64" s="4" t="inlineStr"/>
-      <c r="V64" s="4" t="n">
+      <c r="V64" s="4" t="inlineStr"/>
+      <c r="W64" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W64" s="4" t="inlineStr"/>
       <c r="X64" s="4" t="inlineStr"/>
       <c r="Y64" s="4" t="inlineStr"/>
       <c r="Z64" s="4" t="inlineStr"/>
       <c r="AA64" s="4" t="inlineStr"/>
       <c r="AB64" s="4" t="inlineStr"/>
-      <c r="AC64" s="4" t="n">
+      <c r="AC64" s="4" t="inlineStr"/>
+      <c r="AD64" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD64" s="8" t="inlineStr">
+      <c r="AE64" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE64" s="4" t="inlineStr"/>
-      <c r="AF64" s="4" t="inlineStr">
+      <c r="AF64" s="4" t="inlineStr"/>
+      <c r="AG64" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG64" s="4" t="inlineStr">
+      <c r="AH64" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт mansnu.edu.eg недоступен (503 / блокировка прокси); поисковая квота исчерпана — руководство и контакты НЕ проверены
 • Национальный (ахлия) некоммерческий университет при Mansoura University (кампус 42 федданa в Новой Мансуре); обычно возглавляется президентом Mansoura University — уточнить
 • Перечень факультетов частичный (по арабской Википедии)
 • Космической активности не проверено
-• Перепроверка: Сайт mansnu.edu.eg (www и без www) недоступен — таймаут через curl и reader-сервис 04.10.2026; данные не изменены</t>
-        </is>
-      </c>
-      <c r="AH64" s="4" t="inlineStr">
+• Перепроверка: Сайт mansnu.edu.eg (www и без www) недоступен — таймаут через curl и reader-сервис 04.10.2026; данные не изменены
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026. Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI64" s="4" t="inlineStr">
         <is>
           <t>• Https://www.wikidata.org/wiki/Q114817413
 • Https://ar.wikipedia.org/wiki/جامعة_المنصورة_الأهلية</t>
         </is>
       </c>
-      <c r="AI64" s="4" t="inlineStr">
+      <c r="AJ64" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ64" s="4" t="inlineStr"/>
+      <c r="AK64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -11802,53 +12805,71 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S65" s="4" t="inlineStr"/>
-      <c r="T65" s="4" t="inlineStr"/>
-      <c r="U65" s="4" t="inlineStr"/>
-      <c r="V65" s="4" t="n">
+      <c r="S65" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T65" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U65" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V65" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W65" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W65" s="4" t="inlineStr"/>
       <c r="X65" s="4" t="inlineStr"/>
       <c r="Y65" s="4" t="inlineStr"/>
       <c r="Z65" s="4" t="inlineStr"/>
       <c r="AA65" s="4" t="inlineStr"/>
       <c r="AB65" s="4" t="inlineStr"/>
-      <c r="AC65" s="4" t="n">
+      <c r="AC65" s="4" t="inlineStr"/>
+      <c r="AD65" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD65" s="8" t="inlineStr">
+      <c r="AE65" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE65" s="4" t="inlineStr"/>
-      <c r="AF65" s="4" t="inlineStr">
+      <c r="AF65" s="4" t="inlineStr"/>
+      <c r="AG65" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG65" s="4" t="inlineStr">
+      <c r="AH65" s="4" t="inlineStr">
         <is>
           <t>• Сайт mau.edu.eg (Blazor, рендер JS) открыт через reader-сервис 04.10.2026: на сайте нет e-mail и телефонов (в т.ч. на странице International Relations) — официальный общий и международный e-mail не найдены (в каталоге WIPO только личный адрес сотрудника)
 • Президент назван «President» (новость 01.10.2026) и «Acting President» (сентябрь 2025/2026) — статус и.о. мог измениться после конкурса (собеседования ноябрь 2025)
 • Телефон +20 46 4948489 взят ранее из стороннего источника, на официальном сайте не подтверждён. Генеральный секретарь — Walid Yahya
 • Спутниковой активности не найдено
-• Перепроверка: Президент Prof. Amr Ahmed El-Masry и адрес кампуса (Km 9) подтверждены на mau.edu.eg 04.10.2026 (новость от 01.10.2026); e-mail на сайте не опубликован; адрес исправлен (было «Km 4»)</t>
-        </is>
-      </c>
-      <c r="AH65" s="4" t="inlineStr">
+• Перепроверка: Президент Prof. Amr Ahmed El-Masry и адрес кампуса (Km 9) подтверждены на mau.edu.eg 04.10.2026 (новость от 01.10.2026); e-mail на сайте не опубликован; адрес исправлен (было «Km 4»)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI65" s="4" t="inlineStr">
         <is>
           <t>• Https://www.maspero.eg/our-reporters/2026/09/17/990072/
 • Https://www.wipo.int/tisc/en/search/details.jsp?id=11055</t>
         </is>
       </c>
-      <c r="AI65" s="4" t="inlineStr">
+      <c r="AJ65" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ65" s="4" t="inlineStr"/>
+      <c r="AK65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -11907,55 +12928,61 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S66" s="4" t="inlineStr"/>
+      <c r="S66" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T66" s="4" t="inlineStr">
         <is>
           <t>THE2027 Reporter (unranked)</t>
         </is>
       </c>
       <c r="U66" s="4" t="inlineStr"/>
-      <c r="V66" s="4" t="n">
+      <c r="V66" s="4" t="inlineStr"/>
+      <c r="W66" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W66" s="4" t="inlineStr"/>
       <c r="X66" s="4" t="inlineStr"/>
       <c r="Y66" s="4" t="inlineStr"/>
       <c r="Z66" s="4" t="inlineStr"/>
       <c r="AA66" s="4" t="inlineStr"/>
       <c r="AB66" s="4" t="inlineStr"/>
-      <c r="AC66" s="4" t="n">
+      <c r="AC66" s="4" t="inlineStr"/>
+      <c r="AD66" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD66" s="8" t="inlineStr">
+      <c r="AE66" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE66" s="4" t="inlineStr"/>
-      <c r="AF66" s="4" t="inlineStr">
+      <c r="AF66" s="4" t="inlineStr"/>
+      <c r="AG66" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG66" s="4" t="inlineStr">
+      <c r="AH66" s="4" t="inlineStr">
         <is>
           <t>• Официальный сайт недоступен из нашей сети (503/таймаут), поиск исчерпан — контакты и руководитель не верифицированы; требуется ручная проверка
 • Описание в профиле THE скопировано с государственного Menoufia University — не использовать его для профиля
 • Национальный (ахлия) университет при Menoufia University — проверить точное название и руководство
-• Перепроверка: Сайты mnu.menofia.education, mnu.edu.eg и menofia.edu.eg недоступны (04.10.2026, сброс соединения); данные не изменены</t>
-        </is>
-      </c>
-      <c r="AH66" s="4" t="inlineStr">
+• Перепроверка: Сайты mnu.menofia.education, mnu.edu.eg и menofia.edu.eg недоступны (04.10.2026, сброс соединения); данные не изменены
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026. Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI66" s="4" t="inlineStr">
         <is>
           <t>Https://www.timeshighereducation.com/world-university-rankings/menoufia-national-university</t>
         </is>
       </c>
-      <c r="AI66" s="4" t="inlineStr">
+      <c r="AJ66" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ66" s="4" t="inlineStr"/>
+      <c r="AK66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -12045,58 +13072,77 @@
           <t>Acting President</t>
         </is>
       </c>
-      <c r="S67" s="4" t="inlineStr"/>
-      <c r="T67" s="4" t="inlineStr"/>
-      <c r="U67" s="4" t="inlineStr"/>
-      <c r="V67" s="4" t="n">
+      <c r="S67" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T67" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U67" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V67" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W67" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W67" s="4" t="inlineStr"/>
       <c r="X67" s="4" t="inlineStr"/>
       <c r="Y67" s="4" t="inlineStr"/>
       <c r="Z67" s="4" t="inlineStr"/>
       <c r="AA67" s="4" t="inlineStr"/>
       <c r="AB67" s="4" t="inlineStr"/>
-      <c r="AC67" s="4" t="n">
+      <c r="AC67" s="4" t="inlineStr"/>
+      <c r="AD67" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD67" s="8" t="inlineStr">
+      <c r="AE67" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE67" s="4" t="inlineStr">
+      <c r="AF67" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF67" s="4" t="inlineStr">
+      <c r="AG67" s="4" t="inlineStr">
         <is>
           <t>высокая</t>
         </is>
       </c>
-      <c r="AG67" s="4" t="inlineStr">
+      <c r="AH67" s="4" t="inlineStr">
         <is>
           <t>• THE2027: только статус Reporter (без ранга)
 • Руководитель — и.о. президента (июль 2026); председатель попечительского совета — Mohamed El Rashidi
 • Есть раздел International office, но отдельный e-mail не опубликован; горячая линия 19648
-• Спутниковой активности не найдено</t>
-        </is>
-      </c>
-      <c r="AH67" s="4" t="inlineStr">
+• Спутниковой активности не найдено
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI67" s="4" t="inlineStr">
         <is>
           <t>• Https://www.miuegypt.edu.eg/
 • Https://www.miuegypt.edu.eg/contact-us/
 • Https://www.miuegypt.edu.eg/international-partners/
-• Https://www.miuegypt.edu.eg/computer-science-graduation-projects-expo-2026/</t>
-        </is>
-      </c>
-      <c r="AI67" s="4" t="inlineStr">
+• Https://www.miuegypt.edu.eg/computer-science-graduation-projects-expo-2026/
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ67" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ67" s="4" t="inlineStr"/>
+      <c r="AK67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -12186,45 +13232,63 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S68" s="4" t="inlineStr"/>
-      <c r="T68" s="4" t="inlineStr"/>
-      <c r="U68" s="4" t="inlineStr"/>
-      <c r="V68" s="4" t="n">
+      <c r="S68" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T68" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U68" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V68" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W68" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W68" s="4" t="inlineStr"/>
       <c r="X68" s="4" t="inlineStr"/>
       <c r="Y68" s="4" t="inlineStr"/>
       <c r="Z68" s="4" t="inlineStr"/>
       <c r="AA68" s="4" t="inlineStr"/>
       <c r="AB68" s="4" t="inlineStr"/>
-      <c r="AC68" s="4" t="n">
+      <c r="AC68" s="4" t="inlineStr"/>
+      <c r="AD68" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD68" s="8" t="inlineStr">
+      <c r="AE68" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE68" s="4" t="inlineStr">
+      <c r="AF68" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF68" s="4" t="inlineStr">
+      <c r="AG68" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG68" s="4" t="inlineStr">
+      <c r="AH68" s="4" t="inlineStr">
         <is>
           <t>• Президент указан на текущем арабском портале (послание президента), но англ. страница датирована 2015 г. — актуальность желательно подтвердить
 • Телефон: только горячая линия 19041
 • E-mail международного отдела не опубликован
-• Спутниковой активности не найдено</t>
-        </is>
-      </c>
-      <c r="AH68" s="4" t="inlineStr">
+• Спутниковой активности не найдено
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI68" s="4" t="inlineStr">
         <is>
           <t>• Https://mti.edu.eg/default1.aspx
 • Https://mti.edu.eg/629748
@@ -12232,12 +13296,12 @@
 • Https://ar.mti.edu.eg/default.aspx</t>
         </is>
       </c>
-      <c r="AI68" s="4" t="inlineStr">
+      <c r="AJ68" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ68" s="4" t="inlineStr"/>
+      <c r="AK68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -12317,53 +13381,71 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S69" s="4" t="inlineStr"/>
-      <c r="T69" s="4" t="inlineStr"/>
-      <c r="U69" s="4" t="inlineStr"/>
-      <c r="V69" s="4" t="n">
+      <c r="S69" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T69" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U69" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V69" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W69" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W69" s="4" t="inlineStr"/>
       <c r="X69" s="4" t="inlineStr"/>
       <c r="Y69" s="4" t="inlineStr"/>
       <c r="Z69" s="4" t="inlineStr"/>
       <c r="AA69" s="4" t="inlineStr"/>
       <c r="AB69" s="4" t="inlineStr"/>
-      <c r="AC69" s="4" t="n">
+      <c r="AC69" s="4" t="inlineStr"/>
+      <c r="AD69" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD69" s="8" t="inlineStr">
+      <c r="AE69" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE69" s="4" t="inlineStr"/>
-      <c r="AF69" s="4" t="inlineStr">
+      <c r="AF69" s="4" t="inlineStr"/>
+      <c r="AG69" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG69" s="4" t="inlineStr">
+      <c r="AH69" s="4" t="inlineStr">
         <is>
           <t>• E-mail на сайте не опубликован (только веб-форма); телефон — короткий номер 19206, факс +20 82 2284688
 • Президент Prof. Hossam El-Malahy — советник Президента Египта по высшему образованию и науке, член Сената; одновременно президент Badya University — влиятельный адресат
 • Космической активности на сайте не найдено (поисковая проверка не выполнена — исчерпана квота поиска); в QS2027/THE2027 не найден
-• Арабское название (جامعة النهضة) не подтверждено на сайте</t>
-        </is>
-      </c>
-      <c r="AH69" s="4" t="inlineStr">
+• Арабское название (جامعة النهضة) не подтверждено на сайте
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI69" s="4" t="inlineStr">
         <is>
           <t>• Https://www.nub.edu.eg/
 • Https://www.nub.edu.eg/about/office-of-the-president/
 • Https://www.nub.edu.eg/contact/</t>
         </is>
       </c>
-      <c r="AI69" s="4" t="inlineStr">
+      <c r="AJ69" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ69" s="4" t="inlineStr"/>
+      <c r="AK69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -12434,53 +13516,63 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S70" s="4" t="inlineStr"/>
-      <c r="T70" s="4" t="inlineStr"/>
+      <c r="S70" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T70" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="U70" s="4" t="inlineStr"/>
-      <c r="V70" s="4" t="n">
+      <c r="V70" s="4" t="inlineStr"/>
+      <c r="W70" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W70" s="4" t="inlineStr"/>
       <c r="X70" s="4" t="inlineStr"/>
       <c r="Y70" s="4" t="inlineStr"/>
       <c r="Z70" s="4" t="inlineStr"/>
       <c r="AA70" s="4" t="inlineStr"/>
       <c r="AB70" s="4" t="inlineStr"/>
-      <c r="AC70" s="4" t="n">
+      <c r="AC70" s="4" t="inlineStr"/>
+      <c r="AD70" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD70" s="8" t="inlineStr">
+      <c r="AE70" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE70" s="4" t="inlineStr"/>
-      <c r="AF70" s="4" t="inlineStr">
+      <c r="AF70" s="4" t="inlineStr"/>
+      <c r="AG70" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG70" s="4" t="inlineStr">
+      <c r="AH70" s="4" t="inlineStr">
         <is>
           <t>• Государственный технологический университет (прикладное технологическое образование); подтверждён только факультет технологий промышленности и энергетики (по арабской Википедии)
 • Космической активности не проверено
 • Сайт nctu.edu.eg по-прежнему недоступен (04.10.2026) — контакты не найдены
 • Президент д-р Тарек Абдель Малак (طارق عبد الملاك) — по статье Masrawy от 18.09.2026 (выпуск 2025/2026); на официальном сайте не проверен
-• Перепроверка: Сайт недоступен; по СМИ 09.2026 добавлен президент д-р Тарек Абдель Малак; контактов по-прежнему нет</t>
-        </is>
-      </c>
-      <c r="AH70" s="4" t="inlineStr">
+• Перепроверка: Сайт недоступен; по СМИ 09.2026 добавлен президент д-р Тарек Абдель Малак; контактов по-прежнему нет
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026; THE 2027 — список THE World University Rankings 2027 (data/sources/the2027.json). Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI70" s="4" t="inlineStr">
         <is>
           <t>• Https://www.wikidata.org/wiki/Q100257877
 • Https://ar.wikipedia.org/wiki/جامعة_القاهرة_الجديدة_التكنولوجية</t>
         </is>
       </c>
-      <c r="AI70" s="4" t="inlineStr">
+      <c r="AJ70" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ70" s="4" t="inlineStr"/>
+      <c r="AK70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -12575,59 +13667,77 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S71" s="4" t="inlineStr"/>
-      <c r="T71" s="4" t="inlineStr"/>
-      <c r="U71" s="4" t="inlineStr"/>
-      <c r="V71" s="4" t="n">
+      <c r="S71" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T71" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U71" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V71" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W71" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W71" s="4" t="inlineStr"/>
       <c r="X71" s="4" t="inlineStr"/>
       <c r="Y71" s="4" t="inlineStr"/>
       <c r="Z71" s="4" t="inlineStr"/>
       <c r="AA71" s="4" t="inlineStr"/>
       <c r="AB71" s="4" t="inlineStr"/>
-      <c r="AC71" s="4" t="n">
+      <c r="AC71" s="4" t="inlineStr"/>
+      <c r="AD71" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD71" s="8" t="inlineStr">
+      <c r="AE71" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE71" s="4" t="inlineStr">
+      <c r="AF71" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF71" s="4" t="inlineStr">
+      <c r="AG71" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG71" s="4" t="inlineStr">
+      <c r="AH71" s="4" t="inlineStr">
         <is>
           <t>• Общего e-mail / e-mail офиса президента нет; указан ящик приёмной комиссии enrollment@ngu.edu.eg (единственный, кроме careers@) — лучше дополнительно связаться по телефону
 • Президент-основатель Prof. A. Sameh Farid — бывший министр здравоохранения Египта (2011)
 • Горячая линия 16623; «международный номер» +20 106 829 4242
 • Партнёрства с UCL и King's College London
 • Космической активности на сайте не найдено (поисковая проверка не выполнена — исчерпана квота поиска); в рейтингах QS2027/THE2027 не найден
-• Арабское название (جامعة نيو جيزة) не подтверждено на сайте</t>
-        </is>
-      </c>
-      <c r="AH71" s="4" t="inlineStr">
+• Арабское название (جامعة نيو جيزة) не подтверждено на сайте
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI71" s="4" t="inlineStr">
         <is>
           <t>• Https://ngu.edu.eg/
 • Https://ngu.edu.eg/about-ngu/
 • Https://ngu.edu.eg/contact</t>
         </is>
       </c>
-      <c r="AI71" s="4" t="inlineStr">
+      <c r="AJ71" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ71" s="4" t="inlineStr"/>
+      <c r="AK71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -12716,57 +13826,76 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S72" s="4" t="inlineStr"/>
-      <c r="T72" s="4" t="inlineStr"/>
-      <c r="U72" s="4" t="inlineStr"/>
-      <c r="V72" s="4" t="n">
+      <c r="S72" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T72" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: Reporter</t>
+        </is>
+      </c>
+      <c r="U72" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V72" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W72" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W72" s="4" t="inlineStr"/>
       <c r="X72" s="4" t="inlineStr"/>
       <c r="Y72" s="4" t="inlineStr"/>
       <c r="Z72" s="4" t="inlineStr"/>
       <c r="AA72" s="4" t="inlineStr"/>
       <c r="AB72" s="4" t="inlineStr"/>
-      <c r="AC72" s="4" t="n">
+      <c r="AC72" s="4" t="inlineStr"/>
+      <c r="AD72" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD72" s="8" t="inlineStr">
+      <c r="AE72" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE72" s="4" t="inlineStr">
+      <c r="AF72" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF72" s="4" t="inlineStr">
+      <c r="AG72" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG72" s="4" t="inlineStr">
+      <c r="AH72" s="4" t="inlineStr">
         <is>
           <t>• Форма собственности на сайте не указана (вероятно частный — не подтверждено), поле оставлено пустым
 • На сайте указан только короткий номер горячей линии 16308 (без +20) и адрес «Rd. 21 Cairo-Belbeis» (вероятно, 21-й км шоссе Каир–Бильбейс)
 • Отдельного e-mail международного отдела нет; космическая активность поиском не проверялась (лимит поиска исчерпан)
-• В THE 2027 — статус Reporter (без ранга)</t>
-        </is>
-      </c>
-      <c r="AH72" s="4" t="inlineStr">
+• В THE 2027 — статус Reporter (без ранга)
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI72" s="4" t="inlineStr">
         <is>
           <t>• Https://oust.edu.eg/en
 • Https://oust.edu.eg/en/pages/about-oust
-• Https://oust.edu.eg/en/posts/prof-dr-ramadan-el-domany-university-president-joined-a-tour-with-the-student-welfare-department-to-follow-up-on-student-activities-and-interact-with-students</t>
-        </is>
-      </c>
-      <c r="AI72" s="4" t="inlineStr">
+• Https://oust.edu.eg/en/posts/prof-dr-ramadan-el-domany-university-president-joined-a-tour-with-the-student-welfare-department-to-follow-up-on-student-activities-and-interact-with-students
+https://www.timeshighereducation.com/world-university-rankings/2027/world-ranking</t>
+        </is>
+      </c>
+      <c r="AJ72" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ72" s="4" t="inlineStr"/>
+      <c r="AK72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -12852,44 +13981,62 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S73" s="4" t="inlineStr"/>
-      <c r="T73" s="4" t="inlineStr"/>
-      <c r="U73" s="4" t="inlineStr"/>
-      <c r="V73" s="4" t="n">
+      <c r="S73" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="T73" s="4" t="inlineStr">
+        <is>
+          <t>THE2027: не в рейтинге</t>
+        </is>
+      </c>
+      <c r="U73" s="4" t="inlineStr">
+        <is>
+          <t>нет общенационального рейтинга</t>
+        </is>
+      </c>
+      <c r="V73" s="4" t="inlineStr">
+        <is>
+          <t>нет в опубл. списке</t>
+        </is>
+      </c>
+      <c r="W73" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W73" s="4" t="inlineStr"/>
       <c r="X73" s="4" t="inlineStr"/>
       <c r="Y73" s="4" t="inlineStr"/>
       <c r="Z73" s="4" t="inlineStr"/>
       <c r="AA73" s="4" t="inlineStr"/>
       <c r="AB73" s="4" t="inlineStr"/>
-      <c r="AC73" s="4" t="n">
+      <c r="AC73" s="4" t="inlineStr"/>
+      <c r="AD73" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD73" s="8" t="inlineStr">
+      <c r="AE73" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE73" s="4" t="inlineStr">
+      <c r="AF73" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF73" s="4" t="inlineStr">
+      <c r="AG73" s="4" t="inlineStr">
         <is>
           <t>средняя</t>
         </is>
       </c>
-      <c r="AG73" s="4" t="inlineStr">
+      <c r="AH73" s="4" t="inlineStr">
         <is>
           <t>• Есть Centre for International Cooperation and Foreign Relations (ICFR), но его e-mail/руководитель не найдены
 • Два кампуса: Эль-Ариш и Эль-Кантара (Восточная)
-• Арабское официальное название на сайте не сверено</t>
-        </is>
-      </c>
-      <c r="AH73" s="4" t="inlineStr">
+• Арабское официальное название на сайте не сверено
+• Рейтинги: Национального рейтинга с местами нет: Минвуз/Высший совет университетов Египта собственного рейтинга не публикуют (ориентируются на QS/THE/ARWU и региональный Arab Ranking — исключены)</t>
+        </is>
+      </c>
+      <c r="AI73" s="4" t="inlineStr">
         <is>
           <t>• Https://www.su.edu.eg/
 • Https://www.su.edu.eg/su_glance/
@@ -12897,12 +14044,12 @@
 • Https://www.timeshighereducation.com/world-university-rankings/sinai-university</t>
         </is>
       </c>
-      <c r="AI73" s="4" t="inlineStr">
+      <c r="AJ73" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ73" s="4" t="inlineStr"/>
+      <c r="AK73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -12991,41 +14138,46 @@
           <t>President</t>
         </is>
       </c>
-      <c r="S74" s="4" t="inlineStr"/>
+      <c r="S74" s="4" t="inlineStr">
+        <is>
+          <t>QS2027: не в рейтинге</t>
+        </is>
+      </c>
       <c r="T74" s="4" t="inlineStr">
         <is>
           <t>THE2027 Reporter (unranked)</t>
         </is>
       </c>
       <c r="U74" s="4" t="inlineStr"/>
-      <c r="V74" s="4" t="n">
+      <c r="V74" s="4" t="inlineStr"/>
+      <c r="W74" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="W74" s="4" t="inlineStr"/>
       <c r="X74" s="4" t="inlineStr"/>
       <c r="Y74" s="4" t="inlineStr"/>
       <c r="Z74" s="4" t="inlineStr"/>
       <c r="AA74" s="4" t="inlineStr"/>
       <c r="AB74" s="4" t="inlineStr"/>
-      <c r="AC74" s="4" t="n">
+      <c r="AC74" s="4" t="inlineStr"/>
+      <c r="AD74" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="AD74" s="8" t="inlineStr">
+      <c r="AE74" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AE74" s="4" t="inlineStr">
+      <c r="AF74" s="4" t="inlineStr">
         <is>
           <t>да</t>
         </is>
       </c>
-      <c r="AF74" s="4" t="inlineStr">
+      <c r="AG74" s="4" t="inlineStr">
         <is>
           <t>низкая</t>
         </is>
       </c>
-      <c r="AG74" s="4" t="inlineStr">
+      <c r="AH74" s="4" t="inlineStr">
         <is>
           <t>• Частный университет в Новом Асьюте, создан указом президента №36 от 2019 г
 • Сайт почти пустой (JS, без страниц руководства/контактов) — президент не установлен; поисковая проверка невозможна (исчерпана квота поиска)
@@ -13033,25 +14185,26 @@
 • Международного отдела не найдено; космической активности не найдено
 • Точный почтовый адрес (улица) не опубликован
 • Повторная проверка 04.10.2026: на сайте нет страниц руководства; по поисковой выдаче (СМИ, не официальный источник) и.о. президента — д-р Мансур Каббаш (منصور كباش) — не подтверждено, в поля не внесено
-• Перепроверка: Сайт открылся 04.10.2026: подтверждены только Info@Sphinx.edu.eg, номер 17090 и адрес «Regional service zone, New Assiut»; президент на сайте не указан</t>
-        </is>
-      </c>
-      <c r="AH74" s="4" t="inlineStr">
+• Перепроверка: Сайт открылся 04.10.2026: подтверждены только Info@Sphinx.edu.eg, номер 17090 и адрес «Regional service zone, New Assiut»; президент на сайте не указан
+• Ручная проверка: Рейтинги: QS 2027 — официальный файл данных topuniversities.com (qs-rankings-data/en/4153156.txt), сверка 05.10.2026. Webometrics: webometrics.info не открывается (DNS) — не заполнено</t>
+        </is>
+      </c>
+      <c r="AI74" s="4" t="inlineStr">
         <is>
           <t>• Https://sphinx.edu.eg/en/home/index
 • Https://ar.wikipedia.org/wiki/جامعة_سفنكس
 • Https://sphinx.edu.eg/en/home/index</t>
         </is>
       </c>
-      <c r="AI74" s="4" t="inlineStr">
+      <c r="AJ74" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AJ74" s="4" t="inlineStr"/>
+      <c r="AK74" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ74"/>
+  <autoFilter ref="A1:AK74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>